--- a/uploads/网站信息.xlsx
+++ b/uploads/网站信息.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23145" windowHeight="12375"/>
+    <workbookView windowWidth="24045" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="1007">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1636" uniqueCount="1257">
   <si>
     <t>分类</t>
   </si>
@@ -1835,6 +1835,9 @@
     <t>Popper</t>
   </si>
   <si>
+    <t>170.101.101.29</t>
+  </si>
+  <si>
     <t>5001 Cathann St, Torrance, CA 90503</t>
   </si>
   <si>
@@ -2280,6 +2283,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>Designed for passionate corgi lovers.</t>
     </r>
     <r>
@@ -2294,6 +2303,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>专为狂热的柯基爱好者设计。</t>
     </r>
     <r>
@@ -2332,6 +2347,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>Build your dream garage</t>
     </r>
     <r>
@@ -2346,6 +2367,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>打造您的梦想车库。</t>
     </r>
     <r>
@@ -2384,6 +2411,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>Made for endless summer fun and everyday play.</t>
     </r>
     <r>
@@ -2398,6 +2431,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>专为无限夏日乐趣与日常玩耍打造。</t>
     </r>
     <r>
@@ -2436,6 +2475,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>Create enchanting tiny worlds.</t>
     </r>
     <r>
@@ -2450,6 +2495,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>创造迷人的微观世界。</t>
     </r>
     <r>
@@ -2488,6 +2539,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>Engineered for historical accuracy.</t>
     </r>
     <r>
@@ -2502,6 +2559,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>为还原真实历史而设计。</t>
     </r>
     <r>
@@ -2540,6 +2603,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>Spark a lifelong love for music and rhythm.</t>
     </r>
     <r>
@@ -2554,6 +2623,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>激发对音乐与节奏的终身热爱。</t>
     </r>
     <r>
@@ -2592,6 +2667,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>Crafted for ultimate display.</t>
     </r>
     <r>
@@ -2606,6 +2687,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>专为极致摆设陈列而作。</t>
     </r>
     <r>
@@ -2931,6 +3018,9 @@
     <t>包袋|||背包</t>
   </si>
   <si>
+    <t>61407,61412,61417,61422,61427,61432,61437,61442,61447,61452</t>
+  </si>
+  <si>
     <t>Bags|||Backpack</t>
   </si>
   <si>
@@ -2950,6 +3040,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>灵感源自硬核出行与城市探索。</t>
     </r>
     <r>
@@ -2972,6 +3068,9 @@
     <t>护目镜</t>
   </si>
   <si>
+    <t>61408,61413,61418,61423,61428,61433,61438,61443,61448,61453</t>
+  </si>
+  <si>
     <t>Goggle</t>
   </si>
   <si>
@@ -2991,6 +3090,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>备受顶尖运动员信赖，带来无畸变视野。</t>
     </r>
     <r>
@@ -3013,6 +3118,9 @@
     <t>手镯</t>
   </si>
   <si>
+    <t>61409,61414,61419,61424,61429,61434,61439,61444,61449,61454</t>
+  </si>
+  <si>
     <t>Bracelet</t>
   </si>
   <si>
@@ -3032,6 +3140,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>专为轻松的日常风格与终身耐用性打造。</t>
     </r>
     <r>
@@ -3051,6 +3165,9 @@
     <t>软木饰品</t>
   </si>
   <si>
+    <t>61410,61415,61420,61425,61430,61435,61440,61445,61450,61455</t>
+  </si>
+  <si>
     <t>Cork Jewelry</t>
   </si>
   <si>
@@ -3070,6 +3187,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>敏感肌肤与环保衣橱的完美之选。</t>
     </r>
     <r>
@@ -3089,6 +3212,9 @@
     <t>香水</t>
   </si>
   <si>
+    <t>61411,61416,61421,61426,61431,61436,61441,61446,61451,61456</t>
+  </si>
+  <si>
     <t>Eau De Parfum</t>
   </si>
   <si>
@@ -3108,6 +3234,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>专为令人难忘的余香与深沉留香调制。</t>
     </r>
     <r>
@@ -3127,6 +3259,9 @@
     <t>手提包</t>
   </si>
   <si>
+    <t>61457,61458,61459</t>
+  </si>
+  <si>
     <t>Handbag</t>
   </si>
   <si>
@@ -3146,6 +3281,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>兼具永恒的优雅感与现代实用性设计。</t>
     </r>
     <r>
@@ -3184,6 +3325,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>高端轻奢酒店与井然有序的宾客收纳之理想选择。</t>
     </r>
     <r>
@@ -3222,6 +3369,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>为绝对的精准度与经典声望而生。</t>
     </r>
     <r>
@@ -3263,6 +3416,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>探索专为敏感耳廓打造的日常闪耀之美。</t>
     </r>
     <r>
@@ -3301,6 +3460,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>经过市场测试，具备极佳的抗冲击性与顺畅的旅行体验。</t>
     </r>
     <r>
@@ -3316,6 +3481,735 @@
   <si>
     <t>carry on luggage, checked luggage, spinner suitcase, hardside luggage, travel suitcase</t>
   </si>
+  <si>
+    <t>橱柜五金件|||橱柜拉手</t>
+  </si>
+  <si>
+    <t>61842,61849,61856,61863,61877,61886,61893,61900,61907,61914,61922</t>
+  </si>
+  <si>
+    <t>Cabinet Hardware|||Cabinet Pull</t>
+  </si>
+  <si>
+    <t>1212 Martin Luther King Dr, Hayward, CA 94541</t>
+  </si>
+  <si>
+    <t>cabinepull.com</t>
+  </si>
+  <si>
+    <t>Sleek Cabinet Pulls – Premium Kitchen &amp; Vanity Hardware Upgrades</t>
+  </si>
+  <si>
+    <t>现代极简橱柜拉手：高级厨房与卫浴美妆柜五金升级首选</t>
+  </si>
+  <si>
+    <t>Shop modern cabinet pulls to instantly elevate your kitchen. Explore our hardware collection for soft-close drawer slides, heavy-duty hinges, and alignment templates.</t>
+  </si>
+  <si>
+    <t>选购现代橱柜拉手，瞬间提升您的厨房格调。欢迎浏览我们的五金专区，一站式配齐阻尼抽屉导轨、重型门铰链及安装定位模板。</t>
+  </si>
+  <si>
+    <t>cabinet pulls</t>
+  </si>
+  <si>
+    <t>modern matte black cabinet pulls for kitchen renovation 5 inch</t>
+  </si>
+  <si>
+    <t>4英寸中心距浴室水龙头</t>
+  </si>
+  <si>
+    <t>61843,61850,61857,61865,61880,61887,61894,61901,61908,61915,61923</t>
+  </si>
+  <si>
+    <t>4" Centerset Bathroom Faucet</t>
+  </si>
+  <si>
+    <t>819 S Locust St, Visalia, CA 93277</t>
+  </si>
+  <si>
+    <t>bathfaucetsdirect.com</t>
+  </si>
+  <si>
+    <t>Elite 4" Centerset Bathroom Faucets – Reliable, Easy-Install Designs</t>
+  </si>
+  <si>
+    <t>精英4寸三孔卫浴水龙头：防漏耐用与轻松安装的面盆美学</t>
+  </si>
+  <si>
+    <t>Discover leak-free 4" centerset bathroom faucets built for busy homes. Browse our bath store for pop-up sink drains, vanity light fixtures, and plush hand towels.</t>
+  </si>
+  <si>
+    <t>探索专为高频使用家庭打造的防漏4寸三孔水龙头。同步浏览卫浴专区，搭配选购弹跳落水头、浴室镜前灯以及高档面巾。</t>
+  </si>
+  <si>
+    <t>4 inch centerset bathroom faucet</t>
+  </si>
+  <si>
+    <t>brushed nickel 4 inch centerset bathroom faucet with pop up drain</t>
+  </si>
+  <si>
+    <t>马桶水箱拉杆</t>
+  </si>
+  <si>
+    <t>61844,61851,61858,61867,61881,61888,61895,61902,61909,61916,61924</t>
+  </si>
+  <si>
+    <t>Toilet Tank Lever</t>
+  </si>
+  <si>
+    <t>904 S Court St, Visalia, CA 93277</t>
+  </si>
+  <si>
+    <t>toilettanklevers.com</t>
+  </si>
+  <si>
+    <t>Universal Toilet Tank Levers – Smooth Flush Handle Replacements</t>
+  </si>
+  <si>
+    <t>通用型马桶冲水扳手：顺畅按压与耐腐蚀水箱冲水杆替换件</t>
+  </si>
+  <si>
+    <t>Replace sticking handles with universal toilet tank levers. Shop our bath repair section for heavy-duty flapper valves, fill valves, and stylish toilet brush holders.</t>
+  </si>
+  <si>
+    <t>告别卡顿，更换通用型马桶水箱冲水扳手。欢迎选购卫浴维修专区的重型拍盖阀、进水阀以及时尚马桶刷套装。</t>
+  </si>
+  <si>
+    <t>toilet tank lever</t>
+  </si>
+  <si>
+    <t>side mount toilet tank lever replacement chrome finish universal fit</t>
+  </si>
+  <si>
+    <t>灯具|||户外灯|||地埋灯</t>
+  </si>
+  <si>
+    <t>61845,61852,61859,61869,61882,61889,61896,61903,61910,61917,61925</t>
+  </si>
+  <si>
+    <t>Light|||Outdoor Light|||Well Light</t>
+  </si>
+  <si>
+    <t>1944 Walker St, Las Vegas, NV 89106</t>
+  </si>
+  <si>
+    <t>outdoorwelllights.com</t>
+  </si>
+  <si>
+    <t>Low-Voltage LED Well Lights – Pro Landscape &amp; Architectural Lighting</t>
+  </si>
+  <si>
+    <t>低压LED地埋灯：专业级庭院景观与外墙建筑亮化照明</t>
+  </si>
+  <si>
+    <t>Upgrade curb appeal with weatherproof LED well lights. Check out our outdoor range for low-voltage transformers, burial wire, and solar pathway stakes.</t>
+  </si>
+  <si>
+    <t>选用防水防尘的LED地埋灯，大幅提升房屋外观质感。浏览户外照明专区，一站式搭配变压器、直埋电线和太阳能路径灯。</t>
+  </si>
+  <si>
+    <t>well lights</t>
+  </si>
+  <si>
+    <t>waterproof low voltage led well lights for outdoor tree uplighting</t>
+  </si>
+  <si>
+    <t>五金件|||工具|||砂光机</t>
+  </si>
+  <si>
+    <t>61846,61853,61860,61871,61883,61890,61897,61904,61911,61919,61926</t>
+  </si>
+  <si>
+    <t>Hardware|||Tool|||Sander</t>
+  </si>
+  <si>
+    <t>5557 Damico Dr, Las Vegas, NV 89120</t>
+  </si>
+  <si>
+    <t>prosanders.com</t>
+  </si>
+  <si>
+    <t>High-Efficiency Electric Sanders – Flawless Woodworking Finish Tools</t>
+  </si>
+  <si>
+    <t>高效电动木工砂纸机：打造平整无痕漆面的专业打磨工具</t>
+  </si>
+  <si>
+    <t>Achieve ultra-smooth surfaces with orbital electric sanders. Explore our workshop line for multi-grit sandpaper discs, dust collection bags, and safety goggles.</t>
+  </si>
+  <si>
+    <t>选用高效轨道式电动砂纸机，轻松打造极致平滑的表面。探索工作坊专区，一站式配齐多目数砂纸片、集尘袋与防护护目镜。</t>
+  </si>
+  <si>
+    <t>electric sander</t>
+  </si>
+  <si>
+    <t>random orbital electric sander with dust collection for woodworking</t>
+  </si>
+  <si>
+    <t>淋浴喷头</t>
+  </si>
+  <si>
+    <t>61847,61854,61861,61873,61884,61891,61898,61905,61912,61920</t>
+  </si>
+  <si>
+    <t>Shower Head</t>
+  </si>
+  <si>
+    <t>1002 E Pasadena Ave, Phoenix, AZ 85014</t>
+  </si>
+  <si>
+    <t>showerheadshub.com</t>
+  </si>
+  <si>
+    <t>High-Pressure Shower Heads – Luxury Rainfall &amp; Spa Wall Mounts</t>
+  </si>
+  <si>
+    <t>高压增压淋浴花洒：奢华雨淋体验与水疗级墙装喷头系统</t>
+  </si>
+  <si>
+    <t>Upgrade your morning routine with high-pressure shower heads. Shop our bath collection for leakproof teflon tape, flexible stainless hoses, and moisturizing body washes.</t>
+  </si>
+  <si>
+    <t>用高压增压花洒开启全新清爽的一天。欢迎浏览洗浴专区，一站式购买防漏生料带、不锈钢软管以及滋润型沐浴露。</t>
+  </si>
+  <si>
+    <t>shower head</t>
+  </si>
+  <si>
+    <t>high pressure rainfall shower head with handheld combo replacement</t>
+  </si>
+  <si>
+    <t>管道|||零件|||马桶零件</t>
+  </si>
+  <si>
+    <t>61848,61855,61862,61875,61885,61892,61899,61906,61913,61921</t>
+  </si>
+  <si>
+    <t>Plumb|||Part|||Toilet Part</t>
+  </si>
+  <si>
+    <t>3671 John F. Kennedy Blvd, Jersey City, NJ 07307</t>
+  </si>
+  <si>
+    <t>toiletpartsstore.com</t>
+  </si>
+  <si>
+    <t>Heavy-Duty Toilet Repair Parts – Universal Plumbing Fix Kits</t>
+  </si>
+  <si>
+    <t>耐用马桶维修配件：通用型水暖管道故障快速修复工具包</t>
+  </si>
+  <si>
+    <t>Fix leaks instantly with universal toilet repair parts. Check our plumbing catalog for wax ring seals, corrosion-resistant bolts, and adjustable supply lines.</t>
+  </si>
+  <si>
+    <t>选用通用马桶维修配件，快速解决漏水烦恼。浏览我们的水暖目录，轻松搭配防臭法兰密封圈、耐腐蚀固定螺丝及可调节进水软管。</t>
+  </si>
+  <si>
+    <t>toilet parts</t>
+  </si>
+  <si>
+    <t>universal toilet repair kit with dual flush valve and tank to bowl gasket</t>
+  </si>
+  <si>
+    <t>水族箱过滤器</t>
+  </si>
+  <si>
+    <t>61929,61934,61939,61944,61949,61954,61959,61964,61969,61974,61979</t>
+  </si>
+  <si>
+    <t>Aquarium Filter</t>
+  </si>
+  <si>
+    <t>动物</t>
+  </si>
+  <si>
+    <t>84 Terrace Ave, Jersey City, NJ 07307</t>
+  </si>
+  <si>
+    <t>clearwateratic.com</t>
+  </si>
+  <si>
+    <t>Crystal-Clear Aquarium Filters – Quiet &amp; Powerful Tank Filtration</t>
+  </si>
+  <si>
+    <t>剔透水质水族过滤器：静音强劲的高效鱼缸生态过滤系统</t>
+  </si>
+  <si>
+    <t>Shop advanced aquarium filters for a pristine aquatic habitat. Browse our pet store for carbon filter media, water conditioners, and fish nets.</t>
+  </si>
+  <si>
+    <t>选购先进鱼缸过滤器，打造纯净水族生态。同步浏览宠物专区，一站式配齐活性炭滤材、水质稳定剂与捞鱼网。</t>
+  </si>
+  <si>
+    <t>aquarium filter</t>
+  </si>
+  <si>
+    <t>quiet canister aquarium filter for 50 gallon planted tank</t>
+  </si>
+  <si>
+    <t>珊瑚</t>
+  </si>
+  <si>
+    <t>61930,61935,61940,61945,61950,61955,61960,61965,61970,61975,61980</t>
+  </si>
+  <si>
+    <t>Coral</t>
+  </si>
+  <si>
+    <t>509 S Clayton St, Wilmington, DE 19805</t>
+  </si>
+  <si>
+    <t>reefbuilderfrags.com</t>
+  </si>
+  <si>
+    <t>Premium Live Coral Frags – Vibrant LPS, SPS &amp; Soft Corals for Reefs</t>
+  </si>
+  <si>
+    <t>极品活体珊瑚断枝：色彩斑斓的LPS、SPS与软珊瑚海水硬骨</t>
+  </si>
+  <si>
+    <t>Buy healthy live coral frags to build a breathtaking reef tank. Explore our coral shop for marine salt mixes, reef LED lights, and frag plugs.</t>
+  </si>
+  <si>
+    <t>选购健康活体珊瑚断枝，打造震撼的海水礁岩缸。探索珊瑚专区，一站式搭配专业海水盐、珊瑚专用LED灯及断枝基座。</t>
+  </si>
+  <si>
+    <t>live coral frags</t>
+  </si>
+  <si>
+    <t>ultra color lps sps live coral frags for marine reef tank</t>
+  </si>
+  <si>
+    <t>宠物用品|||宠物碗和喂食器</t>
+  </si>
+  <si>
+    <t>61931,61936,61941,61946,61951,61956,61961,61966,61971,61976</t>
+  </si>
+  <si>
+    <t>Dog|||Supply|||Bowl &amp; Feeder</t>
+  </si>
+  <si>
+    <t>428 N Poplar St, Charlotte, NC 28202</t>
+  </si>
+  <si>
+    <t>wagfeeders.com</t>
+  </si>
+  <si>
+    <t>Ergonomic Dog Bowls &amp; Feeders – Mess-Free Feeding Stations</t>
+  </si>
+  <si>
+    <t>人体工学犬用碗具喂食器：防打翻与健康吞咽的进食黄金站</t>
+  </si>
+  <si>
+    <t>Discover elevated dog bowls and feeders designed for healthier digestion. Shop our dog aisle for leakproof water bottles, silicone food mats, and dry kibble.</t>
+  </si>
+  <si>
+    <t>探索专为促进健康消化设计的抬高式犬用碗具。同步逛逛狗狗专区，轻松搭配防漏随行水杯、硅胶防滑餐垫与天然干粮。</t>
+  </si>
+  <si>
+    <t>dog bowls</t>
+  </si>
+  <si>
+    <t>elevated stainless steel dog bowls with non slip silicone mat</t>
+  </si>
+  <si>
+    <t>狗绳</t>
+  </si>
+  <si>
+    <t>61932,61937,61942,61947,61952,61957,61962,61967,61972,61977</t>
+  </si>
+  <si>
+    <t>Dog Leash</t>
+  </si>
+  <si>
+    <t>1105 Ralph Rd NE, Atlanta, GA 30324</t>
+  </si>
+  <si>
+    <t>apexcaninegear.com</t>
+  </si>
+  <si>
+    <t>Heavy-Duty Dog Leashes – Durable Reflective Walking &amp; Training Leads</t>
+  </si>
+  <si>
+    <t>战术重型牵引绳：反光防爆冲的专业级户外散步与训犬拉绳</t>
+  </si>
+  <si>
+    <t>Upgrade daily walks with heavy-duty dog leashes built for control and comfort. Check out our gear for padded no-pull harnesses, waste bag dispensers, and training treats.</t>
+  </si>
+  <si>
+    <t>选用控绳舒适的重型犬用牵引绳，升级每日散步体验。浏览出行装备区，一站式配齐加厚防爆冲胸背带、拾便袋分配器与训练零食。</t>
+  </si>
+  <si>
+    <t>dog leash</t>
+  </si>
+  <si>
+    <t>heavy duty reflective dog leash with padded handle for large dogs</t>
+  </si>
+  <si>
+    <t>猫粮（湿粮）</t>
+  </si>
+  <si>
+    <t>61933,61938,61943,61948,61953,61958,61963,61968,61973,61978</t>
+  </si>
+  <si>
+    <t>Cat Food Wet</t>
+  </si>
+  <si>
+    <t>2296 Raeford Rd, Orlando, FL 32806</t>
+  </si>
+  <si>
+    <t>purrfectionbites.com</t>
+  </si>
+  <si>
+    <t>Premium Wet Cat Food – Grain-Free, Hydrating Nutrient-Rich Recipes</t>
+  </si>
+  <si>
+    <t>高端天然猫湿粮：无谷补水与高肉含量的全价营养主食罐/餐包</t>
+  </si>
+  <si>
+    <t>Nourish your feline with grain-free wet cat food packed with real protein. Explore our cat shop for crunchy dental treats, freeze-dried toppers, and salmon oil.</t>
+  </si>
+  <si>
+    <t>用富含真肉蛋白的无谷猫湿粮滋养您的爱猫。浏览猫咪专区，同步选购洁齿松脆零食、冻干伴侣及纯正三文鱼油。</t>
+  </si>
+  <si>
+    <t>wet cat food</t>
+  </si>
+  <si>
+    <t>grain free high protein wet cat food cans for sensitive stomach</t>
+  </si>
+  <si>
+    <t>滑板</t>
+  </si>
+  <si>
+    <t>62340,62345,62350,62355,62360,62365,62370,62375</t>
+  </si>
+  <si>
+    <t>Skateboard</t>
+  </si>
+  <si>
+    <t>13 County Rd 665, Jersey City, NJ 07307</t>
+  </si>
+  <si>
+    <t>skateboardsup.com</t>
+  </si>
+  <si>
+    <t>Pro Skateboards &amp; Decks – High-Performance Complete Setups</t>
+  </si>
+  <si>
+    <t>专业级滑板与板面：高弹耐磨的街头刷街与技巧硬核整板</t>
+  </si>
+  <si>
+    <t>Shop high-performance complete skateboards built for street and park sessions. Browse our skate shop for multi-grit griptape, durable trucks, and fast-rolling bearings.</t>
+  </si>
+  <si>
+    <t>选购专为街头与滑板场打造的高性能滑板整板。同步浏览滑板专区，一站式配齐高摩擦砂纸、耐磨支架与高转速轴承。</t>
+  </si>
+  <si>
+    <t>skateboards</t>
+  </si>
+  <si>
+    <t>complete maple wood skateboards for park skating and street tricks</t>
+  </si>
+  <si>
+    <t>滑水板</t>
+  </si>
+  <si>
+    <t>62341,62346,62351,62356,62361,62366,62371,62376</t>
+  </si>
+  <si>
+    <t>Wakeboard</t>
+  </si>
+  <si>
+    <t>2132 Gilles St, Wilmington, DE 19805</t>
+  </si>
+  <si>
+    <t>wakeboardhq.com</t>
+  </si>
+  <si>
+    <t>Wakeboards &amp; Bindings – Pro Cable &amp; Boat Board Setups</t>
+  </si>
+  <si>
+    <t>尾波滑板与固定鞋：专业级索道与船载牵引全套滑水整板</t>
+  </si>
+  <si>
+    <t>Discover aggressive rocker wakeboards engineered for massive pop. Explore our pro water store for adjustable boots, floating tow ropes, and impact vests.</t>
+  </si>
+  <si>
+    <t>探索专为强劲激波腾空设计的激进摇摆线尾波板。浏览专业水上装备区，一站式搭配可调滑水鞋、水上漂浮牵引绳及防撞浮力衣。</t>
+  </si>
+  <si>
+    <t>wakeboards</t>
+  </si>
+  <si>
+    <t>continuous rocker wakeboards with open toe boots combo for boat riding</t>
+  </si>
+  <si>
+    <t>轮滑鞋</t>
+  </si>
+  <si>
+    <t>62342,62347,62352,62357,62362,62367,62372,62377</t>
+  </si>
+  <si>
+    <t>Rollerblade</t>
+  </si>
+  <si>
+    <t>inlineproskates.com</t>
+  </si>
+  <si>
+    <t>Precision Inline Skates – Comfortable Roller Skates for Urban Cruising</t>
+  </si>
+  <si>
+    <t>精巧动能直排轮滑鞋：适合城市刷街与速滑的舒适成人旱冰鞋</t>
+  </si>
+  <si>
+    <t>Upgrade your urban cruise with sleek inline skates built for speed and comfort. Shop our roller shop for replacement PU wheels, brake pads, and protective gear sets.</t>
+  </si>
+  <si>
+    <t>选用专为速度与舒适打造的流线型直排轮滑鞋，升级城市刷街体验。欢迎选购配件专区，一站式更换高弹PU轮、刹车块及全套防护护目镜。</t>
+  </si>
+  <si>
+    <t>inline skates</t>
+  </si>
+  <si>
+    <t>adjustable inline skates for adult fitness and street cruising</t>
+  </si>
+  <si>
+    <t>冲浪板鳍片</t>
+  </si>
+  <si>
+    <t>62343,62348,62353,62358,62363,62368,62373</t>
+  </si>
+  <si>
+    <t>Surfboard Fin</t>
+  </si>
+  <si>
+    <t>983 Palmetto Ave SW, Atlanta, GA 30314</t>
+  </si>
+  <si>
+    <t>surfboardfinsdirect.com</t>
+  </si>
+  <si>
+    <t>High-Performance Surfboard Fins – Fiberglass Thruster &amp; Quad Sets</t>
+  </si>
+  <si>
+    <t>高性能冲浪板尾鳍：玻璃纤维三鳍与四鳍专业冲浪控浪舵组合</t>
+  </si>
+  <si>
+    <t>Optimize your board's drive and hold with premium surfboard fins. Check our surf catalog for fin keys, leash strings, and heavy-duty surf wax.</t>
+  </si>
+  <si>
+    <t>选用高级冲浪板尾鳍，优化冲浪板的推进力与抓浪控浪性能。浏览水上目录，轻松搭配尾鳍螺丝钥匙、脚绳连接绳及高效冲浪蜡。</t>
+  </si>
+  <si>
+    <t>surfboard fins</t>
+  </si>
+  <si>
+    <t>fiberglass thruster surfboard fins for ocean reef breaks</t>
+  </si>
+  <si>
+    <t>潜水服</t>
+  </si>
+  <si>
+    <t>62344,62349,62354,62359,62364,62369,62374</t>
+  </si>
+  <si>
+    <t>Wetsuit</t>
+  </si>
+  <si>
+    <t>1306 Stevens Ave, Orlando, FL 32806</t>
+  </si>
+  <si>
+    <t>wetsuitlab.com</t>
+  </si>
+  <si>
+    <t>Thermal Neoprene Wetsuits – Premium Surf &amp; Dive Suits</t>
+  </si>
+  <si>
+    <t>高效御寒潜水冲浪服：专业级潜水与冲浪全体保暖防寒衣</t>
+  </si>
+  <si>
+    <t>Stay warm in colder waters with flexible neoprene wetsuits. Explore our marine range for thermal surf booties, rash guards, and eco-friendly wetsuit cleaner.</t>
+  </si>
+  <si>
+    <t>穿上高弹氯丁橡胶防寒衣，在低温海水中保持温暖。探索水上运动专区，一站式配齐御寒冲浪保暖鞋、防晒水母衣及环保防寒服清洗剂。</t>
+  </si>
+  <si>
+    <t>wetsuits</t>
+  </si>
+  <si>
+    <t>3mm 2mm full body neoprene wetsuit for cold-water diving</t>
+  </si>
+  <si>
+    <t>泡沫印章</t>
+  </si>
+  <si>
+    <t>62383,62388,62393,62398,62403,62408,62413,62418</t>
+  </si>
+  <si>
+    <t>Foam Stamp</t>
+  </si>
+  <si>
+    <t>艺术与娱乐</t>
+  </si>
+  <si>
+    <t>402 Madison St, Hoboken, NJ 07030</t>
+  </si>
+  <si>
+    <t>foamstampshop.com</t>
+  </si>
+  <si>
+    <t>Professional Foam Stamps – Precision Crafting &amp; Printmaking</t>
+  </si>
+  <si>
+    <t>专业级泡沫印章：手工艺与纸艺制作的精细化模具</t>
+  </si>
+  <si>
+    <t>Create sharp imprints with durable foam stamps for papercrafts. Shop our store for archival ink pads, acrylic blocks, and colorful embossing powders.</t>
+  </si>
+  <si>
+    <t>使用耐用泡沫印章，为纸艺创作打造清晰印记。探索手工艺术专区，一站式配齐档案级印台、亚克力垫块及缤纷凸粉。</t>
+  </si>
+  <si>
+    <t>foam stamps</t>
+  </si>
+  <si>
+    <t>durable foam stamp sets for scrapbooking and textile printing</t>
+  </si>
+  <si>
+    <t>贴纸</t>
+  </si>
+  <si>
+    <t>62384,62389,62394,62399,62404,62409,62414,62424</t>
+  </si>
+  <si>
+    <t>Decal</t>
+  </si>
+  <si>
+    <t>103 Dickinson Ln, Wilmington, DE 19807</t>
+  </si>
+  <si>
+    <t>vinylstickerhub.com</t>
+  </si>
+  <si>
+    <t>Weather-Resistant Vinyl Decals – Universal Surface Stickers</t>
+  </si>
+  <si>
+    <t>耐候乙烯基贴纸：汽车与居家装饰的通用型防晒贴花</t>
+  </si>
+  <si>
+    <t>Apply professional-grade vinyl decals engineered for outdoor durability. Browse our shop for transfer tape, application squeegees, and surface cleaners.</t>
+  </si>
+  <si>
+    <t>选用专为户外耐久设计的高品质乙烯基贴纸。浏览我们的店铺，搭配选购配套转移膜、施工刮板以及表面清洁剂。</t>
+  </si>
+  <si>
+    <t>vinyl decals</t>
+  </si>
+  <si>
+    <t>weather-resistant vinyl stickers for car windows and home decor</t>
+  </si>
+  <si>
+    <t>帆布</t>
+  </si>
+  <si>
+    <t>62385,62390,62395,62400,62405,62410,62415,62425</t>
+  </si>
+  <si>
+    <t>Canva</t>
+  </si>
+  <si>
+    <t>332 Lockley Dr, Charlotte, NC 28207</t>
+  </si>
+  <si>
+    <t>designassetpro.com</t>
+  </si>
+  <si>
+    <t>Canva-Ready Design Templates – Business Creative Assets</t>
+  </si>
+  <si>
+    <t>Canva成品设计模版：小微企业即用型可视化创意素材</t>
+  </si>
+  <si>
+    <t>Accelerate your workflow with professional design templates ready for Canva. Shop our library for color palettes, typography sets, and icon collections.</t>
+  </si>
+  <si>
+    <t>使用可直接加载的 Canva 模版加速设计流程。浏览设计资源库，配齐配色方案、字体排版库与专业图标集。</t>
+  </si>
+  <si>
+    <t>canva templates</t>
+  </si>
+  <si>
+    <t>ready-to-use canva design templates for social media branding</t>
+  </si>
+  <si>
+    <t>十字绣</t>
+  </si>
+  <si>
+    <t>62386,62391,62396,62401,62406,62411,62416</t>
+  </si>
+  <si>
+    <t>Cross Stitch</t>
+  </si>
+  <si>
+    <t>997 Fair St SW, Atlanta, GA 30314</t>
+  </si>
+  <si>
+    <t>crossstitchsupp.com</t>
+  </si>
+  <si>
+    <t>Premium Cross Stitch Kits – Complete Embroidery Sets</t>
+  </si>
+  <si>
+    <t>十字绣全套工具包：适合各阶段爱好者的专业级刺绣方案</t>
+  </si>
+  <si>
+    <t>Master your next embroidery project with complete cross stitch kits. Explore our catalog for DMC floss, linen fabric, and ergonomic hoops.</t>
+  </si>
+  <si>
+    <t>开启您的刺绣创作，选用全套十字绣工具包。探索刺绣目录，一站式选购专业 DMC 绣线、亚麻面料与人体工学绣绷。</t>
+  </si>
+  <si>
+    <t>cross stitch kits</t>
+  </si>
+  <si>
+    <t>all-in-one cross stitch kits for beginners with complete supplies</t>
+  </si>
+  <si>
+    <t>钥匙扣</t>
+  </si>
+  <si>
+    <t>62387,62392,62397,62402,62407,62412,62417</t>
+  </si>
+  <si>
+    <t>Keychain</t>
+  </si>
+  <si>
+    <t>4335 Ilene Ct, Orlando, FL 32806</t>
+  </si>
+  <si>
+    <t>keychainacc.com</t>
+  </si>
+  <si>
+    <t>Durable Acrylic Keychains – Universal Decorative Charms</t>
+  </si>
+  <si>
+    <t>亚克力钥匙扣：简约时尚的通用型潮流挂件与钥匙配饰</t>
+  </si>
+  <si>
+    <t>Shop stylish acrylic keychains perfect for bags and keys. Browse our accessory catalog for heavy-duty split rings, colorful tassels, and display pouches.</t>
+  </si>
+  <si>
+    <t>选购简约时尚的亚克力钥匙扣，完美适配包袋与钥匙。浏览配件专区，一站式配齐高强度开口环、彩色流苏与展示收纳袋。</t>
+  </si>
+  <si>
+    <t>acrylic keychains</t>
+  </si>
+  <si>
+    <t>clear acrylic keychain charms for bags and keys</t>
+  </si>
 </sst>
 </file>
 
@@ -3327,7 +4221,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3368,12 +4262,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Microsoft YaHei"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10.5"/>
       <color rgb="FF1A1A2E"/>
       <name val="Segoe UI"/>
@@ -3383,6 +4271,44 @@
       <sz val="11"/>
       <color rgb="FF1F1F1F"/>
       <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF666666"/>
+      <name val="Helvetica"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3886,137 +4812,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4051,49 +4977,25 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -4101,8 +5003,29 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -4110,16 +5033,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -9917,7 +10831,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q92"/>
+  <dimension ref="A1:Q118"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="50.625" customWidth="1"/>
@@ -9993,10 +10907,10 @@
       <c r="A2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="29" t="s">
         <v>19</v>
       </c>
       <c r="D2" s="6" t="s">
@@ -10099,7 +11013,7 @@
       <c r="A4" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="28" t="s">
         <v>46</v>
       </c>
       <c r="C4" s="4">
@@ -10152,7 +11066,7 @@
       <c r="A5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="28" t="s">
         <v>58</v>
       </c>
       <c r="C5" s="4">
@@ -10205,7 +11119,7 @@
       <c r="A6" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="28" t="s">
         <v>70</v>
       </c>
       <c r="C6" s="4">
@@ -10258,7 +11172,7 @@
       <c r="A7" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="28" t="s">
         <v>82</v>
       </c>
       <c r="C7" s="8">
@@ -10311,7 +11225,7 @@
       <c r="A8" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="28" t="s">
         <v>95</v>
       </c>
       <c r="C8" s="4">
@@ -10364,7 +11278,7 @@
       <c r="A9" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="28" t="s">
         <v>107</v>
       </c>
       <c r="C9" s="4">
@@ -10417,7 +11331,7 @@
       <c r="A10" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="28" t="s">
         <v>118</v>
       </c>
       <c r="C10" s="4">
@@ -10470,7 +11384,7 @@
       <c r="A11" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B11" s="29" t="s">
+      <c r="B11" s="28" t="s">
         <v>130</v>
       </c>
       <c r="C11" s="4">
@@ -10523,7 +11437,7 @@
       <c r="A12" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="28" t="s">
         <v>141</v>
       </c>
       <c r="C12" s="4">
@@ -10735,7 +11649,7 @@
       <c r="A16" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="B16" s="29" t="s">
+      <c r="B16" s="28" t="s">
         <v>186</v>
       </c>
       <c r="C16" s="4">
@@ -11901,7 +12815,7 @@
       <c r="A38" s="4" t="s">
         <v>430</v>
       </c>
-      <c r="B38" s="31" t="s">
+      <c r="B38" s="30" t="s">
         <v>431</v>
       </c>
       <c r="C38" s="8">
@@ -11954,7 +12868,7 @@
       <c r="A39" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="B39" s="31" t="s">
+      <c r="B39" s="30" t="s">
         <v>442</v>
       </c>
       <c r="C39" s="8">
@@ -11975,7 +12889,7 @@
       <c r="H39" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="I39" s="12" t="s">
+      <c r="I39" s="11" t="s">
         <v>444</v>
       </c>
       <c r="J39" s="4" t="s">
@@ -12076,7 +12990,7 @@
         <v>60</v>
       </c>
       <c r="G41" s="4"/>
-      <c r="H41" s="13" t="s">
+      <c r="H41" s="12" t="s">
         <v>466</v>
       </c>
       <c r="I41" s="4" t="s">
@@ -12127,7 +13041,7 @@
         <v>72</v>
       </c>
       <c r="G42" s="4"/>
-      <c r="H42" s="13" t="s">
+      <c r="H42" s="12" t="s">
         <v>466</v>
       </c>
       <c r="I42" s="4" t="s">
@@ -12178,7 +13092,7 @@
         <v>85</v>
       </c>
       <c r="G43" s="4"/>
-      <c r="H43" s="13" t="s">
+      <c r="H43" s="12" t="s">
         <v>466</v>
       </c>
       <c r="I43" s="4" t="s">
@@ -12372,47 +13286,47 @@
       <c r="A47" t="s">
         <v>531</v>
       </c>
-      <c r="B47" s="32" t="s">
+      <c r="B47" s="28" t="s">
         <v>532</v>
       </c>
-      <c r="C47" s="15">
+      <c r="C47" s="8">
         <v>58327</v>
       </c>
-      <c r="D47" s="16" t="s">
+      <c r="D47" s="13" t="s">
         <v>533</v>
       </c>
-      <c r="E47" s="17" t="s">
+      <c r="E47" s="4" t="s">
         <v>500</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="G47" s="18"/>
-      <c r="H47" s="19" t="s">
+      <c r="G47" s="4"/>
+      <c r="H47" s="14" t="s">
         <v>534</v>
       </c>
-      <c r="I47" s="20" t="s">
+      <c r="I47" s="15" t="s">
         <v>535</v>
       </c>
-      <c r="J47" s="20" t="s">
+      <c r="J47" s="15" t="s">
         <v>536</v>
       </c>
-      <c r="K47" s="21" t="s">
+      <c r="K47" s="16" t="s">
         <v>537</v>
       </c>
-      <c r="L47" s="20" t="s">
+      <c r="L47" s="15" t="s">
         <v>538</v>
       </c>
-      <c r="M47" s="21" t="s">
+      <c r="M47" s="16" t="s">
         <v>539</v>
       </c>
-      <c r="N47" s="21" t="s">
+      <c r="N47" s="16" t="s">
         <v>540</v>
       </c>
-      <c r="O47" s="20" t="s">
+      <c r="O47" s="15" t="s">
         <v>541</v>
       </c>
-      <c r="P47" s="21" t="s">
+      <c r="P47" s="16" t="s">
         <v>542</v>
       </c>
     </row>
@@ -12420,47 +13334,47 @@
       <c r="A48" t="s">
         <v>543</v>
       </c>
-      <c r="B48" s="22" t="s">
+      <c r="B48" s="5" t="s">
         <v>544</v>
       </c>
-      <c r="C48" s="15">
+      <c r="C48" s="8">
         <v>58326</v>
       </c>
-      <c r="D48" s="23" t="s">
+      <c r="D48" s="6" t="s">
         <v>545</v>
       </c>
-      <c r="E48" s="17" t="s">
+      <c r="E48" s="4" t="s">
         <v>500</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G48" s="24"/>
-      <c r="H48" s="19" t="s">
+      <c r="G48" s="4"/>
+      <c r="H48" s="14" t="s">
         <v>534</v>
       </c>
-      <c r="I48" s="20" t="s">
+      <c r="I48" s="15" t="s">
         <v>546</v>
       </c>
-      <c r="J48" s="20" t="s">
+      <c r="J48" s="15" t="s">
         <v>547</v>
       </c>
-      <c r="K48" s="21" t="s">
+      <c r="K48" s="16" t="s">
         <v>548</v>
       </c>
-      <c r="L48" s="20" t="s">
+      <c r="L48" s="15" t="s">
         <v>549</v>
       </c>
-      <c r="M48" s="21" t="s">
+      <c r="M48" s="16" t="s">
         <v>550</v>
       </c>
-      <c r="N48" s="21" t="s">
+      <c r="N48" s="16" t="s">
         <v>551</v>
       </c>
-      <c r="O48" s="20" t="s">
+      <c r="O48" s="15" t="s">
         <v>552</v>
       </c>
-      <c r="P48" s="21" t="s">
+      <c r="P48" s="16" t="s">
         <v>553</v>
       </c>
     </row>
@@ -12468,47 +13382,47 @@
       <c r="A49" t="s">
         <v>554</v>
       </c>
-      <c r="B49" s="22" t="s">
+      <c r="B49" s="5" t="s">
         <v>555</v>
       </c>
-      <c r="C49" s="15">
+      <c r="C49" s="8">
         <v>58325</v>
       </c>
-      <c r="D49" s="23" t="s">
+      <c r="D49" s="6" t="s">
         <v>556</v>
       </c>
-      <c r="E49" s="17" t="s">
+      <c r="E49" s="4" t="s">
         <v>500</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="G49" s="24"/>
-      <c r="H49" s="19" t="s">
+      <c r="G49" s="4"/>
+      <c r="H49" s="14" t="s">
         <v>534</v>
       </c>
-      <c r="I49" s="20" t="s">
+      <c r="I49" s="15" t="s">
         <v>557</v>
       </c>
-      <c r="J49" s="20" t="s">
+      <c r="J49" s="15" t="s">
         <v>558</v>
       </c>
-      <c r="K49" s="21" t="s">
+      <c r="K49" s="16" t="s">
         <v>559</v>
       </c>
-      <c r="L49" s="20" t="s">
+      <c r="L49" s="15" t="s">
         <v>560</v>
       </c>
-      <c r="M49" s="21" t="s">
+      <c r="M49" s="16" t="s">
         <v>561</v>
       </c>
-      <c r="N49" s="21" t="s">
+      <c r="N49" s="16" t="s">
         <v>562</v>
       </c>
-      <c r="O49" s="20" t="s">
+      <c r="O49" s="15" t="s">
         <v>563</v>
       </c>
-      <c r="P49" s="21" t="s">
+      <c r="P49" s="16" t="s">
         <v>564</v>
       </c>
     </row>
@@ -12516,47 +13430,47 @@
       <c r="A50" t="s">
         <v>565</v>
       </c>
-      <c r="B50" s="22" t="s">
+      <c r="B50" s="5" t="s">
         <v>566</v>
       </c>
-      <c r="C50" s="15">
+      <c r="C50" s="8">
         <v>58328</v>
       </c>
-      <c r="D50" s="23" t="s">
+      <c r="D50" s="6" t="s">
         <v>567</v>
       </c>
-      <c r="E50" s="17" t="s">
+      <c r="E50" s="4" t="s">
         <v>500</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="G50" s="24"/>
-      <c r="H50" s="19" t="s">
+      <c r="G50" s="4"/>
+      <c r="H50" s="14" t="s">
         <v>534</v>
       </c>
-      <c r="I50" s="20" t="s">
+      <c r="I50" s="15" t="s">
         <v>568</v>
       </c>
-      <c r="J50" s="20" t="s">
+      <c r="J50" s="15" t="s">
         <v>569</v>
       </c>
-      <c r="K50" s="21" t="s">
+      <c r="K50" s="16" t="s">
         <v>570</v>
       </c>
-      <c r="L50" s="20" t="s">
+      <c r="L50" s="15" t="s">
         <v>571</v>
       </c>
-      <c r="M50" s="21" t="s">
+      <c r="M50" s="16" t="s">
         <v>572</v>
       </c>
-      <c r="N50" s="21" t="s">
+      <c r="N50" s="16" t="s">
         <v>573</v>
       </c>
-      <c r="O50" s="20" t="s">
+      <c r="O50" s="15" t="s">
         <v>574</v>
       </c>
-      <c r="P50" s="21" t="s">
+      <c r="P50" s="16" t="s">
         <v>575</v>
       </c>
     </row>
@@ -12564,47 +13478,47 @@
       <c r="A51" t="s">
         <v>576</v>
       </c>
-      <c r="B51" s="22" t="s">
+      <c r="B51" s="5" t="s">
         <v>577</v>
       </c>
-      <c r="C51" s="24">
+      <c r="C51" s="4">
         <v>58324</v>
       </c>
-      <c r="D51" s="23" t="s">
+      <c r="D51" s="6" t="s">
         <v>578</v>
       </c>
-      <c r="E51" s="17" t="s">
+      <c r="E51" s="4" t="s">
         <v>500</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="G51" s="24"/>
-      <c r="H51" s="19" t="s">
+      <c r="G51" s="4"/>
+      <c r="H51" s="14" t="s">
         <v>534</v>
       </c>
-      <c r="I51" s="20" t="s">
+      <c r="I51" s="15" t="s">
         <v>579</v>
       </c>
-      <c r="J51" s="20" t="s">
+      <c r="J51" s="15" t="s">
         <v>580</v>
       </c>
-      <c r="K51" s="21" t="s">
+      <c r="K51" s="16" t="s">
         <v>581</v>
       </c>
-      <c r="L51" s="20" t="s">
+      <c r="L51" s="15" t="s">
         <v>582</v>
       </c>
-      <c r="M51" s="21" t="s">
+      <c r="M51" s="16" t="s">
         <v>583</v>
       </c>
-      <c r="N51" s="21" t="s">
+      <c r="N51" s="16" t="s">
         <v>584</v>
       </c>
-      <c r="O51" s="20" t="s">
+      <c r="O51" s="15" t="s">
         <v>585</v>
       </c>
-      <c r="P51" s="21" t="s">
+      <c r="P51" s="16" t="s">
         <v>586</v>
       </c>
     </row>
@@ -12612,47 +13526,47 @@
       <c r="A52" t="s">
         <v>587</v>
       </c>
-      <c r="B52" s="22" t="s">
+      <c r="B52" s="5" t="s">
         <v>588</v>
       </c>
-      <c r="C52" s="24">
+      <c r="C52" s="4">
         <v>58655</v>
       </c>
-      <c r="D52" s="23" t="s">
+      <c r="D52" s="6" t="s">
         <v>589</v>
       </c>
-      <c r="E52" s="17" t="s">
+      <c r="E52" s="4" t="s">
         <v>500</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G52" s="24"/>
-      <c r="H52" s="19" t="s">
+      <c r="G52" s="4"/>
+      <c r="H52" s="14" t="s">
         <v>534</v>
       </c>
-      <c r="I52" s="17" t="s">
+      <c r="I52" s="4" t="s">
         <v>590</v>
       </c>
-      <c r="J52" s="17" t="s">
+      <c r="J52" s="4" t="s">
         <v>591</v>
       </c>
-      <c r="K52" s="21" t="s">
+      <c r="K52" s="16" t="s">
         <v>592</v>
       </c>
-      <c r="L52" s="20" t="s">
+      <c r="L52" s="15" t="s">
         <v>593</v>
       </c>
-      <c r="M52" s="21" t="s">
+      <c r="M52" s="16" t="s">
         <v>594</v>
       </c>
-      <c r="N52" s="21" t="s">
+      <c r="N52" s="16" t="s">
         <v>595</v>
       </c>
-      <c r="O52" s="20" t="s">
+      <c r="O52" s="15" t="s">
         <v>596</v>
       </c>
-      <c r="P52" s="21" t="s">
+      <c r="P52" s="16" t="s">
         <v>597</v>
       </c>
     </row>
@@ -12660,302 +13574,302 @@
       <c r="A53" t="s">
         <v>598</v>
       </c>
-      <c r="B53" s="22" t="s">
+      <c r="B53" s="5" t="s">
         <v>599</v>
       </c>
-      <c r="C53" s="15">
+      <c r="C53" s="8">
         <v>58652</v>
       </c>
-      <c r="D53" s="23" t="s">
+      <c r="D53" s="6" t="s">
         <v>600</v>
       </c>
-      <c r="E53" s="17" t="s">
+      <c r="E53" s="4" t="s">
         <v>500</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="G53" s="24"/>
-      <c r="H53" s="19" t="s">
-        <v>534</v>
-      </c>
-      <c r="I53" s="20" t="s">
+      <c r="G53" s="4"/>
+      <c r="H53" s="17" t="s">
         <v>601</v>
       </c>
-      <c r="J53" s="20" t="s">
+      <c r="I53" s="15" t="s">
         <v>602</v>
       </c>
-      <c r="K53" s="21" t="s">
+      <c r="J53" s="15" t="s">
         <v>603</v>
       </c>
-      <c r="L53" s="20" t="s">
+      <c r="K53" s="16" t="s">
         <v>604</v>
       </c>
-      <c r="M53" s="21" t="s">
+      <c r="L53" s="15" t="s">
         <v>605</v>
       </c>
-      <c r="N53" s="21" t="s">
+      <c r="M53" s="16" t="s">
         <v>606</v>
       </c>
-      <c r="O53" s="20" t="s">
+      <c r="N53" s="16" t="s">
         <v>607</v>
       </c>
-      <c r="P53" s="21" t="s">
+      <c r="O53" s="15" t="s">
         <v>608</v>
+      </c>
+      <c r="P53" s="16" t="s">
+        <v>609</v>
       </c>
     </row>
     <row r="54" ht="63.5" customHeight="1" spans="1:16">
       <c r="A54" t="s">
-        <v>609</v>
-      </c>
-      <c r="B54" s="22" t="s">
         <v>610</v>
       </c>
-      <c r="C54" s="15">
+      <c r="B54" s="5" t="s">
+        <v>611</v>
+      </c>
+      <c r="C54" s="8">
         <v>58654</v>
       </c>
-      <c r="D54" s="23" t="s">
-        <v>611</v>
-      </c>
-      <c r="E54" s="17" t="s">
+      <c r="D54" s="6" t="s">
+        <v>612</v>
+      </c>
+      <c r="E54" s="4" t="s">
         <v>500</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G54" s="24"/>
-      <c r="H54" s="19" t="s">
-        <v>534</v>
-      </c>
-      <c r="I54" s="20" t="s">
-        <v>612</v>
-      </c>
-      <c r="J54" s="20" t="s">
+      <c r="G54" s="4"/>
+      <c r="H54" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I54" s="15" t="s">
         <v>613</v>
       </c>
-      <c r="K54" s="21" t="s">
+      <c r="J54" s="15" t="s">
         <v>614</v>
       </c>
-      <c r="L54" s="20" t="s">
+      <c r="K54" s="16" t="s">
         <v>615</v>
       </c>
-      <c r="M54" s="21" t="s">
+      <c r="L54" s="15" t="s">
         <v>616</v>
       </c>
-      <c r="N54" s="21" t="s">
+      <c r="M54" s="16" t="s">
         <v>617</v>
       </c>
-      <c r="O54" s="20" t="s">
+      <c r="N54" s="16" t="s">
         <v>618</v>
       </c>
-      <c r="P54" s="21" t="s">
+      <c r="O54" s="15" t="s">
         <v>619</v>
+      </c>
+      <c r="P54" s="16" t="s">
+        <v>620</v>
       </c>
     </row>
     <row r="55" ht="63.5" customHeight="1" spans="1:16">
       <c r="A55" t="s">
-        <v>620</v>
-      </c>
-      <c r="B55" s="22" t="s">
         <v>621</v>
       </c>
-      <c r="C55" s="15">
+      <c r="B55" s="5" t="s">
+        <v>622</v>
+      </c>
+      <c r="C55" s="8">
         <v>58651</v>
       </c>
-      <c r="D55" s="23" t="s">
-        <v>622</v>
-      </c>
-      <c r="E55" s="17" t="s">
+      <c r="D55" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="E55" s="4" t="s">
         <v>500</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="G55" s="24"/>
-      <c r="H55" s="19" t="s">
-        <v>534</v>
-      </c>
-      <c r="I55" s="20" t="s">
-        <v>623</v>
-      </c>
-      <c r="J55" s="20" t="s">
+      <c r="G55" s="4"/>
+      <c r="H55" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I55" s="15" t="s">
         <v>624</v>
       </c>
-      <c r="K55" s="21" t="s">
+      <c r="J55" s="15" t="s">
         <v>625</v>
       </c>
-      <c r="L55" s="20" t="s">
+      <c r="K55" s="16" t="s">
         <v>626</v>
       </c>
-      <c r="M55" s="21" t="s">
+      <c r="L55" s="15" t="s">
         <v>627</v>
       </c>
-      <c r="N55" s="21" t="s">
+      <c r="M55" s="16" t="s">
         <v>628</v>
       </c>
-      <c r="O55" s="20" t="s">
+      <c r="N55" s="16" t="s">
         <v>629</v>
       </c>
-      <c r="P55" s="21" t="s">
+      <c r="O55" s="15" t="s">
         <v>630</v>
+      </c>
+      <c r="P55" s="16" t="s">
+        <v>631</v>
       </c>
     </row>
     <row r="56" ht="63.5" customHeight="1" spans="1:16">
       <c r="A56" t="s">
-        <v>631</v>
-      </c>
-      <c r="B56" s="22" t="s">
         <v>632</v>
       </c>
-      <c r="C56" s="15">
+      <c r="B56" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="C56" s="8">
         <v>58647</v>
       </c>
-      <c r="D56" s="23" t="s">
-        <v>633</v>
-      </c>
-      <c r="E56" s="17" t="s">
+      <c r="D56" s="6" t="s">
+        <v>634</v>
+      </c>
+      <c r="E56" s="4" t="s">
         <v>500</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="G56" s="24"/>
-      <c r="H56" s="19" t="s">
-        <v>534</v>
-      </c>
-      <c r="I56" s="20" t="s">
-        <v>634</v>
-      </c>
-      <c r="J56" s="20" t="s">
+      <c r="G56" s="4"/>
+      <c r="H56" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I56" s="15" t="s">
         <v>635</v>
       </c>
-      <c r="K56" s="21" t="s">
+      <c r="J56" s="15" t="s">
         <v>636</v>
       </c>
-      <c r="L56" s="20" t="s">
+      <c r="K56" s="16" t="s">
         <v>637</v>
       </c>
-      <c r="M56" s="21" t="s">
+      <c r="L56" s="15" t="s">
         <v>638</v>
       </c>
-      <c r="N56" s="21" t="s">
+      <c r="M56" s="16" t="s">
         <v>639</v>
       </c>
-      <c r="O56" s="20" t="s">
+      <c r="N56" s="16" t="s">
         <v>640</v>
       </c>
-      <c r="P56" s="21" t="s">
+      <c r="O56" s="15" t="s">
         <v>641</v>
+      </c>
+      <c r="P56" s="16" t="s">
+        <v>642</v>
       </c>
     </row>
     <row r="57" ht="63.5" customHeight="1" spans="1:16">
       <c r="A57" t="s">
-        <v>642</v>
-      </c>
-      <c r="B57" s="22" t="s">
         <v>643</v>
       </c>
-      <c r="C57" s="15">
+      <c r="B57" s="5" t="s">
+        <v>644</v>
+      </c>
+      <c r="C57" s="8">
         <v>58650</v>
       </c>
-      <c r="D57" s="23" t="s">
-        <v>644</v>
-      </c>
-      <c r="E57" s="17" t="s">
+      <c r="D57" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="E57" s="4" t="s">
         <v>500</v>
       </c>
       <c r="F57" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G57" s="24"/>
-      <c r="H57" s="19" t="s">
+      <c r="G57" s="4"/>
+      <c r="H57" s="14" t="s">
         <v>534</v>
       </c>
-      <c r="I57" s="20" t="s">
-        <v>645</v>
-      </c>
-      <c r="J57" s="20" t="s">
+      <c r="I57" s="15" t="s">
         <v>646</v>
       </c>
-      <c r="K57" s="21" t="s">
+      <c r="J57" s="15" t="s">
         <v>647</v>
       </c>
-      <c r="L57" s="20" t="s">
+      <c r="K57" s="16" t="s">
         <v>648</v>
       </c>
-      <c r="M57" s="21" t="s">
+      <c r="L57" s="15" t="s">
         <v>649</v>
       </c>
-      <c r="N57" s="21" t="s">
+      <c r="M57" s="16" t="s">
         <v>650</v>
       </c>
-      <c r="O57" s="20" t="s">
+      <c r="N57" s="16" t="s">
         <v>651</v>
       </c>
-      <c r="P57" s="21" t="s">
+      <c r="O57" s="15" t="s">
         <v>652</v>
+      </c>
+      <c r="P57" s="16" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="58" ht="47" customHeight="1" spans="1:16">
       <c r="A58" t="s">
-        <v>653</v>
-      </c>
-      <c r="B58" s="22" t="s">
         <v>654</v>
       </c>
-      <c r="C58" s="15">
+      <c r="B58" s="5" t="s">
+        <v>655</v>
+      </c>
+      <c r="C58" s="8">
         <v>58649</v>
       </c>
-      <c r="D58" s="23" t="s">
-        <v>655</v>
-      </c>
-      <c r="E58" s="17" t="s">
+      <c r="D58" s="6" t="s">
+        <v>656</v>
+      </c>
+      <c r="E58" s="4" t="s">
         <v>500</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="G58" s="24"/>
-      <c r="H58" s="19" t="s">
+      <c r="G58" s="4"/>
+      <c r="H58" s="14" t="s">
         <v>534</v>
       </c>
-      <c r="I58" s="20" t="s">
-        <v>656</v>
-      </c>
-      <c r="J58" s="20" t="s">
+      <c r="I58" s="15" t="s">
         <v>657</v>
       </c>
-      <c r="K58" s="21" t="s">
+      <c r="J58" s="15" t="s">
         <v>658</v>
       </c>
-      <c r="L58" s="20" t="s">
+      <c r="K58" s="16" t="s">
         <v>659</v>
       </c>
-      <c r="M58" s="21" t="s">
+      <c r="L58" s="15" t="s">
         <v>660</v>
       </c>
-      <c r="N58" s="21" t="s">
+      <c r="M58" s="16" t="s">
         <v>661</v>
       </c>
-      <c r="O58" s="20" t="s">
+      <c r="N58" s="16" t="s">
         <v>662</v>
       </c>
-      <c r="P58" s="21" t="s">
+      <c r="O58" s="15" t="s">
         <v>663</v>
+      </c>
+      <c r="P58" s="16" t="s">
+        <v>664</v>
       </c>
     </row>
     <row r="59" ht="47" customHeight="1" spans="1:16">
       <c r="A59" t="s">
-        <v>664</v>
-      </c>
-      <c r="B59" s="22" t="s">
         <v>665</v>
       </c>
-      <c r="C59" s="15">
+      <c r="B59" s="5" t="s">
+        <v>666</v>
+      </c>
+      <c r="C59" s="8">
         <v>58460</v>
       </c>
-      <c r="D59" s="23" t="s">
-        <v>666</v>
+      <c r="D59" s="6" t="s">
+        <v>667</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>233</v>
@@ -12963,47 +13877,47 @@
       <c r="F59" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G59" s="24"/>
-      <c r="H59" s="19" t="s">
+      <c r="G59" s="4"/>
+      <c r="H59" s="14" t="s">
         <v>534</v>
       </c>
-      <c r="I59" s="24" t="s">
-        <v>667</v>
-      </c>
-      <c r="J59" s="21" t="s">
+      <c r="I59" s="4" t="s">
         <v>668</v>
       </c>
-      <c r="K59" s="21" t="s">
+      <c r="J59" s="16" t="s">
         <v>669</v>
       </c>
-      <c r="L59" s="20" t="s">
+      <c r="K59" s="16" t="s">
         <v>670</v>
       </c>
-      <c r="M59" s="21" t="s">
+      <c r="L59" s="15" t="s">
         <v>671</v>
       </c>
-      <c r="N59" s="21" t="s">
+      <c r="M59" s="16" t="s">
         <v>672</v>
       </c>
-      <c r="O59" s="20" t="s">
+      <c r="N59" s="16" t="s">
         <v>673</v>
       </c>
-      <c r="P59" s="21" t="s">
+      <c r="O59" s="15" t="s">
         <v>674</v>
+      </c>
+      <c r="P59" s="16" t="s">
+        <v>675</v>
       </c>
     </row>
     <row r="60" ht="47" customHeight="1" spans="1:16">
       <c r="A60" t="s">
-        <v>675</v>
-      </c>
-      <c r="B60" s="22" t="s">
         <v>676</v>
       </c>
-      <c r="C60" s="15">
+      <c r="B60" s="5" t="s">
+        <v>677</v>
+      </c>
+      <c r="C60" s="8">
         <v>58458</v>
       </c>
-      <c r="D60" s="23" t="s">
-        <v>677</v>
+      <c r="D60" s="6" t="s">
+        <v>678</v>
       </c>
       <c r="E60" s="4" t="s">
         <v>233</v>
@@ -13011,47 +13925,47 @@
       <c r="F60" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="G60" s="24"/>
-      <c r="H60" s="19" t="s">
+      <c r="G60" s="4"/>
+      <c r="H60" s="14" t="s">
         <v>534</v>
       </c>
-      <c r="I60" s="24" t="s">
-        <v>678</v>
-      </c>
-      <c r="J60" s="21" t="s">
+      <c r="I60" s="4" t="s">
         <v>679</v>
       </c>
-      <c r="K60" s="21" t="s">
+      <c r="J60" s="16" t="s">
         <v>680</v>
       </c>
-      <c r="L60" s="20" t="s">
+      <c r="K60" s="16" t="s">
         <v>681</v>
       </c>
-      <c r="M60" s="21" t="s">
+      <c r="L60" s="15" t="s">
         <v>682</v>
       </c>
-      <c r="N60" s="21" t="s">
+      <c r="M60" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="O60" s="20" t="s">
+      <c r="N60" s="16" t="s">
         <v>684</v>
       </c>
-      <c r="P60" s="21" t="s">
+      <c r="O60" s="15" t="s">
         <v>685</v>
+      </c>
+      <c r="P60" s="16" t="s">
+        <v>686</v>
       </c>
     </row>
     <row r="61" ht="47" customHeight="1" spans="1:16">
       <c r="A61" t="s">
-        <v>686</v>
-      </c>
-      <c r="B61" s="33" t="s">
         <v>687</v>
       </c>
-      <c r="C61" s="15">
+      <c r="B61" s="28" t="s">
+        <v>688</v>
+      </c>
+      <c r="C61" s="8">
         <v>58465</v>
       </c>
-      <c r="D61" s="16" t="s">
-        <v>688</v>
+      <c r="D61" s="13" t="s">
+        <v>689</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>233</v>
@@ -13059,47 +13973,47 @@
       <c r="F61" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="G61" s="24"/>
-      <c r="H61" s="19" t="s">
+      <c r="G61" s="4"/>
+      <c r="H61" s="14" t="s">
         <v>534</v>
       </c>
-      <c r="I61" s="24" t="s">
-        <v>689</v>
-      </c>
-      <c r="J61" s="21" t="s">
+      <c r="I61" s="4" t="s">
         <v>690</v>
       </c>
-      <c r="K61" s="21" t="s">
+      <c r="J61" s="16" t="s">
         <v>691</v>
       </c>
-      <c r="L61" s="20" t="s">
+      <c r="K61" s="16" t="s">
         <v>692</v>
       </c>
-      <c r="M61" s="21" t="s">
+      <c r="L61" s="15" t="s">
         <v>693</v>
       </c>
-      <c r="N61" s="21" t="s">
+      <c r="M61" s="16" t="s">
         <v>694</v>
       </c>
-      <c r="O61" s="20" t="s">
+      <c r="N61" s="16" t="s">
         <v>695</v>
       </c>
-      <c r="P61" s="21" t="s">
+      <c r="O61" s="15" t="s">
         <v>696</v>
+      </c>
+      <c r="P61" s="16" t="s">
+        <v>697</v>
       </c>
     </row>
     <row r="62" ht="63.5" customHeight="1" spans="1:16">
       <c r="A62" t="s">
-        <v>697</v>
-      </c>
-      <c r="B62" s="22" t="s">
         <v>698</v>
       </c>
-      <c r="C62" s="15">
+      <c r="B62" s="5" t="s">
+        <v>699</v>
+      </c>
+      <c r="C62" s="8">
         <v>58457</v>
       </c>
-      <c r="D62" s="16" t="s">
-        <v>699</v>
+      <c r="D62" s="13" t="s">
+        <v>700</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>233</v>
@@ -13107,46 +14021,46 @@
       <c r="F62" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="H62" s="19" t="s">
+      <c r="H62" s="14" t="s">
         <v>534</v>
       </c>
-      <c r="I62" s="24" t="s">
-        <v>700</v>
-      </c>
-      <c r="J62" s="21" t="s">
+      <c r="I62" s="4" t="s">
         <v>701</v>
       </c>
-      <c r="K62" s="21" t="s">
+      <c r="J62" s="16" t="s">
         <v>702</v>
       </c>
-      <c r="L62" s="20" t="s">
+      <c r="K62" s="16" t="s">
         <v>703</v>
       </c>
-      <c r="M62" s="21" t="s">
+      <c r="L62" s="15" t="s">
         <v>704</v>
       </c>
-      <c r="N62" s="21" t="s">
+      <c r="M62" s="16" t="s">
         <v>705</v>
       </c>
-      <c r="O62" s="20" t="s">
+      <c r="N62" s="16" t="s">
         <v>706</v>
       </c>
-      <c r="P62" s="21" t="s">
+      <c r="O62" s="15" t="s">
         <v>707</v>
+      </c>
+      <c r="P62" s="16" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="63" ht="47" customHeight="1" spans="1:16">
       <c r="A63" t="s">
-        <v>708</v>
-      </c>
-      <c r="B63" s="22" t="s">
         <v>709</v>
       </c>
-      <c r="C63" s="15">
+      <c r="B63" s="5" t="s">
+        <v>710</v>
+      </c>
+      <c r="C63" s="8">
         <v>58464</v>
       </c>
-      <c r="D63" s="23" t="s">
-        <v>710</v>
+      <c r="D63" s="6" t="s">
+        <v>711</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>233</v>
@@ -13154,46 +14068,46 @@
       <c r="F63" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="H63" s="19" t="s">
+      <c r="H63" s="14" t="s">
         <v>534</v>
       </c>
-      <c r="I63" s="24" t="s">
-        <v>711</v>
-      </c>
-      <c r="J63" s="21" t="s">
+      <c r="I63" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="K63" s="21" t="s">
+      <c r="J63" s="16" t="s">
         <v>713</v>
       </c>
-      <c r="L63" s="20" t="s">
+      <c r="K63" s="16" t="s">
         <v>714</v>
       </c>
-      <c r="M63" s="21" t="s">
+      <c r="L63" s="15" t="s">
         <v>715</v>
       </c>
-      <c r="N63" s="21" t="s">
+      <c r="M63" s="16" t="s">
         <v>716</v>
       </c>
-      <c r="O63" s="20" t="s">
+      <c r="N63" s="16" t="s">
         <v>717</v>
       </c>
-      <c r="P63" s="21" t="s">
+      <c r="O63" s="15" t="s">
         <v>718</v>
+      </c>
+      <c r="P63" s="16" t="s">
+        <v>719</v>
       </c>
     </row>
     <row r="64" ht="47" customHeight="1" spans="1:16">
       <c r="A64" t="s">
-        <v>719</v>
-      </c>
-      <c r="B64" s="22" t="s">
         <v>720</v>
       </c>
-      <c r="C64" s="15">
+      <c r="B64" s="5" t="s">
+        <v>721</v>
+      </c>
+      <c r="C64" s="8">
         <v>58461</v>
       </c>
-      <c r="D64" s="23" t="s">
-        <v>721</v>
+      <c r="D64" s="6" t="s">
+        <v>722</v>
       </c>
       <c r="E64" s="4" t="s">
         <v>233</v>
@@ -13201,46 +14115,46 @@
       <c r="F64" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="H64" s="19" t="s">
+      <c r="H64" s="14" t="s">
         <v>534</v>
       </c>
-      <c r="I64" s="24" t="s">
-        <v>722</v>
-      </c>
-      <c r="J64" s="21" t="s">
+      <c r="I64" s="4" t="s">
         <v>723</v>
       </c>
-      <c r="K64" s="21" t="s">
+      <c r="J64" s="16" t="s">
         <v>724</v>
       </c>
-      <c r="L64" s="20" t="s">
+      <c r="K64" s="16" t="s">
         <v>725</v>
       </c>
-      <c r="M64" s="21" t="s">
+      <c r="L64" s="15" t="s">
         <v>726</v>
       </c>
-      <c r="N64" s="21" t="s">
+      <c r="M64" s="16" t="s">
         <v>727</v>
       </c>
-      <c r="O64" s="20" t="s">
+      <c r="N64" s="16" t="s">
         <v>728</v>
       </c>
-      <c r="P64" s="21" t="s">
+      <c r="O64" s="15" t="s">
         <v>729</v>
+      </c>
+      <c r="P64" s="16" t="s">
+        <v>730</v>
       </c>
     </row>
     <row r="65" ht="47" customHeight="1" spans="1:16">
       <c r="A65" t="s">
-        <v>730</v>
-      </c>
-      <c r="B65" s="22" t="s">
         <v>731</v>
       </c>
-      <c r="C65" s="15">
+      <c r="B65" s="5" t="s">
+        <v>732</v>
+      </c>
+      <c r="C65" s="8">
         <v>58463</v>
       </c>
-      <c r="D65" s="23" t="s">
-        <v>732</v>
+      <c r="D65" s="6" t="s">
+        <v>733</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>233</v>
@@ -13248,376 +14162,376 @@
       <c r="F65" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="H65" s="19" t="s">
+      <c r="H65" s="14" t="s">
         <v>534</v>
       </c>
-      <c r="I65" s="24" t="s">
-        <v>733</v>
-      </c>
-      <c r="J65" s="21" t="s">
+      <c r="I65" s="4" t="s">
         <v>734</v>
       </c>
-      <c r="K65" s="21" t="s">
+      <c r="J65" s="16" t="s">
         <v>735</v>
       </c>
-      <c r="L65" s="20" t="s">
+      <c r="K65" s="16" t="s">
         <v>736</v>
       </c>
-      <c r="M65" s="21" t="s">
+      <c r="L65" s="15" t="s">
         <v>737</v>
       </c>
-      <c r="N65" s="21" t="s">
+      <c r="M65" s="16" t="s">
         <v>738</v>
       </c>
-      <c r="O65" s="20" t="s">
+      <c r="N65" s="16" t="s">
         <v>739</v>
       </c>
-      <c r="P65" s="21" t="s">
+      <c r="O65" s="15" t="s">
         <v>740</v>
+      </c>
+      <c r="P65" s="16" t="s">
+        <v>741</v>
       </c>
     </row>
     <row r="66" ht="47" customHeight="1" spans="1:16">
       <c r="A66" t="s">
-        <v>741</v>
-      </c>
-      <c r="B66" s="34" t="s">
         <v>742</v>
       </c>
-      <c r="C66" s="24">
+      <c r="B66" s="28" t="s">
+        <v>743</v>
+      </c>
+      <c r="C66" s="4">
         <v>58730</v>
       </c>
-      <c r="D66" s="23" t="s">
-        <v>743</v>
-      </c>
-      <c r="E66" s="17" t="s">
+      <c r="D66" s="6" t="s">
         <v>744</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>745</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H66" s="19" t="s">
+      <c r="H66" s="14" t="s">
         <v>534</v>
       </c>
-      <c r="I66" s="24" t="s">
-        <v>745</v>
-      </c>
-      <c r="J66" s="23" t="s">
+      <c r="I66" s="4" t="s">
         <v>746</v>
       </c>
-      <c r="K66" s="21" t="s">
+      <c r="J66" s="6" t="s">
         <v>747</v>
       </c>
-      <c r="L66" s="20" t="s">
+      <c r="K66" s="16" t="s">
         <v>748</v>
       </c>
-      <c r="M66" s="21" t="s">
+      <c r="L66" s="15" t="s">
         <v>749</v>
       </c>
-      <c r="N66" s="21" t="s">
+      <c r="M66" s="16" t="s">
         <v>750</v>
       </c>
-      <c r="O66" s="20" t="s">
-        <v>743</v>
-      </c>
-      <c r="P66" s="21" t="s">
+      <c r="N66" s="16" t="s">
         <v>751</v>
+      </c>
+      <c r="O66" s="15" t="s">
+        <v>744</v>
+      </c>
+      <c r="P66" s="16" t="s">
+        <v>752</v>
       </c>
     </row>
     <row r="67" ht="47" customHeight="1" spans="1:16">
       <c r="A67" t="s">
-        <v>752</v>
-      </c>
-      <c r="B67" s="34" t="s">
         <v>753</v>
       </c>
-      <c r="C67" s="15">
+      <c r="B67" s="28" t="s">
+        <v>754</v>
+      </c>
+      <c r="C67" s="8">
         <v>58732</v>
       </c>
-      <c r="D67" s="23" t="s">
-        <v>754</v>
-      </c>
-      <c r="E67" s="17" t="s">
-        <v>744</v>
+      <c r="D67" s="6" t="s">
+        <v>755</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>745</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="H67" s="19" t="s">
+      <c r="H67" s="14" t="s">
         <v>534</v>
       </c>
-      <c r="I67" s="24" t="s">
+      <c r="I67" s="4" t="s">
+        <v>756</v>
+      </c>
+      <c r="J67" s="6" t="s">
+        <v>757</v>
+      </c>
+      <c r="K67" s="16" t="s">
+        <v>758</v>
+      </c>
+      <c r="L67" s="15" t="s">
+        <v>759</v>
+      </c>
+      <c r="M67" s="16" t="s">
+        <v>760</v>
+      </c>
+      <c r="N67" s="16" t="s">
+        <v>761</v>
+      </c>
+      <c r="O67" s="15" t="s">
         <v>755</v>
       </c>
-      <c r="J67" s="23" t="s">
-        <v>756</v>
-      </c>
-      <c r="K67" s="21" t="s">
-        <v>757</v>
-      </c>
-      <c r="L67" s="20" t="s">
-        <v>758</v>
-      </c>
-      <c r="M67" s="21" t="s">
-        <v>759</v>
-      </c>
-      <c r="N67" s="21" t="s">
-        <v>760</v>
-      </c>
-      <c r="O67" s="20" t="s">
-        <v>754</v>
-      </c>
-      <c r="P67" s="21" t="s">
-        <v>761</v>
+      <c r="P67" s="16" t="s">
+        <v>762</v>
       </c>
     </row>
     <row r="68" ht="47" customHeight="1" spans="1:16">
       <c r="A68" t="s">
-        <v>762</v>
-      </c>
-      <c r="B68" s="34" t="s">
         <v>763</v>
       </c>
-      <c r="C68" s="15">
+      <c r="B68" s="28" t="s">
+        <v>764</v>
+      </c>
+      <c r="C68" s="8">
         <v>58734</v>
       </c>
-      <c r="D68" s="23" t="s">
-        <v>764</v>
-      </c>
-      <c r="E68" s="17" t="s">
-        <v>744</v>
+      <c r="D68" s="6" t="s">
+        <v>765</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>745</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H68" s="19" t="s">
+      <c r="H68" s="14" t="s">
         <v>534</v>
       </c>
-      <c r="I68" s="24" t="s">
+      <c r="I68" s="4" t="s">
+        <v>766</v>
+      </c>
+      <c r="J68" s="6" t="s">
+        <v>767</v>
+      </c>
+      <c r="K68" s="16" t="s">
+        <v>768</v>
+      </c>
+      <c r="L68" s="15" t="s">
+        <v>769</v>
+      </c>
+      <c r="M68" s="16" t="s">
+        <v>770</v>
+      </c>
+      <c r="N68" s="16" t="s">
+        <v>771</v>
+      </c>
+      <c r="O68" s="15" t="s">
         <v>765</v>
       </c>
-      <c r="J68" s="23" t="s">
-        <v>766</v>
-      </c>
-      <c r="K68" s="21" t="s">
-        <v>767</v>
-      </c>
-      <c r="L68" s="20" t="s">
-        <v>768</v>
-      </c>
-      <c r="M68" s="21" t="s">
-        <v>769</v>
-      </c>
-      <c r="N68" s="21" t="s">
-        <v>770</v>
-      </c>
-      <c r="O68" s="20" t="s">
-        <v>764</v>
-      </c>
-      <c r="P68" s="21" t="s">
-        <v>771</v>
+      <c r="P68" s="16" t="s">
+        <v>772</v>
       </c>
     </row>
     <row r="69" ht="47" customHeight="1" spans="1:16">
       <c r="A69" t="s">
-        <v>772</v>
-      </c>
-      <c r="B69" s="34" t="s">
         <v>773</v>
       </c>
-      <c r="C69" s="24">
+      <c r="B69" s="28" t="s">
+        <v>774</v>
+      </c>
+      <c r="C69" s="4">
         <v>58731</v>
       </c>
-      <c r="D69" s="23" t="s">
-        <v>774</v>
-      </c>
-      <c r="E69" s="17" t="s">
-        <v>744</v>
+      <c r="D69" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>745</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="H69" s="19" t="s">
+      <c r="H69" s="14" t="s">
         <v>534</v>
       </c>
-      <c r="I69" s="24" t="s">
+      <c r="I69" s="4" t="s">
+        <v>776</v>
+      </c>
+      <c r="J69" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="K69" s="16" t="s">
+        <v>778</v>
+      </c>
+      <c r="L69" s="15" t="s">
+        <v>779</v>
+      </c>
+      <c r="M69" s="16" t="s">
+        <v>780</v>
+      </c>
+      <c r="N69" s="16" t="s">
+        <v>781</v>
+      </c>
+      <c r="O69" s="15" t="s">
         <v>775</v>
       </c>
-      <c r="J69" s="23" t="s">
-        <v>776</v>
-      </c>
-      <c r="K69" s="21" t="s">
-        <v>777</v>
-      </c>
-      <c r="L69" s="20" t="s">
-        <v>778</v>
-      </c>
-      <c r="M69" s="21" t="s">
-        <v>779</v>
-      </c>
-      <c r="N69" s="21" t="s">
-        <v>780</v>
-      </c>
-      <c r="O69" s="20" t="s">
-        <v>774</v>
-      </c>
-      <c r="P69" s="21" t="s">
-        <v>781</v>
+      <c r="P69" s="16" t="s">
+        <v>782</v>
       </c>
     </row>
     <row r="70" ht="47" customHeight="1" spans="1:16">
       <c r="A70" t="s">
-        <v>782</v>
-      </c>
-      <c r="B70" s="34" t="s">
         <v>783</v>
       </c>
-      <c r="C70" s="15">
+      <c r="B70" s="28" t="s">
+        <v>784</v>
+      </c>
+      <c r="C70" s="8">
         <v>58729</v>
       </c>
-      <c r="D70" s="23" t="s">
-        <v>784</v>
-      </c>
-      <c r="E70" s="17" t="s">
-        <v>744</v>
+      <c r="D70" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>745</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="H70" s="19" t="s">
+      <c r="H70" s="14" t="s">
         <v>534</v>
       </c>
-      <c r="I70" s="24" t="s">
+      <c r="I70" s="4" t="s">
+        <v>786</v>
+      </c>
+      <c r="J70" s="6" t="s">
+        <v>787</v>
+      </c>
+      <c r="K70" s="16" t="s">
+        <v>788</v>
+      </c>
+      <c r="L70" s="15" t="s">
+        <v>789</v>
+      </c>
+      <c r="M70" s="16" t="s">
+        <v>790</v>
+      </c>
+      <c r="N70" s="16" t="s">
+        <v>791</v>
+      </c>
+      <c r="O70" s="15" t="s">
         <v>785</v>
       </c>
-      <c r="J70" s="23" t="s">
-        <v>786</v>
-      </c>
-      <c r="K70" s="21" t="s">
-        <v>787</v>
-      </c>
-      <c r="L70" s="20" t="s">
-        <v>788</v>
-      </c>
-      <c r="M70" s="21" t="s">
-        <v>789</v>
-      </c>
-      <c r="N70" s="21" t="s">
-        <v>790</v>
-      </c>
-      <c r="O70" s="20" t="s">
-        <v>784</v>
-      </c>
-      <c r="P70" s="21" t="s">
-        <v>791</v>
+      <c r="P70" s="16" t="s">
+        <v>792</v>
       </c>
     </row>
     <row r="71" ht="66.75" spans="1:16">
       <c r="A71" t="s">
-        <v>792</v>
-      </c>
-      <c r="B71" s="34" t="s">
         <v>793</v>
       </c>
-      <c r="C71" s="15">
+      <c r="B71" s="28" t="s">
+        <v>794</v>
+      </c>
+      <c r="C71" s="8">
         <v>58733</v>
       </c>
-      <c r="D71" s="23" t="s">
-        <v>794</v>
-      </c>
-      <c r="E71" s="17" t="s">
-        <v>744</v>
+      <c r="D71" s="6" t="s">
+        <v>795</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>745</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="H71" s="19" t="s">
+      <c r="H71" s="14" t="s">
         <v>534</v>
       </c>
-      <c r="I71" s="24" t="s">
+      <c r="I71" s="4" t="s">
+        <v>796</v>
+      </c>
+      <c r="J71" s="6" t="s">
+        <v>797</v>
+      </c>
+      <c r="K71" s="16" t="s">
+        <v>798</v>
+      </c>
+      <c r="L71" s="15" t="s">
+        <v>799</v>
+      </c>
+      <c r="M71" s="16" t="s">
+        <v>800</v>
+      </c>
+      <c r="N71" s="16" t="s">
+        <v>801</v>
+      </c>
+      <c r="O71" s="15" t="s">
         <v>795</v>
       </c>
-      <c r="J71" s="23" t="s">
-        <v>796</v>
-      </c>
-      <c r="K71" s="21" t="s">
-        <v>797</v>
-      </c>
-      <c r="L71" s="20" t="s">
-        <v>798</v>
-      </c>
-      <c r="M71" s="21" t="s">
-        <v>799</v>
-      </c>
-      <c r="N71" s="21" t="s">
-        <v>800</v>
-      </c>
-      <c r="O71" s="20" t="s">
-        <v>794</v>
-      </c>
-      <c r="P71" s="21" t="s">
-        <v>801</v>
+      <c r="P71" s="16" t="s">
+        <v>802</v>
       </c>
     </row>
     <row r="72" ht="66.75" spans="1:16">
       <c r="A72" t="s">
-        <v>802</v>
-      </c>
-      <c r="B72" s="34" t="s">
         <v>803</v>
       </c>
-      <c r="C72" s="15">
+      <c r="B72" s="28" t="s">
+        <v>804</v>
+      </c>
+      <c r="C72" s="8">
         <v>58735</v>
       </c>
-      <c r="D72" s="23" t="s">
-        <v>804</v>
-      </c>
-      <c r="E72" s="17" t="s">
-        <v>744</v>
+      <c r="D72" s="6" t="s">
+        <v>805</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>745</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="G72" s="24"/>
-      <c r="H72" s="19" t="s">
+      <c r="G72" s="4"/>
+      <c r="H72" s="14" t="s">
         <v>534</v>
       </c>
-      <c r="I72" s="24" t="s">
+      <c r="I72" s="4" t="s">
+        <v>806</v>
+      </c>
+      <c r="J72" s="6" t="s">
+        <v>807</v>
+      </c>
+      <c r="K72" s="16" t="s">
+        <v>808</v>
+      </c>
+      <c r="L72" s="15" t="s">
+        <v>809</v>
+      </c>
+      <c r="M72" s="16" t="s">
+        <v>810</v>
+      </c>
+      <c r="N72" s="16" t="s">
+        <v>811</v>
+      </c>
+      <c r="O72" s="15" t="s">
         <v>805</v>
       </c>
-      <c r="J72" s="23" t="s">
-        <v>806</v>
-      </c>
-      <c r="K72" s="21" t="s">
-        <v>807</v>
-      </c>
-      <c r="L72" s="20" t="s">
-        <v>808</v>
-      </c>
-      <c r="M72" s="21" t="s">
-        <v>809</v>
-      </c>
-      <c r="N72" s="21" t="s">
-        <v>810</v>
-      </c>
-      <c r="O72" s="20" t="s">
-        <v>804</v>
-      </c>
-      <c r="P72" s="21" t="s">
-        <v>811</v>
+      <c r="P72" s="16" t="s">
+        <v>812</v>
       </c>
     </row>
     <row r="73" ht="50.25" spans="1:16">
       <c r="A73" t="s">
-        <v>812</v>
-      </c>
-      <c r="B73" s="34" t="s">
         <v>813</v>
       </c>
-      <c r="C73" s="15">
+      <c r="B73" s="28" t="s">
+        <v>814</v>
+      </c>
+      <c r="C73" s="8">
         <v>59020</v>
       </c>
-      <c r="D73" s="23" t="s">
-        <v>814</v>
+      <c r="D73" s="6" t="s">
+        <v>815</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>199</v>
@@ -13625,47 +14539,47 @@
       <c r="F73" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G73" s="24"/>
-      <c r="H73" s="19" t="s">
+      <c r="G73" s="4"/>
+      <c r="H73" s="14" t="s">
         <v>534</v>
       </c>
-      <c r="I73" s="24" t="s">
+      <c r="I73" s="4" t="s">
+        <v>816</v>
+      </c>
+      <c r="J73" s="18" t="s">
+        <v>817</v>
+      </c>
+      <c r="K73" s="18" t="s">
+        <v>818</v>
+      </c>
+      <c r="L73" s="19" t="s">
+        <v>819</v>
+      </c>
+      <c r="M73" s="18" t="s">
+        <v>820</v>
+      </c>
+      <c r="N73" s="18" t="s">
+        <v>821</v>
+      </c>
+      <c r="O73" s="19" t="s">
         <v>815</v>
       </c>
-      <c r="J73" s="26" t="s">
-        <v>816</v>
-      </c>
-      <c r="K73" s="26" t="s">
-        <v>817</v>
-      </c>
-      <c r="L73" s="27" t="s">
-        <v>818</v>
-      </c>
-      <c r="M73" s="26" t="s">
-        <v>819</v>
-      </c>
-      <c r="N73" s="26" t="s">
-        <v>820</v>
-      </c>
-      <c r="O73" s="27" t="s">
-        <v>814</v>
-      </c>
-      <c r="P73" s="26" t="s">
-        <v>821</v>
+      <c r="P73" s="18" t="s">
+        <v>822</v>
       </c>
     </row>
     <row r="74" ht="50.25" spans="1:16">
       <c r="A74" t="s">
-        <v>822</v>
-      </c>
-      <c r="B74" s="34" t="s">
         <v>823</v>
       </c>
-      <c r="C74" s="15">
+      <c r="B74" s="28" t="s">
+        <v>824</v>
+      </c>
+      <c r="C74" s="8">
         <v>59021</v>
       </c>
-      <c r="D74" s="23" t="s">
-        <v>824</v>
+      <c r="D74" s="6" t="s">
+        <v>825</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>199</v>
@@ -13673,47 +14587,47 @@
       <c r="F74" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="G74" s="24"/>
-      <c r="H74" s="19" t="s">
+      <c r="G74" s="4"/>
+      <c r="H74" s="14" t="s">
         <v>534</v>
       </c>
-      <c r="I74" s="24" t="s">
-        <v>825</v>
-      </c>
-      <c r="J74" s="26" t="s">
+      <c r="I74" s="4" t="s">
         <v>826</v>
       </c>
-      <c r="K74" s="26" t="s">
+      <c r="J74" s="18" t="s">
         <v>827</v>
       </c>
-      <c r="L74" s="27" t="s">
+      <c r="K74" s="18" t="s">
         <v>828</v>
       </c>
-      <c r="M74" s="26" t="s">
+      <c r="L74" s="19" t="s">
         <v>829</v>
       </c>
-      <c r="N74" s="26" t="s">
+      <c r="M74" s="18" t="s">
         <v>830</v>
       </c>
-      <c r="O74" s="27" t="s">
+      <c r="N74" s="18" t="s">
         <v>831</v>
       </c>
-      <c r="P74" s="26" t="s">
+      <c r="O74" s="19" t="s">
         <v>832</v>
+      </c>
+      <c r="P74" s="18" t="s">
+        <v>833</v>
       </c>
     </row>
     <row r="75" ht="50.25" spans="1:16">
       <c r="A75" t="s">
-        <v>833</v>
-      </c>
-      <c r="B75" s="34" t="s">
         <v>834</v>
       </c>
-      <c r="C75" s="15">
+      <c r="B75" s="28" t="s">
+        <v>835</v>
+      </c>
+      <c r="C75" s="8">
         <v>59024</v>
       </c>
-      <c r="D75" s="23" t="s">
-        <v>835</v>
+      <c r="D75" s="6" t="s">
+        <v>836</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>199</v>
@@ -13721,47 +14635,47 @@
       <c r="F75" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G75" s="24"/>
-      <c r="H75" s="19" t="s">
+      <c r="G75" s="4"/>
+      <c r="H75" s="14" t="s">
         <v>534</v>
       </c>
-      <c r="I75" s="24" t="s">
+      <c r="I75" s="4" t="s">
+        <v>837</v>
+      </c>
+      <c r="J75" s="18" t="s">
+        <v>838</v>
+      </c>
+      <c r="K75" s="18" t="s">
+        <v>839</v>
+      </c>
+      <c r="L75" s="19" t="s">
+        <v>840</v>
+      </c>
+      <c r="M75" s="18" t="s">
+        <v>841</v>
+      </c>
+      <c r="N75" s="18" t="s">
+        <v>842</v>
+      </c>
+      <c r="O75" s="19" t="s">
         <v>836</v>
       </c>
-      <c r="J75" s="26" t="s">
-        <v>837</v>
-      </c>
-      <c r="K75" s="26" t="s">
-        <v>838</v>
-      </c>
-      <c r="L75" s="27" t="s">
-        <v>839</v>
-      </c>
-      <c r="M75" s="26" t="s">
-        <v>840</v>
-      </c>
-      <c r="N75" s="26" t="s">
-        <v>841</v>
-      </c>
-      <c r="O75" s="27" t="s">
-        <v>835</v>
-      </c>
-      <c r="P75" s="26" t="s">
-        <v>842</v>
+      <c r="P75" s="18" t="s">
+        <v>843</v>
       </c>
     </row>
     <row r="76" ht="66.75" spans="1:16">
       <c r="A76" t="s">
-        <v>843</v>
-      </c>
-      <c r="B76" s="34" t="s">
         <v>844</v>
       </c>
-      <c r="C76" s="15">
+      <c r="B76" s="28" t="s">
+        <v>845</v>
+      </c>
+      <c r="C76" s="8">
         <v>59019</v>
       </c>
-      <c r="D76" s="23" t="s">
-        <v>845</v>
+      <c r="D76" s="6" t="s">
+        <v>846</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>199</v>
@@ -13769,47 +14683,47 @@
       <c r="F76" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="G76" s="24"/>
-      <c r="H76" s="19" t="s">
+      <c r="G76" s="4"/>
+      <c r="H76" s="14" t="s">
         <v>534</v>
       </c>
-      <c r="I76" s="24" t="s">
+      <c r="I76" s="4" t="s">
+        <v>847</v>
+      </c>
+      <c r="J76" s="18" t="s">
+        <v>848</v>
+      </c>
+      <c r="K76" s="18" t="s">
+        <v>849</v>
+      </c>
+      <c r="L76" s="19" t="s">
+        <v>850</v>
+      </c>
+      <c r="M76" s="18" t="s">
+        <v>851</v>
+      </c>
+      <c r="N76" s="18" t="s">
+        <v>852</v>
+      </c>
+      <c r="O76" s="19" t="s">
         <v>846</v>
       </c>
-      <c r="J76" s="26" t="s">
-        <v>847</v>
-      </c>
-      <c r="K76" s="26" t="s">
-        <v>848</v>
-      </c>
-      <c r="L76" s="27" t="s">
-        <v>849</v>
-      </c>
-      <c r="M76" s="26" t="s">
-        <v>850</v>
-      </c>
-      <c r="N76" s="26" t="s">
-        <v>851</v>
-      </c>
-      <c r="O76" s="27" t="s">
-        <v>845</v>
-      </c>
-      <c r="P76" s="26" t="s">
-        <v>852</v>
+      <c r="P76" s="18" t="s">
+        <v>853</v>
       </c>
     </row>
     <row r="77" ht="50.25" spans="1:16">
       <c r="A77" t="s">
-        <v>853</v>
-      </c>
-      <c r="B77" s="34" t="s">
         <v>854</v>
       </c>
-      <c r="C77" s="15">
+      <c r="B77" s="28" t="s">
+        <v>855</v>
+      </c>
+      <c r="C77" s="8">
         <v>59023</v>
       </c>
-      <c r="D77" s="23" t="s">
-        <v>855</v>
+      <c r="D77" s="6" t="s">
+        <v>856</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>199</v>
@@ -13817,44 +14731,44 @@
       <c r="F77" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H77" s="19" t="s">
+      <c r="H77" s="14" t="s">
         <v>534</v>
       </c>
-      <c r="I77" s="24" t="s">
-        <v>856</v>
-      </c>
-      <c r="J77" s="26" t="s">
+      <c r="I77" s="4" t="s">
         <v>857</v>
       </c>
-      <c r="K77" s="26" t="s">
+      <c r="J77" s="18" t="s">
         <v>858</v>
       </c>
-      <c r="L77" s="27" t="s">
+      <c r="K77" s="18" t="s">
         <v>859</v>
       </c>
-      <c r="M77" s="26" t="s">
+      <c r="L77" s="19" t="s">
         <v>860</v>
       </c>
-      <c r="N77" s="26" t="s">
+      <c r="M77" s="18" t="s">
         <v>861</v>
       </c>
-      <c r="O77" s="27" t="s">
+      <c r="N77" s="18" t="s">
         <v>862</v>
       </c>
-      <c r="P77" s="26" t="s">
+      <c r="O77" s="19" t="s">
         <v>863</v>
+      </c>
+      <c r="P77" s="18" t="s">
+        <v>864</v>
       </c>
     </row>
     <row r="78" ht="50.25" spans="1:16">
       <c r="A78" t="s">
-        <v>864</v>
-      </c>
-      <c r="B78" s="25"/>
-      <c r="C78" s="15">
+        <v>865</v>
+      </c>
+      <c r="B78" s="5"/>
+      <c r="C78" s="8">
         <v>59031</v>
       </c>
-      <c r="D78" s="23" t="s">
-        <v>865</v>
+      <c r="D78" s="6" t="s">
+        <v>866</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>199</v>
@@ -13862,44 +14776,44 @@
       <c r="F78" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="H78" s="19" t="s">
-        <v>534</v>
-      </c>
-      <c r="I78" s="24" t="s">
-        <v>866</v>
-      </c>
-      <c r="J78" s="26" t="s">
+      <c r="H78" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I78" s="4" t="s">
         <v>867</v>
       </c>
-      <c r="K78" s="26" t="s">
+      <c r="J78" s="18" t="s">
         <v>868</v>
       </c>
-      <c r="L78" s="27" t="s">
+      <c r="K78" s="18" t="s">
         <v>869</v>
       </c>
-      <c r="M78" s="26" t="s">
+      <c r="L78" s="19" t="s">
         <v>870</v>
       </c>
-      <c r="N78" s="26" t="s">
+      <c r="M78" s="18" t="s">
         <v>871</v>
       </c>
-      <c r="O78" s="27" t="s">
+      <c r="N78" s="18" t="s">
         <v>872</v>
       </c>
-      <c r="P78" s="26" t="s">
+      <c r="O78" s="19" t="s">
         <v>873</v>
+      </c>
+      <c r="P78" s="18" t="s">
+        <v>874</v>
       </c>
     </row>
     <row r="79" ht="50.25" spans="1:16">
       <c r="A79" t="s">
-        <v>874</v>
-      </c>
-      <c r="B79" s="25"/>
-      <c r="C79" s="15">
+        <v>875</v>
+      </c>
+      <c r="B79" s="5"/>
+      <c r="C79" s="8">
         <v>59022</v>
       </c>
-      <c r="D79" s="23" t="s">
-        <v>875</v>
+      <c r="D79" s="6" t="s">
+        <v>876</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>199</v>
@@ -13907,44 +14821,44 @@
       <c r="F79" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="H79" s="19" t="s">
-        <v>534</v>
-      </c>
-      <c r="I79" s="24" t="s">
-        <v>876</v>
-      </c>
-      <c r="J79" s="26" t="s">
+      <c r="H79" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I79" s="4" t="s">
         <v>877</v>
       </c>
-      <c r="K79" s="26" t="s">
+      <c r="J79" s="18" t="s">
         <v>878</v>
       </c>
-      <c r="L79" s="27" t="s">
+      <c r="K79" s="18" t="s">
         <v>879</v>
       </c>
-      <c r="M79" s="26" t="s">
+      <c r="L79" s="19" t="s">
         <v>880</v>
       </c>
-      <c r="N79" s="26" t="s">
+      <c r="M79" s="18" t="s">
         <v>881</v>
       </c>
-      <c r="O79" s="27" t="s">
+      <c r="N79" s="18" t="s">
         <v>882</v>
       </c>
-      <c r="P79" s="26" t="s">
+      <c r="O79" s="19" t="s">
         <v>883</v>
+      </c>
+      <c r="P79" s="18" t="s">
+        <v>884</v>
       </c>
     </row>
     <row r="80" ht="50.25" spans="1:16">
       <c r="A80" t="s">
-        <v>884</v>
-      </c>
-      <c r="B80" s="25"/>
-      <c r="C80" s="15">
+        <v>885</v>
+      </c>
+      <c r="B80" s="5"/>
+      <c r="C80" s="8">
         <v>59035</v>
       </c>
-      <c r="D80" s="23" t="s">
-        <v>885</v>
+      <c r="D80" s="6" t="s">
+        <v>886</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>199</v>
@@ -13952,44 +14866,44 @@
       <c r="F80" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H80" s="19" t="s">
-        <v>534</v>
-      </c>
-      <c r="I80" s="24" t="s">
-        <v>886</v>
-      </c>
-      <c r="J80" s="26" t="s">
+      <c r="H80" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I80" s="4" t="s">
         <v>887</v>
       </c>
-      <c r="K80" s="26" t="s">
+      <c r="J80" s="18" t="s">
         <v>888</v>
       </c>
-      <c r="L80" s="27" t="s">
+      <c r="K80" s="18" t="s">
         <v>889</v>
       </c>
-      <c r="M80" s="26" t="s">
+      <c r="L80" s="19" t="s">
         <v>890</v>
       </c>
-      <c r="N80" s="26" t="s">
+      <c r="M80" s="18" t="s">
         <v>891</v>
       </c>
-      <c r="O80" s="27" t="s">
+      <c r="N80" s="18" t="s">
         <v>892</v>
       </c>
-      <c r="P80" s="26" t="s">
+      <c r="O80" s="19" t="s">
         <v>893</v>
+      </c>
+      <c r="P80" s="18" t="s">
+        <v>894</v>
       </c>
     </row>
     <row r="81" ht="50.25" spans="1:16">
       <c r="A81" t="s">
-        <v>894</v>
-      </c>
-      <c r="B81" s="25"/>
-      <c r="C81" s="15">
+        <v>895</v>
+      </c>
+      <c r="B81" s="5"/>
+      <c r="C81" s="8">
         <v>59026</v>
       </c>
-      <c r="D81" s="23" t="s">
-        <v>895</v>
+      <c r="D81" s="6" t="s">
+        <v>896</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>199</v>
@@ -13997,45 +14911,45 @@
       <c r="F81" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="G81" s="24"/>
-      <c r="H81" s="19" t="s">
-        <v>534</v>
-      </c>
-      <c r="I81" s="24" t="s">
-        <v>896</v>
-      </c>
-      <c r="J81" s="26" t="s">
+      <c r="G81" s="4"/>
+      <c r="H81" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I81" s="4" t="s">
         <v>897</v>
       </c>
-      <c r="K81" s="26" t="s">
+      <c r="J81" s="18" t="s">
         <v>898</v>
       </c>
-      <c r="L81" s="27" t="s">
+      <c r="K81" s="18" t="s">
         <v>899</v>
       </c>
-      <c r="M81" s="26" t="s">
+      <c r="L81" s="19" t="s">
         <v>900</v>
       </c>
-      <c r="N81" s="26" t="s">
+      <c r="M81" s="18" t="s">
         <v>901</v>
       </c>
-      <c r="O81" s="27" t="s">
+      <c r="N81" s="18" t="s">
         <v>902</v>
       </c>
-      <c r="P81" s="26" t="s">
+      <c r="O81" s="19" t="s">
         <v>903</v>
+      </c>
+      <c r="P81" s="18" t="s">
+        <v>904</v>
       </c>
     </row>
     <row r="82" ht="50.25" spans="1:16">
       <c r="A82" t="s">
-        <v>904</v>
-      </c>
-      <c r="B82" s="25"/>
-      <c r="C82" s="15">
+        <v>905</v>
+      </c>
+      <c r="B82" s="5"/>
+      <c r="C82" s="8">
         <v>59028</v>
       </c>
-      <c r="D82" s="23" t="s">
-        <v>905</v>
+      <c r="D82" s="6" t="s">
+        <v>906</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>199</v>
@@ -14043,494 +14957,1556 @@
       <c r="F82" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="G82" s="24"/>
-      <c r="H82" s="19" t="s">
-        <v>534</v>
-      </c>
-      <c r="I82" s="24" t="s">
-        <v>906</v>
-      </c>
-      <c r="J82" s="26" t="s">
+      <c r="G82" s="4"/>
+      <c r="H82" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I82" s="4" t="s">
         <v>907</v>
       </c>
-      <c r="K82" s="26" t="s">
+      <c r="J82" s="18" t="s">
         <v>908</v>
       </c>
-      <c r="L82" s="27" t="s">
+      <c r="K82" s="18" t="s">
         <v>909</v>
       </c>
-      <c r="M82" s="26" t="s">
+      <c r="L82" s="19" t="s">
         <v>910</v>
       </c>
-      <c r="N82" s="26" t="s">
+      <c r="M82" s="18" t="s">
         <v>911</v>
       </c>
-      <c r="O82" s="27" t="s">
+      <c r="N82" s="18" t="s">
         <v>912</v>
       </c>
-      <c r="P82" s="26" t="s">
+      <c r="O82" s="19" t="s">
         <v>913</v>
+      </c>
+      <c r="P82" s="18" t="s">
+        <v>914</v>
       </c>
     </row>
     <row r="83" ht="50.25" spans="1:16">
       <c r="A83" t="s">
-        <v>914</v>
-      </c>
-      <c r="B83" s="25"/>
-      <c r="C83" s="15">
+        <v>915</v>
+      </c>
+      <c r="B83" s="28" t="s">
+        <v>916</v>
+      </c>
+      <c r="C83" s="8">
         <v>59121</v>
       </c>
-      <c r="D83" s="23" t="s">
-        <v>915</v>
-      </c>
-      <c r="E83" s="28" t="s">
+      <c r="D83" s="6" t="s">
+        <v>917</v>
+      </c>
+      <c r="E83" s="20" t="s">
         <v>84</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G83" s="24"/>
-      <c r="H83" s="19" t="s">
-        <v>534</v>
-      </c>
-      <c r="I83" s="24" t="s">
-        <v>916</v>
-      </c>
-      <c r="J83" s="26" t="s">
-        <v>917</v>
-      </c>
-      <c r="K83" s="26" t="s">
+      <c r="G83" s="4"/>
+      <c r="H83" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I83" s="4" t="s">
         <v>918</v>
       </c>
-      <c r="L83" s="27" t="s">
+      <c r="J83" s="18" t="s">
         <v>919</v>
       </c>
-      <c r="M83" s="26" t="s">
+      <c r="K83" s="18" t="s">
         <v>920</v>
       </c>
-      <c r="N83" s="26" t="s">
+      <c r="L83" s="19" t="s">
         <v>921</v>
       </c>
-      <c r="O83" s="27" t="s">
+      <c r="M83" s="18" t="s">
         <v>922</v>
       </c>
-      <c r="P83" s="26" t="s">
+      <c r="N83" s="18" t="s">
         <v>923</v>
+      </c>
+      <c r="O83" s="19" t="s">
+        <v>924</v>
+      </c>
+      <c r="P83" s="18" t="s">
+        <v>925</v>
       </c>
     </row>
     <row r="84" ht="50.25" spans="1:16">
       <c r="A84" t="s">
-        <v>924</v>
-      </c>
-      <c r="B84" s="25"/>
-      <c r="C84" s="15">
+        <v>926</v>
+      </c>
+      <c r="B84" s="28" t="s">
+        <v>927</v>
+      </c>
+      <c r="C84" s="8">
         <v>59126</v>
       </c>
-      <c r="D84" s="23" t="s">
-        <v>925</v>
-      </c>
-      <c r="E84" s="28" t="s">
+      <c r="D84" s="6" t="s">
+        <v>928</v>
+      </c>
+      <c r="E84" s="20" t="s">
         <v>84</v>
       </c>
       <c r="F84" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="G84" s="24"/>
-      <c r="H84" s="19" t="s">
-        <v>534</v>
-      </c>
-      <c r="I84" s="24" t="s">
-        <v>926</v>
-      </c>
-      <c r="J84" s="26" t="s">
-        <v>927</v>
-      </c>
-      <c r="K84" s="26" t="s">
-        <v>928</v>
-      </c>
-      <c r="L84" s="27" t="s">
+      <c r="G84" s="4"/>
+      <c r="H84" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I84" s="4" t="s">
         <v>929</v>
       </c>
-      <c r="M84" s="26" t="s">
+      <c r="J84" s="18" t="s">
         <v>930</v>
       </c>
-      <c r="N84" s="26" t="s">
+      <c r="K84" s="18" t="s">
         <v>931</v>
       </c>
-      <c r="O84" s="27" t="s">
+      <c r="L84" s="19" t="s">
         <v>932</v>
       </c>
-      <c r="P84" s="26" t="s">
+      <c r="M84" s="18" t="s">
         <v>933</v>
+      </c>
+      <c r="N84" s="18" t="s">
+        <v>934</v>
+      </c>
+      <c r="O84" s="19" t="s">
+        <v>935</v>
+      </c>
+      <c r="P84" s="18" t="s">
+        <v>936</v>
       </c>
     </row>
     <row r="85" ht="50.25" spans="1:16">
       <c r="A85" t="s">
-        <v>934</v>
-      </c>
-      <c r="B85" s="25"/>
-      <c r="C85" s="24">
+        <v>937</v>
+      </c>
+      <c r="B85" s="28" t="s">
+        <v>938</v>
+      </c>
+      <c r="C85" s="4">
         <v>59122</v>
       </c>
-      <c r="D85" s="23" t="s">
-        <v>935</v>
-      </c>
-      <c r="E85" s="28" t="s">
+      <c r="D85" s="6" t="s">
+        <v>939</v>
+      </c>
+      <c r="E85" s="20" t="s">
         <v>84</v>
       </c>
       <c r="F85" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="G85" s="24"/>
-      <c r="H85" s="19" t="s">
-        <v>534</v>
-      </c>
-      <c r="I85" s="24" t="s">
-        <v>936</v>
-      </c>
-      <c r="J85" s="26" t="s">
-        <v>937</v>
-      </c>
-      <c r="K85" s="26" t="s">
-        <v>938</v>
-      </c>
-      <c r="L85" s="27" t="s">
+      <c r="G85" s="4"/>
+      <c r="H85" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I85" s="4" t="s">
+        <v>940</v>
+      </c>
+      <c r="J85" s="18" t="s">
+        <v>941</v>
+      </c>
+      <c r="K85" s="18" t="s">
+        <v>942</v>
+      </c>
+      <c r="L85" s="19" t="s">
+        <v>943</v>
+      </c>
+      <c r="M85" s="18" t="s">
+        <v>944</v>
+      </c>
+      <c r="N85" s="18" t="s">
+        <v>945</v>
+      </c>
+      <c r="O85" s="19" t="s">
         <v>939</v>
       </c>
-      <c r="M85" s="26" t="s">
-        <v>940</v>
-      </c>
-      <c r="N85" s="26" t="s">
-        <v>941</v>
-      </c>
-      <c r="O85" s="27" t="s">
-        <v>935</v>
-      </c>
-      <c r="P85" s="26" t="s">
-        <v>942</v>
+      <c r="P85" s="18" t="s">
+        <v>946</v>
       </c>
     </row>
     <row r="86" ht="50.25" spans="1:16">
       <c r="A86" t="s">
-        <v>943</v>
-      </c>
-      <c r="B86" s="25"/>
-      <c r="C86" s="24">
+        <v>947</v>
+      </c>
+      <c r="B86" s="28" t="s">
+        <v>948</v>
+      </c>
+      <c r="C86" s="4">
         <v>59123</v>
       </c>
-      <c r="D86" s="23" t="s">
-        <v>944</v>
-      </c>
-      <c r="E86" s="28" t="s">
+      <c r="D86" s="6" t="s">
+        <v>949</v>
+      </c>
+      <c r="E86" s="20" t="s">
         <v>84</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="G86" s="24"/>
-      <c r="H86" s="19" t="s">
-        <v>534</v>
-      </c>
-      <c r="I86" s="24" t="s">
-        <v>945</v>
-      </c>
-      <c r="J86" s="26" t="s">
-        <v>946</v>
-      </c>
-      <c r="K86" s="26" t="s">
-        <v>947</v>
-      </c>
-      <c r="L86" s="27" t="s">
-        <v>948</v>
-      </c>
-      <c r="M86" s="26" t="s">
+      <c r="G86" s="4"/>
+      <c r="H86" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I86" s="4" t="s">
+        <v>950</v>
+      </c>
+      <c r="J86" s="18" t="s">
+        <v>951</v>
+      </c>
+      <c r="K86" s="18" t="s">
+        <v>952</v>
+      </c>
+      <c r="L86" s="19" t="s">
+        <v>953</v>
+      </c>
+      <c r="M86" s="18" t="s">
+        <v>954</v>
+      </c>
+      <c r="N86" s="18" t="s">
+        <v>955</v>
+      </c>
+      <c r="O86" s="19" t="s">
         <v>949</v>
       </c>
-      <c r="N86" s="26" t="s">
-        <v>950</v>
-      </c>
-      <c r="O86" s="27" t="s">
-        <v>944</v>
-      </c>
-      <c r="P86" s="26" t="s">
-        <v>951</v>
+      <c r="P86" s="18" t="s">
+        <v>956</v>
       </c>
     </row>
     <row r="87" ht="50.25" spans="1:16">
       <c r="A87" t="s">
-        <v>952</v>
-      </c>
-      <c r="B87" s="25"/>
-      <c r="C87" s="15">
+        <v>957</v>
+      </c>
+      <c r="B87" s="28" t="s">
+        <v>958</v>
+      </c>
+      <c r="C87" s="8">
         <v>59125</v>
       </c>
-      <c r="D87" s="23" t="s">
-        <v>953</v>
-      </c>
-      <c r="E87" s="28" t="s">
+      <c r="D87" s="6" t="s">
+        <v>959</v>
+      </c>
+      <c r="E87" s="20" t="s">
         <v>84</v>
       </c>
       <c r="F87" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G87" s="24"/>
-      <c r="H87" s="19" t="s">
-        <v>534</v>
-      </c>
-      <c r="I87" s="24" t="s">
-        <v>954</v>
-      </c>
-      <c r="J87" s="26" t="s">
-        <v>955</v>
-      </c>
-      <c r="K87" s="26" t="s">
-        <v>956</v>
-      </c>
-      <c r="L87" s="27" t="s">
-        <v>957</v>
-      </c>
-      <c r="M87" s="26" t="s">
-        <v>958</v>
-      </c>
-      <c r="N87" s="26" t="s">
+      <c r="G87" s="4"/>
+      <c r="H87" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I87" s="4" t="s">
+        <v>960</v>
+      </c>
+      <c r="J87" s="18" t="s">
+        <v>961</v>
+      </c>
+      <c r="K87" s="18" t="s">
+        <v>962</v>
+      </c>
+      <c r="L87" s="19" t="s">
+        <v>963</v>
+      </c>
+      <c r="M87" s="18" t="s">
+        <v>964</v>
+      </c>
+      <c r="N87" s="18" t="s">
+        <v>965</v>
+      </c>
+      <c r="O87" s="19" t="s">
         <v>959</v>
       </c>
-      <c r="O87" s="27" t="s">
-        <v>953</v>
-      </c>
-      <c r="P87" s="26" t="s">
-        <v>960</v>
+      <c r="P87" s="18" t="s">
+        <v>966</v>
       </c>
     </row>
     <row r="88" ht="50.25" spans="1:16">
       <c r="A88" t="s">
-        <v>961</v>
-      </c>
-      <c r="B88" s="25"/>
-      <c r="C88" s="15">
+        <v>967</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>968</v>
+      </c>
+      <c r="C88" s="8">
         <v>59127</v>
       </c>
-      <c r="D88" s="23" t="s">
-        <v>962</v>
-      </c>
-      <c r="E88" s="28" t="s">
+      <c r="D88" s="6" t="s">
+        <v>969</v>
+      </c>
+      <c r="E88" s="20" t="s">
         <v>84</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="G88" s="24"/>
-      <c r="H88" s="19" t="s">
-        <v>534</v>
-      </c>
-      <c r="I88" s="24" t="s">
-        <v>963</v>
-      </c>
-      <c r="J88" s="26" t="s">
-        <v>964</v>
-      </c>
-      <c r="K88" s="26" t="s">
-        <v>965</v>
-      </c>
-      <c r="L88" s="27" t="s">
-        <v>966</v>
-      </c>
-      <c r="M88" s="26" t="s">
-        <v>967</v>
-      </c>
-      <c r="N88" s="26" t="s">
-        <v>968</v>
-      </c>
-      <c r="O88" s="27" t="s">
-        <v>962</v>
-      </c>
-      <c r="P88" s="26" t="s">
+      <c r="G88" s="4"/>
+      <c r="H88" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I88" s="4" t="s">
+        <v>970</v>
+      </c>
+      <c r="J88" s="18" t="s">
+        <v>971</v>
+      </c>
+      <c r="K88" s="18" t="s">
+        <v>972</v>
+      </c>
+      <c r="L88" s="19" t="s">
+        <v>973</v>
+      </c>
+      <c r="M88" s="18" t="s">
+        <v>974</v>
+      </c>
+      <c r="N88" s="18" t="s">
+        <v>975</v>
+      </c>
+      <c r="O88" s="19" t="s">
         <v>969</v>
+      </c>
+      <c r="P88" s="18" t="s">
+        <v>976</v>
       </c>
     </row>
     <row r="89" ht="50.25" spans="1:16">
       <c r="A89" t="s">
-        <v>970</v>
-      </c>
-      <c r="B89" s="25"/>
-      <c r="C89" s="15">
+        <v>977</v>
+      </c>
+      <c r="B89" s="5"/>
+      <c r="C89" s="8">
         <v>59129</v>
       </c>
-      <c r="D89" s="23" t="s">
-        <v>971</v>
-      </c>
-      <c r="E89" s="28" t="s">
+      <c r="D89" s="6" t="s">
+        <v>978</v>
+      </c>
+      <c r="E89" s="20" t="s">
         <v>84</v>
       </c>
       <c r="F89" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="G89" s="24"/>
-      <c r="H89" s="19" t="s">
-        <v>534</v>
-      </c>
-      <c r="I89" s="24" t="s">
-        <v>972</v>
-      </c>
-      <c r="J89" s="26" t="s">
-        <v>973</v>
-      </c>
-      <c r="K89" s="26" t="s">
-        <v>974</v>
-      </c>
-      <c r="L89" s="27" t="s">
-        <v>975</v>
-      </c>
-      <c r="M89" s="26" t="s">
-        <v>976</v>
-      </c>
-      <c r="N89" s="26" t="s">
-        <v>977</v>
-      </c>
-      <c r="O89" s="27" t="s">
-        <v>971</v>
-      </c>
-      <c r="P89" s="26" t="s">
+      <c r="G89" s="4"/>
+      <c r="H89" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I89" s="4" t="s">
+        <v>979</v>
+      </c>
+      <c r="J89" s="18" t="s">
+        <v>980</v>
+      </c>
+      <c r="K89" s="18" t="s">
+        <v>981</v>
+      </c>
+      <c r="L89" s="19" t="s">
+        <v>982</v>
+      </c>
+      <c r="M89" s="18" t="s">
+        <v>983</v>
+      </c>
+      <c r="N89" s="18" t="s">
+        <v>984</v>
+      </c>
+      <c r="O89" s="19" t="s">
         <v>978</v>
+      </c>
+      <c r="P89" s="18" t="s">
+        <v>985</v>
       </c>
     </row>
     <row r="90" ht="50.25" spans="1:16">
       <c r="A90" t="s">
-        <v>979</v>
-      </c>
-      <c r="B90" s="22"/>
-      <c r="C90" s="15">
+        <v>986</v>
+      </c>
+      <c r="B90" s="5"/>
+      <c r="C90" s="8">
         <v>59131</v>
       </c>
-      <c r="D90" s="23" t="s">
-        <v>980</v>
-      </c>
-      <c r="E90" s="28" t="s">
+      <c r="D90" s="6" t="s">
+        <v>987</v>
+      </c>
+      <c r="E90" s="20" t="s">
         <v>84</v>
       </c>
       <c r="F90" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G90" s="24"/>
-      <c r="H90" s="19" t="s">
-        <v>534</v>
-      </c>
-      <c r="I90" s="24" t="s">
-        <v>981</v>
-      </c>
-      <c r="J90" s="26" t="s">
-        <v>982</v>
-      </c>
-      <c r="K90" s="26" t="s">
-        <v>983</v>
-      </c>
-      <c r="L90" s="27" t="s">
-        <v>984</v>
-      </c>
-      <c r="M90" s="26" t="s">
-        <v>985</v>
-      </c>
-      <c r="N90" s="26" t="s">
-        <v>986</v>
-      </c>
-      <c r="O90" s="27" t="s">
-        <v>987</v>
-      </c>
-      <c r="P90" s="26" t="s">
+      <c r="G90" s="4"/>
+      <c r="H90" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I90" s="4" t="s">
         <v>988</v>
+      </c>
+      <c r="J90" s="18" t="s">
+        <v>989</v>
+      </c>
+      <c r="K90" s="18" t="s">
+        <v>990</v>
+      </c>
+      <c r="L90" s="19" t="s">
+        <v>991</v>
+      </c>
+      <c r="M90" s="18" t="s">
+        <v>992</v>
+      </c>
+      <c r="N90" s="18" t="s">
+        <v>993</v>
+      </c>
+      <c r="O90" s="19" t="s">
+        <v>994</v>
+      </c>
+      <c r="P90" s="18" t="s">
+        <v>995</v>
       </c>
     </row>
     <row r="91" ht="50.25" spans="1:16">
       <c r="A91" t="s">
-        <v>989</v>
-      </c>
-      <c r="B91" s="22"/>
-      <c r="C91" s="15">
+        <v>996</v>
+      </c>
+      <c r="B91" s="5"/>
+      <c r="C91" s="8">
         <v>59124</v>
       </c>
-      <c r="D91" s="23" t="s">
-        <v>990</v>
-      </c>
-      <c r="E91" s="28" t="s">
+      <c r="D91" s="6" t="s">
+        <v>997</v>
+      </c>
+      <c r="E91" s="20" t="s">
         <v>84</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="G91" s="24"/>
-      <c r="H91" s="19" t="s">
-        <v>534</v>
-      </c>
-      <c r="I91" s="24" t="s">
-        <v>991</v>
-      </c>
-      <c r="J91" s="26" t="s">
-        <v>992</v>
-      </c>
-      <c r="K91" s="26" t="s">
-        <v>993</v>
-      </c>
-      <c r="L91" s="27" t="s">
-        <v>994</v>
-      </c>
-      <c r="M91" s="26" t="s">
-        <v>995</v>
-      </c>
-      <c r="N91" s="26" t="s">
-        <v>996</v>
-      </c>
-      <c r="O91" s="27" t="s">
-        <v>990</v>
-      </c>
-      <c r="P91" s="26" t="s">
+      <c r="G91" s="4"/>
+      <c r="H91" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I91" s="4" t="s">
+        <v>998</v>
+      </c>
+      <c r="J91" s="18" t="s">
+        <v>999</v>
+      </c>
+      <c r="K91" s="18" t="s">
+        <v>1000</v>
+      </c>
+      <c r="L91" s="19" t="s">
+        <v>1001</v>
+      </c>
+      <c r="M91" s="18" t="s">
+        <v>1002</v>
+      </c>
+      <c r="N91" s="18" t="s">
+        <v>1003</v>
+      </c>
+      <c r="O91" s="19" t="s">
         <v>997</v>
+      </c>
+      <c r="P91" s="18" t="s">
+        <v>1004</v>
       </c>
     </row>
     <row r="92" ht="50.25" spans="1:16">
       <c r="A92" t="s">
-        <v>998</v>
-      </c>
-      <c r="B92" s="22"/>
-      <c r="C92" s="15">
+        <v>1005</v>
+      </c>
+      <c r="B92" s="5"/>
+      <c r="C92" s="8">
         <v>59128</v>
       </c>
-      <c r="D92" s="23" t="s">
-        <v>999</v>
-      </c>
-      <c r="E92" s="28" t="s">
+      <c r="D92" s="6" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E92" s="20" t="s">
         <v>84</v>
       </c>
       <c r="F92" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="G92" s="24"/>
-      <c r="H92" s="19" t="s">
-        <v>534</v>
-      </c>
-      <c r="I92" s="24" t="s">
-        <v>1000</v>
-      </c>
-      <c r="J92" s="26" t="s">
-        <v>1001</v>
-      </c>
-      <c r="K92" s="26" t="s">
-        <v>1002</v>
-      </c>
-      <c r="L92" s="27" t="s">
-        <v>1003</v>
-      </c>
-      <c r="M92" s="26" t="s">
-        <v>1004</v>
-      </c>
-      <c r="N92" s="26" t="s">
-        <v>1005</v>
-      </c>
-      <c r="O92" s="27" t="s">
-        <v>999</v>
-      </c>
-      <c r="P92" s="26" t="s">
+      <c r="G92" s="4"/>
+      <c r="H92" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I92" s="4" t="s">
+        <v>1007</v>
+      </c>
+      <c r="J92" s="18" t="s">
+        <v>1008</v>
+      </c>
+      <c r="K92" s="18" t="s">
+        <v>1009</v>
+      </c>
+      <c r="L92" s="19" t="s">
+        <v>1010</v>
+      </c>
+      <c r="M92" s="18" t="s">
+        <v>1011</v>
+      </c>
+      <c r="N92" s="18" t="s">
+        <v>1012</v>
+      </c>
+      <c r="O92" s="19" t="s">
         <v>1006</v>
       </c>
+      <c r="P92" s="18" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="93" ht="43.5" spans="1:16">
+      <c r="A93" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C93" s="21">
+        <v>61813</v>
+      </c>
+      <c r="D93" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H93" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I93" t="s">
+        <v>1017</v>
+      </c>
+      <c r="J93" t="s">
+        <v>1018</v>
+      </c>
+      <c r="K93" s="22" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L93" s="22" t="s">
+        <v>1020</v>
+      </c>
+      <c r="M93" s="22" t="s">
+        <v>1021</v>
+      </c>
+      <c r="N93" s="22" t="s">
+        <v>1022</v>
+      </c>
+      <c r="O93" s="22" t="s">
+        <v>1023</v>
+      </c>
+      <c r="P93" s="22" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="94" ht="43.5" spans="1:16">
+      <c r="A94" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C94" s="21">
+        <v>61812</v>
+      </c>
+      <c r="D94" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H94" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I94" t="s">
+        <v>1028</v>
+      </c>
+      <c r="J94" t="s">
+        <v>1029</v>
+      </c>
+      <c r="K94" s="22" t="s">
+        <v>1030</v>
+      </c>
+      <c r="L94" s="22" t="s">
+        <v>1031</v>
+      </c>
+      <c r="M94" s="22" t="s">
+        <v>1032</v>
+      </c>
+      <c r="N94" s="22" t="s">
+        <v>1033</v>
+      </c>
+      <c r="O94" s="22" t="s">
+        <v>1034</v>
+      </c>
+      <c r="P94" s="22" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="95" ht="43.5" spans="1:16">
+      <c r="A95" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C95" s="21">
+        <v>61818</v>
+      </c>
+      <c r="D95" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H95" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I95" t="s">
+        <v>1039</v>
+      </c>
+      <c r="J95" t="s">
+        <v>1040</v>
+      </c>
+      <c r="K95" s="22" t="s">
+        <v>1041</v>
+      </c>
+      <c r="L95" s="22" t="s">
+        <v>1042</v>
+      </c>
+      <c r="M95" s="22" t="s">
+        <v>1043</v>
+      </c>
+      <c r="N95" s="22" t="s">
+        <v>1044</v>
+      </c>
+      <c r="O95" s="22" t="s">
+        <v>1045</v>
+      </c>
+      <c r="P95" s="22" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="96" ht="43.5" spans="1:16">
+      <c r="A96" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C96" s="21">
+        <v>61815</v>
+      </c>
+      <c r="D96" t="s">
+        <v>1049</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H96" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I96" t="s">
+        <v>1050</v>
+      </c>
+      <c r="J96" t="s">
+        <v>1051</v>
+      </c>
+      <c r="K96" s="22" t="s">
+        <v>1052</v>
+      </c>
+      <c r="L96" s="22" t="s">
+        <v>1053</v>
+      </c>
+      <c r="M96" s="22" t="s">
+        <v>1054</v>
+      </c>
+      <c r="N96" s="22" t="s">
+        <v>1055</v>
+      </c>
+      <c r="O96" s="22" t="s">
+        <v>1056</v>
+      </c>
+      <c r="P96" s="22" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="97" ht="43.5" spans="1:16">
+      <c r="A97" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C97" s="21">
+        <v>61814</v>
+      </c>
+      <c r="D97" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H97" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I97" t="s">
+        <v>1061</v>
+      </c>
+      <c r="J97" t="s">
+        <v>1062</v>
+      </c>
+      <c r="K97" s="22" t="s">
+        <v>1063</v>
+      </c>
+      <c r="L97" s="22" t="s">
+        <v>1064</v>
+      </c>
+      <c r="M97" s="22" t="s">
+        <v>1065</v>
+      </c>
+      <c r="N97" s="22" t="s">
+        <v>1066</v>
+      </c>
+      <c r="O97" s="22" t="s">
+        <v>1067</v>
+      </c>
+      <c r="P97" s="22" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="98" ht="43.5" spans="1:16">
+      <c r="A98" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C98" s="21">
+        <v>61817</v>
+      </c>
+      <c r="D98" t="s">
+        <v>1071</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H98" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I98" t="s">
+        <v>1072</v>
+      </c>
+      <c r="J98" t="s">
+        <v>1073</v>
+      </c>
+      <c r="K98" s="22" t="s">
+        <v>1074</v>
+      </c>
+      <c r="L98" s="22" t="s">
+        <v>1075</v>
+      </c>
+      <c r="M98" s="22" t="s">
+        <v>1076</v>
+      </c>
+      <c r="N98" s="22" t="s">
+        <v>1077</v>
+      </c>
+      <c r="O98" s="22" t="s">
+        <v>1078</v>
+      </c>
+      <c r="P98" s="22" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="99" ht="43.5" spans="1:16">
+      <c r="A99" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C99" s="21">
+        <v>61816</v>
+      </c>
+      <c r="D99" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H99" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I99" t="s">
+        <v>1083</v>
+      </c>
+      <c r="J99" t="s">
+        <v>1084</v>
+      </c>
+      <c r="K99" s="22" t="s">
+        <v>1085</v>
+      </c>
+      <c r="L99" s="22" t="s">
+        <v>1086</v>
+      </c>
+      <c r="M99" s="22" t="s">
+        <v>1087</v>
+      </c>
+      <c r="N99" s="22" t="s">
+        <v>1088</v>
+      </c>
+      <c r="O99" s="22" t="s">
+        <v>1089</v>
+      </c>
+      <c r="P99" s="22" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="100" ht="43.5" spans="1:16">
+      <c r="A100" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C100" s="21">
+        <v>61827</v>
+      </c>
+      <c r="D100" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E100" t="s">
+        <v>1094</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H100" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I100" t="s">
+        <v>1095</v>
+      </c>
+      <c r="J100" t="s">
+        <v>1096</v>
+      </c>
+      <c r="K100" s="22" t="s">
+        <v>1097</v>
+      </c>
+      <c r="L100" s="22" t="s">
+        <v>1098</v>
+      </c>
+      <c r="M100" s="22" t="s">
+        <v>1099</v>
+      </c>
+      <c r="N100" s="22" t="s">
+        <v>1100</v>
+      </c>
+      <c r="O100" s="22" t="s">
+        <v>1101</v>
+      </c>
+      <c r="P100" s="22" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="101" ht="43.5" spans="1:16">
+      <c r="A101" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C101" s="21">
+        <v>61829</v>
+      </c>
+      <c r="D101" t="s">
+        <v>1105</v>
+      </c>
+      <c r="E101" t="s">
+        <v>1094</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H101" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I101" t="s">
+        <v>1106</v>
+      </c>
+      <c r="J101" t="s">
+        <v>1107</v>
+      </c>
+      <c r="K101" s="22" t="s">
+        <v>1108</v>
+      </c>
+      <c r="L101" s="22" t="s">
+        <v>1109</v>
+      </c>
+      <c r="M101" s="22" t="s">
+        <v>1110</v>
+      </c>
+      <c r="N101" s="22" t="s">
+        <v>1111</v>
+      </c>
+      <c r="O101" s="22" t="s">
+        <v>1112</v>
+      </c>
+      <c r="P101" s="22" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="102" ht="43.5" spans="1:16">
+      <c r="A102" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C102" s="21">
+        <v>61831</v>
+      </c>
+      <c r="D102" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E102" t="s">
+        <v>1094</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H102" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I102" t="s">
+        <v>1117</v>
+      </c>
+      <c r="J102" t="s">
+        <v>1118</v>
+      </c>
+      <c r="K102" s="22" t="s">
+        <v>1119</v>
+      </c>
+      <c r="L102" s="22" t="s">
+        <v>1120</v>
+      </c>
+      <c r="M102" s="22" t="s">
+        <v>1121</v>
+      </c>
+      <c r="N102" s="22" t="s">
+        <v>1122</v>
+      </c>
+      <c r="O102" s="22" t="s">
+        <v>1123</v>
+      </c>
+      <c r="P102" s="22" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="103" ht="43.5" spans="1:16">
+      <c r="A103" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C103" s="21">
+        <v>61830</v>
+      </c>
+      <c r="D103" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E103" t="s">
+        <v>1094</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H103" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I103" t="s">
+        <v>1128</v>
+      </c>
+      <c r="J103" t="s">
+        <v>1129</v>
+      </c>
+      <c r="K103" s="22" t="s">
+        <v>1130</v>
+      </c>
+      <c r="L103" s="22" t="s">
+        <v>1131</v>
+      </c>
+      <c r="M103" s="22" t="s">
+        <v>1132</v>
+      </c>
+      <c r="N103" s="22" t="s">
+        <v>1133</v>
+      </c>
+      <c r="O103" s="22" t="s">
+        <v>1134</v>
+      </c>
+      <c r="P103" s="22" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="104" ht="43.5" spans="1:16">
+      <c r="A104" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C104" s="21">
+        <v>61828</v>
+      </c>
+      <c r="D104" t="s">
+        <v>1138</v>
+      </c>
+      <c r="E104" t="s">
+        <v>1094</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H104" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I104" t="s">
+        <v>1139</v>
+      </c>
+      <c r="J104" t="s">
+        <v>1140</v>
+      </c>
+      <c r="K104" s="22" t="s">
+        <v>1141</v>
+      </c>
+      <c r="L104" s="22" t="s">
+        <v>1142</v>
+      </c>
+      <c r="M104" s="22" t="s">
+        <v>1143</v>
+      </c>
+      <c r="N104" s="22" t="s">
+        <v>1144</v>
+      </c>
+      <c r="O104" s="22" t="s">
+        <v>1145</v>
+      </c>
+      <c r="P104" s="22" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="105" ht="43.5" spans="1:16">
+      <c r="A105" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C105" s="21">
+        <v>62336</v>
+      </c>
+      <c r="D105" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E105" t="s">
+        <v>500</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H105" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I105" t="s">
+        <v>1150</v>
+      </c>
+      <c r="J105" s="23" t="s">
+        <v>1151</v>
+      </c>
+      <c r="K105" s="24" t="s">
+        <v>1152</v>
+      </c>
+      <c r="L105" s="24" t="s">
+        <v>1153</v>
+      </c>
+      <c r="M105" s="24" t="s">
+        <v>1154</v>
+      </c>
+      <c r="N105" s="24" t="s">
+        <v>1155</v>
+      </c>
+      <c r="O105" s="24" t="s">
+        <v>1156</v>
+      </c>
+      <c r="P105" s="24" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="106" ht="43.5" spans="1:16">
+      <c r="A106" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C106" s="21">
+        <v>62338</v>
+      </c>
+      <c r="D106" s="25" t="s">
+        <v>1160</v>
+      </c>
+      <c r="E106" t="s">
+        <v>500</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G106"/>
+      <c r="H106" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I106" t="s">
+        <v>1161</v>
+      </c>
+      <c r="J106" s="23" t="s">
+        <v>1162</v>
+      </c>
+      <c r="K106" s="24" t="s">
+        <v>1163</v>
+      </c>
+      <c r="L106" s="24" t="s">
+        <v>1164</v>
+      </c>
+      <c r="M106" s="24" t="s">
+        <v>1165</v>
+      </c>
+      <c r="N106" s="24" t="s">
+        <v>1166</v>
+      </c>
+      <c r="O106" s="24" t="s">
+        <v>1167</v>
+      </c>
+      <c r="P106" s="24" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="107" ht="43.5" spans="1:16">
+      <c r="A107" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C107" s="21">
+        <v>62335</v>
+      </c>
+      <c r="D107" s="26" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E107" t="s">
+        <v>500</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G107"/>
+      <c r="H107" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I107" t="s">
+        <v>1117</v>
+      </c>
+      <c r="J107" s="26" t="s">
+        <v>1172</v>
+      </c>
+      <c r="K107" s="24" t="s">
+        <v>1173</v>
+      </c>
+      <c r="L107" s="24" t="s">
+        <v>1174</v>
+      </c>
+      <c r="M107" s="24" t="s">
+        <v>1175</v>
+      </c>
+      <c r="N107" s="24" t="s">
+        <v>1176</v>
+      </c>
+      <c r="O107" s="24" t="s">
+        <v>1177</v>
+      </c>
+      <c r="P107" s="24" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="108" ht="43.5" spans="1:16">
+      <c r="A108" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C108" s="21">
+        <v>62337</v>
+      </c>
+      <c r="D108" s="26" t="s">
+        <v>1181</v>
+      </c>
+      <c r="E108" t="s">
+        <v>500</v>
+      </c>
+      <c r="F108" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G108"/>
+      <c r="H108" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I108" t="s">
+        <v>1182</v>
+      </c>
+      <c r="J108" s="23" t="s">
+        <v>1183</v>
+      </c>
+      <c r="K108" s="24" t="s">
+        <v>1184</v>
+      </c>
+      <c r="L108" s="24" t="s">
+        <v>1185</v>
+      </c>
+      <c r="M108" s="24" t="s">
+        <v>1186</v>
+      </c>
+      <c r="N108" s="24" t="s">
+        <v>1187</v>
+      </c>
+      <c r="O108" s="24" t="s">
+        <v>1188</v>
+      </c>
+      <c r="P108" s="24" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="109" ht="43.5" spans="1:16">
+      <c r="A109" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C109" s="21">
+        <v>62339</v>
+      </c>
+      <c r="D109" s="26" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E109" t="s">
+        <v>500</v>
+      </c>
+      <c r="F109" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G109"/>
+      <c r="H109" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I109" t="s">
+        <v>1193</v>
+      </c>
+      <c r="J109" s="23" t="s">
+        <v>1194</v>
+      </c>
+      <c r="K109" s="24" t="s">
+        <v>1195</v>
+      </c>
+      <c r="L109" s="24" t="s">
+        <v>1196</v>
+      </c>
+      <c r="M109" s="24" t="s">
+        <v>1197</v>
+      </c>
+      <c r="N109" s="24" t="s">
+        <v>1198</v>
+      </c>
+      <c r="O109" s="24" t="s">
+        <v>1199</v>
+      </c>
+      <c r="P109" s="24" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="110" ht="43.5" spans="1:16">
+      <c r="A110" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C110" s="21">
+        <v>62381</v>
+      </c>
+      <c r="D110" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E110" t="s">
+        <v>1204</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H110" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I110" t="s">
+        <v>1205</v>
+      </c>
+      <c r="J110" s="26" t="s">
+        <v>1206</v>
+      </c>
+      <c r="K110" s="22" t="s">
+        <v>1207</v>
+      </c>
+      <c r="L110" s="22" t="s">
+        <v>1208</v>
+      </c>
+      <c r="M110" s="22" t="s">
+        <v>1209</v>
+      </c>
+      <c r="N110" s="22" t="s">
+        <v>1210</v>
+      </c>
+      <c r="O110" s="22" t="s">
+        <v>1211</v>
+      </c>
+      <c r="P110" s="22" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="111" ht="43.5" spans="1:16">
+      <c r="A111" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C111">
+        <v>62380</v>
+      </c>
+      <c r="D111" t="s">
+        <v>1215</v>
+      </c>
+      <c r="E111" t="s">
+        <v>1204</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H111" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I111" t="s">
+        <v>1216</v>
+      </c>
+      <c r="J111" s="27" t="s">
+        <v>1217</v>
+      </c>
+      <c r="K111" s="22" t="s">
+        <v>1218</v>
+      </c>
+      <c r="L111" s="22" t="s">
+        <v>1219</v>
+      </c>
+      <c r="M111" s="22" t="s">
+        <v>1220</v>
+      </c>
+      <c r="N111" s="22" t="s">
+        <v>1221</v>
+      </c>
+      <c r="O111" s="22" t="s">
+        <v>1222</v>
+      </c>
+      <c r="P111" s="22" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="112" ht="43.5" spans="1:16">
+      <c r="A112" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C112" s="21">
+        <v>62378</v>
+      </c>
+      <c r="D112" t="s">
+        <v>1226</v>
+      </c>
+      <c r="E112" t="s">
+        <v>1204</v>
+      </c>
+      <c r="F112" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H112" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I112" t="s">
+        <v>1227</v>
+      </c>
+      <c r="J112" s="27" t="s">
+        <v>1228</v>
+      </c>
+      <c r="K112" s="22" t="s">
+        <v>1229</v>
+      </c>
+      <c r="L112" s="22" t="s">
+        <v>1230</v>
+      </c>
+      <c r="M112" s="22" t="s">
+        <v>1231</v>
+      </c>
+      <c r="N112" s="22" t="s">
+        <v>1232</v>
+      </c>
+      <c r="O112" s="22" t="s">
+        <v>1233</v>
+      </c>
+      <c r="P112" s="22" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="113" ht="43.5" spans="1:16">
+      <c r="A113" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C113" s="21">
+        <v>62379</v>
+      </c>
+      <c r="D113" t="s">
+        <v>1237</v>
+      </c>
+      <c r="E113" t="s">
+        <v>1204</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H113" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I113" t="s">
+        <v>1238</v>
+      </c>
+      <c r="J113" s="27" t="s">
+        <v>1239</v>
+      </c>
+      <c r="K113" s="22" t="s">
+        <v>1240</v>
+      </c>
+      <c r="L113" s="22" t="s">
+        <v>1241</v>
+      </c>
+      <c r="M113" s="22" t="s">
+        <v>1242</v>
+      </c>
+      <c r="N113" s="22" t="s">
+        <v>1243</v>
+      </c>
+      <c r="O113" s="22" t="s">
+        <v>1244</v>
+      </c>
+      <c r="P113" s="22" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="114" ht="43.5" spans="1:16">
+      <c r="A114" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C114" s="21">
+        <v>62382</v>
+      </c>
+      <c r="D114" t="s">
+        <v>1248</v>
+      </c>
+      <c r="E114" t="s">
+        <v>1204</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H114" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="I114" t="s">
+        <v>1249</v>
+      </c>
+      <c r="J114" s="27" t="s">
+        <v>1250</v>
+      </c>
+      <c r="K114" s="22" t="s">
+        <v>1251</v>
+      </c>
+      <c r="L114" s="22" t="s">
+        <v>1252</v>
+      </c>
+      <c r="M114" s="22" t="s">
+        <v>1253</v>
+      </c>
+      <c r="N114" s="22" t="s">
+        <v>1254</v>
+      </c>
+      <c r="O114" s="22" t="s">
+        <v>1255</v>
+      </c>
+      <c r="P114" s="22" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="115" ht="16.5" spans="1:16">
+      <c r="F115" s="4"/>
+    </row>
+    <row r="116" ht="16.5" spans="1:16">
+      <c r="F116" s="4"/>
+    </row>
+    <row r="117" ht="16.5" spans="1:16">
+      <c r="F117" s="4"/>
+    </row>
+    <row r="118" ht="16.5" spans="1:16">
+      <c r="F118" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/uploads/网站信息.xlsx
+++ b/uploads/网站信息.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1636" uniqueCount="1257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1859" uniqueCount="1434">
   <si>
     <t>分类</t>
   </si>
@@ -2868,9 +2868,15 @@
     <t>电脑|||相纸</t>
   </si>
   <si>
+    <t>63979,63984,63989,63994,63999,64004,64009,64014,64019,64024,64029</t>
+  </si>
+  <si>
     <t>Comput|||Photo Paper</t>
   </si>
   <si>
+    <t>170.101.101.208</t>
+  </si>
+  <si>
     <t>803 W 133rd St, Gardena, CA 90247</t>
   </si>
   <si>
@@ -2898,6 +2904,9 @@
     <t>iPhone 备用零件</t>
   </si>
   <si>
+    <t>63980,63985,63990,63995,64000,64005,64010,64015,64020,64025,64030</t>
+  </si>
+  <si>
     <t>Iphone Spare Part</t>
   </si>
   <si>
@@ -2928,6 +2937,9 @@
     <t>相机包|||单肩包</t>
   </si>
   <si>
+    <t>63981,63986,63991,63996,64001,64006,64011,64016,64021,64026,64031</t>
+  </si>
+  <si>
     <t>Bag|||Shoulder Bag</t>
   </si>
   <si>
@@ -2958,6 +2970,9 @@
     <t>小画幅镜头|||索尼美能达 A 卡口镜头</t>
   </si>
   <si>
+    <t>63982,63987,63992,63997,64002,64007,64012,64017,64022,64027</t>
+  </si>
+  <si>
     <t>Lens Small Format|||Sonyminolta A Mount Lens</t>
   </si>
   <si>
@@ -2986,6 +3001,9 @@
   </si>
   <si>
     <t>小画幅镜头|||佳能 EOS 卡口镜头|||佳能 EF 全画幅镜头</t>
+  </si>
+  <si>
+    <t>63983,63988,63993,63998,64003,64008,64013,64018,64023,64028</t>
   </si>
   <si>
     <t>Lens Small Format|||Canon Eos Mount Lens|||Canon Ef Full Frame Lens</t>
@@ -3259,7 +3277,7 @@
     <t>手提包</t>
   </si>
   <si>
-    <t>61457,61458,61459</t>
+    <t>61457,61458,61459,61418,61455,62447,50491</t>
   </si>
   <si>
     <t>Handbag</t>
@@ -3306,6 +3324,9 @@
     <t>行李架</t>
   </si>
   <si>
+    <t>62429,62432,62435,62438,62441,62444,50492</t>
+  </si>
+  <si>
     <t>Luggage Rack</t>
   </si>
   <si>
@@ -3350,6 +3371,9 @@
     <t>男士手表</t>
   </si>
   <si>
+    <t>62430,62433,62436,62439,62442,62445,50423</t>
+  </si>
+  <si>
     <t>Watch For Man</t>
   </si>
   <si>
@@ -3397,6 +3421,9 @@
     <t>耳环</t>
   </si>
   <si>
+    <t>62431,62434,62437,62440,62443,62446,50424</t>
+  </si>
+  <si>
     <t>Earring</t>
   </si>
   <si>
@@ -4210,6 +4237,510 @@
   <si>
     <t>clear acrylic keychain charms for bags and keys</t>
   </si>
+  <si>
+    <t>63159,63166,63173,63180,63187,63194,63201,63208,63215,63222,63229</t>
+  </si>
+  <si>
+    <t>Wall Sconce</t>
+  </si>
+  <si>
+    <t>2014 23rd St, Sacramento, CA 95818</t>
+  </si>
+  <si>
+    <t>lumivoraes.com</t>
+  </si>
+  <si>
+    <t>Modern Wall Sconces for Bedroom, Bathroom &amp; Hallway</t>
+  </si>
+  <si>
+    <t>现代壁灯：卧室、卫浴与玄关的氛围照明首选</t>
+  </si>
+  <si>
+    <t>Elevate your space with timeless wall sconces. Shop sleek bedroom, bathroom, and farmhouse styles. Find your perfect fit today.</t>
+  </si>
+  <si>
+    <t>用永恒感壁灯提升格调。探索卧室、卫浴及农舍风格。今天就为您家找到完美灯饰。</t>
+  </si>
+  <si>
+    <t>wall sconce</t>
+  </si>
+  <si>
+    <t>black, gold, hardwired, plug-in, LED, farmhouse, bathroom sconces</t>
+  </si>
+  <si>
+    <t>63160,63167,63174,63181,63188,63195,63202,63209,63216,63223</t>
+  </si>
+  <si>
+    <t>Vegetable</t>
+  </si>
+  <si>
+    <t>1221 F St, Sacramento, CA 95814</t>
+  </si>
+  <si>
+    <t>gardenovas.com</t>
+  </si>
+  <si>
+    <t>Organic Vegetable Seeds for Home Gardens &amp; Planters</t>
+  </si>
+  <si>
+    <t>有机蔬菜种子：家庭园艺与四季种植方案</t>
+  </si>
+  <si>
+    <t>Start your organic garden today. Shop high-yield vegetable seeds, nutrient-rich soil, and ergonomic hand tools. Grow your own food now.</t>
+  </si>
+  <si>
+    <t>即刻开启有机菜园。选购高产蔬菜种子、营养土及人体工学工具。现在就亲手种植您的专属食材。</t>
+  </si>
+  <si>
+    <t>vegetable seeds</t>
+  </si>
+  <si>
+    <t>organic, heirloom, non-gmo, raised bed, indoor, hydroponic</t>
+  </si>
+  <si>
+    <t>63161,63168,63175,63182,63189,63196,63203,63210,63217,63224</t>
+  </si>
+  <si>
+    <t>Candle</t>
+  </si>
+  <si>
+    <t>6930 Escallonia Dr, Orangevale, CA 95662</t>
+  </si>
+  <si>
+    <t>glodwick.com</t>
+  </si>
+  <si>
+    <t>Premium Scented Candles – Natural Soy Wax Home Fragrance</t>
+  </si>
+  <si>
+    <t>高端香薰蜡烛：自然大豆蜡居家香氛系列</t>
+  </si>
+  <si>
+    <t>Set the mood with our premium soy candles. Shop elegant scents, lead-free wicks, and luxury gift sets. Transform your home atmosphere.</t>
+  </si>
+  <si>
+    <t>用高端大豆蜡烛营造格调。选购优雅香氛、无铅烛芯及奢华礼盒。焕新您的居家氛围。</t>
+  </si>
+  <si>
+    <t>scented candles</t>
+  </si>
+  <si>
+    <t>soy wax, aromatherapy, luxury gift sets, clean burning, hand-poured</t>
+  </si>
+  <si>
+    <t>63162,63169,63176,63183,63190,63197,63204,63211,63218,63225</t>
+  </si>
+  <si>
+    <t>Mirror</t>
+  </si>
+  <si>
+    <t>6537 Wooded Creek Way, Orangevale, CA 95662</t>
+  </si>
+  <si>
+    <t>reflectoreas.com</t>
+  </si>
+  <si>
+    <t>Modern Wall Mirrors for Bathroom, Entryway &amp; Bedroom</t>
+  </si>
+  <si>
+    <t>装饰挂镜：浴室、玄关与卧室的现代光感焦点</t>
+  </si>
+  <si>
+    <t>Find the perfect wall mirror for your bathroom or entryway. Shop modern LED, vanity, and statement decor mirrors. Free shipping today.</t>
+  </si>
+  <si>
+    <t>为卫浴或玄关寻找完美挂镜。选购现代 LED 镜、梳妆框及艺术装饰品。今日下单享免运费。</t>
+  </si>
+  <si>
+    <t>wall mirror</t>
+  </si>
+  <si>
+    <t>bathroom, LED, full-length, farmhouse, entryway, round, frameless</t>
+  </si>
+  <si>
+    <t>63163,63170,63177,63184,63191,63198,63205,63212,63219,63226</t>
+  </si>
+  <si>
+    <t>Kitchen Appliance</t>
+  </si>
+  <si>
+    <t>2883 W Rome Ave, Anaheim, CA 92804</t>
+  </si>
+  <si>
+    <t>cookloomro.com</t>
+  </si>
+  <si>
+    <t>High-Performance Kitchen Appliances for Modern Cooking</t>
+  </si>
+  <si>
+    <t>高效能厨电：现代化家居烹饪的专业助手</t>
+  </si>
+  <si>
+    <t>Upgrade your culinary game with high-performance kitchen appliances. Shop blenders, air fryers, and spare parts. Simplify your cooking today.</t>
+  </si>
+  <si>
+    <t>升级您的烹饪装备，选用高性能厨电。选购破壁机、空气炸锅及原厂配件。让烹饪更简单。</t>
+  </si>
+  <si>
+    <t>kitchen appliances</t>
+  </si>
+  <si>
+    <t>blender, air fryer, food processor, spare parts, stainless steel</t>
+  </si>
+  <si>
+    <t>63164,63171,63178,63185,63192,63199,63206,63213,63220,63227</t>
+  </si>
+  <si>
+    <t>Area Rug</t>
+  </si>
+  <si>
+    <t>30 Manhattan Ave, Jersey City, NJ 07307</t>
+  </si>
+  <si>
+    <t>rugrodef.com</t>
+  </si>
+  <si>
+    <t>Modern Area Rugs for Living Rooms &amp; Bedrooms</t>
+  </si>
+  <si>
+    <t>现代地毯：适配多空间的舒适地面铺装</t>
+  </si>
+  <si>
+    <t>Transform your floors with our washable area rugs. Find durable wool, jute, and machine-washable designs. Upgrade your home style now.</t>
+  </si>
+  <si>
+    <t>用我们可水洗的地毯焕新地面。探索羊毛、黄麻及机洗设计，即刻升级家居风尚。</t>
+  </si>
+  <si>
+    <t>area rugs</t>
+  </si>
+  <si>
+    <t>washable, wool, jute, non-slip, living room, bedroom, vintage</t>
+  </si>
+  <si>
+    <t>63165,63172,63179,63186,63193,63200,63207,63214,63221,63228</t>
+  </si>
+  <si>
+    <t>Tea Towel</t>
+  </si>
+  <si>
+    <t>70 Corbin Ave, Jersey City, NJ 07306</t>
+  </si>
+  <si>
+    <t>linenluxethe.com</t>
+  </si>
+  <si>
+    <t>Absorbent Kitchen Tea Towels – Everyday Linen Essentials</t>
+  </si>
+  <si>
+    <t>厨房吸水茶巾：日常耐用的精选纺织品</t>
+  </si>
+  <si>
+    <t>Keep your kitchen clean with absorbent and durable tea towels. Shop cotton, linen, and matching oven mitts. Upgrade your kitchen linens.</t>
+  </si>
+  <si>
+    <t>用高吸水性耐用茶巾保持厨房整洁。选购纯棉、亚麻及配套烤箱手套。升级您的厨房织物。</t>
+  </si>
+  <si>
+    <t>tea towels</t>
+  </si>
+  <si>
+    <t>absorbent, cotton, linen, kitchen cleaning, dish cloth, sets</t>
+  </si>
+  <si>
+    <t>Plate</t>
+  </si>
+  <si>
+    <t>44 Dales Ave, Jersey City, NJ 07306</t>
+  </si>
+  <si>
+    <t>dinenovand.com</t>
+  </si>
+  <si>
+    <t>Modern Ceramic Dinner Plates &amp; Tableware Sets</t>
+  </si>
+  <si>
+    <t>陶瓷餐盘：现代简约餐桌美学套装</t>
+  </si>
+  <si>
+    <t>Set the perfect table with our durable ceramic dinner plates. Shop stoneware, porcelain, and matching bowls. Explore the collection today.</t>
+  </si>
+  <si>
+    <t>用耐用陶瓷餐盘装点完美餐桌。选购炻器、瓷器及配套碗具。立即探索最新餐具系列。</t>
+  </si>
+  <si>
+    <t>dinner plates</t>
+  </si>
+  <si>
+    <t>ceramic, stoneware, porcelain, dinnerware sets, reactive glaze</t>
+  </si>
+  <si>
+    <t>Pots|||Planter</t>
+  </si>
+  <si>
+    <t>460 S 12th St, Newark, NJ 07103</t>
+  </si>
+  <si>
+    <t>terraformanther.com</t>
+  </si>
+  <si>
+    <t>Modern Planters &amp; Raised Garden Beds for Gardens</t>
+  </si>
+  <si>
+    <t>现代种植箱：适合户外与露台的专业栽培容器</t>
+  </si>
+  <si>
+    <t>Elevate your garden with durable modern planters. Explore our selection of weather-resistant materials and tiered garden beds. Shop now.</t>
+  </si>
+  <si>
+    <t>用耐用现代种植箱美化花园。探索我们的耐候材质系列及阶梯式种植床。即刻进店选购。</t>
+  </si>
+  <si>
+    <t>modern planters</t>
+  </si>
+  <si>
+    <t>raised garden bed, large outdoor, weather-resistant, tiered</t>
+  </si>
+  <si>
+    <t>Ceil Fan</t>
+  </si>
+  <si>
+    <t>261 S 22nd St, Philadelphia, PA 19103</t>
+  </si>
+  <si>
+    <t>airflowro.com</t>
+  </si>
+  <si>
+    <t>Quiet Ceiling Fans with Remote – Energy-Efficient</t>
+  </si>
+  <si>
+    <t>静音吊扇：高能效的智能室内循环设备</t>
+  </si>
+  <si>
+    <t>Maintain comfort with our energy-efficient, quiet ceiling fans. Shop modern designs with remotes and LED lights. Upgrade your air quality.</t>
+  </si>
+  <si>
+    <t>选用高能效静音吊扇，保持室内舒适。选购带遥控及 LED 灯的现代款。优化您的室内空气。</t>
+  </si>
+  <si>
+    <t>ceiling fan</t>
+  </si>
+  <si>
+    <t>smart, DC motor, reversible, low profile, industrial, remote</t>
+  </si>
+  <si>
+    <t>64047,64054,64061,64068,64075,64082,64089,64096,64103,64110</t>
+  </si>
+  <si>
+    <t>Alloy Wheel</t>
+  </si>
+  <si>
+    <t>交通工具</t>
+  </si>
+  <si>
+    <t>2321 E St, Sacramento, CA 95816</t>
+  </si>
+  <si>
+    <t>rimforgeand.com</t>
+  </si>
+  <si>
+    <t>Performance Alloy Wheels – Lightweight Custom Rims</t>
+  </si>
+  <si>
+    <t>铝合金轮毂：轻量化高性能车辆升级方案</t>
+  </si>
+  <si>
+    <t>Upgrade your ride with high-performance alloy wheels. Shop sleek designs for improved handling, durability, and style. Find your fit today.</t>
+  </si>
+  <si>
+    <t>用高性能铝合金轮毂焕新您的座驾。探索提升操控、耐用性与外观的潮流设计。立即查找您的专属尺寸。</t>
+  </si>
+  <si>
+    <t>alloy wheels</t>
+  </si>
+  <si>
+    <t>lightweight racing rims, matte black alloy wheels, custom fitment</t>
+  </si>
+  <si>
+    <t>64048,64055,64062,64069,64076,64083,64090,64097,64104,64111</t>
+  </si>
+  <si>
+    <t>Front Bumper</t>
+  </si>
+  <si>
+    <t>1017 V St, Sacramento, CA 95818</t>
+  </si>
+  <si>
+    <t>aeroguardth.com</t>
+  </si>
+  <si>
+    <t>Front Bumpers &amp; Aerodynamic Body Kits</t>
+  </si>
+  <si>
+    <t>前保险杠：提升车辆气动布局的防护模组</t>
+  </si>
+  <si>
+    <t>Enhance your vehicle's look and protection with our durable front bumpers. Browse aerokits, grilles, and mounting hardware. Upgrade today.</t>
+  </si>
+  <si>
+    <t>用我们耐用的前保险杠提升车辆颜值与防护力。浏览空气动力学套件、进气格栅及安装五金件。立即升级。</t>
+  </si>
+  <si>
+    <t>front bumper</t>
+  </si>
+  <si>
+    <t>aftermarket front bumpers, body kit, grille guards, impact protection</t>
+  </si>
+  <si>
+    <t>64049,64056,64063,64070,64077,64084,64091,64098,64105</t>
+  </si>
+  <si>
+    <t>Car Mat</t>
+  </si>
+  <si>
+    <t>8205 Crossoak Way, Orangevale, CA 95662</t>
+  </si>
+  <si>
+    <t>treadguarden.com</t>
+  </si>
+  <si>
+    <t>Custom Car Floor Mats – Durable Interior Protection</t>
+  </si>
+  <si>
+    <t>车载地垫：重型耐用且全天候的内饰防护垫</t>
+  </si>
+  <si>
+    <t>Protect your interior with high-quality, weather-resistant car mats. Shop custom-fit designs for every make and model. Keep your floors clean.</t>
+  </si>
+  <si>
+    <t>用高品质耐候车载地垫防护您的内饰。选购适配各车型与品牌的定制版地垫，时刻保持车厢洁净。</t>
+  </si>
+  <si>
+    <t>car mats</t>
+  </si>
+  <si>
+    <t>all-weather floor liners, rubber car mats, custom fit interior protection</t>
+  </si>
+  <si>
+    <t>64050,64057,64064,64071,64078,64085,64092,64099,64106</t>
+  </si>
+  <si>
+    <t>Brake Pad</t>
+  </si>
+  <si>
+    <t>6508 Almond Ave, Orangevale, CA 95662</t>
+  </si>
+  <si>
+    <t>stoptechelite.com</t>
+  </si>
+  <si>
+    <t>Premium Brake Pads – High-Performance Stopping Power</t>
+  </si>
+  <si>
+    <t>高性能刹车片：为安全驾驶设计的精准制动组件</t>
+  </si>
+  <si>
+    <t>Experience reliable stopping power with our performance brake pads. Shop ceramic, semi-metallic, and low-dust options for your vehicle. Shop now.</t>
+  </si>
+  <si>
+    <t>体验卓越的制动性能，选用我们高性能刹车片。探索陶瓷、半金属及低粉尘选项，保障行车安全。下单选购。</t>
+  </si>
+  <si>
+    <t>brake pads</t>
+  </si>
+  <si>
+    <t>ceramic brake pads, performance stopping, low-dust pads, brake rotors</t>
+  </si>
+  <si>
+    <t>64051,64058,64065,64072,64079,64086,64093,64100,64107</t>
+  </si>
+  <si>
+    <t>Headlight</t>
+  </si>
+  <si>
+    <t>2814 W Rome Ave, Anaheim, CA 92804</t>
+  </si>
+  <si>
+    <t>beamcraftxe.com</t>
+  </si>
+  <si>
+    <t>High-Performance Headlight Assemblies &amp; LED Upgrades</t>
+  </si>
+  <si>
+    <t>前照灯模组：提升夜间可视度的现代化照明方案</t>
+  </si>
+  <si>
+    <t>Improve your night vision with custom headlight assemblies. Shop durable LED, HID, and projector upgrades. See the road clearly today.</t>
+  </si>
+  <si>
+    <t>用前照灯总成改善您的夜间视野。选购耐用 LED、HID 及透镜升级模组。即刻让前路清晰可见。</t>
+  </si>
+  <si>
+    <t>headlight</t>
+  </si>
+  <si>
+    <t>LED headlight assemblies, projector headlights, fog light upgrades</t>
+  </si>
+  <si>
+    <t>64052,64059,64066,64073,64080,64087,64094,64101,64108</t>
+  </si>
+  <si>
+    <t>Hitch</t>
+  </si>
+  <si>
+    <t>9811 Pacific Ave, Anaheim, CA 92804</t>
+  </si>
+  <si>
+    <t>towmasterpro.com</t>
+  </si>
+  <si>
+    <t>Heavy-Duty Hitches &amp; Towing Accessories</t>
+  </si>
+  <si>
+    <t>拖挂连接装置：高性能牵引与装载的专业挂钩</t>
+  </si>
+  <si>
+    <t>Tackle any load with our heavy-duty trailer hitches. Explore receiver hitches, ball mounts, and towing wiring kits. Upgrade your towing capacity.</t>
+  </si>
+  <si>
+    <t>无论是何种装载需求，我们的重型拖挂连接装置皆可满足。探索接收口、球头支架及拖车线束套件。提升牵引力。</t>
+  </si>
+  <si>
+    <t>trailer hitch</t>
+  </si>
+  <si>
+    <t>receiver hitch, ball mount, towing wiring, towing capacity</t>
+  </si>
+  <si>
+    <t>64053,64060,64067,64074,64081,64088,64095,64102,64109</t>
+  </si>
+  <si>
+    <t>High Output Alternator</t>
+  </si>
+  <si>
+    <t>101 Ferry St, Jersey City, NJ 07307</t>
+  </si>
+  <si>
+    <t>voltmaxengine.com</t>
+  </si>
+  <si>
+    <t>High Output Alternators – Maximum Power for Car Audio &amp; Tech</t>
+  </si>
+  <si>
+    <t>大功率发电机：为车载音响与电子设备提供的巅峰电力</t>
+  </si>
+  <si>
+    <t>Power your custom audio and tech upgrades with a high output alternator. Engineered for reliability and high voltage demand. Shop now.</t>
+  </si>
+  <si>
+    <t>用大功率发电机驱动您的车载音响与设备升级。专为高电压需求与长期可靠性设计。即刻进店选购。</t>
+  </si>
+  <si>
+    <t>high output alternator</t>
+  </si>
+  <si>
+    <t>high amperage alternator, car audio power, voltage regulator</t>
+  </si>
 </sst>
 </file>
 
@@ -4221,7 +4752,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4286,13 +4817,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -4302,13 +4826,6 @@
       <sz val="11"/>
       <color rgb="FF1F1F1F"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -4812,133 +5329,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4994,9 +5511,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -5016,15 +5530,18 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
@@ -5034,6 +5551,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -10831,7 +11351,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q118"/>
+  <dimension ref="A1:Q134"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="50.625" customWidth="1"/>
@@ -13590,7 +14110,7 @@
         <v>120</v>
       </c>
       <c r="G53" s="4"/>
-      <c r="H53" s="17" t="s">
+      <c r="H53" s="14" t="s">
         <v>601</v>
       </c>
       <c r="I53" s="15" t="s">
@@ -13638,7 +14158,7 @@
         <v>22</v>
       </c>
       <c r="G54" s="4"/>
-      <c r="H54" s="17" t="s">
+      <c r="H54" s="14" t="s">
         <v>601</v>
       </c>
       <c r="I54" s="15" t="s">
@@ -13686,7 +14206,7 @@
         <v>36</v>
       </c>
       <c r="G55" s="4"/>
-      <c r="H55" s="17" t="s">
+      <c r="H55" s="14" t="s">
         <v>601</v>
       </c>
       <c r="I55" s="15" t="s">
@@ -13734,7 +14254,7 @@
         <v>48</v>
       </c>
       <c r="G56" s="4"/>
-      <c r="H56" s="17" t="s">
+      <c r="H56" s="14" t="s">
         <v>601</v>
       </c>
       <c r="I56" s="15" t="s">
@@ -14546,25 +15066,25 @@
       <c r="I73" s="4" t="s">
         <v>816</v>
       </c>
-      <c r="J73" s="18" t="s">
+      <c r="J73" s="17" t="s">
         <v>817</v>
       </c>
-      <c r="K73" s="18" t="s">
+      <c r="K73" s="17" t="s">
         <v>818</v>
       </c>
-      <c r="L73" s="19" t="s">
+      <c r="L73" s="18" t="s">
         <v>819</v>
       </c>
-      <c r="M73" s="18" t="s">
+      <c r="M73" s="17" t="s">
         <v>820</v>
       </c>
-      <c r="N73" s="18" t="s">
+      <c r="N73" s="17" t="s">
         <v>821</v>
       </c>
-      <c r="O73" s="19" t="s">
+      <c r="O73" s="18" t="s">
         <v>815</v>
       </c>
-      <c r="P73" s="18" t="s">
+      <c r="P73" s="17" t="s">
         <v>822</v>
       </c>
     </row>
@@ -14594,25 +15114,25 @@
       <c r="I74" s="4" t="s">
         <v>826</v>
       </c>
-      <c r="J74" s="18" t="s">
+      <c r="J74" s="17" t="s">
         <v>827</v>
       </c>
-      <c r="K74" s="18" t="s">
+      <c r="K74" s="17" t="s">
         <v>828</v>
       </c>
-      <c r="L74" s="19" t="s">
+      <c r="L74" s="18" t="s">
         <v>829</v>
       </c>
-      <c r="M74" s="18" t="s">
+      <c r="M74" s="17" t="s">
         <v>830</v>
       </c>
-      <c r="N74" s="18" t="s">
+      <c r="N74" s="17" t="s">
         <v>831</v>
       </c>
-      <c r="O74" s="19" t="s">
+      <c r="O74" s="18" t="s">
         <v>832</v>
       </c>
-      <c r="P74" s="18" t="s">
+      <c r="P74" s="17" t="s">
         <v>833</v>
       </c>
     </row>
@@ -14642,25 +15162,25 @@
       <c r="I75" s="4" t="s">
         <v>837</v>
       </c>
-      <c r="J75" s="18" t="s">
+      <c r="J75" s="17" t="s">
         <v>838</v>
       </c>
-      <c r="K75" s="18" t="s">
+      <c r="K75" s="17" t="s">
         <v>839</v>
       </c>
-      <c r="L75" s="19" t="s">
+      <c r="L75" s="18" t="s">
         <v>840</v>
       </c>
-      <c r="M75" s="18" t="s">
+      <c r="M75" s="17" t="s">
         <v>841</v>
       </c>
-      <c r="N75" s="18" t="s">
+      <c r="N75" s="17" t="s">
         <v>842</v>
       </c>
-      <c r="O75" s="19" t="s">
+      <c r="O75" s="18" t="s">
         <v>836</v>
       </c>
-      <c r="P75" s="18" t="s">
+      <c r="P75" s="17" t="s">
         <v>843</v>
       </c>
     </row>
@@ -14690,25 +15210,25 @@
       <c r="I76" s="4" t="s">
         <v>847</v>
       </c>
-      <c r="J76" s="18" t="s">
+      <c r="J76" s="17" t="s">
         <v>848</v>
       </c>
-      <c r="K76" s="18" t="s">
+      <c r="K76" s="17" t="s">
         <v>849</v>
       </c>
-      <c r="L76" s="19" t="s">
+      <c r="L76" s="18" t="s">
         <v>850</v>
       </c>
-      <c r="M76" s="18" t="s">
+      <c r="M76" s="17" t="s">
         <v>851</v>
       </c>
-      <c r="N76" s="18" t="s">
+      <c r="N76" s="17" t="s">
         <v>852</v>
       </c>
-      <c r="O76" s="19" t="s">
+      <c r="O76" s="18" t="s">
         <v>846</v>
       </c>
-      <c r="P76" s="18" t="s">
+      <c r="P76" s="17" t="s">
         <v>853</v>
       </c>
     </row>
@@ -14737,25 +15257,25 @@
       <c r="I77" s="4" t="s">
         <v>857</v>
       </c>
-      <c r="J77" s="18" t="s">
+      <c r="J77" s="17" t="s">
         <v>858</v>
       </c>
-      <c r="K77" s="18" t="s">
+      <c r="K77" s="17" t="s">
         <v>859</v>
       </c>
-      <c r="L77" s="19" t="s">
+      <c r="L77" s="18" t="s">
         <v>860</v>
       </c>
-      <c r="M77" s="18" t="s">
+      <c r="M77" s="17" t="s">
         <v>861</v>
       </c>
-      <c r="N77" s="18" t="s">
+      <c r="N77" s="17" t="s">
         <v>862</v>
       </c>
-      <c r="O77" s="19" t="s">
+      <c r="O77" s="18" t="s">
         <v>863</v>
       </c>
-      <c r="P77" s="18" t="s">
+      <c r="P77" s="17" t="s">
         <v>864</v>
       </c>
     </row>
@@ -14763,12 +15283,14 @@
       <c r="A78" t="s">
         <v>865</v>
       </c>
-      <c r="B78" s="5"/>
+      <c r="B78" s="31" t="s">
+        <v>866</v>
+      </c>
       <c r="C78" s="8">
         <v>59031</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>199</v>
@@ -14776,44 +15298,46 @@
       <c r="F78" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="H78" s="17" t="s">
-        <v>601</v>
+      <c r="H78" s="14" t="s">
+        <v>868</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>867</v>
-      </c>
-      <c r="J78" s="18" t="s">
-        <v>868</v>
-      </c>
-      <c r="K78" s="18" t="s">
         <v>869</v>
       </c>
-      <c r="L78" s="19" t="s">
+      <c r="J78" s="17" t="s">
         <v>870</v>
       </c>
-      <c r="M78" s="18" t="s">
+      <c r="K78" s="17" t="s">
         <v>871</v>
       </c>
-      <c r="N78" s="18" t="s">
+      <c r="L78" s="18" t="s">
         <v>872</v>
       </c>
-      <c r="O78" s="19" t="s">
+      <c r="M78" s="17" t="s">
         <v>873</v>
       </c>
-      <c r="P78" s="18" t="s">
+      <c r="N78" s="17" t="s">
         <v>874</v>
+      </c>
+      <c r="O78" s="18" t="s">
+        <v>875</v>
+      </c>
+      <c r="P78" s="17" t="s">
+        <v>876</v>
       </c>
     </row>
     <row r="79" ht="50.25" spans="1:16">
       <c r="A79" t="s">
-        <v>875</v>
-      </c>
-      <c r="B79" s="5"/>
+        <v>877</v>
+      </c>
+      <c r="B79" s="31" t="s">
+        <v>878</v>
+      </c>
       <c r="C79" s="8">
         <v>59022</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>199</v>
@@ -14821,44 +15345,46 @@
       <c r="F79" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="H79" s="17" t="s">
-        <v>601</v>
+      <c r="H79" s="14" t="s">
+        <v>868</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>877</v>
-      </c>
-      <c r="J79" s="18" t="s">
-        <v>878</v>
-      </c>
-      <c r="K79" s="18" t="s">
-        <v>879</v>
-      </c>
-      <c r="L79" s="19" t="s">
         <v>880</v>
       </c>
-      <c r="M79" s="18" t="s">
+      <c r="J79" s="17" t="s">
         <v>881</v>
       </c>
-      <c r="N79" s="18" t="s">
+      <c r="K79" s="17" t="s">
         <v>882</v>
       </c>
-      <c r="O79" s="19" t="s">
+      <c r="L79" s="18" t="s">
         <v>883</v>
       </c>
-      <c r="P79" s="18" t="s">
+      <c r="M79" s="17" t="s">
         <v>884</v>
+      </c>
+      <c r="N79" s="17" t="s">
+        <v>885</v>
+      </c>
+      <c r="O79" s="18" t="s">
+        <v>886</v>
+      </c>
+      <c r="P79" s="17" t="s">
+        <v>887</v>
       </c>
     </row>
     <row r="80" ht="50.25" spans="1:16">
       <c r="A80" t="s">
-        <v>885</v>
-      </c>
-      <c r="B80" s="5"/>
+        <v>888</v>
+      </c>
+      <c r="B80" s="31" t="s">
+        <v>889</v>
+      </c>
       <c r="C80" s="8">
         <v>59035</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>199</v>
@@ -14866,44 +15392,46 @@
       <c r="F80" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H80" s="17" t="s">
-        <v>601</v>
+      <c r="H80" s="14" t="s">
+        <v>868</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>887</v>
-      </c>
-      <c r="J80" s="18" t="s">
-        <v>888</v>
-      </c>
-      <c r="K80" s="18" t="s">
-        <v>889</v>
-      </c>
-      <c r="L80" s="19" t="s">
-        <v>890</v>
-      </c>
-      <c r="M80" s="18" t="s">
         <v>891</v>
       </c>
-      <c r="N80" s="18" t="s">
+      <c r="J80" s="17" t="s">
         <v>892</v>
       </c>
-      <c r="O80" s="19" t="s">
+      <c r="K80" s="17" t="s">
         <v>893</v>
       </c>
-      <c r="P80" s="18" t="s">
+      <c r="L80" s="18" t="s">
         <v>894</v>
+      </c>
+      <c r="M80" s="17" t="s">
+        <v>895</v>
+      </c>
+      <c r="N80" s="17" t="s">
+        <v>896</v>
+      </c>
+      <c r="O80" s="18" t="s">
+        <v>897</v>
+      </c>
+      <c r="P80" s="17" t="s">
+        <v>898</v>
       </c>
     </row>
     <row r="81" ht="50.25" spans="1:16">
       <c r="A81" t="s">
-        <v>895</v>
-      </c>
-      <c r="B81" s="5"/>
+        <v>899</v>
+      </c>
+      <c r="B81" s="31" t="s">
+        <v>900</v>
+      </c>
       <c r="C81" s="8">
         <v>59026</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>896</v>
+        <v>901</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>199</v>
@@ -14912,44 +15440,46 @@
         <v>36</v>
       </c>
       <c r="G81" s="4"/>
-      <c r="H81" s="17" t="s">
-        <v>601</v>
+      <c r="H81" s="14" t="s">
+        <v>868</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>897</v>
-      </c>
-      <c r="J81" s="18" t="s">
-        <v>898</v>
-      </c>
-      <c r="K81" s="18" t="s">
-        <v>899</v>
-      </c>
-      <c r="L81" s="19" t="s">
-        <v>900</v>
-      </c>
-      <c r="M81" s="18" t="s">
-        <v>901</v>
-      </c>
-      <c r="N81" s="18" t="s">
         <v>902</v>
       </c>
-      <c r="O81" s="19" t="s">
+      <c r="J81" s="17" t="s">
         <v>903</v>
       </c>
-      <c r="P81" s="18" t="s">
+      <c r="K81" s="17" t="s">
         <v>904</v>
+      </c>
+      <c r="L81" s="18" t="s">
+        <v>905</v>
+      </c>
+      <c r="M81" s="17" t="s">
+        <v>906</v>
+      </c>
+      <c r="N81" s="17" t="s">
+        <v>907</v>
+      </c>
+      <c r="O81" s="18" t="s">
+        <v>908</v>
+      </c>
+      <c r="P81" s="17" t="s">
+        <v>909</v>
       </c>
     </row>
     <row r="82" ht="50.25" spans="1:16">
       <c r="A82" t="s">
-        <v>905</v>
-      </c>
-      <c r="B82" s="5"/>
+        <v>910</v>
+      </c>
+      <c r="B82" s="31" t="s">
+        <v>911</v>
+      </c>
       <c r="C82" s="8">
         <v>59028</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>199</v>
@@ -14958,518 +15488,524 @@
         <v>48</v>
       </c>
       <c r="G82" s="4"/>
-      <c r="H82" s="17" t="s">
-        <v>601</v>
+      <c r="H82" s="14" t="s">
+        <v>868</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>907</v>
-      </c>
-      <c r="J82" s="18" t="s">
-        <v>908</v>
-      </c>
-      <c r="K82" s="18" t="s">
-        <v>909</v>
-      </c>
-      <c r="L82" s="19" t="s">
-        <v>910</v>
-      </c>
-      <c r="M82" s="18" t="s">
-        <v>911</v>
-      </c>
-      <c r="N82" s="18" t="s">
-        <v>912</v>
-      </c>
-      <c r="O82" s="19" t="s">
         <v>913</v>
       </c>
-      <c r="P82" s="18" t="s">
+      <c r="J82" s="17" t="s">
         <v>914</v>
+      </c>
+      <c r="K82" s="17" t="s">
+        <v>915</v>
+      </c>
+      <c r="L82" s="18" t="s">
+        <v>916</v>
+      </c>
+      <c r="M82" s="17" t="s">
+        <v>917</v>
+      </c>
+      <c r="N82" s="17" t="s">
+        <v>918</v>
+      </c>
+      <c r="O82" s="18" t="s">
+        <v>919</v>
+      </c>
+      <c r="P82" s="17" t="s">
+        <v>920</v>
       </c>
     </row>
     <row r="83" ht="50.25" spans="1:16">
       <c r="A83" t="s">
-        <v>915</v>
+        <v>921</v>
       </c>
       <c r="B83" s="28" t="s">
-        <v>916</v>
+        <v>922</v>
       </c>
       <c r="C83" s="8">
         <v>59121</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>917</v>
-      </c>
-      <c r="E83" s="20" t="s">
+        <v>923</v>
+      </c>
+      <c r="E83" s="19" t="s">
         <v>84</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>60</v>
       </c>
       <c r="G83" s="4"/>
-      <c r="H83" s="17" t="s">
+      <c r="H83" s="14" t="s">
         <v>601</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>918</v>
-      </c>
-      <c r="J83" s="18" t="s">
-        <v>919</v>
-      </c>
-      <c r="K83" s="18" t="s">
-        <v>920</v>
-      </c>
-      <c r="L83" s="19" t="s">
-        <v>921</v>
-      </c>
-      <c r="M83" s="18" t="s">
-        <v>922</v>
-      </c>
-      <c r="N83" s="18" t="s">
-        <v>923</v>
-      </c>
-      <c r="O83" s="19" t="s">
         <v>924</v>
       </c>
-      <c r="P83" s="18" t="s">
+      <c r="J83" s="17" t="s">
         <v>925</v>
+      </c>
+      <c r="K83" s="17" t="s">
+        <v>926</v>
+      </c>
+      <c r="L83" s="18" t="s">
+        <v>927</v>
+      </c>
+      <c r="M83" s="17" t="s">
+        <v>928</v>
+      </c>
+      <c r="N83" s="17" t="s">
+        <v>929</v>
+      </c>
+      <c r="O83" s="18" t="s">
+        <v>930</v>
+      </c>
+      <c r="P83" s="17" t="s">
+        <v>931</v>
       </c>
     </row>
     <row r="84" ht="50.25" spans="1:16">
       <c r="A84" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="B84" s="28" t="s">
-        <v>927</v>
+        <v>933</v>
       </c>
       <c r="C84" s="8">
         <v>59126</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>928</v>
-      </c>
-      <c r="E84" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="E84" s="19" t="s">
         <v>84</v>
       </c>
       <c r="F84" s="4" t="s">
         <v>72</v>
       </c>
       <c r="G84" s="4"/>
-      <c r="H84" s="17" t="s">
+      <c r="H84" s="14" t="s">
         <v>601</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>929</v>
-      </c>
-      <c r="J84" s="18" t="s">
-        <v>930</v>
-      </c>
-      <c r="K84" s="18" t="s">
-        <v>931</v>
-      </c>
-      <c r="L84" s="19" t="s">
-        <v>932</v>
-      </c>
-      <c r="M84" s="18" t="s">
-        <v>933</v>
-      </c>
-      <c r="N84" s="18" t="s">
-        <v>934</v>
-      </c>
-      <c r="O84" s="19" t="s">
         <v>935</v>
       </c>
-      <c r="P84" s="18" t="s">
+      <c r="J84" s="17" t="s">
         <v>936</v>
+      </c>
+      <c r="K84" s="17" t="s">
+        <v>937</v>
+      </c>
+      <c r="L84" s="18" t="s">
+        <v>938</v>
+      </c>
+      <c r="M84" s="17" t="s">
+        <v>939</v>
+      </c>
+      <c r="N84" s="17" t="s">
+        <v>940</v>
+      </c>
+      <c r="O84" s="18" t="s">
+        <v>941</v>
+      </c>
+      <c r="P84" s="17" t="s">
+        <v>942</v>
       </c>
     </row>
     <row r="85" ht="50.25" spans="1:16">
       <c r="A85" t="s">
-        <v>937</v>
+        <v>943</v>
       </c>
       <c r="B85" s="28" t="s">
-        <v>938</v>
+        <v>944</v>
       </c>
       <c r="C85" s="4">
         <v>59122</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>939</v>
-      </c>
-      <c r="E85" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="E85" s="19" t="s">
         <v>84</v>
       </c>
       <c r="F85" s="4" t="s">
         <v>85</v>
       </c>
       <c r="G85" s="4"/>
-      <c r="H85" s="17" t="s">
+      <c r="H85" s="14" t="s">
         <v>601</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>940</v>
-      </c>
-      <c r="J85" s="18" t="s">
-        <v>941</v>
-      </c>
-      <c r="K85" s="18" t="s">
-        <v>942</v>
-      </c>
-      <c r="L85" s="19" t="s">
-        <v>943</v>
-      </c>
-      <c r="M85" s="18" t="s">
-        <v>944</v>
-      </c>
-      <c r="N85" s="18" t="s">
+        <v>946</v>
+      </c>
+      <c r="J85" s="17" t="s">
+        <v>947</v>
+      </c>
+      <c r="K85" s="17" t="s">
+        <v>948</v>
+      </c>
+      <c r="L85" s="18" t="s">
+        <v>949</v>
+      </c>
+      <c r="M85" s="17" t="s">
+        <v>950</v>
+      </c>
+      <c r="N85" s="17" t="s">
+        <v>951</v>
+      </c>
+      <c r="O85" s="18" t="s">
         <v>945</v>
       </c>
-      <c r="O85" s="19" t="s">
-        <v>939</v>
-      </c>
-      <c r="P85" s="18" t="s">
-        <v>946</v>
+      <c r="P85" s="17" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="86" ht="50.25" spans="1:16">
       <c r="A86" t="s">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="B86" s="28" t="s">
-        <v>948</v>
+        <v>954</v>
       </c>
       <c r="C86" s="4">
         <v>59123</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>949</v>
-      </c>
-      <c r="E86" s="20" t="s">
+        <v>955</v>
+      </c>
+      <c r="E86" s="19" t="s">
         <v>84</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>97</v>
       </c>
       <c r="G86" s="4"/>
-      <c r="H86" s="17" t="s">
+      <c r="H86" s="14" t="s">
         <v>601</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>950</v>
-      </c>
-      <c r="J86" s="18" t="s">
-        <v>951</v>
-      </c>
-      <c r="K86" s="18" t="s">
-        <v>952</v>
-      </c>
-      <c r="L86" s="19" t="s">
-        <v>953</v>
-      </c>
-      <c r="M86" s="18" t="s">
-        <v>954</v>
-      </c>
-      <c r="N86" s="18" t="s">
+        <v>956</v>
+      </c>
+      <c r="J86" s="17" t="s">
+        <v>957</v>
+      </c>
+      <c r="K86" s="17" t="s">
+        <v>958</v>
+      </c>
+      <c r="L86" s="18" t="s">
+        <v>959</v>
+      </c>
+      <c r="M86" s="17" t="s">
+        <v>960</v>
+      </c>
+      <c r="N86" s="17" t="s">
+        <v>961</v>
+      </c>
+      <c r="O86" s="18" t="s">
         <v>955</v>
       </c>
-      <c r="O86" s="19" t="s">
-        <v>949</v>
-      </c>
-      <c r="P86" s="18" t="s">
-        <v>956</v>
+      <c r="P86" s="17" t="s">
+        <v>962</v>
       </c>
     </row>
     <row r="87" ht="50.25" spans="1:16">
       <c r="A87" t="s">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="B87" s="28" t="s">
-        <v>958</v>
+        <v>964</v>
       </c>
       <c r="C87" s="8">
         <v>59125</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>959</v>
-      </c>
-      <c r="E87" s="20" t="s">
+        <v>965</v>
+      </c>
+      <c r="E87" s="19" t="s">
         <v>84</v>
       </c>
       <c r="F87" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G87" s="4"/>
-      <c r="H87" s="17" t="s">
+      <c r="H87" s="14" t="s">
         <v>601</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>960</v>
-      </c>
-      <c r="J87" s="18" t="s">
-        <v>961</v>
-      </c>
-      <c r="K87" s="18" t="s">
-        <v>962</v>
-      </c>
-      <c r="L87" s="19" t="s">
-        <v>963</v>
-      </c>
-      <c r="M87" s="18" t="s">
-        <v>964</v>
-      </c>
-      <c r="N87" s="18" t="s">
+        <v>966</v>
+      </c>
+      <c r="J87" s="17" t="s">
+        <v>967</v>
+      </c>
+      <c r="K87" s="17" t="s">
+        <v>968</v>
+      </c>
+      <c r="L87" s="18" t="s">
+        <v>969</v>
+      </c>
+      <c r="M87" s="17" t="s">
+        <v>970</v>
+      </c>
+      <c r="N87" s="17" t="s">
+        <v>971</v>
+      </c>
+      <c r="O87" s="18" t="s">
         <v>965</v>
       </c>
-      <c r="O87" s="19" t="s">
-        <v>959</v>
-      </c>
-      <c r="P87" s="18" t="s">
-        <v>966</v>
+      <c r="P87" s="17" t="s">
+        <v>972</v>
       </c>
     </row>
     <row r="88" ht="50.25" spans="1:16">
       <c r="A88" t="s">
-        <v>967</v>
+        <v>973</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>968</v>
+        <v>974</v>
       </c>
       <c r="C88" s="8">
         <v>59127</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>969</v>
-      </c>
-      <c r="E88" s="20" t="s">
+        <v>975</v>
+      </c>
+      <c r="E88" s="19" t="s">
         <v>84</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>120</v>
       </c>
       <c r="G88" s="4"/>
-      <c r="H88" s="17" t="s">
-        <v>601</v>
+      <c r="H88" s="14" t="s">
+        <v>868</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>970</v>
-      </c>
-      <c r="J88" s="18" t="s">
-        <v>971</v>
-      </c>
-      <c r="K88" s="18" t="s">
-        <v>972</v>
-      </c>
-      <c r="L88" s="19" t="s">
-        <v>973</v>
-      </c>
-      <c r="M88" s="18" t="s">
-        <v>974</v>
-      </c>
-      <c r="N88" s="18" t="s">
+        <v>976</v>
+      </c>
+      <c r="J88" s="17" t="s">
+        <v>977</v>
+      </c>
+      <c r="K88" s="17" t="s">
+        <v>978</v>
+      </c>
+      <c r="L88" s="18" t="s">
+        <v>979</v>
+      </c>
+      <c r="M88" s="17" t="s">
+        <v>980</v>
+      </c>
+      <c r="N88" s="17" t="s">
+        <v>981</v>
+      </c>
+      <c r="O88" s="18" t="s">
         <v>975</v>
       </c>
-      <c r="O88" s="19" t="s">
-        <v>969</v>
-      </c>
-      <c r="P88" s="18" t="s">
-        <v>976</v>
+      <c r="P88" s="17" t="s">
+        <v>982</v>
       </c>
     </row>
     <row r="89" ht="50.25" spans="1:16">
       <c r="A89" t="s">
-        <v>977</v>
-      </c>
-      <c r="B89" s="5"/>
+        <v>983</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>984</v>
+      </c>
       <c r="C89" s="8">
         <v>59129</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>978</v>
-      </c>
-      <c r="E89" s="20" t="s">
+        <v>985</v>
+      </c>
+      <c r="E89" s="19" t="s">
         <v>84</v>
       </c>
       <c r="F89" s="4" t="s">
         <v>48</v>
       </c>
       <c r="G89" s="4"/>
-      <c r="H89" s="17" t="s">
-        <v>601</v>
+      <c r="H89" s="14" t="s">
+        <v>868</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>979</v>
-      </c>
-      <c r="J89" s="18" t="s">
-        <v>980</v>
-      </c>
-      <c r="K89" s="18" t="s">
-        <v>981</v>
-      </c>
-      <c r="L89" s="19" t="s">
-        <v>982</v>
-      </c>
-      <c r="M89" s="18" t="s">
-        <v>983</v>
-      </c>
-      <c r="N89" s="18" t="s">
-        <v>984</v>
-      </c>
-      <c r="O89" s="19" t="s">
-        <v>978</v>
-      </c>
-      <c r="P89" s="18" t="s">
+        <v>986</v>
+      </c>
+      <c r="J89" s="17" t="s">
+        <v>987</v>
+      </c>
+      <c r="K89" s="17" t="s">
+        <v>988</v>
+      </c>
+      <c r="L89" s="18" t="s">
+        <v>989</v>
+      </c>
+      <c r="M89" s="17" t="s">
+        <v>990</v>
+      </c>
+      <c r="N89" s="17" t="s">
+        <v>991</v>
+      </c>
+      <c r="O89" s="18" t="s">
         <v>985</v>
+      </c>
+      <c r="P89" s="17" t="s">
+        <v>992</v>
       </c>
     </row>
     <row r="90" ht="50.25" spans="1:16">
       <c r="A90" t="s">
-        <v>986</v>
-      </c>
-      <c r="B90" s="5"/>
+        <v>993</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>994</v>
+      </c>
       <c r="C90" s="8">
         <v>59131</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>987</v>
-      </c>
-      <c r="E90" s="20" t="s">
+        <v>995</v>
+      </c>
+      <c r="E90" s="19" t="s">
         <v>84</v>
       </c>
       <c r="F90" s="4" t="s">
         <v>60</v>
       </c>
       <c r="G90" s="4"/>
-      <c r="H90" s="17" t="s">
-        <v>601</v>
+      <c r="H90" s="14" t="s">
+        <v>868</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>988</v>
-      </c>
-      <c r="J90" s="18" t="s">
-        <v>989</v>
-      </c>
-      <c r="K90" s="18" t="s">
-        <v>990</v>
-      </c>
-      <c r="L90" s="19" t="s">
-        <v>991</v>
-      </c>
-      <c r="M90" s="18" t="s">
-        <v>992</v>
-      </c>
-      <c r="N90" s="18" t="s">
-        <v>993</v>
-      </c>
-      <c r="O90" s="19" t="s">
-        <v>994</v>
-      </c>
-      <c r="P90" s="18" t="s">
-        <v>995</v>
+        <v>996</v>
+      </c>
+      <c r="J90" s="17" t="s">
+        <v>997</v>
+      </c>
+      <c r="K90" s="17" t="s">
+        <v>998</v>
+      </c>
+      <c r="L90" s="18" t="s">
+        <v>999</v>
+      </c>
+      <c r="M90" s="17" t="s">
+        <v>1000</v>
+      </c>
+      <c r="N90" s="17" t="s">
+        <v>1001</v>
+      </c>
+      <c r="O90" s="18" t="s">
+        <v>1002</v>
+      </c>
+      <c r="P90" s="17" t="s">
+        <v>1003</v>
       </c>
     </row>
     <row r="91" ht="50.25" spans="1:16">
       <c r="A91" t="s">
-        <v>996</v>
-      </c>
-      <c r="B91" s="5"/>
+        <v>1004</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>1005</v>
+      </c>
       <c r="C91" s="8">
         <v>59124</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>997</v>
-      </c>
-      <c r="E91" s="20" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E91" s="19" t="s">
         <v>84</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>72</v>
       </c>
       <c r="G91" s="4"/>
-      <c r="H91" s="17" t="s">
-        <v>601</v>
+      <c r="H91" s="14" t="s">
+        <v>868</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>998</v>
-      </c>
-      <c r="J91" s="18" t="s">
-        <v>999</v>
-      </c>
-      <c r="K91" s="18" t="s">
-        <v>1000</v>
-      </c>
-      <c r="L91" s="19" t="s">
-        <v>1001</v>
-      </c>
-      <c r="M91" s="18" t="s">
-        <v>1002</v>
-      </c>
-      <c r="N91" s="18" t="s">
-        <v>1003</v>
-      </c>
-      <c r="O91" s="19" t="s">
-        <v>997</v>
-      </c>
-      <c r="P91" s="18" t="s">
-        <v>1004</v>
+        <v>1007</v>
+      </c>
+      <c r="J91" s="17" t="s">
+        <v>1008</v>
+      </c>
+      <c r="K91" s="17" t="s">
+        <v>1009</v>
+      </c>
+      <c r="L91" s="18" t="s">
+        <v>1010</v>
+      </c>
+      <c r="M91" s="17" t="s">
+        <v>1011</v>
+      </c>
+      <c r="N91" s="17" t="s">
+        <v>1012</v>
+      </c>
+      <c r="O91" s="18" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P91" s="17" t="s">
+        <v>1013</v>
       </c>
     </row>
     <row r="92" ht="50.25" spans="1:16">
       <c r="A92" t="s">
-        <v>1005</v>
+        <v>1014</v>
       </c>
       <c r="B92" s="5"/>
       <c r="C92" s="8">
         <v>59128</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>1006</v>
-      </c>
-      <c r="E92" s="20" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E92" s="19" t="s">
         <v>84</v>
       </c>
       <c r="F92" s="4" t="s">
         <v>85</v>
       </c>
       <c r="G92" s="4"/>
-      <c r="H92" s="17" t="s">
-        <v>601</v>
+      <c r="H92" s="14" t="s">
+        <v>868</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>1007</v>
-      </c>
-      <c r="J92" s="18" t="s">
-        <v>1008</v>
-      </c>
-      <c r="K92" s="18" t="s">
-        <v>1009</v>
-      </c>
-      <c r="L92" s="19" t="s">
-        <v>1010</v>
-      </c>
-      <c r="M92" s="18" t="s">
-        <v>1011</v>
-      </c>
-      <c r="N92" s="18" t="s">
-        <v>1012</v>
-      </c>
-      <c r="O92" s="19" t="s">
-        <v>1006</v>
-      </c>
-      <c r="P92" s="18" t="s">
-        <v>1013</v>
+        <v>1016</v>
+      </c>
+      <c r="J92" s="17" t="s">
+        <v>1017</v>
+      </c>
+      <c r="K92" s="17" t="s">
+        <v>1018</v>
+      </c>
+      <c r="L92" s="18" t="s">
+        <v>1019</v>
+      </c>
+      <c r="M92" s="17" t="s">
+        <v>1020</v>
+      </c>
+      <c r="N92" s="17" t="s">
+        <v>1021</v>
+      </c>
+      <c r="O92" s="18" t="s">
+        <v>1015</v>
+      </c>
+      <c r="P92" s="17" t="s">
+        <v>1022</v>
       </c>
     </row>
     <row r="93" ht="43.5" spans="1:16">
       <c r="A93" t="s">
-        <v>1014</v>
+        <v>1023</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>1015</v>
-      </c>
-      <c r="C93" s="21">
+        <v>1024</v>
+      </c>
+      <c r="C93" s="20">
         <v>61813</v>
       </c>
       <c r="D93" t="s">
-        <v>1016</v>
+        <v>1025</v>
       </c>
       <c r="E93" s="4" t="s">
         <v>21</v>
@@ -15477,46 +16013,46 @@
       <c r="F93" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H93" s="17" t="s">
-        <v>601</v>
+      <c r="H93" s="14" t="s">
+        <v>868</v>
       </c>
       <c r="I93" t="s">
-        <v>1017</v>
+        <v>1026</v>
       </c>
       <c r="J93" t="s">
-        <v>1018</v>
-      </c>
-      <c r="K93" s="22" t="s">
-        <v>1019</v>
-      </c>
-      <c r="L93" s="22" t="s">
-        <v>1020</v>
-      </c>
-      <c r="M93" s="22" t="s">
-        <v>1021</v>
-      </c>
-      <c r="N93" s="22" t="s">
-        <v>1022</v>
-      </c>
-      <c r="O93" s="22" t="s">
-        <v>1023</v>
-      </c>
-      <c r="P93" s="22" t="s">
-        <v>1024</v>
+        <v>1027</v>
+      </c>
+      <c r="K93" s="21" t="s">
+        <v>1028</v>
+      </c>
+      <c r="L93" s="21" t="s">
+        <v>1029</v>
+      </c>
+      <c r="M93" s="21" t="s">
+        <v>1030</v>
+      </c>
+      <c r="N93" s="21" t="s">
+        <v>1031</v>
+      </c>
+      <c r="O93" s="21" t="s">
+        <v>1032</v>
+      </c>
+      <c r="P93" s="21" t="s">
+        <v>1033</v>
       </c>
     </row>
     <row r="94" ht="43.5" spans="1:16">
       <c r="A94" t="s">
-        <v>1025</v>
+        <v>1034</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>1026</v>
-      </c>
-      <c r="C94" s="21">
+        <v>1035</v>
+      </c>
+      <c r="C94" s="20">
         <v>61812</v>
       </c>
       <c r="D94" t="s">
-        <v>1027</v>
+        <v>1036</v>
       </c>
       <c r="E94" s="4" t="s">
         <v>21</v>
@@ -15524,46 +16060,46 @@
       <c r="F94" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H94" s="17" t="s">
+      <c r="H94" s="14" t="s">
         <v>601</v>
       </c>
       <c r="I94" t="s">
-        <v>1028</v>
+        <v>1037</v>
       </c>
       <c r="J94" t="s">
-        <v>1029</v>
-      </c>
-      <c r="K94" s="22" t="s">
-        <v>1030</v>
-      </c>
-      <c r="L94" s="22" t="s">
-        <v>1031</v>
-      </c>
-      <c r="M94" s="22" t="s">
-        <v>1032</v>
-      </c>
-      <c r="N94" s="22" t="s">
-        <v>1033</v>
-      </c>
-      <c r="O94" s="22" t="s">
-        <v>1034</v>
-      </c>
-      <c r="P94" s="22" t="s">
-        <v>1035</v>
+        <v>1038</v>
+      </c>
+      <c r="K94" s="21" t="s">
+        <v>1039</v>
+      </c>
+      <c r="L94" s="21" t="s">
+        <v>1040</v>
+      </c>
+      <c r="M94" s="21" t="s">
+        <v>1041</v>
+      </c>
+      <c r="N94" s="21" t="s">
+        <v>1042</v>
+      </c>
+      <c r="O94" s="21" t="s">
+        <v>1043</v>
+      </c>
+      <c r="P94" s="21" t="s">
+        <v>1044</v>
       </c>
     </row>
     <row r="95" ht="43.5" spans="1:16">
       <c r="A95" t="s">
-        <v>1036</v>
+        <v>1045</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>1037</v>
-      </c>
-      <c r="C95" s="21">
+        <v>1046</v>
+      </c>
+      <c r="C95" s="20">
         <v>61818</v>
       </c>
       <c r="D95" t="s">
-        <v>1038</v>
+        <v>1047</v>
       </c>
       <c r="E95" s="4" t="s">
         <v>21</v>
@@ -15571,46 +16107,46 @@
       <c r="F95" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="H95" s="17" t="s">
+      <c r="H95" s="14" t="s">
         <v>601</v>
       </c>
       <c r="I95" t="s">
-        <v>1039</v>
+        <v>1048</v>
       </c>
       <c r="J95" t="s">
-        <v>1040</v>
-      </c>
-      <c r="K95" s="22" t="s">
-        <v>1041</v>
-      </c>
-      <c r="L95" s="22" t="s">
-        <v>1042</v>
-      </c>
-      <c r="M95" s="22" t="s">
-        <v>1043</v>
-      </c>
-      <c r="N95" s="22" t="s">
-        <v>1044</v>
-      </c>
-      <c r="O95" s="22" t="s">
-        <v>1045</v>
-      </c>
-      <c r="P95" s="22" t="s">
-        <v>1046</v>
+        <v>1049</v>
+      </c>
+      <c r="K95" s="21" t="s">
+        <v>1050</v>
+      </c>
+      <c r="L95" s="21" t="s">
+        <v>1051</v>
+      </c>
+      <c r="M95" s="21" t="s">
+        <v>1052</v>
+      </c>
+      <c r="N95" s="21" t="s">
+        <v>1053</v>
+      </c>
+      <c r="O95" s="21" t="s">
+        <v>1054</v>
+      </c>
+      <c r="P95" s="21" t="s">
+        <v>1055</v>
       </c>
     </row>
     <row r="96" ht="43.5" spans="1:16">
       <c r="A96" t="s">
-        <v>1047</v>
+        <v>1056</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>1048</v>
-      </c>
-      <c r="C96" s="21">
+        <v>1057</v>
+      </c>
+      <c r="C96" s="20">
         <v>61815</v>
       </c>
       <c r="D96" t="s">
-        <v>1049</v>
+        <v>1058</v>
       </c>
       <c r="E96" s="4" t="s">
         <v>21</v>
@@ -15618,46 +16154,46 @@
       <c r="F96" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="H96" s="17" t="s">
+      <c r="H96" s="14" t="s">
         <v>601</v>
       </c>
       <c r="I96" t="s">
-        <v>1050</v>
+        <v>1059</v>
       </c>
       <c r="J96" t="s">
-        <v>1051</v>
-      </c>
-      <c r="K96" s="22" t="s">
-        <v>1052</v>
-      </c>
-      <c r="L96" s="22" t="s">
-        <v>1053</v>
-      </c>
-      <c r="M96" s="22" t="s">
-        <v>1054</v>
-      </c>
-      <c r="N96" s="22" t="s">
-        <v>1055</v>
-      </c>
-      <c r="O96" s="22" t="s">
-        <v>1056</v>
-      </c>
-      <c r="P96" s="22" t="s">
-        <v>1057</v>
+        <v>1060</v>
+      </c>
+      <c r="K96" s="21" t="s">
+        <v>1061</v>
+      </c>
+      <c r="L96" s="21" t="s">
+        <v>1062</v>
+      </c>
+      <c r="M96" s="21" t="s">
+        <v>1063</v>
+      </c>
+      <c r="N96" s="21" t="s">
+        <v>1064</v>
+      </c>
+      <c r="O96" s="21" t="s">
+        <v>1065</v>
+      </c>
+      <c r="P96" s="21" t="s">
+        <v>1066</v>
       </c>
     </row>
     <row r="97" ht="43.5" spans="1:16">
       <c r="A97" t="s">
-        <v>1058</v>
+        <v>1067</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>1059</v>
-      </c>
-      <c r="C97" s="21">
+        <v>1068</v>
+      </c>
+      <c r="C97" s="20">
         <v>61814</v>
       </c>
       <c r="D97" t="s">
-        <v>1060</v>
+        <v>1069</v>
       </c>
       <c r="E97" s="4" t="s">
         <v>21</v>
@@ -15665,46 +16201,46 @@
       <c r="F97" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="H97" s="17" t="s">
+      <c r="H97" s="14" t="s">
         <v>601</v>
       </c>
       <c r="I97" t="s">
-        <v>1061</v>
+        <v>1070</v>
       </c>
       <c r="J97" t="s">
-        <v>1062</v>
-      </c>
-      <c r="K97" s="22" t="s">
-        <v>1063</v>
-      </c>
-      <c r="L97" s="22" t="s">
-        <v>1064</v>
-      </c>
-      <c r="M97" s="22" t="s">
-        <v>1065</v>
-      </c>
-      <c r="N97" s="22" t="s">
-        <v>1066</v>
-      </c>
-      <c r="O97" s="22" t="s">
-        <v>1067</v>
-      </c>
-      <c r="P97" s="22" t="s">
-        <v>1068</v>
+        <v>1071</v>
+      </c>
+      <c r="K97" s="21" t="s">
+        <v>1072</v>
+      </c>
+      <c r="L97" s="21" t="s">
+        <v>1073</v>
+      </c>
+      <c r="M97" s="21" t="s">
+        <v>1074</v>
+      </c>
+      <c r="N97" s="21" t="s">
+        <v>1075</v>
+      </c>
+      <c r="O97" s="21" t="s">
+        <v>1076</v>
+      </c>
+      <c r="P97" s="21" t="s">
+        <v>1077</v>
       </c>
     </row>
     <row r="98" ht="43.5" spans="1:16">
       <c r="A98" t="s">
-        <v>1069</v>
+        <v>1078</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>1070</v>
-      </c>
-      <c r="C98" s="21">
+        <v>1079</v>
+      </c>
+      <c r="C98" s="20">
         <v>61817</v>
       </c>
       <c r="D98" t="s">
-        <v>1071</v>
+        <v>1080</v>
       </c>
       <c r="E98" s="4" t="s">
         <v>21</v>
@@ -15712,46 +16248,46 @@
       <c r="F98" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="H98" s="17" t="s">
+      <c r="H98" s="14" t="s">
         <v>601</v>
       </c>
       <c r="I98" t="s">
-        <v>1072</v>
+        <v>1081</v>
       </c>
       <c r="J98" t="s">
-        <v>1073</v>
-      </c>
-      <c r="K98" s="22" t="s">
-        <v>1074</v>
-      </c>
-      <c r="L98" s="22" t="s">
-        <v>1075</v>
-      </c>
-      <c r="M98" s="22" t="s">
-        <v>1076</v>
-      </c>
-      <c r="N98" s="22" t="s">
-        <v>1077</v>
-      </c>
-      <c r="O98" s="22" t="s">
-        <v>1078</v>
-      </c>
-      <c r="P98" s="22" t="s">
-        <v>1079</v>
+        <v>1082</v>
+      </c>
+      <c r="K98" s="21" t="s">
+        <v>1083</v>
+      </c>
+      <c r="L98" s="21" t="s">
+        <v>1084</v>
+      </c>
+      <c r="M98" s="21" t="s">
+        <v>1085</v>
+      </c>
+      <c r="N98" s="21" t="s">
+        <v>1086</v>
+      </c>
+      <c r="O98" s="21" t="s">
+        <v>1087</v>
+      </c>
+      <c r="P98" s="21" t="s">
+        <v>1088</v>
       </c>
     </row>
     <row r="99" ht="43.5" spans="1:16">
       <c r="A99" t="s">
-        <v>1080</v>
+        <v>1089</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>1081</v>
-      </c>
-      <c r="C99" s="21">
+        <v>1090</v>
+      </c>
+      <c r="C99" s="20">
         <v>61816</v>
       </c>
       <c r="D99" t="s">
-        <v>1082</v>
+        <v>1091</v>
       </c>
       <c r="E99" s="4" t="s">
         <v>21</v>
@@ -15759,281 +16295,281 @@
       <c r="F99" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H99" s="17" t="s">
+      <c r="H99" s="14" t="s">
         <v>601</v>
       </c>
       <c r="I99" t="s">
-        <v>1083</v>
+        <v>1092</v>
       </c>
       <c r="J99" t="s">
-        <v>1084</v>
-      </c>
-      <c r="K99" s="22" t="s">
-        <v>1085</v>
-      </c>
-      <c r="L99" s="22" t="s">
-        <v>1086</v>
-      </c>
-      <c r="M99" s="22" t="s">
-        <v>1087</v>
-      </c>
-      <c r="N99" s="22" t="s">
-        <v>1088</v>
-      </c>
-      <c r="O99" s="22" t="s">
-        <v>1089</v>
-      </c>
-      <c r="P99" s="22" t="s">
-        <v>1090</v>
+        <v>1093</v>
+      </c>
+      <c r="K99" s="21" t="s">
+        <v>1094</v>
+      </c>
+      <c r="L99" s="21" t="s">
+        <v>1095</v>
+      </c>
+      <c r="M99" s="21" t="s">
+        <v>1096</v>
+      </c>
+      <c r="N99" s="21" t="s">
+        <v>1097</v>
+      </c>
+      <c r="O99" s="21" t="s">
+        <v>1098</v>
+      </c>
+      <c r="P99" s="21" t="s">
+        <v>1099</v>
       </c>
     </row>
     <row r="100" ht="43.5" spans="1:16">
       <c r="A100" t="s">
-        <v>1091</v>
+        <v>1100</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>1092</v>
-      </c>
-      <c r="C100" s="21">
+        <v>1101</v>
+      </c>
+      <c r="C100" s="20">
         <v>61827</v>
       </c>
       <c r="D100" t="s">
-        <v>1093</v>
+        <v>1102</v>
       </c>
       <c r="E100" t="s">
-        <v>1094</v>
+        <v>1103</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="H100" s="17" t="s">
+      <c r="H100" s="14" t="s">
         <v>601</v>
       </c>
       <c r="I100" t="s">
-        <v>1095</v>
+        <v>1104</v>
       </c>
       <c r="J100" t="s">
-        <v>1096</v>
-      </c>
-      <c r="K100" s="22" t="s">
-        <v>1097</v>
-      </c>
-      <c r="L100" s="22" t="s">
-        <v>1098</v>
-      </c>
-      <c r="M100" s="22" t="s">
-        <v>1099</v>
-      </c>
-      <c r="N100" s="22" t="s">
-        <v>1100</v>
-      </c>
-      <c r="O100" s="22" t="s">
-        <v>1101</v>
-      </c>
-      <c r="P100" s="22" t="s">
-        <v>1102</v>
+        <v>1105</v>
+      </c>
+      <c r="K100" s="21" t="s">
+        <v>1106</v>
+      </c>
+      <c r="L100" s="21" t="s">
+        <v>1107</v>
+      </c>
+      <c r="M100" s="21" t="s">
+        <v>1108</v>
+      </c>
+      <c r="N100" s="21" t="s">
+        <v>1109</v>
+      </c>
+      <c r="O100" s="21" t="s">
+        <v>1110</v>
+      </c>
+      <c r="P100" s="21" t="s">
+        <v>1111</v>
       </c>
     </row>
     <row r="101" ht="43.5" spans="1:16">
       <c r="A101" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C101" s="20">
+        <v>61829</v>
+      </c>
+      <c r="D101" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E101" t="s">
         <v>1103</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>1104</v>
-      </c>
-      <c r="C101" s="21">
-        <v>61829</v>
-      </c>
-      <c r="D101" t="s">
-        <v>1105</v>
-      </c>
-      <c r="E101" t="s">
-        <v>1094</v>
       </c>
       <c r="F101" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H101" s="17" t="s">
+      <c r="H101" s="14" t="s">
         <v>601</v>
       </c>
       <c r="I101" t="s">
-        <v>1106</v>
+        <v>1115</v>
       </c>
       <c r="J101" t="s">
-        <v>1107</v>
-      </c>
-      <c r="K101" s="22" t="s">
-        <v>1108</v>
-      </c>
-      <c r="L101" s="22" t="s">
-        <v>1109</v>
-      </c>
-      <c r="M101" s="22" t="s">
-        <v>1110</v>
-      </c>
-      <c r="N101" s="22" t="s">
-        <v>1111</v>
-      </c>
-      <c r="O101" s="22" t="s">
-        <v>1112</v>
-      </c>
-      <c r="P101" s="22" t="s">
-        <v>1113</v>
+        <v>1116</v>
+      </c>
+      <c r="K101" s="21" t="s">
+        <v>1117</v>
+      </c>
+      <c r="L101" s="21" t="s">
+        <v>1118</v>
+      </c>
+      <c r="M101" s="21" t="s">
+        <v>1119</v>
+      </c>
+      <c r="N101" s="21" t="s">
+        <v>1120</v>
+      </c>
+      <c r="O101" s="21" t="s">
+        <v>1121</v>
+      </c>
+      <c r="P101" s="21" t="s">
+        <v>1122</v>
       </c>
     </row>
     <row r="102" ht="43.5" spans="1:16">
       <c r="A102" t="s">
-        <v>1114</v>
+        <v>1123</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>1115</v>
-      </c>
-      <c r="C102" s="21">
+        <v>1124</v>
+      </c>
+      <c r="C102" s="20">
         <v>61831</v>
       </c>
       <c r="D102" t="s">
-        <v>1116</v>
+        <v>1125</v>
       </c>
       <c r="E102" t="s">
-        <v>1094</v>
+        <v>1103</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="H102" s="17" t="s">
+      <c r="H102" s="14" t="s">
         <v>601</v>
       </c>
       <c r="I102" t="s">
-        <v>1117</v>
+        <v>1126</v>
       </c>
       <c r="J102" t="s">
-        <v>1118</v>
-      </c>
-      <c r="K102" s="22" t="s">
-        <v>1119</v>
-      </c>
-      <c r="L102" s="22" t="s">
-        <v>1120</v>
-      </c>
-      <c r="M102" s="22" t="s">
-        <v>1121</v>
-      </c>
-      <c r="N102" s="22" t="s">
-        <v>1122</v>
-      </c>
-      <c r="O102" s="22" t="s">
-        <v>1123</v>
-      </c>
-      <c r="P102" s="22" t="s">
-        <v>1124</v>
+        <v>1127</v>
+      </c>
+      <c r="K102" s="21" t="s">
+        <v>1128</v>
+      </c>
+      <c r="L102" s="21" t="s">
+        <v>1129</v>
+      </c>
+      <c r="M102" s="21" t="s">
+        <v>1130</v>
+      </c>
+      <c r="N102" s="21" t="s">
+        <v>1131</v>
+      </c>
+      <c r="O102" s="21" t="s">
+        <v>1132</v>
+      </c>
+      <c r="P102" s="21" t="s">
+        <v>1133</v>
       </c>
     </row>
     <row r="103" ht="43.5" spans="1:16">
       <c r="A103" t="s">
-        <v>1125</v>
+        <v>1134</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>1126</v>
-      </c>
-      <c r="C103" s="21">
+        <v>1135</v>
+      </c>
+      <c r="C103" s="20">
         <v>61830</v>
       </c>
       <c r="D103" t="s">
-        <v>1127</v>
+        <v>1136</v>
       </c>
       <c r="E103" t="s">
-        <v>1094</v>
+        <v>1103</v>
       </c>
       <c r="F103" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="H103" s="17" t="s">
+      <c r="H103" s="14" t="s">
         <v>601</v>
       </c>
       <c r="I103" t="s">
-        <v>1128</v>
+        <v>1137</v>
       </c>
       <c r="J103" t="s">
-        <v>1129</v>
-      </c>
-      <c r="K103" s="22" t="s">
-        <v>1130</v>
-      </c>
-      <c r="L103" s="22" t="s">
-        <v>1131</v>
-      </c>
-      <c r="M103" s="22" t="s">
-        <v>1132</v>
-      </c>
-      <c r="N103" s="22" t="s">
-        <v>1133</v>
-      </c>
-      <c r="O103" s="22" t="s">
-        <v>1134</v>
-      </c>
-      <c r="P103" s="22" t="s">
-        <v>1135</v>
+        <v>1138</v>
+      </c>
+      <c r="K103" s="21" t="s">
+        <v>1139</v>
+      </c>
+      <c r="L103" s="21" t="s">
+        <v>1140</v>
+      </c>
+      <c r="M103" s="21" t="s">
+        <v>1141</v>
+      </c>
+      <c r="N103" s="21" t="s">
+        <v>1142</v>
+      </c>
+      <c r="O103" s="21" t="s">
+        <v>1143</v>
+      </c>
+      <c r="P103" s="21" t="s">
+        <v>1144</v>
       </c>
     </row>
     <row r="104" ht="43.5" spans="1:16">
       <c r="A104" t="s">
-        <v>1136</v>
+        <v>1145</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>1137</v>
-      </c>
-      <c r="C104" s="21">
+        <v>1146</v>
+      </c>
+      <c r="C104" s="20">
         <v>61828</v>
       </c>
       <c r="D104" t="s">
-        <v>1138</v>
+        <v>1147</v>
       </c>
       <c r="E104" t="s">
-        <v>1094</v>
+        <v>1103</v>
       </c>
       <c r="F104" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="H104" s="17" t="s">
+      <c r="H104" s="14" t="s">
         <v>601</v>
       </c>
       <c r="I104" t="s">
-        <v>1139</v>
+        <v>1148</v>
       </c>
       <c r="J104" t="s">
-        <v>1140</v>
-      </c>
-      <c r="K104" s="22" t="s">
-        <v>1141</v>
-      </c>
-      <c r="L104" s="22" t="s">
-        <v>1142</v>
-      </c>
-      <c r="M104" s="22" t="s">
-        <v>1143</v>
-      </c>
-      <c r="N104" s="22" t="s">
-        <v>1144</v>
-      </c>
-      <c r="O104" s="22" t="s">
-        <v>1145</v>
-      </c>
-      <c r="P104" s="22" t="s">
-        <v>1146</v>
+        <v>1149</v>
+      </c>
+      <c r="K104" s="21" t="s">
+        <v>1150</v>
+      </c>
+      <c r="L104" s="21" t="s">
+        <v>1151</v>
+      </c>
+      <c r="M104" s="21" t="s">
+        <v>1152</v>
+      </c>
+      <c r="N104" s="21" t="s">
+        <v>1153</v>
+      </c>
+      <c r="O104" s="21" t="s">
+        <v>1154</v>
+      </c>
+      <c r="P104" s="21" t="s">
+        <v>1155</v>
       </c>
     </row>
     <row r="105" ht="43.5" spans="1:16">
       <c r="A105" t="s">
-        <v>1147</v>
+        <v>1156</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>1148</v>
-      </c>
-      <c r="C105" s="21">
+        <v>1157</v>
+      </c>
+      <c r="C105" s="20">
         <v>62336</v>
       </c>
       <c r="D105" t="s">
-        <v>1149</v>
+        <v>1158</v>
       </c>
       <c r="E105" t="s">
         <v>500</v>
@@ -16041,46 +16577,46 @@
       <c r="F105" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="H105" s="17" t="s">
+      <c r="H105" s="14" t="s">
         <v>601</v>
       </c>
       <c r="I105" t="s">
-        <v>1150</v>
-      </c>
-      <c r="J105" s="23" t="s">
-        <v>1151</v>
-      </c>
-      <c r="K105" s="24" t="s">
-        <v>1152</v>
-      </c>
-      <c r="L105" s="24" t="s">
-        <v>1153</v>
-      </c>
-      <c r="M105" s="24" t="s">
-        <v>1154</v>
-      </c>
-      <c r="N105" s="24" t="s">
-        <v>1155</v>
-      </c>
-      <c r="O105" s="24" t="s">
-        <v>1156</v>
-      </c>
-      <c r="P105" s="24" t="s">
-        <v>1157</v>
+        <v>1159</v>
+      </c>
+      <c r="J105" s="22" t="s">
+        <v>1160</v>
+      </c>
+      <c r="K105" s="22" t="s">
+        <v>1161</v>
+      </c>
+      <c r="L105" s="22" t="s">
+        <v>1162</v>
+      </c>
+      <c r="M105" s="22" t="s">
+        <v>1163</v>
+      </c>
+      <c r="N105" s="22" t="s">
+        <v>1164</v>
+      </c>
+      <c r="O105" s="22" t="s">
+        <v>1165</v>
+      </c>
+      <c r="P105" s="22" t="s">
+        <v>1166</v>
       </c>
     </row>
     <row r="106" ht="43.5" spans="1:16">
       <c r="A106" t="s">
-        <v>1158</v>
+        <v>1167</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>1159</v>
-      </c>
-      <c r="C106" s="21">
+        <v>1168</v>
+      </c>
+      <c r="C106" s="20">
         <v>62338</v>
       </c>
-      <c r="D106" s="25" t="s">
-        <v>1160</v>
+      <c r="D106" s="23" t="s">
+        <v>1169</v>
       </c>
       <c r="E106" t="s">
         <v>500</v>
@@ -16088,47 +16624,46 @@
       <c r="F106" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G106"/>
-      <c r="H106" s="17" t="s">
+      <c r="H106" s="14" t="s">
         <v>601</v>
       </c>
       <c r="I106" t="s">
-        <v>1161</v>
-      </c>
-      <c r="J106" s="23" t="s">
-        <v>1162</v>
-      </c>
-      <c r="K106" s="24" t="s">
-        <v>1163</v>
-      </c>
-      <c r="L106" s="24" t="s">
-        <v>1164</v>
-      </c>
-      <c r="M106" s="24" t="s">
-        <v>1165</v>
-      </c>
-      <c r="N106" s="24" t="s">
-        <v>1166</v>
-      </c>
-      <c r="O106" s="24" t="s">
-        <v>1167</v>
-      </c>
-      <c r="P106" s="24" t="s">
-        <v>1168</v>
+        <v>1170</v>
+      </c>
+      <c r="J106" s="22" t="s">
+        <v>1171</v>
+      </c>
+      <c r="K106" s="22" t="s">
+        <v>1172</v>
+      </c>
+      <c r="L106" s="22" t="s">
+        <v>1173</v>
+      </c>
+      <c r="M106" s="22" t="s">
+        <v>1174</v>
+      </c>
+      <c r="N106" s="22" t="s">
+        <v>1175</v>
+      </c>
+      <c r="O106" s="22" t="s">
+        <v>1176</v>
+      </c>
+      <c r="P106" s="22" t="s">
+        <v>1177</v>
       </c>
     </row>
     <row r="107" ht="43.5" spans="1:16">
       <c r="A107" t="s">
-        <v>1169</v>
+        <v>1178</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>1170</v>
-      </c>
-      <c r="C107" s="21">
+        <v>1179</v>
+      </c>
+      <c r="C107" s="20">
         <v>62335</v>
       </c>
-      <c r="D107" s="26" t="s">
-        <v>1171</v>
+      <c r="D107" s="21" t="s">
+        <v>1180</v>
       </c>
       <c r="E107" t="s">
         <v>500</v>
@@ -16136,47 +16671,46 @@
       <c r="F107" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="G107"/>
-      <c r="H107" s="17" t="s">
+      <c r="H107" s="14" t="s">
         <v>601</v>
       </c>
       <c r="I107" t="s">
-        <v>1117</v>
-      </c>
-      <c r="J107" s="26" t="s">
-        <v>1172</v>
-      </c>
-      <c r="K107" s="24" t="s">
-        <v>1173</v>
-      </c>
-      <c r="L107" s="24" t="s">
-        <v>1174</v>
-      </c>
-      <c r="M107" s="24" t="s">
-        <v>1175</v>
-      </c>
-      <c r="N107" s="24" t="s">
-        <v>1176</v>
-      </c>
-      <c r="O107" s="24" t="s">
-        <v>1177</v>
-      </c>
-      <c r="P107" s="24" t="s">
-        <v>1178</v>
+        <v>1126</v>
+      </c>
+      <c r="J107" s="21" t="s">
+        <v>1181</v>
+      </c>
+      <c r="K107" s="22" t="s">
+        <v>1182</v>
+      </c>
+      <c r="L107" s="22" t="s">
+        <v>1183</v>
+      </c>
+      <c r="M107" s="22" t="s">
+        <v>1184</v>
+      </c>
+      <c r="N107" s="22" t="s">
+        <v>1185</v>
+      </c>
+      <c r="O107" s="22" t="s">
+        <v>1186</v>
+      </c>
+      <c r="P107" s="22" t="s">
+        <v>1187</v>
       </c>
     </row>
     <row r="108" ht="43.5" spans="1:16">
       <c r="A108" t="s">
-        <v>1179</v>
+        <v>1188</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>1180</v>
-      </c>
-      <c r="C108" s="21">
+        <v>1189</v>
+      </c>
+      <c r="C108" s="20">
         <v>62337</v>
       </c>
-      <c r="D108" s="26" t="s">
-        <v>1181</v>
+      <c r="D108" s="21" t="s">
+        <v>1190</v>
       </c>
       <c r="E108" t="s">
         <v>500</v>
@@ -16184,47 +16718,46 @@
       <c r="F108" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G108"/>
-      <c r="H108" s="17" t="s">
+      <c r="H108" s="14" t="s">
         <v>601</v>
       </c>
       <c r="I108" t="s">
-        <v>1182</v>
-      </c>
-      <c r="J108" s="23" t="s">
-        <v>1183</v>
-      </c>
-      <c r="K108" s="24" t="s">
-        <v>1184</v>
-      </c>
-      <c r="L108" s="24" t="s">
-        <v>1185</v>
-      </c>
-      <c r="M108" s="24" t="s">
-        <v>1186</v>
-      </c>
-      <c r="N108" s="24" t="s">
-        <v>1187</v>
-      </c>
-      <c r="O108" s="24" t="s">
-        <v>1188</v>
-      </c>
-      <c r="P108" s="24" t="s">
-        <v>1189</v>
+        <v>1191</v>
+      </c>
+      <c r="J108" s="22" t="s">
+        <v>1192</v>
+      </c>
+      <c r="K108" s="22" t="s">
+        <v>1193</v>
+      </c>
+      <c r="L108" s="22" t="s">
+        <v>1194</v>
+      </c>
+      <c r="M108" s="22" t="s">
+        <v>1195</v>
+      </c>
+      <c r="N108" s="22" t="s">
+        <v>1196</v>
+      </c>
+      <c r="O108" s="22" t="s">
+        <v>1197</v>
+      </c>
+      <c r="P108" s="22" t="s">
+        <v>1198</v>
       </c>
     </row>
     <row r="109" ht="43.5" spans="1:16">
       <c r="A109" t="s">
-        <v>1190</v>
+        <v>1199</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>1191</v>
-      </c>
-      <c r="C109" s="21">
+        <v>1200</v>
+      </c>
+      <c r="C109" s="20">
         <v>62339</v>
       </c>
-      <c r="D109" s="26" t="s">
-        <v>1192</v>
+      <c r="D109" s="21" t="s">
+        <v>1201</v>
       </c>
       <c r="E109" t="s">
         <v>500</v>
@@ -16232,281 +16765,1008 @@
       <c r="F109" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="G109"/>
-      <c r="H109" s="17" t="s">
+      <c r="H109" s="14" t="s">
         <v>601</v>
       </c>
       <c r="I109" t="s">
-        <v>1193</v>
-      </c>
-      <c r="J109" s="23" t="s">
-        <v>1194</v>
-      </c>
-      <c r="K109" s="24" t="s">
-        <v>1195</v>
-      </c>
-      <c r="L109" s="24" t="s">
-        <v>1196</v>
-      </c>
-      <c r="M109" s="24" t="s">
-        <v>1197</v>
-      </c>
-      <c r="N109" s="24" t="s">
-        <v>1198</v>
-      </c>
-      <c r="O109" s="24" t="s">
-        <v>1199</v>
-      </c>
-      <c r="P109" s="24" t="s">
-        <v>1200</v>
+        <v>1202</v>
+      </c>
+      <c r="J109" s="22" t="s">
+        <v>1203</v>
+      </c>
+      <c r="K109" s="22" t="s">
+        <v>1204</v>
+      </c>
+      <c r="L109" s="22" t="s">
+        <v>1205</v>
+      </c>
+      <c r="M109" s="22" t="s">
+        <v>1206</v>
+      </c>
+      <c r="N109" s="22" t="s">
+        <v>1207</v>
+      </c>
+      <c r="O109" s="22" t="s">
+        <v>1208</v>
+      </c>
+      <c r="P109" s="22" t="s">
+        <v>1209</v>
       </c>
     </row>
     <row r="110" ht="43.5" spans="1:16">
       <c r="A110" t="s">
-        <v>1201</v>
+        <v>1210</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>1202</v>
-      </c>
-      <c r="C110" s="21">
+        <v>1211</v>
+      </c>
+      <c r="C110" s="20">
         <v>62381</v>
       </c>
       <c r="D110" t="s">
-        <v>1203</v>
+        <v>1212</v>
       </c>
       <c r="E110" t="s">
-        <v>1204</v>
+        <v>1213</v>
       </c>
       <c r="F110" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H110" s="17" t="s">
+      <c r="H110" s="14" t="s">
         <v>601</v>
       </c>
       <c r="I110" t="s">
-        <v>1205</v>
-      </c>
-      <c r="J110" s="26" t="s">
-        <v>1206</v>
-      </c>
-      <c r="K110" s="22" t="s">
-        <v>1207</v>
-      </c>
-      <c r="L110" s="22" t="s">
-        <v>1208</v>
-      </c>
-      <c r="M110" s="22" t="s">
-        <v>1209</v>
-      </c>
-      <c r="N110" s="22" t="s">
-        <v>1210</v>
-      </c>
-      <c r="O110" s="22" t="s">
-        <v>1211</v>
-      </c>
-      <c r="P110" s="22" t="s">
-        <v>1212</v>
+        <v>1214</v>
+      </c>
+      <c r="J110" s="21" t="s">
+        <v>1215</v>
+      </c>
+      <c r="K110" s="21" t="s">
+        <v>1216</v>
+      </c>
+      <c r="L110" s="21" t="s">
+        <v>1217</v>
+      </c>
+      <c r="M110" s="21" t="s">
+        <v>1218</v>
+      </c>
+      <c r="N110" s="21" t="s">
+        <v>1219</v>
+      </c>
+      <c r="O110" s="21" t="s">
+        <v>1220</v>
+      </c>
+      <c r="P110" s="21" t="s">
+        <v>1221</v>
       </c>
     </row>
     <row r="111" ht="43.5" spans="1:16">
       <c r="A111" t="s">
-        <v>1213</v>
+        <v>1222</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>1214</v>
+        <v>1223</v>
       </c>
       <c r="C111">
         <v>62380</v>
       </c>
       <c r="D111" t="s">
-        <v>1215</v>
+        <v>1224</v>
       </c>
       <c r="E111" t="s">
-        <v>1204</v>
+        <v>1213</v>
       </c>
       <c r="F111" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="H111" s="17" t="s">
+      <c r="H111" s="14" t="s">
         <v>601</v>
       </c>
       <c r="I111" t="s">
-        <v>1216</v>
-      </c>
-      <c r="J111" s="27" t="s">
-        <v>1217</v>
-      </c>
-      <c r="K111" s="22" t="s">
-        <v>1218</v>
-      </c>
-      <c r="L111" s="22" t="s">
-        <v>1219</v>
-      </c>
-      <c r="M111" s="22" t="s">
-        <v>1220</v>
-      </c>
-      <c r="N111" s="22" t="s">
-        <v>1221</v>
-      </c>
-      <c r="O111" s="22" t="s">
-        <v>1222</v>
-      </c>
-      <c r="P111" s="22" t="s">
-        <v>1223</v>
+        <v>1225</v>
+      </c>
+      <c r="J111" s="21" t="s">
+        <v>1226</v>
+      </c>
+      <c r="K111" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="L111" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="M111" s="21" t="s">
+        <v>1229</v>
+      </c>
+      <c r="N111" s="21" t="s">
+        <v>1230</v>
+      </c>
+      <c r="O111" s="21" t="s">
+        <v>1231</v>
+      </c>
+      <c r="P111" s="21" t="s">
+        <v>1232</v>
       </c>
     </row>
     <row r="112" ht="43.5" spans="1:16">
       <c r="A112" t="s">
-        <v>1224</v>
+        <v>1233</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>1225</v>
-      </c>
-      <c r="C112" s="21">
+        <v>1234</v>
+      </c>
+      <c r="C112" s="20">
         <v>62378</v>
       </c>
       <c r="D112" t="s">
-        <v>1226</v>
+        <v>1235</v>
       </c>
       <c r="E112" t="s">
-        <v>1204</v>
+        <v>1213</v>
       </c>
       <c r="F112" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="H112" s="17" t="s">
+      <c r="H112" s="14" t="s">
         <v>601</v>
       </c>
       <c r="I112" t="s">
-        <v>1227</v>
-      </c>
-      <c r="J112" s="27" t="s">
-        <v>1228</v>
-      </c>
-      <c r="K112" s="22" t="s">
-        <v>1229</v>
-      </c>
-      <c r="L112" s="22" t="s">
-        <v>1230</v>
-      </c>
-      <c r="M112" s="22" t="s">
-        <v>1231</v>
-      </c>
-      <c r="N112" s="22" t="s">
-        <v>1232</v>
-      </c>
-      <c r="O112" s="22" t="s">
-        <v>1233</v>
-      </c>
-      <c r="P112" s="22" t="s">
-        <v>1234</v>
+        <v>1236</v>
+      </c>
+      <c r="J112" s="21" t="s">
+        <v>1237</v>
+      </c>
+      <c r="K112" s="21" t="s">
+        <v>1238</v>
+      </c>
+      <c r="L112" s="21" t="s">
+        <v>1239</v>
+      </c>
+      <c r="M112" s="21" t="s">
+        <v>1240</v>
+      </c>
+      <c r="N112" s="21" t="s">
+        <v>1241</v>
+      </c>
+      <c r="O112" s="21" t="s">
+        <v>1242</v>
+      </c>
+      <c r="P112" s="21" t="s">
+        <v>1243</v>
       </c>
     </row>
     <row r="113" ht="43.5" spans="1:16">
       <c r="A113" t="s">
-        <v>1235</v>
+        <v>1244</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>1236</v>
-      </c>
-      <c r="C113" s="21">
+        <v>1245</v>
+      </c>
+      <c r="C113" s="20">
         <v>62379</v>
       </c>
       <c r="D113" t="s">
-        <v>1237</v>
+        <v>1246</v>
       </c>
       <c r="E113" t="s">
-        <v>1204</v>
+        <v>1213</v>
       </c>
       <c r="F113" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H113" s="17" t="s">
+      <c r="H113" s="14" t="s">
         <v>601</v>
       </c>
       <c r="I113" t="s">
-        <v>1238</v>
-      </c>
-      <c r="J113" s="27" t="s">
-        <v>1239</v>
-      </c>
-      <c r="K113" s="22" t="s">
-        <v>1240</v>
-      </c>
-      <c r="L113" s="22" t="s">
-        <v>1241</v>
-      </c>
-      <c r="M113" s="22" t="s">
-        <v>1242</v>
-      </c>
-      <c r="N113" s="22" t="s">
-        <v>1243</v>
-      </c>
-      <c r="O113" s="22" t="s">
-        <v>1244</v>
-      </c>
-      <c r="P113" s="22" t="s">
-        <v>1245</v>
+        <v>1247</v>
+      </c>
+      <c r="J113" s="21" t="s">
+        <v>1248</v>
+      </c>
+      <c r="K113" s="21" t="s">
+        <v>1249</v>
+      </c>
+      <c r="L113" s="21" t="s">
+        <v>1250</v>
+      </c>
+      <c r="M113" s="21" t="s">
+        <v>1251</v>
+      </c>
+      <c r="N113" s="21" t="s">
+        <v>1252</v>
+      </c>
+      <c r="O113" s="21" t="s">
+        <v>1253</v>
+      </c>
+      <c r="P113" s="21" t="s">
+        <v>1254</v>
       </c>
     </row>
     <row r="114" ht="43.5" spans="1:16">
       <c r="A114" t="s">
-        <v>1246</v>
+        <v>1255</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>1247</v>
-      </c>
-      <c r="C114" s="21">
+        <v>1256</v>
+      </c>
+      <c r="C114" s="20">
         <v>62382</v>
       </c>
       <c r="D114" t="s">
-        <v>1248</v>
+        <v>1257</v>
       </c>
       <c r="E114" t="s">
-        <v>1204</v>
+        <v>1213</v>
       </c>
       <c r="F114" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H114" s="17" t="s">
+      <c r="H114" s="14" t="s">
         <v>601</v>
       </c>
       <c r="I114" t="s">
-        <v>1249</v>
-      </c>
-      <c r="J114" s="27" t="s">
-        <v>1250</v>
-      </c>
-      <c r="K114" s="22" t="s">
-        <v>1251</v>
-      </c>
-      <c r="L114" s="22" t="s">
-        <v>1252</v>
-      </c>
-      <c r="M114" s="22" t="s">
-        <v>1253</v>
-      </c>
-      <c r="N114" s="22" t="s">
-        <v>1254</v>
-      </c>
-      <c r="O114" s="22" t="s">
-        <v>1255</v>
-      </c>
-      <c r="P114" s="22" t="s">
-        <v>1256</v>
+        <v>1258</v>
+      </c>
+      <c r="J114" s="21" t="s">
+        <v>1259</v>
+      </c>
+      <c r="K114" s="21" t="s">
+        <v>1260</v>
+      </c>
+      <c r="L114" s="21" t="s">
+        <v>1261</v>
+      </c>
+      <c r="M114" s="21" t="s">
+        <v>1262</v>
+      </c>
+      <c r="N114" s="21" t="s">
+        <v>1263</v>
+      </c>
+      <c r="O114" s="21" t="s">
+        <v>1264</v>
+      </c>
+      <c r="P114" s="21" t="s">
+        <v>1265</v>
       </c>
     </row>
-    <row r="115" ht="16.5" spans="1:16">
-      <c r="F115" s="4"/>
+    <row r="115" ht="43.5" spans="1:16">
+      <c r="B115" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C115" s="20">
+        <v>63158</v>
+      </c>
+      <c r="D115" t="s">
+        <v>1267</v>
+      </c>
+      <c r="E115" t="s">
+        <v>233</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H115" s="24" t="s">
+        <v>868</v>
+      </c>
+      <c r="I115" s="25" t="s">
+        <v>1268</v>
+      </c>
+      <c r="J115" s="26" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K115" s="26" t="s">
+        <v>1270</v>
+      </c>
+      <c r="L115" s="26" t="s">
+        <v>1271</v>
+      </c>
+      <c r="M115" s="26" t="s">
+        <v>1272</v>
+      </c>
+      <c r="N115" s="26" t="s">
+        <v>1273</v>
+      </c>
+      <c r="O115" s="26" t="s">
+        <v>1274</v>
+      </c>
+      <c r="P115" s="26" t="s">
+        <v>1275</v>
+      </c>
     </row>
-    <row r="116" ht="16.5" spans="1:16">
-      <c r="F116" s="4"/>
+    <row r="116" ht="43.5" spans="1:16">
+      <c r="B116" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C116" s="20">
+        <v>63156</v>
+      </c>
+      <c r="D116" t="s">
+        <v>1277</v>
+      </c>
+      <c r="E116" t="s">
+        <v>233</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H116" s="24" t="s">
+        <v>868</v>
+      </c>
+      <c r="I116" s="25" t="s">
+        <v>1278</v>
+      </c>
+      <c r="J116" s="26" t="s">
+        <v>1279</v>
+      </c>
+      <c r="K116" s="26" t="s">
+        <v>1280</v>
+      </c>
+      <c r="L116" s="26" t="s">
+        <v>1281</v>
+      </c>
+      <c r="M116" s="26" t="s">
+        <v>1282</v>
+      </c>
+      <c r="N116" s="26" t="s">
+        <v>1283</v>
+      </c>
+      <c r="O116" s="26" t="s">
+        <v>1284</v>
+      </c>
+      <c r="P116" s="26" t="s">
+        <v>1285</v>
+      </c>
     </row>
-    <row r="117" ht="16.5" spans="1:16">
-      <c r="F117" s="4"/>
+    <row r="117" ht="43.5" spans="1:16">
+      <c r="B117" s="1" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C117" s="20">
+        <v>63150</v>
+      </c>
+      <c r="D117" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E117" t="s">
+        <v>233</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H117" s="24" t="s">
+        <v>868</v>
+      </c>
+      <c r="I117" s="25" t="s">
+        <v>1288</v>
+      </c>
+      <c r="J117" s="26" t="s">
+        <v>1289</v>
+      </c>
+      <c r="K117" s="26" t="s">
+        <v>1290</v>
+      </c>
+      <c r="L117" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="M117" s="26" t="s">
+        <v>1292</v>
+      </c>
+      <c r="N117" s="26" t="s">
+        <v>1293</v>
+      </c>
+      <c r="O117" s="26" t="s">
+        <v>1294</v>
+      </c>
+      <c r="P117" s="26" t="s">
+        <v>1295</v>
+      </c>
     </row>
-    <row r="118" ht="16.5" spans="1:16">
-      <c r="F118" s="4"/>
+    <row r="118" ht="43.5" spans="1:16">
+      <c r="B118" s="1" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C118" s="20">
+        <v>63153</v>
+      </c>
+      <c r="D118" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E118" t="s">
+        <v>233</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H118" s="24" t="s">
+        <v>868</v>
+      </c>
+      <c r="I118" s="25" t="s">
+        <v>1298</v>
+      </c>
+      <c r="J118" s="26" t="s">
+        <v>1299</v>
+      </c>
+      <c r="K118" s="26" t="s">
+        <v>1300</v>
+      </c>
+      <c r="L118" s="26" t="s">
+        <v>1301</v>
+      </c>
+      <c r="M118" s="26" t="s">
+        <v>1302</v>
+      </c>
+      <c r="N118" s="26" t="s">
+        <v>1303</v>
+      </c>
+      <c r="O118" s="26" t="s">
+        <v>1304</v>
+      </c>
+      <c r="P118" s="26" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="119" ht="43.5" spans="1:16">
+      <c r="B119" s="1" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C119" s="20">
+        <v>63152</v>
+      </c>
+      <c r="D119" t="s">
+        <v>1307</v>
+      </c>
+      <c r="E119" t="s">
+        <v>233</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H119" s="24" t="s">
+        <v>868</v>
+      </c>
+      <c r="I119" s="25" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J119" s="26" t="s">
+        <v>1309</v>
+      </c>
+      <c r="K119" s="26" t="s">
+        <v>1310</v>
+      </c>
+      <c r="L119" s="26" t="s">
+        <v>1311</v>
+      </c>
+      <c r="M119" s="26" t="s">
+        <v>1312</v>
+      </c>
+      <c r="N119" s="26" t="s">
+        <v>1313</v>
+      </c>
+      <c r="O119" s="26" t="s">
+        <v>1314</v>
+      </c>
+      <c r="P119" s="26" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="120" ht="43.5" spans="1:16">
+      <c r="B120" s="1" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C120" s="20">
+        <v>63149</v>
+      </c>
+      <c r="D120" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E120" t="s">
+        <v>233</v>
+      </c>
+      <c r="F120" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H120" s="24" t="s">
+        <v>868</v>
+      </c>
+      <c r="I120" s="25" t="s">
+        <v>1318</v>
+      </c>
+      <c r="J120" s="26" t="s">
+        <v>1319</v>
+      </c>
+      <c r="K120" s="26" t="s">
+        <v>1320</v>
+      </c>
+      <c r="L120" s="26" t="s">
+        <v>1321</v>
+      </c>
+      <c r="M120" s="26" t="s">
+        <v>1322</v>
+      </c>
+      <c r="N120" s="26" t="s">
+        <v>1323</v>
+      </c>
+      <c r="O120" s="26" t="s">
+        <v>1324</v>
+      </c>
+      <c r="P120" s="26" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="121" ht="43.5" spans="1:16">
+      <c r="B121" s="1" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C121" s="20">
+        <v>63156</v>
+      </c>
+      <c r="D121" t="s">
+        <v>1327</v>
+      </c>
+      <c r="E121" t="s">
+        <v>233</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H121" s="24" t="s">
+        <v>868</v>
+      </c>
+      <c r="I121" s="25" t="s">
+        <v>1328</v>
+      </c>
+      <c r="J121" s="26" t="s">
+        <v>1329</v>
+      </c>
+      <c r="K121" s="26" t="s">
+        <v>1330</v>
+      </c>
+      <c r="L121" s="26" t="s">
+        <v>1331</v>
+      </c>
+      <c r="M121" s="26" t="s">
+        <v>1332</v>
+      </c>
+      <c r="N121" s="26" t="s">
+        <v>1333</v>
+      </c>
+      <c r="O121" s="26" t="s">
+        <v>1334</v>
+      </c>
+      <c r="P121" s="26" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="122" ht="43.5" spans="1:16">
+      <c r="C122" s="20">
+        <v>63154</v>
+      </c>
+      <c r="D122" t="s">
+        <v>1336</v>
+      </c>
+      <c r="E122" t="s">
+        <v>233</v>
+      </c>
+      <c r="F122" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I122" s="25" t="s">
+        <v>1337</v>
+      </c>
+      <c r="J122" s="26" t="s">
+        <v>1338</v>
+      </c>
+      <c r="K122" s="26" t="s">
+        <v>1339</v>
+      </c>
+      <c r="L122" s="26" t="s">
+        <v>1340</v>
+      </c>
+      <c r="M122" s="26" t="s">
+        <v>1341</v>
+      </c>
+      <c r="N122" s="26" t="s">
+        <v>1342</v>
+      </c>
+      <c r="O122" s="26" t="s">
+        <v>1343</v>
+      </c>
+      <c r="P122" s="26" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="123" ht="43.5" spans="1:16">
+      <c r="C123" s="20">
+        <v>63155</v>
+      </c>
+      <c r="D123" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E123" t="s">
+        <v>233</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I123" s="25" t="s">
+        <v>1346</v>
+      </c>
+      <c r="J123" s="26" t="s">
+        <v>1347</v>
+      </c>
+      <c r="K123" s="26" t="s">
+        <v>1348</v>
+      </c>
+      <c r="L123" s="26" t="s">
+        <v>1349</v>
+      </c>
+      <c r="M123" s="26" t="s">
+        <v>1350</v>
+      </c>
+      <c r="N123" s="26" t="s">
+        <v>1351</v>
+      </c>
+      <c r="O123" s="26" t="s">
+        <v>1352</v>
+      </c>
+      <c r="P123" s="26" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="124" ht="43.5" spans="1:16">
+      <c r="C124" s="20">
+        <v>63151</v>
+      </c>
+      <c r="D124" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E124" t="s">
+        <v>233</v>
+      </c>
+      <c r="F124" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I124" s="25" t="s">
+        <v>1355</v>
+      </c>
+      <c r="J124" s="26" t="s">
+        <v>1356</v>
+      </c>
+      <c r="K124" s="26" t="s">
+        <v>1357</v>
+      </c>
+      <c r="L124" s="26" t="s">
+        <v>1358</v>
+      </c>
+      <c r="M124" s="26" t="s">
+        <v>1359</v>
+      </c>
+      <c r="N124" s="26" t="s">
+        <v>1360</v>
+      </c>
+      <c r="O124" s="26" t="s">
+        <v>1361</v>
+      </c>
+      <c r="P124" s="26" t="s">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="125" ht="43.5" spans="1:16">
+      <c r="B125" s="1" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C125" s="20">
+        <v>63972</v>
+      </c>
+      <c r="D125" t="s">
+        <v>1364</v>
+      </c>
+      <c r="E125" t="s">
+        <v>1365</v>
+      </c>
+      <c r="F125" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H125" s="24" t="s">
+        <v>868</v>
+      </c>
+      <c r="I125" s="25" t="s">
+        <v>1366</v>
+      </c>
+      <c r="J125" s="26" t="s">
+        <v>1367</v>
+      </c>
+      <c r="K125" s="26" t="s">
+        <v>1368</v>
+      </c>
+      <c r="L125" s="26" t="s">
+        <v>1369</v>
+      </c>
+      <c r="M125" s="26" t="s">
+        <v>1370</v>
+      </c>
+      <c r="N125" s="26" t="s">
+        <v>1371</v>
+      </c>
+      <c r="O125" s="26" t="s">
+        <v>1372</v>
+      </c>
+      <c r="P125" s="26" t="s">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="126" ht="43.5" spans="1:16">
+      <c r="B126" s="1" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C126" s="20">
+        <v>63975</v>
+      </c>
+      <c r="D126" t="s">
+        <v>1375</v>
+      </c>
+      <c r="E126" t="s">
+        <v>1365</v>
+      </c>
+      <c r="F126" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H126" s="24" t="s">
+        <v>868</v>
+      </c>
+      <c r="I126" s="25" t="s">
+        <v>1376</v>
+      </c>
+      <c r="J126" s="26" t="s">
+        <v>1377</v>
+      </c>
+      <c r="K126" s="26" t="s">
+        <v>1378</v>
+      </c>
+      <c r="L126" s="26" t="s">
+        <v>1379</v>
+      </c>
+      <c r="M126" s="26" t="s">
+        <v>1380</v>
+      </c>
+      <c r="N126" s="26" t="s">
+        <v>1381</v>
+      </c>
+      <c r="O126" s="26" t="s">
+        <v>1382</v>
+      </c>
+      <c r="P126" s="26" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="127" ht="43.5" spans="1:16">
+      <c r="B127" s="1" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C127" s="20">
+        <v>63974</v>
+      </c>
+      <c r="D127" t="s">
+        <v>1385</v>
+      </c>
+      <c r="E127" t="s">
+        <v>1365</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H127" s="24" t="s">
+        <v>868</v>
+      </c>
+      <c r="I127" s="25" t="s">
+        <v>1386</v>
+      </c>
+      <c r="J127" s="26" t="s">
+        <v>1387</v>
+      </c>
+      <c r="K127" s="26" t="s">
+        <v>1388</v>
+      </c>
+      <c r="L127" s="26" t="s">
+        <v>1389</v>
+      </c>
+      <c r="M127" s="26" t="s">
+        <v>1390</v>
+      </c>
+      <c r="N127" s="26" t="s">
+        <v>1391</v>
+      </c>
+      <c r="O127" s="26" t="s">
+        <v>1392</v>
+      </c>
+      <c r="P127" s="26" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="128" ht="43.5" spans="1:16">
+      <c r="B128" s="1" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C128" s="20">
+        <v>63973</v>
+      </c>
+      <c r="D128" t="s">
+        <v>1395</v>
+      </c>
+      <c r="E128" t="s">
+        <v>1365</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H128" s="24" t="s">
+        <v>868</v>
+      </c>
+      <c r="I128" s="25" t="s">
+        <v>1396</v>
+      </c>
+      <c r="J128" s="26" t="s">
+        <v>1397</v>
+      </c>
+      <c r="K128" s="26" t="s">
+        <v>1398</v>
+      </c>
+      <c r="L128" s="26" t="s">
+        <v>1399</v>
+      </c>
+      <c r="M128" s="26" t="s">
+        <v>1400</v>
+      </c>
+      <c r="N128" s="26" t="s">
+        <v>1401</v>
+      </c>
+      <c r="O128" s="26" t="s">
+        <v>1402</v>
+      </c>
+      <c r="P128" s="26" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="129" ht="43.5" spans="2:16">
+      <c r="B129" s="1" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C129" s="20">
+        <v>63976</v>
+      </c>
+      <c r="D129" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E129" t="s">
+        <v>1365</v>
+      </c>
+      <c r="F129" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H129" s="24" t="s">
+        <v>868</v>
+      </c>
+      <c r="I129" s="25" t="s">
+        <v>1406</v>
+      </c>
+      <c r="J129" s="26" t="s">
+        <v>1407</v>
+      </c>
+      <c r="K129" s="26" t="s">
+        <v>1408</v>
+      </c>
+      <c r="L129" s="26" t="s">
+        <v>1409</v>
+      </c>
+      <c r="M129" s="26" t="s">
+        <v>1410</v>
+      </c>
+      <c r="N129" s="26" t="s">
+        <v>1411</v>
+      </c>
+      <c r="O129" s="26" t="s">
+        <v>1412</v>
+      </c>
+      <c r="P129" s="26" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="130" ht="43.5" spans="2:16">
+      <c r="B130" s="1" t="s">
+        <v>1414</v>
+      </c>
+      <c r="C130" s="20">
+        <v>63977</v>
+      </c>
+      <c r="D130" t="s">
+        <v>1415</v>
+      </c>
+      <c r="E130" t="s">
+        <v>1365</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H130" s="24" t="s">
+        <v>868</v>
+      </c>
+      <c r="I130" s="25" t="s">
+        <v>1416</v>
+      </c>
+      <c r="J130" s="26" t="s">
+        <v>1417</v>
+      </c>
+      <c r="K130" s="26" t="s">
+        <v>1418</v>
+      </c>
+      <c r="L130" s="26" t="s">
+        <v>1419</v>
+      </c>
+      <c r="M130" s="26" t="s">
+        <v>1420</v>
+      </c>
+      <c r="N130" s="26" t="s">
+        <v>1421</v>
+      </c>
+      <c r="O130" s="26" t="s">
+        <v>1422</v>
+      </c>
+      <c r="P130" s="26" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="131" ht="43.5" spans="2:16">
+      <c r="B131" s="1" t="s">
+        <v>1424</v>
+      </c>
+      <c r="C131" s="20">
+        <v>63978</v>
+      </c>
+      <c r="D131" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E131" t="s">
+        <v>1365</v>
+      </c>
+      <c r="F131" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H131" s="24" t="s">
+        <v>868</v>
+      </c>
+      <c r="I131" s="27" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J131" s="26" t="s">
+        <v>1427</v>
+      </c>
+      <c r="K131" s="26" t="s">
+        <v>1428</v>
+      </c>
+      <c r="L131" s="26" t="s">
+        <v>1429</v>
+      </c>
+      <c r="M131" s="26" t="s">
+        <v>1430</v>
+      </c>
+      <c r="N131" s="26" t="s">
+        <v>1431</v>
+      </c>
+      <c r="O131" s="26" t="s">
+        <v>1432</v>
+      </c>
+      <c r="P131" s="26" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="132" ht="16.5" spans="2:16">
+      <c r="F132" s="4"/>
+      <c r="H132" s="24"/>
+    </row>
+    <row r="133" ht="15.75" spans="2:16">
+      <c r="H133" s="24"/>
+    </row>
+    <row r="134" ht="15.75" spans="2:16">
+      <c r="H134" s="24"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/uploads/网站信息.xlsx
+++ b/uploads/网站信息.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3921" uniqueCount="2884">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4627" uniqueCount="3441">
   <si>
     <t>分类</t>
   </si>
@@ -9096,6 +9096,1677 @@
   <si>
     <t>buy bubble dresses online; bubble dresses for girls; bubble dresses for parties; toddler bubble dresses; baby bubble dresses; bubble dress set; bubble dresses for special occasions; quality bubble dresses; twirl bubble dresses; shop bubble dresses; bubble dresses like Janie and Jack; bubble dresses alternative; bubble dresses boutique; affordable bubble dresses; cute bubble dresses</t>
   </si>
+  <si>
+    <t>74299,74308,74317,74326,74335,74344,74353,74362,74371,74380</t>
+  </si>
+  <si>
+    <t>Seasonal &amp; Holiday|||Christmas Decor</t>
+  </si>
+  <si>
+    <t>8643 Jellico Ave, Northridge, CA 91325</t>
+  </si>
+  <si>
+    <t>tinselvia.com</t>
+  </si>
+  <si>
+    <t>Shop Christmas Decor | Festive Quality | Tinselvia</t>
+  </si>
+  <si>
+    <t>选购圣诞装饰 | 节日品质 | Tinselvia</t>
+  </si>
+  <si>
+    <t>Bring holiday warmth to every room with Christmas decor built for seasonal style. Explore ornaments, wreaths, garlands, tree skirts, and stockings. See collection.</t>
+  </si>
+  <si>
+    <t>将节日温暖带入每个房间，使用为季节性风格打造的圣诞装饰。探索装饰品、花环、彩带、树裙和长袜。查看系列。</t>
+  </si>
+  <si>
+    <t>Christmas Decor</t>
+  </si>
+  <si>
+    <t>buy christmas decor online; christmas decor for living room; modern christmas decor set; outdoor christmas decor for front porch; quality christmas decor bundle; christmas decor for small apartment; durable shatterproof christmas decor; christmas decor kit with lights; order christmas decor online; christmas decor for stairs; christmas decor like pottery barn; christmas decor starter set; budget christmas decor; elegant christmas decor collection</t>
+  </si>
+  <si>
+    <t>74300,74309,74318,74327,74336,74345,74354,74363,74372,74381</t>
+  </si>
+  <si>
+    <t>Seasonal &amp; Holiday|||Christmas Trees</t>
+  </si>
+  <si>
+    <t>1363 Noe St, San Francisco, CA 94131</t>
+  </si>
+  <si>
+    <t>evergleamk.com</t>
+  </si>
+  <si>
+    <t>Evergleam: Christmas Trees &amp; Seasonal Tree Decorations</t>
+  </si>
+  <si>
+    <t>Evergleam：圣诞树与季节性树木装饰</t>
+  </si>
+  <si>
+    <t>Find a lasting centerpiece with Christmas trees designed for easy setup and storage. Browse pre-lit trees, stands, skirts, and storage bags. Start here.</t>
+  </si>
+  <si>
+    <t>找到持久的中心装饰，使用为易于安装和收纳而设计的圣诞树。浏览预亮灯圣诞树、树架、树裙和收纳袋。从这里开始。</t>
+  </si>
+  <si>
+    <t>Christmas Trees</t>
+  </si>
+  <si>
+    <t>buy christmas trees online; christmas trees for small spaces; pre-lit christmas trees; quality christmas trees; christmas trees for apartment; artificial christmas trees set; christmas trees with stand; order christmas trees online; christmas trees for front porch; slim christmas trees; christmas trees bundle with lights; christmas trees like balsam hill; durable christmas trees; christmas trees for high ceilings; christmas trees starter kit</t>
+  </si>
+  <si>
+    <t>74301,74310,74319,74328,74337,74346,74355,74364,74373,74382</t>
+  </si>
+  <si>
+    <t>Seasonal &amp; Holiday|||Halloween</t>
+  </si>
+  <si>
+    <t>931 Primrose Ave, Sunnyvale, CA 94086</t>
+  </si>
+  <si>
+    <t>bramwickl.com</t>
+  </si>
+  <si>
+    <t>Halloween | Authentic Seasonal Home Decor | Bramwick</t>
+  </si>
+  <si>
+    <t>Halloween | 正宗季节性家居装饰 | Bramwick</t>
+  </si>
+  <si>
+    <t>Set a spooky scene with Halloween decor built for porches, yards, and living rooms. Browse string lights, inflatables, wreaths, and doormats. Shop now.</t>
+  </si>
+  <si>
+    <t>营造诡异场景，使用为门廊、庭院和客厅打造的万圣节装饰。浏览串灯、充气装饰、花环和门垫。立即选购。</t>
+  </si>
+  <si>
+    <t>Halloween</t>
+  </si>
+  <si>
+    <t>buy halloween decor online; halloween decor for front yard; outdoor halloween decor; quality halloween decor; halloween decor for porch; halloween decor set; halloween decor bundle; order halloween decor online; halloween decor for apartment; spooky halloween decor; halloween decoration starter kit; halloween decor like home depot; durable outdoor halloween decor; halloween decor for yard</t>
+  </si>
+  <si>
+    <t>74302,74311,74320,74329,74338,74347,74356,74365,74374</t>
+  </si>
+  <si>
+    <t>Seasonal &amp; Holiday|||Christmas</t>
+  </si>
+  <si>
+    <t>4841 C St, Sacramento, CA 95819</t>
+  </si>
+  <si>
+    <t>noeloray.com</t>
+  </si>
+  <si>
+    <t>Noelora: Modern Christmas Decorations &amp; Accessories</t>
+  </si>
+  <si>
+    <t>Noelora：现代圣诞装饰与配件</t>
+  </si>
+  <si>
+    <t>Make the season bright with Christmas decor and gifts designed for cozy holiday moments. Explore ornaments, wreaths, stockings, and table accents. Find yours today.</t>
+  </si>
+  <si>
+    <t>用为温馨节日时刻设计的圣诞装饰和礼物点亮这个季节。探索装饰品、花环、长袜和桌面点缀。今天就找到你的。</t>
+  </si>
+  <si>
+    <t>Christmas</t>
+  </si>
+  <si>
+    <t>buy christmas decorations online; christmas decor for living room; christmas decorations for front porch; quality christmas decorations; christmas decor set; christmas gifts bundle; order christmas decor online; christmas decorations for apartment; modern christmas decorations; christmas decor starter kit; christmas decorations like target; durable outdoor christmas decorations; christmas tree ornaments set; christmas lights for home</t>
+  </si>
+  <si>
+    <t>74303,74312,74321,74330,74339,74348,74357,74366,74375</t>
+  </si>
+  <si>
+    <t>Floral|||Artificial Flowers</t>
+  </si>
+  <si>
+    <t>2905 Chestnut St, Oakland, CA 94608</t>
+  </si>
+  <si>
+    <t>petalurem.com</t>
+  </si>
+  <si>
+    <t>Artificial Flowers &amp; Faux Plants - Classic | Petalure</t>
+  </si>
+  <si>
+    <t>人造花与仿真植物——经典 | Petalure</t>
+  </si>
+  <si>
+    <t>Refresh any space with artificial flowers and faux stems designed for easy color. Browse silk blooms, potted arrangements, and garlands. See collection.</t>
+  </si>
+  <si>
+    <t>用人造花和仿真茎为任何空间增添新意，轻松获得色彩。浏览丝绸花、盆栽花艺和花环。查看系列。</t>
+  </si>
+  <si>
+    <t>Artificial Flowers</t>
+  </si>
+  <si>
+    <t>buy artificial flowers online; artificial flowers for home decor; realistic artificial flowers; quality artificial flowers; artificial flowers for wedding centerpieces; artificial flowers arrangement set; artificial flowers bundle; order artificial flowers online; artificial flowers for kitchen table; silk artificial flowers; artificial flowers like afloral; durable outdoor artificial flowers; artificial flowers starter kit; artificial flowers for bathroom; artificial flowers with vase</t>
+  </si>
+  <si>
+    <t>74304,74313,74322,74331,74340,74349,74358,74367,74376</t>
+  </si>
+  <si>
+    <t>Kitchen &amp; Dining|||Serveware</t>
+  </si>
+  <si>
+    <t>5110 New Kent Rd, Richmond, VA 23225</t>
+  </si>
+  <si>
+    <t>serevas.com</t>
+  </si>
+  <si>
+    <t>Sereva. Serveware built for everyday hosting and dining.</t>
+  </si>
+  <si>
+    <t>Sereva. 为日常款待与用餐打造的餐具。</t>
+  </si>
+  <si>
+    <t>Create a warm table with serveware built for everyday meals and special gatherings. Browse serving bowls, platters, trays, cake stands, and utensil rests. Shop now.</t>
+  </si>
+  <si>
+    <t>用为日常用餐和特别聚会打造的餐具营造温馨餐桌。浏览上菜碗、大盘、托盘、蛋糕架和餐具架。立即选购。</t>
+  </si>
+  <si>
+    <t>Serveware</t>
+  </si>
+  <si>
+    <t>buy serveware online; serveware for dinner parties; modern serveware set; quality serveware; serveware for everyday use; ceramic serveware; serveware bundle; order serveware online; serveware for kitchen table; stoneware serveware; serveware starter set; serveware like crate and barrel; durable serveware; serveware for buffet; serveware with lids</t>
+  </si>
+  <si>
+    <t>74305,74314,74323,74332,74341,74350,74359,74368,74377</t>
+  </si>
+  <si>
+    <t>Rugs|||Oriental Rugs</t>
+  </si>
+  <si>
+    <t>947 Quince Ave, Santa Clara, CA 95051</t>
+  </si>
+  <si>
+    <t>knotwelly.com</t>
+  </si>
+  <si>
+    <t>Timeless Style Underfoot | Oriental Rugs | Knotwell</t>
+  </si>
+  <si>
+    <t>脚下永恒风格 | 东方地毯 | Knotwell</t>
+  </si>
+  <si>
+    <t>Anchor your rooms with oriental rugs designed for lasting color and soft texture. Explore traditional, vintage, indoor, runner, and round styles. Start here.</t>
+  </si>
+  <si>
+    <t>用为持久色彩和柔软质感设计的东方地毯奠定房间基调。探索传统、复古、室内、长条和圆形款式。从这里开始。</t>
+  </si>
+  <si>
+    <t>Oriental Rugs</t>
+  </si>
+  <si>
+    <t>buy oriental rugs online; oriental rugs for living room; traditional oriental rugs; quality oriental rugs; oriental rugs for bedroom; vintage oriental rugs; oriental rugs set; oriental rugs bundle; order oriental rugs online; oriental rugs for high traffic areas; wool oriental rugs; oriental rugs like revival rugs; durable oriental rugs; oriental rugs for dining room; oriental rugs starter set</t>
+  </si>
+  <si>
+    <t>74306,74315,74324,74333,74342,74351,74360,74369,74378</t>
+  </si>
+  <si>
+    <t>Lighting|||Flush Mount Lights</t>
+  </si>
+  <si>
+    <t>551 38th St, Sacramento, CA 95816</t>
+  </si>
+  <si>
+    <t>haloftt.com</t>
+  </si>
+  <si>
+    <t>Flush Mount Lights for Modern Low Ceilings | Haloft</t>
+  </si>
+  <si>
+    <t>适用于现代低天花板的吸顶灯 | Haloft</t>
+  </si>
+  <si>
+    <t>Brighten low-ceiling rooms with flush mount lights built for clean, even illumination. Browse modern, dimmable, LED, brass, and matte black styles. See collection.</t>
+  </si>
+  <si>
+    <t>用为干净均匀照明设计的吸顶灯照亮低天花板房间。浏览现代、可调光、LED、黄铜和哑光黑款式。查看系列。</t>
+  </si>
+  <si>
+    <t>Flush Mount Lights</t>
+  </si>
+  <si>
+    <t>buy flush mount lights online; flush mount lights for low ceilings; modern flush mount lights; quality flush mount lights; flush mount lights for bedroom; dimmable flush mount lights; flush mount lights set; flush mount lights bundle; order flush mount lights online; flush mount lights for hallway; brass flush mount lights; flush mount lights like west elm; durable flush mount lights; flush mount lights for kitchen; flush mount lights starter kit</t>
+  </si>
+  <si>
+    <t>74307,74316,74325,74334,74343,74352,74361,74370,74379</t>
+  </si>
+  <si>
+    <t>Decor|||Vases</t>
+  </si>
+  <si>
+    <t>5608 Lansing Dr, Temple Hills, MD 20748</t>
+  </si>
+  <si>
+    <t>vessoral.com</t>
+  </si>
+  <si>
+    <t>Vessora | Vases &amp; Floral Centerpiece Home Essentials</t>
+  </si>
+  <si>
+    <t>Vessora | 花瓶与花卉中心装饰家居必需品</t>
+  </si>
+  <si>
+    <t>Add height and color to shelves and tables with vases designed for fresh or dried stems. Browse ceramic, glass, stoneware, bud, and floor styles. Find yours today.</t>
+  </si>
+  <si>
+    <t>用为鲜花或干枝设计的花瓶为搁架和桌子增添高度和色彩。浏览陶瓷、玻璃、炻器、小花瓶和落地式款式。今天就找到你的。</t>
+  </si>
+  <si>
+    <t>Vases</t>
+  </si>
+  <si>
+    <t>buy vases online; vases for living room decor; ceramic vases; quality vases; vases for dining table; glass vases; vases set; vases bundle; order vases online; vases for entryway; stoneware vases; vases like anthropologie; durable vases; vases for office desk; vases starter kit</t>
+  </si>
+  <si>
+    <t>76057,76067,76077,76087,76097,76107,76117,76127,76137,76147</t>
+  </si>
+  <si>
+    <t>Jewelry|||Brooches</t>
+  </si>
+  <si>
+    <t>服饰与配饰</t>
+  </si>
+  <si>
+    <t>20437 Schoenborn St, Winnetka, CA 91306</t>
+  </si>
+  <si>
+    <t>lusteral.com</t>
+  </si>
+  <si>
+    <t>Shop Brooches | Timeless Jewelry &amp; Gifts | Lustera</t>
+  </si>
+  <si>
+    <t>选购胸针 | 永恒珠宝与礼品 | Lustera</t>
+  </si>
+  <si>
+    <t>Shop brooches designed for everyday elegance and special occasions. Add lasting shine to jackets and bags with quality metal pins and jewelry sets. Find yours today.</t>
+  </si>
+  <si>
+    <t>选购专为日常优雅与特殊场合设计的胸针。用优质金属别针和珠宝套装为夹克和包包增添持久光泽。今天就找到适合你的。</t>
+  </si>
+  <si>
+    <t>Brooches</t>
+  </si>
+  <si>
+    <t>buy brooches online; brooches for women fashion; brooches for jackets and coats; vintage style brooches; metal brooches with pin backs; brooches for weddings; brooches gift set; pearl brooches for special occasions; brooches like Swarovski; affordable brooches for everyday wear; brooches for sale online; enamel brooches for hats; crystal brooches alternative; order brooches online</t>
+  </si>
+  <si>
+    <t>76058,76068,76078,76088,76098,76108,76118,76128,76138</t>
+  </si>
+  <si>
+    <t>Office Supplies|||Greeting Cards</t>
+  </si>
+  <si>
+    <t>2081 Nobili Ave, Santa Clara, CA 95051</t>
+  </si>
+  <si>
+    <t>ardellel.com</t>
+  </si>
+  <si>
+    <t>Ardelle: Greeting Cards &amp; Stationery for Every Occasion</t>
+  </si>
+  <si>
+    <t>Ardelle：适合各种场合的贺卡与文具</t>
+  </si>
+  <si>
+    <t>Send warmer wishes with greeting cards made for birthdays, thank-yous, and everyday notes. Browse stationery, envelopes, and note sets crafted from quality paper.</t>
+  </si>
+  <si>
+    <t>用为生日、感谢和日常留言而制作的贺卡，送出更温暖的祝福。浏览采用优质纸张制作的文具、信封和便签套装。</t>
+  </si>
+  <si>
+    <t>Greeting Cards</t>
+  </si>
+  <si>
+    <t>buy greeting cards online; greeting cards for birthdays; greeting cards for thank you; funny greeting cards for friends; blank greeting cards with envelopes; greeting cards set boxed; greeting cards for business; greeting cards like Hallmark; affordable greeting cards bulk; greeting cards for holidays; greeting cards for weddings; greeting cards for kids; quality greeting cards pack; greeting cards for sympathy; greeting cards for new baby</t>
+  </si>
+  <si>
+    <t>76059,76069,76079,76089,76099,76109,76119,76129,76139</t>
+  </si>
+  <si>
+    <t>Apparel &amp; Accessories|||Watches</t>
+  </si>
+  <si>
+    <t>2611 Phyllis Ave, Sacramento, CA 95820</t>
+  </si>
+  <si>
+    <t>temverra.com</t>
+  </si>
+  <si>
+    <t>Watches | Precision Timepieces &amp; Straps | Temverra</t>
+  </si>
+  <si>
+    <t>手表 | 精密时计与表带 | Temverra</t>
+  </si>
+  <si>
+    <t>Find watches designed for daily wear, work, and weekend style. Choose metal, leather, or sport straps with durable cases. Explore straps and watch accessories.</t>
+  </si>
+  <si>
+    <t>查找专为日常佩戴、工作和周末风格设计的手表。选择金属、皮革或运动表带，搭配耐用表壳。探索表带和手表配件。</t>
+  </si>
+  <si>
+    <t>Watches</t>
+  </si>
+  <si>
+    <t>buy watches online; watches for men; watches for women; watches for work; watches for everyday wear; watches for small wrists; metal watches with leather straps; watches for outdoor use; watches gift set; watches like MVMT; affordable watches online; watches with durable cases; sport watches for running; watches bundle with straps; order watches for delivery</t>
+  </si>
+  <si>
+    <t>76060,76070,76080,76090,76100,76110,76120,76130,76140</t>
+  </si>
+  <si>
+    <t>Clothing Accessories|||Cufflinks</t>
+  </si>
+  <si>
+    <t>848 Oracle Oak Pl, Sunnyvale, CA 94086</t>
+  </si>
+  <si>
+    <t>mercotta.com</t>
+  </si>
+  <si>
+    <t>Mercotta: Refined Cufflinks for Men's Formal Attire</t>
+  </si>
+  <si>
+    <t>Mercotta：适合男士正装着装的精致袖扣</t>
+  </si>
+  <si>
+    <t>Add refined cufflinks to formal wear for weddings and work. Choose metal cufflinks, tie clips, and dress accessories built to stay secure. Explore shirt accessories.</t>
+  </si>
+  <si>
+    <t>为婚礼和工作的正装增添精致袖扣。选择金属袖扣、领带夹和正装配饰，佩戴牢固。探索衬衫配饰。</t>
+  </si>
+  <si>
+    <t>Cufflinks</t>
+  </si>
+  <si>
+    <t>buy cufflinks online; cufflinks for men; cufflinks for weddings; cufflinks for dress shirts; metal cufflinks with bullet back; cufflinks gift set; cufflinks like Montblanc; affordable cufflinks for work; cufflinks for tuxedo; cufflinks with tie clips; order cufflinks online; cufflinks for groomsmen; cufflinks set and tie clip; silver cufflinks replacement</t>
+  </si>
+  <si>
+    <t>76061,76071,76081,76091,76101,76111,76121,76131,76141</t>
+  </si>
+  <si>
+    <t>Clothing Accessories|||Hair Accessories</t>
+  </si>
+  <si>
+    <t>1104 Evelyn Ln, Sacramento, CA 95864</t>
+  </si>
+  <si>
+    <t>tressoray.com</t>
+  </si>
+  <si>
+    <t>Hair Accessories &amp; Clips - Everyday Style | Tressora</t>
+  </si>
+  <si>
+    <t>发饰与发夹——日常风格 | Tressora</t>
+  </si>
+  <si>
+    <t>Keep hair accessories simple, comfortable, and secure for everyday wear. Choose clips, pins, headbands, and hair ties made from quality materials. Explore hair sets.</t>
+  </si>
+  <si>
+    <t>让发饰保持简单、舒适且牢固，适合日常佩戴。选择采用优质材料制作的发夹、发簪、发箍和发圈。探索发饰套装。</t>
+  </si>
+  <si>
+    <t>Hair Accessories</t>
+  </si>
+  <si>
+    <t>buy hair accessories online; hair accessories for women; hair accessories for curly hair; hair accessories for weddings; hair accessories for kids; hair accessories for everyday wear; metal hair accessories; hair accessories set; hair accessories for thin hair; hair accessories like Scunci; affordable hair accessories bulk; hair accessories with clips and pins; hair accessories for bridesmaids; order hair accessories online</t>
+  </si>
+  <si>
+    <t>76062,76072,76082,76092,76102,76112,76122,76132,76142</t>
+  </si>
+  <si>
+    <t>Clothing Accessories|||Tie Clips</t>
+  </si>
+  <si>
+    <t>3605 Buena Vista Dr, Sacramento, CA 95864</t>
+  </si>
+  <si>
+    <t>brelsonm.com</t>
+  </si>
+  <si>
+    <t>Brelson. Tie Clips built for a sharp professional look.</t>
+  </si>
+  <si>
+    <t>Brelson。为利落职业造型而打造的领带夹。</t>
+  </si>
+  <si>
+    <t>Lock tie clips in place with a secure, polished fit for work and formal events. Choose slim metal tie clips, collar stays, and dress accessories. Find yours today.</t>
+  </si>
+  <si>
+    <t>用牢固、精致的佩戴效果将领带夹固定到位，适合工作和正式活动。选择纤细金属领带夹、领插片和正装配饰。今天就找到适合你的。</t>
+  </si>
+  <si>
+    <t>Tie Clips</t>
+  </si>
+  <si>
+    <t>buy tie clips online; tie clips for men; tie clips for weddings; tie clips for work; metal tie clips with spring clasp; tie clips gift set; tie clips like Tiffany; affordable tie clips for suits; tie clips for groomsmen; tie clips with collar stays; order tie clips online; tie clips for slim ties; tie clips set and cufflinks; silver tie clips alternative</t>
+  </si>
+  <si>
+    <t>76063,76073,76083,76093,76103,76113,76123,76133,76143</t>
+  </si>
+  <si>
+    <t>Apparel &amp; Accessories|||Keychains</t>
+  </si>
+  <si>
+    <t>1409 Talbert Dr, Richmond, VA 23224</t>
+  </si>
+  <si>
+    <t>korvalm.com</t>
+  </si>
+  <si>
+    <t>Everyday Carry Essentials Start Here | Keychains | Korval</t>
+  </si>
+  <si>
+    <t>日常随身必备从这里开始 | 钥匙扣 | Korval</t>
+  </si>
+  <si>
+    <t>Carry keychains built for daily use and travel. Choose durable metal keychains, leather key fobs, and carry accessories. Explore key rings and bag charms.</t>
+  </si>
+  <si>
+    <t>携带专为日常使用和旅行打造的钥匙扣。选择耐用金属钥匙扣、皮革钥匙扣和随身配件。探索钥匙环和包包挂饰。</t>
+  </si>
+  <si>
+    <t>Keychains</t>
+  </si>
+  <si>
+    <t>buy keychains online; keychains for men; keychains for women; keychains for backpacks; metal keychains with bottle opener; keychains gift set; keychains like Coach; affordable keychains bulk; keychains for car keys; keychains for travel; order keychains online; keychains with key rings; leather keychains for everyday use; keychains set and bag charm; durable keychains for everyday carry</t>
+  </si>
+  <si>
+    <t>76064,76074,76084,76094,76104,76114,76124,76134,76144</t>
+  </si>
+  <si>
+    <t>Jewelry|||Anklets</t>
+  </si>
+  <si>
+    <t>2602 Barton Ave, Richmond, VA 23222</t>
+  </si>
+  <si>
+    <t>lunelleas.com</t>
+  </si>
+  <si>
+    <t>Anklets for Warm Weather, Beach &amp; Resort Style | Lunelle</t>
+  </si>
+  <si>
+    <t>适合温暖天气、海滩与度假风格的脚链 | Lunelle</t>
+  </si>
+  <si>
+    <t>Wear light, comfortable anklets made for warm weather and beach days. Choose quality metal, beaded, and layered anklets that resist water. Explore foot jewelry.</t>
+  </si>
+  <si>
+    <t>佩戴专为温暖天气和海滩时光打造的轻盈舒适脚链。选择防水优质金属、串珠和层叠脚链。探索足部珠宝。</t>
+  </si>
+  <si>
+    <t>Anklets</t>
+  </si>
+  <si>
+    <t>buy anklets online; anklets for women; anklets for summer; anklets for beach; metal anklets with charms; anklets gift set; anklets like Pura Vida; affordable anklets for everyday wear; anklets for travel; beaded anklets with shells; order anklets online; anklets set layered; waterproof anklets for swimming; anklets for teens; anklets with adjustable chain</t>
+  </si>
+  <si>
+    <t>76065,76075,76085,76095,76105,76115,76125,76135,76145</t>
+  </si>
+  <si>
+    <t>Clothing Accessories|||Hats</t>
+  </si>
+  <si>
+    <t>471 41st St, Oakland, CA 94609</t>
+  </si>
+  <si>
+    <t>brimlely.com</t>
+  </si>
+  <si>
+    <t>Brimley | Hats &amp; Headwear for Modern Everyday Style</t>
+  </si>
+  <si>
+    <t>Brimley | 帽子与头饰，打造现代日常风格</t>
+  </si>
+  <si>
+    <t>Style hats for sunny days, cool mornings, and everyday wear. Choose breathable cotton hats, wool blends, and packable styles with adjustable fits. Explore caps.</t>
+  </si>
+  <si>
+    <t>为阳光明媚的日子、凉爽早晨和日常佩戴搭配帽子。选择透气棉质帽子、羊毛混纺和可折叠款式，带有可调节帽围。探索棒球帽。</t>
+  </si>
+  <si>
+    <t>Hats</t>
+  </si>
+  <si>
+    <t>buy hats online; hats for men; hats for women; hats for sun protection; hats for hiking; hats for everyday wear; breathable cotton hats; hats with adjustable straps; hats gift set; hats like Patagonia; affordable hats for summer; order hats online; packable hats for travel; hats for winter; hats for beach</t>
+  </si>
+  <si>
+    <t>76066,76076,76086,76096,76106,76116,76126,76136,76146</t>
+  </si>
+  <si>
+    <t>Clothing Accessories|||Scarves</t>
+  </si>
+  <si>
+    <t>2461 Benjamin Dr, Mountain View, CA 94043</t>
+  </si>
+  <si>
+    <t>seralas.com</t>
+  </si>
+  <si>
+    <t>Scarves &amp; Wraps for Soft Layers, Travel &amp; Style | Serala</t>
+  </si>
+  <si>
+    <t>围巾与披肩，适合柔软层叠、旅行与风格 | Serala</t>
+  </si>
+  <si>
+    <t>Wrap up with scarves made for cool mornings, travel, and layered looks. Choose lightweight cotton scarves, soft wool wraps, and woven styles. Explore wraps.</t>
+  </si>
+  <si>
+    <t>用为凉爽早晨、旅行和层叠造型而制作的围巾包裹自己。选择轻质棉质围巾、柔软羊毛披肩和编织款式。探索披肩。</t>
+  </si>
+  <si>
+    <t>Scarves</t>
+  </si>
+  <si>
+    <t>buy scarves online; scarves for women; scarves for winter; scarves for travel; lightweight cotton scarves for summer; scarves gift set; scarves like Burberry; affordable scarves for everyday wear; scarves for men; order scarves online; soft wool scarves for cold weather; scarves and wraps set; scarves for layering; scarves with woven patterns; silk scarves for formal wear</t>
+  </si>
+  <si>
+    <t>76359,76369,76379,76389,76399,76409,76419,76429,76439</t>
+  </si>
+  <si>
+    <t>Decor|||Wallpaper</t>
+  </si>
+  <si>
+    <t>253 S Catalina St, Los Angeles, CA 90004</t>
+  </si>
+  <si>
+    <t>murovial.com</t>
+  </si>
+  <si>
+    <t>Shop Wallpaper | Modern Wall Murals &amp; Decor | Murovia</t>
+  </si>
+  <si>
+    <t>选购墙纸 | 现代壁画与装饰 | Murovia</t>
+  </si>
+  <si>
+    <t>Explore modern wallpaper with easy-to-hang panels and bold patterns. Bring new life to accent walls, bedrooms, or offices with wall murals, borders, and tools.</t>
+  </si>
+  <si>
+    <t>探索现代墙纸，采用易悬挂面板和大胆图案。为背景墙、卧室或办公室带来新意，配套壁画、收边条和工具。</t>
+  </si>
+  <si>
+    <t>Wallpaper</t>
+  </si>
+  <si>
+    <t>buy wallpaper online; shop wallpaper rolls; wallpaper for living room accent wall; peel and stick wallpaper; removable wallpaper for apartments; textured wallpaper rolls; wallpaper for bedroom walls; wallpaper and border kit; wallpaper for office walls; wallpaper roll set; wallpaper like Anthropologie; floral wallpaper rolls</t>
+  </si>
+  <si>
+    <t>76358,76368,76378,76388,76398,76408,76418,76428,76438,76448</t>
+  </si>
+  <si>
+    <t>Lights|||Pendants</t>
+  </si>
+  <si>
+    <t>4140 Manila Ave, Oakland, CA 94609</t>
+  </si>
+  <si>
+    <t>droplites.com</t>
+  </si>
+  <si>
+    <t>Droplite: Modern Pendants &amp; Ceiling Light Fixtures</t>
+  </si>
+  <si>
+    <t>Droplite：现代吊灯与天花板灯具</t>
+  </si>
+  <si>
+    <t>Modern pendants set the right mood over kitchen islands and dining tables. Shop adjustable cord lights, mini pendants, and ceiling hardware for a clean look.</t>
+  </si>
+  <si>
+    <t>现代吊灯为厨房岛台和餐桌营造恰当氛围。选购可调节吊线灯、迷你吊灯和天花板安装件，呈现简洁外观。</t>
+  </si>
+  <si>
+    <t>Pendants</t>
+  </si>
+  <si>
+    <t>buy pendant lights online; shop kitchen pendant lights; pendant lights for kitchen island; pendant lights for dining room; adjustable pendant lights; mini pendant lights; brass pendant lights; pendant light set; pendant light kit; pendant lights for sloped ceilings; black pendant lights; pendant lights like West Elm</t>
+  </si>
+  <si>
+    <t>76357,76367,76377,76387,76397,76407,76417,76427,76437,76447</t>
+  </si>
+  <si>
+    <t>Home &amp; Garden|||Holiday Decor</t>
+  </si>
+  <si>
+    <t>5011 Gilgunn Wy, Sacramento, CA 95822</t>
+  </si>
+  <si>
+    <t>tinselryy.com</t>
+  </si>
+  <si>
+    <t>Holiday Decor | Festive, Durable &amp; Joyful | Tinselry</t>
+  </si>
+  <si>
+    <t>节日装饰 | 喜庆、耐用且充满欢乐 | Tinselry</t>
+  </si>
+  <si>
+    <t>Festive holiday decor brings warmth to mantels, entryways, and tabletops. Discover wreaths, garlands, tree skirts, stockings, and LED candles for the season.</t>
+  </si>
+  <si>
+    <t>喜庆节日装饰为壁炉台、入口和桌面带来温暖。探索花环、花彩、圣诞树裙、长袜和LED蜡烛，装点这个季节。</t>
+  </si>
+  <si>
+    <t>Holiday Decor</t>
+  </si>
+  <si>
+    <t>buy holiday decor online; shop holiday decor; holiday decor for mantel; holiday decor for front porch; holiday decor for small spaces; durable holiday decor; indoor holiday decor; LED holiday decor; holiday decor set; holiday decor bundle; holiday decor like Pottery Barn; outdoor holiday decor</t>
+  </si>
+  <si>
+    <t>76356,76366,76376,76386,76396,76406,76416,76426,76436,76446</t>
+  </si>
+  <si>
+    <t>Ceiling Lights|||Flush Mount Lights</t>
+  </si>
+  <si>
+    <t>3549 Minto Ct, San Jose, CA 95132</t>
+  </si>
+  <si>
+    <t>ceilumel.com</t>
+  </si>
+  <si>
+    <t>Ceilume: Flush Mount Lights &amp; Low-Profile Ceiling Fixtures</t>
+  </si>
+  <si>
+    <t>Ceilume：吸顶灯与低矮天花板灯具</t>
+  </si>
+  <si>
+    <t>Low-profile flush mount lights keep hallways and bedrooms bright without taking up visual space. Browse round, square, and dimmable ceiling fixtures for every room.</t>
+  </si>
+  <si>
+    <t>低矮吸顶灯保持走廊和卧室明亮，不占用视觉空间。浏览圆形、方形和可调光天花板灯具，适合每个房间。</t>
+  </si>
+  <si>
+    <t>buy flush mount lights online; shop flush mount lights; flush mount lights for bedroom; flush mount lights for hallway; flush mount lights for low ceilings; dimmable flush mount lights; LED flush mount lights; brushed nickel flush mount lights; flush mount light set; flush mount light kit; flush mount lights like West Elm; modern flush mount lights</t>
+  </si>
+  <si>
+    <t>76355,76365,76375,76385,76395,76405,76415,76425,76435,76445</t>
+  </si>
+  <si>
+    <t>Rugs &amp; Carpets|||Area Rugs</t>
+  </si>
+  <si>
+    <t>948 W Rose St, Colton, CA 92324</t>
+  </si>
+  <si>
+    <t>weftlly.com</t>
+  </si>
+  <si>
+    <t>Area Rugs &amp; Floor Coverings - Everyday Comfort | Weftly</t>
+  </si>
+  <si>
+    <t>区域地毯与地面覆盖物——日常舒适 | Weftly</t>
+  </si>
+  <si>
+    <t>Soft area rugs anchor living rooms, bedrooms, and dining spaces with color and texture. Shop washable, low-pile, and outdoor rug options in popular sizes.</t>
+  </si>
+  <si>
+    <t>柔软区域地毯以颜色和质感稳定客厅、卧室和餐厅空间。选购可水洗、低绒和户外地毯选项，提供热门尺寸。</t>
+  </si>
+  <si>
+    <t>Area Rugs</t>
+  </si>
+  <si>
+    <t>buy area rugs online; shop area rugs; area rugs for living room; area rugs for bedroom; area rugs for dining room; washable area rugs; low pile area rugs; outdoor area rugs; area rug set; area rug bundle; area rugs like Ruggable; large area rugs</t>
+  </si>
+  <si>
+    <t>76354,76364,76374,76384,76394,76404,76414,76424,76434,76444</t>
+  </si>
+  <si>
+    <t>Kitchen Textiles|||Kitchen Towels</t>
+  </si>
+  <si>
+    <t>740 Goldwood Dr, Dallas, TX 75232</t>
+  </si>
+  <si>
+    <t>wovellem.com</t>
+  </si>
+  <si>
+    <t>Wovelle. Kitchen Towels built for daily cooking tasks.</t>
+  </si>
+  <si>
+    <t>Wovelle。为日常烹饪任务打造的厨房毛巾。</t>
+  </si>
+  <si>
+    <t>Absorbent kitchen towels handle everyday spills, drying, and cleaning with less lint. Explore cotton, waffle-weave, and reusable towel sets in tidy colors.</t>
+  </si>
+  <si>
+    <t>吸水厨房毛巾处理日常泼洒、擦干和清洁，减少棉絮。探索棉质、华夫格和可重复使用毛巾套装，颜色整洁。</t>
+  </si>
+  <si>
+    <t>Kitchen Towels</t>
+  </si>
+  <si>
+    <t>buy kitchen towels online; shop kitchen towels; kitchen towels for everyday use; kitchen towels for cleaning; kitchen towels for drying dishes; absorbent kitchen towels; cotton kitchen towels; waffle weave kitchen towels; kitchen towel set; kitchen towel bundle; kitchen towels like Williams Sonoma; reusable kitchen towels</t>
+  </si>
+  <si>
+    <t>76353,76363,76373,76383,76393,76403,76413,76423,76433,76443</t>
+  </si>
+  <si>
+    <t>Home &amp; Garden|||Vases</t>
+  </si>
+  <si>
+    <t>3041 Montrose Ave, Richmond, VA 23222</t>
+  </si>
+  <si>
+    <t>amforaes.com</t>
+  </si>
+  <si>
+    <t>Simple Floral Moments Start Right Here | Vases | Amfora</t>
+  </si>
+  <si>
+    <t>简单花艺时刻从这里开始 | 花瓶 | Amfora</t>
+  </si>
+  <si>
+    <t>Sculptural vases give fresh or dried stems a clean focal point on shelves and tables. Browse glass, ceramic, and stoneware vases in small to oversized shapes.</t>
+  </si>
+  <si>
+    <t>雕塑感花瓶为鲜花或干枝在搁架和桌面上提供清爽焦点。浏览玻璃、陶瓷和炻器花瓶，从小号到超大尺寸。</t>
+  </si>
+  <si>
+    <t>buy vases online; shop vases; vases for living room decor; vases for dining table; vases for shelf styling; ceramic vases; glass vases; stoneware vases; vase set; vase bundle; vases like West Elm; small bud vases</t>
+  </si>
+  <si>
+    <t>76352,76362,76372,76382,76392,76402,76412,76422,76432,76442</t>
+  </si>
+  <si>
+    <t>Decor|||Mirrors</t>
+  </si>
+  <si>
+    <t>1058 Lake Glen Way, Sacramento, CA 95822</t>
+  </si>
+  <si>
+    <t>reflaires.com</t>
+  </si>
+  <si>
+    <t>Mirrors for Entryways, Bedrooms &amp; Wall Decor | Reflaire</t>
+  </si>
+  <si>
+    <t>适用于入口、卧室和墙面装饰的镜子 | Reflaire</t>
+  </si>
+  <si>
+    <t>Well-placed mirrors open up small rooms and brighten dark corners with reflected light. Find wall mirrors, floor mirrors, and vanity mirrors for every space.</t>
+  </si>
+  <si>
+    <t>摆放得当的镜子通过反射光线让狭小房间更开阔、照亮暗角。查找壁镜、落地镜和化妆镜，适合每个空间。</t>
+  </si>
+  <si>
+    <t>Mirrors</t>
+  </si>
+  <si>
+    <t>buy mirrors online; shop mirrors; mirrors for entryway; mirrors for bedroom walls; mirrors for small rooms; wall mirrors; floor mirrors; vanity mirrors; mirror set; mirror bundle; mirrors like Anthropologie; round mirrors</t>
+  </si>
+  <si>
+    <t>76351,76361,76371,76381,76391,76401,76411,76421,76431,76441</t>
+  </si>
+  <si>
+    <t>Flowers &amp; Plants|||Stems &amp; Branches</t>
+  </si>
+  <si>
+    <t>3353 Isadora Dr, San Jose, CA 95132</t>
+  </si>
+  <si>
+    <t>stemmaram.com</t>
+  </si>
+  <si>
+    <t>Everyday Natural Charm with Stems &amp; Branches | Stemmara</t>
+  </si>
+  <si>
+    <t>日常自然魅力，搭配花茎与枝条 | Stemmara</t>
+  </si>
+  <si>
+    <t>Realistic stems &amp; branches add lasting greenery to vases and shelves. Discover eucalyptus, willow, blossom, and mixed branch bundles for home styling.</t>
+  </si>
+  <si>
+    <t>逼真的花茎与枝条为花瓶和搁架增添持久绿意。探索桉树、柳枝、花枝和混合枝条束，用于家居造型。</t>
+  </si>
+  <si>
+    <t>Stems &amp; Branches</t>
+  </si>
+  <si>
+    <t>buy stems and branches online; shop stems and branches; stems and branches for vases; stems and branches for home decor; stems and branches for centerpieces; realistic stems and branches; dried stems and branches; artificial stems and branches; stems and branches bundle; stems and branches set; stems and branches like Afloral; eucalyptus stems and branches</t>
+  </si>
+  <si>
+    <t>76350,76360,76370,76380,76390,76400,76410,76420,76430,76440</t>
+  </si>
+  <si>
+    <t>Home &amp; Garden|||Cushions &amp; Pillows</t>
+  </si>
+  <si>
+    <t>396 Florence Ave, Oakland, CA 94618</t>
+  </si>
+  <si>
+    <t>plushorae.com</t>
+  </si>
+  <si>
+    <t>Cushions &amp; Pillows | Cozy Throws &amp; Covers | Plushora</t>
+  </si>
+  <si>
+    <t>靠垫与枕头 | 舒适盖毯与套子 | Plushora</t>
+  </si>
+  <si>
+    <t>Layered cushions &amp; pillows make sofas, beds, and reading nooks feel inviting. Shop lumbar, floor, and outdoor pillow inserts and covers in soft fabrics.</t>
+  </si>
+  <si>
+    <t>分层靠垫与枕头让沙发、床和阅读角落倍感温馨。选购腰枕、落地枕和户外枕芯及套子，采用柔软面料。</t>
+  </si>
+  <si>
+    <t>Cushions &amp; Pillows</t>
+  </si>
+  <si>
+    <t>buy cushions and pillows online; shop cushions and pillows; cushions and pillows for sofa; cushions and pillows for bed; cushions and pillows for outdoor seating; soft cushions and pillows; lumbar cushions and pillows; outdoor cushions and pillows; cushion and pillow set; cushion and pillow bundle; cushions and pillows like Pottery Barn; throw cushions and pillows</t>
+  </si>
+  <si>
+    <t>76456,76460,76464,76468,76472,76476,76480,76484,76488</t>
+  </si>
+  <si>
+    <t>Office Supplies|||Laser Toner</t>
+  </si>
+  <si>
+    <t>766 E 41st St, Los Angeles, CA 90011</t>
+  </si>
+  <si>
+    <t>cartivol.com</t>
+  </si>
+  <si>
+    <t>Laser Toner &amp; Cartridges - Reliable Prints | Cartivo</t>
+  </si>
+  <si>
+    <t>激光碳粉及硒鼓——可靠打印 | Cartivo</t>
+  </si>
+  <si>
+    <t>Laser toner cartridges deliver sharp, reliable prints for home offices and work teams. Explore toner cartridges and drum units built to reduce downtime. Shop now.</t>
+  </si>
+  <si>
+    <t>激光碳粉盒为家庭办公室和工作团队提供清晰、可靠的打印效果。选购专为减少停机而设计的碳粉盒和硒鼓单元。立即选购。</t>
+  </si>
+  <si>
+    <t>Laser Toner</t>
+  </si>
+  <si>
+    <t>buy laser toner online; laser toner for sale; order laser toner cartridges; laser toner for home office; laser toner for business; laser toner for everyday printing; high-yield laser toner cartridges; quality laser toner cartridges; durable laser toner cartridges; laser toner cartridge bundle; laser toner starter kit; laser toner and drum unit set; laser toner alternative to oem cartridges; laser toner replacement for oem cartridges</t>
+  </si>
+  <si>
+    <t>76455,76459,76463,76467,76471,76475,76479,76483,76487</t>
+  </si>
+  <si>
+    <t>Office Supplies|||Printer &amp; Copier Paper</t>
+  </si>
+  <si>
+    <t>3551 Millicent Ct, San Jose, CA 95148</t>
+  </si>
+  <si>
+    <t>folieras.com</t>
+  </si>
+  <si>
+    <t>Shop Printer &amp; Copier Paper | Crisp Output | Foliera</t>
+  </si>
+  <si>
+    <t>选购打印机和复印纸 | 清晰输出 | Foliera</t>
+  </si>
+  <si>
+    <t>Printer &amp; copier paper designed for crisp, jam-free results in everyday office printing. Explore multipurpose paper, cardstock, envelopes, and labels. Shop now.</t>
+  </si>
+  <si>
+    <t>专为日常办公打印提供清晰、无卡纸效果的打印机和复印纸。选购多用途纸、卡纸、信封和标签。立即选购。</t>
+  </si>
+  <si>
+    <t>Printer &amp; Copier Paper</t>
+  </si>
+  <si>
+    <t>buy printer &amp; copier paper online; printer &amp; copier paper for sale; order printer &amp; copier paper in bulk; printer &amp; copier paper for office use; printer &amp; copier paper for home office; printer &amp; copier paper for everyday printing; quality printer &amp; copier paper; bright white printer &amp; copier paper; jam-free printer &amp; copier paper; printer &amp; copier paper case pack; printer &amp; copier paper bundle with envelopes; printer &amp; copier paper alternative to generic brands; printer &amp; copier paper vs store brand</t>
+  </si>
+  <si>
+    <t>76454,76458,76462,76466,76470,76474,76478,76482,76486</t>
+  </si>
+  <si>
+    <t>Office Supplies|||Resin</t>
+  </si>
+  <si>
+    <t>5384 Pecan Blossom Dr, San Jose, CA 95123</t>
+  </si>
+  <si>
+    <t>curelaly.com</t>
+  </si>
+  <si>
+    <t>Resin for Office Printing | Clear Results | Curelay</t>
+  </si>
+  <si>
+    <t>办公打印用树脂 | 清晰效果 | Curelay</t>
+  </si>
+  <si>
+    <t>Resin supplies designed for clean, reliable office printing and prototyping. Explore resin cartridges, printheads, and maintenance fluid. Shop now.</t>
+  </si>
+  <si>
+    <t>专为洁净、可靠的办公打印和原型制作而设计的树脂耗材。选购树脂盒、打印头和保养液。立即选购。</t>
+  </si>
+  <si>
+    <t>Resin</t>
+  </si>
+  <si>
+    <t>buy resin for office printers; resin for sale; order resin cartridges online; resin for office printing; resin for home office use; resin for everyday prototyping; quality resin cartridges; durable resin for printing; low-odor resin; resin cartridge bundle; resin starter kit; resin and printhead set; resin alternative to oem cartridges; resin vs oem cartridges</t>
+  </si>
+  <si>
+    <t>76453,76457,76461,76465,76469,76473,76477,76481,76485,76489</t>
+  </si>
+  <si>
+    <t>Office Supplies|||Printers</t>
+  </si>
+  <si>
+    <t>9533 Soaring Oaks Dr, Elk Grove, CA 95758</t>
+  </si>
+  <si>
+    <t>velliex.com</t>
+  </si>
+  <si>
+    <t>Vellix: Reliable Office Printers &amp; Printer Supplies</t>
+  </si>
+  <si>
+    <t>Vellix：可靠办公打印机及打印耗材</t>
+  </si>
+  <si>
+    <t>Printers built for dependable everyday output in home offices and workplaces. Explore laser printers, all-in-one models, printer paper, and ink cartridges. Shop now.</t>
+  </si>
+  <si>
+    <t>为家庭办公室和工作场所提供可靠日常输出的打印机。选购激光打印机、多功能一体机、打印纸和墨盒。立即选购。</t>
+  </si>
+  <si>
+    <t>Printers</t>
+  </si>
+  <si>
+    <t>buy printers online; printers for sale; order office printers; printers for home office; printers for small business; printers for everyday use; quality printers for office; wireless printers; all-in-one printers; compact printers; printers and ink bundle; printers with starter kit; printers alternative to leading brands; printers vs multifunction devices</t>
+  </si>
+  <si>
+    <t>76511,76522,76533,76544,76555,76566,76577</t>
+  </si>
+  <si>
+    <t>Toys &amp; Games|||Stuffed Animals &amp; Plush Toys</t>
+  </si>
+  <si>
+    <t>1151 E 45th St, Los Angeles, CA 90011</t>
+  </si>
+  <si>
+    <t>Stuffed Animals &amp; Plush Toys | Soft &amp; Durable | Plushora</t>
+  </si>
+  <si>
+    <t>毛绒动物和毛绒玩具 | 柔软耐用 | Plushora</t>
+  </si>
+  <si>
+    <t>Soft, durable stuffed animals and plush toys for everyday snuggles. Browse plush bears, cats, dogs, and nursery sets made with quality fabrics. Shop now.</t>
+  </si>
+  <si>
+    <t>柔软耐用的毛绒动物和毛绒玩具，适合日常依偎。浏览毛绒熊、猫、狗和婴儿房套装，采用优质面料制成。立即选购。</t>
+  </si>
+  <si>
+    <t>Stuffed Animals &amp; Plush Toys</t>
+  </si>
+  <si>
+    <t>buy stuffed animals &amp; plush toys online; stuffed animals &amp; plush toys for toddlers; soft stuffed animals &amp; plush toys; stuffed animals &amp; plush toys gift set; affordable stuffed animals &amp; plush toys; large stuffed animals &amp; plush toys; cute stuffed animals &amp; plush toys; stuffed animals &amp; plush toys bundle; stuffed animals &amp; plush toys for nursery; high quality stuffed animals &amp; plush toys; stuffed animals &amp; plush toys set for baby; stuffed animals &amp; plush toys like Jellycat; stuffed animals &amp; plush toys with washable fabric; shop stuffed animals &amp; plush toys; stuffed animals &amp; plush toys for collectors</t>
+  </si>
+  <si>
+    <t>76510,76521,76532,76543,76554,76565,76576</t>
+  </si>
+  <si>
+    <t>Military|||1:35 Scale</t>
+  </si>
+  <si>
+    <t>5958 Pala Mesa Dr, San Jose, CA 95123</t>
+  </si>
+  <si>
+    <t>scalemintt.com</t>
+  </si>
+  <si>
+    <t>Shop 1:35 Scale Military Models &amp; Kits | Scalemint</t>
+  </si>
+  <si>
+    <t>选购 1:35 比例军事模型和套件 | Scalemint</t>
+  </si>
+  <si>
+    <t>1:35 scale military models and kits for collectors and diorama builders. Browse tanks, armored vehicles, figures, and accessory packs with sharp detail. Start here.</t>
+  </si>
+  <si>
+    <t>1:35 比例军事模型和套件，适合收藏家和场景制作者。浏览坦克、装甲车辆、人偶和配件包，细节清晰。从这里开始。</t>
+  </si>
+  <si>
+    <t>1:35 Scale Military Models</t>
+  </si>
+  <si>
+    <t>buy 1:35 scale military models online; 1:35 scale military models for dioramas; quality 1:35 scale military models; 1:35 scale military model kit bundle; 1:35 scale military models for collectors; 1:35 scale military model starter set; 1:35 scale military models tank; 1:35 scale military models and figures; affordable 1:35 scale military models; 1:35 scale military models World War II; 1:35 scale military models with photo etch parts; shop 1:35 scale military models; 1:35 scale military models like Tamiya</t>
+  </si>
+  <si>
+    <t>76509,76520,76531,76542,76553,76564,76575</t>
+  </si>
+  <si>
+    <t>One Piece|||Singles</t>
+  </si>
+  <si>
+    <t>7613 Killdeer Way, Elk Grove, CA 95758</t>
+  </si>
+  <si>
+    <t>deckboundd.com</t>
+  </si>
+  <si>
+    <t>One Piece Singles &amp; Booster Packs | TCG | Deckbound</t>
+  </si>
+  <si>
+    <t>One Piece 单卡和补充包 | TCG | Deckbound</t>
+  </si>
+  <si>
+    <t>One Piece singles and booster packs for collectors and TCG players. Browse rare cards, graded singles, sealed packs, and deck boxes. Find yours today.</t>
+  </si>
+  <si>
+    <t>One Piece 单卡和补充包，适合收藏家和 TCG 玩家。浏览稀有卡牌、评级单卡、密封补充包和卡组盒。今日找到属于你的。</t>
+  </si>
+  <si>
+    <t>One Piece Singles</t>
+  </si>
+  <si>
+    <t>buy One Piece singles online; One Piece singles for deck building; rare One Piece singles; One Piece singles and booster packs; One Piece singles graded; One Piece singles gift bundle; One Piece singles for collectors; One Piece singles like Manga Rare; shop One Piece singles; One Piece singles for TCG players; One Piece singles starter kit; affordable One Piece singles; One Piece singles near mint; One Piece singles set</t>
+  </si>
+  <si>
+    <t>76508,76519,76530,76541,76552,76563,76574</t>
+  </si>
+  <si>
+    <t>Model Trains &amp; Train Sets|||Train Engines &amp; Cars</t>
+  </si>
+  <si>
+    <t>1026 Mountain Blvd, Oakland, CA 94611</t>
+  </si>
+  <si>
+    <t>railtide.com</t>
+  </si>
+  <si>
+    <t>Train Engines &amp; Cars for Model Railroads | Railtide</t>
+  </si>
+  <si>
+    <t>用于模型铁路的火车机车和车厢 | Railtide</t>
+  </si>
+  <si>
+    <t>Train engines and cars for HO scale model railroading. Browse locomotives, freight cars, passenger cars, and track sets from quality model train brands. Start here.</t>
+  </si>
+  <si>
+    <t>用于 HO 比例模型铁路的火车机车和车厢。浏览来自优质模型火车品牌的机车、货运车厢、客运车厢和轨道套装。从这里开始。</t>
+  </si>
+  <si>
+    <t>Train Engines &amp; Cars</t>
+  </si>
+  <si>
+    <t>buy train engines &amp; cars online; train engines &amp; cars for HO scale; durable train engines &amp; cars; train engines &amp; cars bundle; train engines &amp; cars for model railroads; train engines &amp; cars set; train engines &amp; cars like Bachmann; shop train engines &amp; cars; train engines &amp; cars for beginners; train engines &amp; cars with DCC; train engines &amp; cars replacement wheels; train engines &amp; cars and track sets</t>
+  </si>
+  <si>
+    <t>76507,76518,76529,76540,76551,76562,76573</t>
+  </si>
+  <si>
+    <t>Toys &amp; Games|||Action Figures</t>
+  </si>
+  <si>
+    <t>7150 Vía Lomas, San Jose, CA 95139</t>
+  </si>
+  <si>
+    <t>figversel.com</t>
+  </si>
+  <si>
+    <t>Your Display Starts Here | Action Figures | Figverse</t>
+  </si>
+  <si>
+    <t>你的展示从这里开始 | 动作人偶 | Figverse</t>
+  </si>
+  <si>
+    <t>Action figures and collectible display pieces for serious collectors. Browse movie characters, anime heroes, game icons, and display stands. Shop now.</t>
+  </si>
+  <si>
+    <t>动作人偶和收藏展示品，适合认真的收藏家。浏览电影角色、动漫英雄、游戏角色和展示支架。立即选购。</t>
+  </si>
+  <si>
+    <t>Action Figures</t>
+  </si>
+  <si>
+    <t>buy action figures online; action figures for collectors; quality action figures; action figures gift set; action figures for display; action figures bundle; action figures like Marvel Legends; shop action figures; action figures with accessories; action figures for kids; action figures set of 6; action figures and display stands</t>
+  </si>
+  <si>
+    <t>76506,76517,76528,76539,76550,76561,76572</t>
+  </si>
+  <si>
+    <t>Boards|||NCAA Team</t>
+  </si>
+  <si>
+    <t>24662 Via San Anselmo, Mission Viejo, CA 92692</t>
+  </si>
+  <si>
+    <t>boardlineas.com</t>
+  </si>
+  <si>
+    <t>Boardline. NCAA team boards built for tailgate season.</t>
+  </si>
+  <si>
+    <t>Boardline。为车尾派对季打造的 NCAA 球队板。</t>
+  </si>
+  <si>
+    <t>NCAA team boards built for tailgate season and game day. Browse college cornhole boards, wall boards, team sets, and carrying cases in team colors. Shop now</t>
+  </si>
+  <si>
+    <t>为车尾派对季和比赛日打造的 NCAA 球队板。浏览大学玉米洞板、挂板、球队套装和便携包，采用球队配色。立即选购</t>
+  </si>
+  <si>
+    <t>NCAA Team Boards</t>
+  </si>
+  <si>
+    <t>buy NCAA team boards online; NCAA team boards for tailgate parties; durable NCAA team boards; NCAA team boards with carrying case; NCAA team boards set; NCAA team boards for cornhole; NCAA team boards like Victory Tailgate; shop NCAA team boards; NCAA team boards for college game day; NCAA team boards and bags; NCAA team boards for home; NCAA team boards gift</t>
+  </si>
+  <si>
+    <t>76505,76516,76527,76538,76549,76560,76571,76582</t>
+  </si>
+  <si>
+    <t>Remote Control Toys|||RC Airplanes</t>
+  </si>
+  <si>
+    <t>4023 Mt Vernon St, Richmond, VA 23227</t>
+  </si>
+  <si>
+    <t>skyfoill.com</t>
+  </si>
+  <si>
+    <t>Skyfoil: RC Airplanes, Kits &amp; Flight Gear for All Pilots</t>
+  </si>
+  <si>
+    <t>Skyfoil：适合所有飞手的 RC 飞机、套件和飞行装备</t>
+  </si>
+  <si>
+    <t>RC airplanes and flight gear for all pilot levels. Browse remote control planes, foam flyers, spare parts, and starter kits with stable flight control. Shop now.</t>
+  </si>
+  <si>
+    <t>RC 飞机和飞行装备，适合所有飞手水平。浏览遥控飞机、泡沫飞行器、备件和入门套件，飞行控制稳定。立即选购。</t>
+  </si>
+  <si>
+    <t>RC Airplanes</t>
+  </si>
+  <si>
+    <t>buy RC airplanes online; RC airplanes for beginners; durable RC airplanes; RC airplanes starter kit; RC airplanes for kids; RC airplanes bundle; RC airplanes like E-flite; shop RC airplanes; RC airplanes with spare parts; RC airplanes for intermediate pilots; RC airplanes foam; RC airplanes and transmitters</t>
+  </si>
+  <si>
+    <t>76504,76515,76526,76537,76548,76559,76570,76581</t>
+  </si>
+  <si>
+    <t>Toys &amp; Games|||Trading Cards</t>
+  </si>
+  <si>
+    <t>20 Cheltenham Way, San Jose, CA 95139</t>
+  </si>
+  <si>
+    <t>cardrifty.com</t>
+  </si>
+  <si>
+    <t>Trading Cards &amp; Sealed Packs - Collector Grade | Cardrift</t>
+  </si>
+  <si>
+    <t>交易卡和密封补充包——收藏级 | Cardrift</t>
+  </si>
+  <si>
+    <t>Trading cards and sealed packs for collectors and players. Browse sports cards, trading card game singles, graded cards, and storage boxes. Start here.</t>
+  </si>
+  <si>
+    <t>交易卡和密封补充包，适合收藏家和玩家。浏览运动卡、集换式卡牌单卡、评级卡和收纳盒。从这里开始。</t>
+  </si>
+  <si>
+    <t>Trading Cards</t>
+  </si>
+  <si>
+    <t>buy trading cards online; trading cards for collectors; rare trading cards; trading cards and sealed packs; trading cards gift set; trading cards for kids; trading cards like Pokemon; shop trading cards; trading cards box; trading cards and storage boxes; trading cards for deck building; trading cards graded</t>
+  </si>
+  <si>
+    <t>76503,76514,76525,76536,76547,76558,76569,76580</t>
+  </si>
+  <si>
+    <t>RC Parts|||Replacement Parts</t>
+  </si>
+  <si>
+    <t>6501 Castelletto Ct, Elk Grove, CA 95757</t>
+  </si>
+  <si>
+    <t>replixly.com</t>
+  </si>
+  <si>
+    <t>Replix: Durable Replacement Parts for RC Models &amp; Kits</t>
+  </si>
+  <si>
+    <t>Replix：用于 RC 模型和套件的耐用替换零件</t>
+  </si>
+  <si>
+    <t>Durable replacement parts for RC models and kits. Browse axles, gears, body shells, screws, and connectors that fit common remote control brands. Start here.</t>
+  </si>
+  <si>
+    <t>用于 RC 模型和套件的耐用替换零件。浏览适用于常见遥控品牌的车轴、齿轮、车壳、螺丝和连接器。从这里开始。</t>
+  </si>
+  <si>
+    <t>Replacement Parts</t>
+  </si>
+  <si>
+    <t>buy replacement parts for RC cars; replacement parts for RC airplanes; durable replacement parts; replacement parts for RC models; replacement parts bundle; replacement parts for RC trucks; replacement parts like Traxxas; shop replacement parts online; replacement parts for RC boats; replacement parts and hardware; replacement parts set; replacement parts for remote control toys</t>
+  </si>
+  <si>
+    <t>76502,76513,76524,76535,76546,76557,76568,76579</t>
+  </si>
+  <si>
+    <t>Remote Control Toys|||Slot Cars</t>
+  </si>
+  <si>
+    <t>1604 D St SE, Washington, DC 20003</t>
+  </si>
+  <si>
+    <t>lanevolt.com</t>
+  </si>
+  <si>
+    <t>Shop Slot Cars &amp; HO Track Sets | Race Ready | Lanevolt</t>
+  </si>
+  <si>
+    <t>选购 Slot Cars 和 HO 轨道套装 | 竞赛就绪 | Lanevolt</t>
+  </si>
+  <si>
+    <t>Slot cars and HO track sets for home racing. Browse 1:32 and 1:64 scale cars, track pieces, and controllers built for smooth electric racing. Shop now.</t>
+  </si>
+  <si>
+    <t>用于家庭竞速的 Slot Cars 和 HO 轨道套装。浏览 1:32 和 1:64 比例赛车、轨道组件和控制器，为平稳电动竞赛而生。立即选购。</t>
+  </si>
+  <si>
+    <t>Slot Cars</t>
+  </si>
+  <si>
+    <t>buy slot cars online; slot cars for home racing; durable slot cars; slot cars starter set; slot cars for kids; slot cars bundle; slot cars like Carrera; shop slot cars; slot cars and HO track sets; slot cars 1:32 scale; slot cars for collectors; slot cars and controllers</t>
+  </si>
+  <si>
+    <t>76501,76512,76523,76534,76545,76556,76567,76578</t>
+  </si>
+  <si>
+    <t>Dolls &amp; Accessories|||Dolls</t>
+  </si>
+  <si>
+    <t>2131 E Oliver St, Baltimore, MD 21213</t>
+  </si>
+  <si>
+    <t>dollviae.com</t>
+  </si>
+  <si>
+    <t>Soft Dolls &amp; Accessories for Everyday Play | Dollvia</t>
+  </si>
+  <si>
+    <t>用于日常玩耍的柔软娃娃和配件 | Dollvia</t>
+  </si>
+  <si>
+    <t>Dolls and accessories for everyday play. Browse baby dolls, fashion dolls, doll clothes, strollers, and playsets made from child-safe materials. Shop now.</t>
+  </si>
+  <si>
+    <t>用于日常玩耍的娃娃和配件。浏览婴儿娃娃、时尚娃娃、娃娃衣服、推车和游戏套装，采用儿童安全材料制成。立即选购。</t>
+  </si>
+  <si>
+    <t>Dolls</t>
+  </si>
+  <si>
+    <t>buy dolls online; dolls for toddlers; soft dolls; dolls gift set; dolls for kids; dolls bundle; dolls like American Girl; shop dolls; dolls and accessories; dolls with clothes; dolls for collectors; dolls set</t>
+  </si>
+  <si>
+    <t>76752,76764,76776,76788,76800,76812,76824,76836,76848</t>
+  </si>
+  <si>
+    <t>Disc Sports|||Discs</t>
+  </si>
+  <si>
+    <t>1260 E 47th Pl, Los Angeles, CA 90011</t>
+  </si>
+  <si>
+    <t>volarol.com</t>
+  </si>
+  <si>
+    <t>Shop Discs | Premium Quality &amp; Consistent Spin | Volaro</t>
+  </si>
+  <si>
+    <t>选购飞盘 | 优质品质与稳定旋转 | Volaro</t>
+  </si>
+  <si>
+    <t>Durable discs built for precise throws and steady flight, whether for disc golf or ultimate. Explore drivers, putters, bags, and baskets. Shop now.</t>
+  </si>
+  <si>
+    <t>耐用飞盘专为精准投掷和稳定飞行而设计，适用于飞盘高尔夫或极限飞盘。探索驱动盘、推杆盘、飞盘包和收纳篮。立即选购。</t>
+  </si>
+  <si>
+    <t>Discs</t>
+  </si>
+  <si>
+    <t>buy discs online; discs for disc golf; discs for ultimate frisbee; durable discs for beginners; lightweight discs for long throws; disc golf disc set; ultimate frisbee disc pack; starter disc bundle; discs like Innova; Innova disc alternatives; disc replacement for drivers; order discs online; professional disc golf discs</t>
+  </si>
+  <si>
+    <t>76751,76763,76775,76787,76799,76811,76823,76835,76847</t>
+  </si>
+  <si>
+    <t>Activewear|||Jerseys</t>
+  </si>
+  <si>
+    <t>1915 Rose Ave, Richmond, VA 23222</t>
+  </si>
+  <si>
+    <t>averlely.com</t>
+  </si>
+  <si>
+    <t>Averly: Jerseys &amp; Performance Athletic Apparel for Teams</t>
+  </si>
+  <si>
+    <t>Averly：运动衫与高性能运动服饰，适合团队</t>
+  </si>
+  <si>
+    <t>Breathable jerseys designed for team sports, weekend leagues, and everyday training. Explore performance tops, shorts, warm-ups, and socks. Start here.</t>
+  </si>
+  <si>
+    <t>透气运动衫专为团队运动、周末联赛和日常训练而设计。探索运动上衣、短裤、热身服和袜子。从这里开始。</t>
+  </si>
+  <si>
+    <t>Jerseys</t>
+  </si>
+  <si>
+    <t>buy jerseys online; team jerseys for basketball; youth jerseys for leagues; breathable jerseys for summer games; moisture-wicking jerseys for training; matching jersey set; team jersey bundle; starter jersey pack; jerseys like Nike; Nike jersey alternatives; jersey replacement for teams; order jerseys online; affordable jerseys for squads</t>
+  </si>
+  <si>
+    <t>76750,76762,76774,76786,76798,76810,76822,76834,76846</t>
+  </si>
+  <si>
+    <t>Skateboard Accessories|||Wheels</t>
+  </si>
+  <si>
+    <t>1626 Bradley St, Dallas, TX 75208</t>
+  </si>
+  <si>
+    <t>rollixey.com</t>
+  </si>
+  <si>
+    <t>Skateboard Wheels | Durable Smooth Urethane | Rollix</t>
+  </si>
+  <si>
+    <t>滑板轮 | 耐用顺滑聚氨酯 | Rollix</t>
+  </si>
+  <si>
+    <t>Quality wheels built for skate parks, street skating, and everyday commutes. Explore skateboard wheels, bearings, trucks, and grip tape. Shop now.</t>
+  </si>
+  <si>
+    <t>高品质滑板轮专为滑板公园、街式和日常通勤而打造。探索滑板轮、轴承、桥架和防滑砂纸。立即选购。</t>
+  </si>
+  <si>
+    <t>Wheels</t>
+  </si>
+  <si>
+    <t>buy skateboard wheels online; skateboard wheels for street skating; skateboard wheels for park riding; durable skateboard wheels for heavy riders; soft skateboard wheels for rough roads; skateboard wheel set; skateboard wheels bundle with bearings; wheels like Spitfire; Spitfire wheel alternatives; replacement skateboard wheels; order skateboard wheels online; lightweight skateboard wheels; hard skateboard wheels for tricks</t>
+  </si>
+  <si>
+    <t>76749,76761,76773,76785,76797,76809,76821,76833,76845</t>
+  </si>
+  <si>
+    <t>Bicycle Parts|||Grips</t>
+  </si>
+  <si>
+    <t>8257 Barryman Ct, Sacramento, CA 95829</t>
+  </si>
+  <si>
+    <t>tactisy.com</t>
+  </si>
+  <si>
+    <t>Tactis: Comfort-Focused Grips for Skateboard Riders</t>
+  </si>
+  <si>
+    <t>Tactis：面向滑板骑手的舒适型握把</t>
+  </si>
+  <si>
+    <t>Comfort-focused grips designed for better control on skateboards, scooters, and bikes. Explore skateboard grips, handlebar grips, grip tape, and bar ends. Shop now.</t>
+  </si>
+  <si>
+    <t>舒适型握把专为滑板、滑板车和自行车提供更好操控而设计。探索滑板握把、车把握把、防滑胶带和把端。立即选购。</t>
+  </si>
+  <si>
+    <t>Grips</t>
+  </si>
+  <si>
+    <t>buy skateboard grips online; grips for skateboards and scooters; bike grips for everyday riding; durable grips for street use; soft grips for long sessions; skateboard grip tape set; handlebar grips bundle; grips like ODI; ODI grip alternatives; replacement grips for bikes; order grips online; lightweight grips for riders; comfortable grips for commuters</t>
+  </si>
+  <si>
+    <t>76748,76760,76772,76784,76796,76808,76820,76832,76844</t>
+  </si>
+  <si>
+    <t>Protective Gear|||Helmets</t>
+  </si>
+  <si>
+    <t>1243 D St NE, Washington, DC 20002</t>
+  </si>
+  <si>
+    <t>ventixas.com</t>
+  </si>
+  <si>
+    <t>Protective Helmets &amp; Multi-Sport Gear - Stay Safe | Ventix</t>
+  </si>
+  <si>
+    <t>防护头盔与多运动装备——保持安全 | Ventix</t>
+  </si>
+  <si>
+    <t>Protective helmets designed for skating, cycling, and snow sports with lightweight impact protection. Explore skate, bike, and snow helmets plus pads. Shop now.</t>
+  </si>
+  <si>
+    <t>防护头盔专为滑冰、骑行和雪地运动设计，具有轻量冲击防护。探索滑板头盔、自行车头盔、雪地头盔和护具。立即选购。</t>
+  </si>
+  <si>
+    <t>Helmets</t>
+  </si>
+  <si>
+    <t>buy protective helmets online; helmets for skateboarding; bike helmets for commuting; snow helmets for skiing; lightweight helmets for long rides; durable helmets for youth sports; helmet set with pads; helmet bundle with gloves; helmets like Giro; Giro helmet alternatives; replacement helmet for skating; order helmets online; ventilated helmets for summer</t>
+  </si>
+  <si>
+    <t>76747,76759,76771,76783,76795,76807,76819,76831,76843</t>
+  </si>
+  <si>
+    <t>Skiing|||Ski Boots</t>
+  </si>
+  <si>
+    <t>1841 E 68th St, Los Angeles, CA 90001</t>
+  </si>
+  <si>
+    <t>alpivop.com</t>
+  </si>
+  <si>
+    <t>Alpivo. Ski Boots built for all-mountain performance.</t>
+  </si>
+  <si>
+    <t>Alpivo。为全山地性能打造的滑雪靴。</t>
+  </si>
+  <si>
+    <t>Ski boots built for all-mountain control and warm, comfortable days on the slopes. Explore ski boots, insoles, ski socks, and boot bags. Start here.</t>
+  </si>
+  <si>
+    <t>滑雪靴专为全山地控制力和温暖舒适的雪上时光而打造。探索滑雪靴、鞋垫、滑雪袜和雪靴包。从这里开始。</t>
+  </si>
+  <si>
+    <t>Ski Boots</t>
+  </si>
+  <si>
+    <t>buy ski boots online; ski boots for all-mountain skiing; ski boots for beginners; comfortable ski boots for wide feet; lightweight ski boots for touring; ski boot set with insoles; ski boot bundle with bags; ski boots like Salomon; Salomon ski boot alternatives; replacement ski boots for skiers; order ski boots online; stiff ski boots for advanced skiers; warm ski boots for cold days</t>
+  </si>
+  <si>
+    <t>76746,76758,76770,76782,76794,76806,76818,76830,76842</t>
+  </si>
+  <si>
+    <t>Lures|||Hard Baits</t>
+  </si>
+  <si>
+    <t>10015 Broadway Terrace, Oakland, CA 94611</t>
+  </si>
+  <si>
+    <t>finzlly.com</t>
+  </si>
+  <si>
+    <t>Your Next Catch Starts Here | Quality Hard Baits | Finzly</t>
+  </si>
+  <si>
+    <t>你的下一次渔获从这里开始 | 优质硬饵 | Finzly</t>
+  </si>
+  <si>
+    <t>Hard baits engineered for lifelike action and sharp hooks in fresh or salt water. Explore crankbaits, jerkbaits, topwater lures, and tackle boxes. Shop now.</t>
+  </si>
+  <si>
+    <t>硬饵专为逼真泳姿和锋利鱼钩而设计，适用于淡水或海水。探索摇摆饵、抽停饵、水面系假饵和钓具箱。立即选购。</t>
+  </si>
+  <si>
+    <t>Hard Baits</t>
+  </si>
+  <si>
+    <t>buy hard baits online; hard baits for bass fishing; hard baits for saltwater fishing; durable hard baits for pike; topwater hard baits for summer; hard bait set for beginners; hard bait bundle with tackle box; hard baits like Rapala; Rapala hard bait alternatives; replacement hard baits for tackle boxes; order hard baits online; lifelike hard baits for trout; floating hard baits for shallow water</t>
+  </si>
+  <si>
+    <t>76745,76757,76769,76781,76793,76805,76817,76829,76841</t>
+  </si>
+  <si>
+    <t>Camping &amp; Hiking|||Backpacks &amp; Camping</t>
+  </si>
+  <si>
+    <t>3718 Shelley Blvd, Dallas, TX 75211</t>
+  </si>
+  <si>
+    <t>paktoras.com</t>
+  </si>
+  <si>
+    <t>Backpacks &amp; Camping Gear for Weekend Trail Days | Paktora</t>
+  </si>
+  <si>
+    <t>适合周末山径时日的背包与露营装备 | Paktora</t>
+  </si>
+  <si>
+    <t>Backpacks and camping gear built for weekend trips and long trail days. Explore hiking backpacks, tents, sleeping bags, and camp stoves. Shop now.</t>
+  </si>
+  <si>
+    <t>背包和露营装备专为周末旅行和漫长山径而打造。探索登山背包、帐篷、睡袋和露营炉。立即选购。</t>
+  </si>
+  <si>
+    <t>buy backpacks &amp; camping gear online; backpacks &amp; camping gear for weekend trips; hiking backpacks &amp; camping gear for beginners; lightweight backpacks &amp; camping gear for backpacking; durable backpacks &amp; camping gear for families; backpacks &amp; camping set; backpacks &amp; camping bundle; backpacks &amp; camping gear like Osprey; Osprey backpack alternatives; replacement backpacks &amp; camping gear for hikers; order backpacks &amp; camping gear online; waterproof backpacks &amp; camping gear for rain; affordable backpacks &amp; camping gear for scouts</t>
+  </si>
+  <si>
+    <t>76744,76756,76768,76780,76792,76804,76816,76828,76840,76852</t>
+  </si>
+  <si>
+    <t>Tires|||Mountain Bike Tires</t>
+  </si>
+  <si>
+    <t>1223 N 37th St, Richmond, VA 23223</t>
+  </si>
+  <si>
+    <t>treadixr.com</t>
+  </si>
+  <si>
+    <t>Treadix: Mountain Bike Tires &amp; Trail Accessories for Riders</t>
+  </si>
+  <si>
+    <t>Treadix：适合骑手的山地自行车轮胎与越野配件</t>
+  </si>
+  <si>
+    <t>Mountain bike tires built for grip, durability, and confident cornering on rocky or muddy trails. Explore trail tires, tubeless tires, and sealant. Shop now.</t>
+  </si>
+  <si>
+    <t>山地自行车轮胎专为抓地力、耐用性以及在岩石或泥泞小径上的自信转弯而设计。探索越野轮胎、真空轮胎和密封剂。立即选购。</t>
+  </si>
+  <si>
+    <t>Mountain Bike Tires</t>
+  </si>
+  <si>
+    <t>buy mountain bike tires online; mountain bike tires for trail riding; mountain bike tires for downhill; durable mountain bike tires for rocky trails; tubeless mountain bike tires for mud; mountain bike tire set; mountain bike tires bundle with sealant; mountain bike tires like Maxxis; Maxxis mountain bike tire alternatives; replacement mountain bike tires for 29ers; order mountain bike tires online; lightweight mountain bike tires for cross-country; grippy mountain bike tires for wet roots</t>
+  </si>
+  <si>
+    <t>76743,76755,76767,76779,76791,76803,76815,76827,76839,76851</t>
+  </si>
+  <si>
+    <t>Ice Hockey|||Ice Hockey Sticks</t>
+  </si>
+  <si>
+    <t>9254 Louis St, Elk Grove, CA 95624</t>
+  </si>
+  <si>
+    <t>slaprad.com</t>
+  </si>
+  <si>
+    <t>Slapra. Ice Hockey Sticks built for quick release.</t>
+  </si>
+  <si>
+    <t>Slapra。为快速出球打造的冰球杆。</t>
+  </si>
+  <si>
+    <t>Ice hockey sticks designed for quick release, solid puck feel, and reliable performance in league play. Explore hockey sticks, stick tape, gloves &amp; pucks. Shop now.</t>
+  </si>
+  <si>
+    <t>冰球杆专为快速出球、扎实的控球感和联赛中的可靠表现而设计。探索冰球杆、球杆胶带、手套和冰球。立即选购。</t>
+  </si>
+  <si>
+    <t>Ice Hockey Sticks</t>
+  </si>
+  <si>
+    <t>buy ice hockey sticks online; ice hockey sticks for beginners; ice hockey sticks for defensemen; lightweight ice hockey sticks for quick release; durable ice hockey sticks for league play; ice hockey stick set; ice hockey sticks bundle with tape; ice hockey sticks like Bauer; Bauer ice hockey stick alternatives; replacement ice hockey sticks for players; order ice hockey sticks online; composite ice hockey sticks for accuracy; left-handed ice hockey sticks for forwards</t>
+  </si>
+  <si>
+    <t>76742,76754,76766,76778,76790,76802,76814,76826,76838,76850</t>
+  </si>
+  <si>
+    <t>Golf Clubs|||Putters</t>
+  </si>
+  <si>
+    <t>4674 Larue St, Dallas, TX 75211</t>
+  </si>
+  <si>
+    <t>mulliop.com</t>
+  </si>
+  <si>
+    <t>Mullio: Precision-Milled Putters for Serious Golfers</t>
+  </si>
+  <si>
+    <t>Mullio：面向严肃高尔夫球手的精密铣削推杆</t>
+  </si>
+  <si>
+    <t>Precision-milled putters built for consistent roll, better alignment, and lower scores. Explore blade putters, mallet putters, golf grips, and headcovers. Shop now.</t>
+  </si>
+  <si>
+    <t>精密铣削推杆专为稳定滚动、更好瞄准和更低杆数而设计。探索刀背推杆、半圆推杆、高尔夫握把和杆头套。立即选购。</t>
+  </si>
+  <si>
+    <t>Putters</t>
+  </si>
+  <si>
+    <t>buy putters online; putters for high handicappers; putters for beginners; blade putters for better alignment; mallet putters for forgiveness; putter set with headcover; putters bundle with golf grips; putters like Scotty Cameron; Scotty Cameron putter alternatives; replacement putters for golfers; order putters online; milled putters for consistent roll; face-balanced putters for straight strokes</t>
+  </si>
+  <si>
+    <t>76741,76753,76765,76777,76789,76801,76813,76825,76837,76849</t>
+  </si>
+  <si>
+    <t>Skiing|||Ski Bindings</t>
+  </si>
+  <si>
+    <t>1221 E Mayfair Ave, Orange, CA 92867</t>
+  </si>
+  <si>
+    <t>bindrass.com</t>
+  </si>
+  <si>
+    <t>Bindra: Ski Bindings for Confident All-Mountain Riding</t>
+  </si>
+  <si>
+    <t>Bindra：适合自信全山地滑行的滑雪固定器</t>
+  </si>
+  <si>
+    <t>Ski bindings built for reliable release, precise power transfer, and confident descents. Explore ski bindings, ski brakes, mounting jigs, and ski straps. Shop now.</t>
+  </si>
+  <si>
+    <t>滑雪固定器专为可靠释放、精准动力传递和自信下坡而设计。探索滑雪固定器、滑雪制动器、安装夹具和滑雪绑带。立即选购。</t>
+  </si>
+  <si>
+    <t>Ski Bindings</t>
+  </si>
+  <si>
+    <t>buy ski bindings online; ski bindings for all-mountain skiing; ski bindings for beginners; lightweight ski bindings for touring; durable ski bindings for park skiing; ski binding set with brakes; ski bindings bundle with straps; ski bindings like Marker; Marker ski binding alternatives; replacement ski bindings for skiers; order ski bindings online; adjustable ski bindings for growing feet; freeride ski bindings for powder</t>
+  </si>
 </sst>
 </file>
 
@@ -9107,7 +10778,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9182,13 +10853,6 @@
       <color rgb="FF1F1F1F"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -9691,13 +11355,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -9706,118 +11373,115 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -9913,7 +11577,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -15724,7 +17390,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q282"/>
+  <dimension ref="A1:Q339"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="50.625" customWidth="1"/>
@@ -27690,7 +29356,7 @@
       <c r="B249" s="1" t="s">
         <v>2541</v>
       </c>
-      <c r="C249" s="30">
+      <c r="C249" s="20">
         <v>72077</v>
       </c>
       <c r="D249" t="s">
@@ -27725,13 +29391,16 @@
       </c>
       <c r="P249" s="24" t="s">
         <v>2550</v>
+      </c>
+      <c r="Q249" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="250" ht="108" spans="2:17">
       <c r="B250" s="1" t="s">
         <v>2551</v>
       </c>
-      <c r="C250" s="30">
+      <c r="C250" s="20">
         <v>72076</v>
       </c>
       <c r="D250" t="s">
@@ -27766,13 +29435,16 @@
       </c>
       <c r="P250" s="24" t="s">
         <v>2560</v>
+      </c>
+      <c r="Q250" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="251" ht="121.5" spans="2:17">
       <c r="B251" s="1" t="s">
         <v>2561</v>
       </c>
-      <c r="C251" s="30">
+      <c r="C251" s="20">
         <v>72074</v>
       </c>
       <c r="D251" t="s">
@@ -27807,13 +29479,16 @@
       </c>
       <c r="P251" s="24" t="s">
         <v>2570</v>
+      </c>
+      <c r="Q251" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="252" ht="121.5" spans="2:17">
       <c r="B252" s="1" t="s">
         <v>2571</v>
       </c>
-      <c r="C252" s="30">
+      <c r="C252" s="20">
         <v>72075</v>
       </c>
       <c r="D252" t="s">
@@ -27848,13 +29523,16 @@
       </c>
       <c r="P252" s="24" t="s">
         <v>2580</v>
+      </c>
+      <c r="Q252" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="253" ht="121.5" spans="2:17">
       <c r="B253" s="1" t="s">
         <v>2581</v>
       </c>
-      <c r="C253" s="30">
+      <c r="C253" s="20">
         <v>72073</v>
       </c>
       <c r="D253" t="s">
@@ -27889,13 +29567,16 @@
       </c>
       <c r="P253" s="24" t="s">
         <v>2590</v>
+      </c>
+      <c r="Q253" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="254" ht="135" spans="2:17">
       <c r="B254" s="1" t="s">
         <v>2591</v>
       </c>
-      <c r="C254" s="30">
+      <c r="C254" s="20">
         <v>72071</v>
       </c>
       <c r="D254" t="s">
@@ -27930,13 +29611,16 @@
       </c>
       <c r="P254" s="24" t="s">
         <v>2600</v>
+      </c>
+      <c r="Q254" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="255" ht="121.5" spans="2:17">
       <c r="B255" s="1" t="s">
         <v>2601</v>
       </c>
-      <c r="C255" s="30">
+      <c r="C255" s="20">
         <v>72072</v>
       </c>
       <c r="D255" t="s">
@@ -27971,13 +29655,16 @@
       </c>
       <c r="P255" s="24" t="s">
         <v>2610</v>
+      </c>
+      <c r="Q255" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="256" ht="121.5" spans="2:17">
       <c r="B256" s="1" t="s">
         <v>2611</v>
       </c>
-      <c r="C256" s="30">
+      <c r="C256" s="20">
         <v>72149</v>
       </c>
       <c r="D256" t="s">
@@ -28013,12 +29700,15 @@
       <c r="P256" s="24" t="s">
         <v>2621</v>
       </c>
+      <c r="Q256" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="257" ht="94.5" spans="2:16">
+    <row r="257" ht="94.5" spans="2:17">
       <c r="B257" s="1" t="s">
         <v>2622</v>
       </c>
-      <c r="C257" s="30">
+      <c r="C257" s="20">
         <v>72148</v>
       </c>
       <c r="D257" t="s">
@@ -28054,12 +29744,15 @@
       <c r="P257" s="24" t="s">
         <v>2631</v>
       </c>
+      <c r="Q257" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="258" ht="81" spans="2:16">
+    <row r="258" ht="81" spans="2:17">
       <c r="B258" s="1" t="s">
         <v>2632</v>
       </c>
-      <c r="C258" s="30">
+      <c r="C258" s="20">
         <v>72147</v>
       </c>
       <c r="D258" t="s">
@@ -28095,12 +29788,15 @@
       <c r="P258" s="24" t="s">
         <v>2641</v>
       </c>
+      <c r="Q258" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="259" ht="81" spans="2:16">
+    <row r="259" ht="81" spans="2:17">
       <c r="B259" s="1" t="s">
         <v>2642</v>
       </c>
-      <c r="C259" s="30">
+      <c r="C259" s="20">
         <v>72144</v>
       </c>
       <c r="D259" t="s">
@@ -28136,12 +29832,15 @@
       <c r="P259" s="24" t="s">
         <v>2651</v>
       </c>
+      <c r="Q259" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="260" ht="94.5" spans="2:16">
+    <row r="260" ht="94.5" spans="2:17">
       <c r="B260" s="1" t="s">
         <v>2652</v>
       </c>
-      <c r="C260" s="30">
+      <c r="C260" s="20">
         <v>72145</v>
       </c>
       <c r="D260" t="s">
@@ -28177,12 +29876,15 @@
       <c r="P260" s="24" t="s">
         <v>2661</v>
       </c>
+      <c r="Q260" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="261" ht="121.5" spans="2:16">
+    <row r="261" ht="121.5" spans="2:17">
       <c r="B261" s="1" t="s">
         <v>2662</v>
       </c>
-      <c r="C261" s="30">
+      <c r="C261" s="20">
         <v>72146</v>
       </c>
       <c r="D261" t="s">
@@ -28218,12 +29920,15 @@
       <c r="P261" s="24" t="s">
         <v>2671</v>
       </c>
+      <c r="Q261" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="262" ht="121.5" spans="2:16">
+    <row r="262" ht="121.5" spans="2:17">
       <c r="B262" s="1" t="s">
         <v>2672</v>
       </c>
-      <c r="C262" s="30">
+      <c r="C262" s="20">
         <v>72349</v>
       </c>
       <c r="D262" t="s">
@@ -28260,12 +29965,15 @@
       <c r="P262" s="24" t="s">
         <v>2682</v>
       </c>
+      <c r="Q262" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="263" ht="148.5" spans="2:16">
+    <row r="263" ht="148.5" spans="2:17">
       <c r="B263" s="1" t="s">
         <v>2683</v>
       </c>
-      <c r="C263" s="30">
+      <c r="C263" s="20">
         <v>72345</v>
       </c>
       <c r="D263" t="s">
@@ -28302,12 +30010,15 @@
       <c r="P263" s="24" t="s">
         <v>2692</v>
       </c>
+      <c r="Q263" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="264" ht="121.5" spans="2:16">
+    <row r="264" ht="121.5" spans="2:17">
       <c r="B264" s="1" t="s">
         <v>2693</v>
       </c>
-      <c r="C264" s="30">
+      <c r="C264" s="20">
         <v>72352</v>
       </c>
       <c r="D264" t="s">
@@ -28344,12 +30055,15 @@
       <c r="P264" s="24" t="s">
         <v>2702</v>
       </c>
+      <c r="Q264" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="265" ht="121.5" spans="2:16">
+    <row r="265" ht="121.5" spans="2:17">
       <c r="B265" s="36" t="s">
         <v>2703</v>
       </c>
-      <c r="C265" s="30">
+      <c r="C265" s="20">
         <v>72341</v>
       </c>
       <c r="D265" t="s">
@@ -28386,12 +30100,15 @@
       <c r="P265" s="24" t="s">
         <v>2712</v>
       </c>
+      <c r="Q265" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="266" ht="108" spans="2:16">
+    <row r="266" ht="108" spans="2:17">
       <c r="B266" s="1" t="s">
         <v>2713</v>
       </c>
-      <c r="C266" s="30">
+      <c r="C266" s="20">
         <v>72350</v>
       </c>
       <c r="D266" t="s">
@@ -28428,12 +30145,15 @@
       <c r="P266" s="24" t="s">
         <v>2722</v>
       </c>
+      <c r="Q266" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="267" ht="108" spans="2:16">
+    <row r="267" ht="108" spans="2:17">
       <c r="B267" s="1" t="s">
         <v>2723</v>
       </c>
-      <c r="C267" s="30">
+      <c r="C267" s="20">
         <v>72353</v>
       </c>
       <c r="D267" t="s">
@@ -28470,12 +30190,15 @@
       <c r="P267" s="24" t="s">
         <v>2732</v>
       </c>
+      <c r="Q267" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="268" ht="135" spans="2:16">
+    <row r="268" ht="135" spans="2:17">
       <c r="B268" s="1" t="s">
         <v>2733</v>
       </c>
-      <c r="C268" s="30">
+      <c r="C268" s="20">
         <v>72343</v>
       </c>
       <c r="D268" t="s">
@@ -28512,12 +30235,15 @@
       <c r="P268" s="24" t="s">
         <v>2742</v>
       </c>
+      <c r="Q268" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="269" ht="121.5" spans="2:16">
+    <row r="269" ht="121.5" spans="2:17">
       <c r="B269" s="1" t="s">
         <v>2743</v>
       </c>
-      <c r="C269" s="30">
+      <c r="C269" s="20">
         <v>72347</v>
       </c>
       <c r="D269" t="s">
@@ -28554,12 +30280,15 @@
       <c r="P269" s="24" t="s">
         <v>2752</v>
       </c>
+      <c r="Q269" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="270" ht="121.5" spans="2:16">
+    <row r="270" ht="121.5" spans="2:17">
       <c r="B270" s="1" t="s">
         <v>2753</v>
       </c>
-      <c r="C270" s="30">
+      <c r="C270" s="20">
         <v>72342</v>
       </c>
       <c r="D270" t="s">
@@ -28596,12 +30325,15 @@
       <c r="P270" s="24" t="s">
         <v>2762</v>
       </c>
+      <c r="Q270" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="271" ht="94.5" spans="2:16">
+    <row r="271" ht="94.5" spans="2:17">
       <c r="B271" s="1" t="s">
         <v>2763</v>
       </c>
-      <c r="C271" s="30">
+      <c r="C271" s="20">
         <v>72346</v>
       </c>
       <c r="D271" t="s">
@@ -28638,12 +30370,15 @@
       <c r="P271" s="24" t="s">
         <v>2772</v>
       </c>
+      <c r="Q271" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="272" ht="94.5" spans="2:16">
+    <row r="272" ht="94.5" spans="2:17">
       <c r="B272" s="1" t="s">
         <v>2773</v>
       </c>
-      <c r="C272" s="30">
+      <c r="C272" s="20">
         <v>72361</v>
       </c>
       <c r="D272" t="s">
@@ -28680,12 +30415,15 @@
       <c r="P272" s="24" t="s">
         <v>2782</v>
       </c>
+      <c r="Q272" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="273" ht="94.5" spans="2:16">
+    <row r="273" ht="94.5" spans="2:17">
       <c r="B273" s="1" t="s">
         <v>2783</v>
       </c>
-      <c r="C273" s="30">
+      <c r="C273" s="20">
         <v>72363</v>
       </c>
       <c r="D273" t="s">
@@ -28722,12 +30460,15 @@
       <c r="P273" s="24" t="s">
         <v>2792</v>
       </c>
+      <c r="Q273" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="274" ht="121.5" spans="2:16">
+    <row r="274" ht="121.5" spans="2:17">
       <c r="B274" s="1" t="s">
         <v>2793</v>
       </c>
-      <c r="C274" s="30">
+      <c r="C274" s="20">
         <v>72360</v>
       </c>
       <c r="D274" t="s">
@@ -28764,12 +30505,15 @@
       <c r="P274" s="24" t="s">
         <v>2802</v>
       </c>
+      <c r="Q274" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="275" ht="108" spans="2:16">
+    <row r="275" ht="108" spans="2:17">
       <c r="B275" s="1" t="s">
         <v>2803</v>
       </c>
-      <c r="C275" s="30">
+      <c r="C275" s="20">
         <v>72359</v>
       </c>
       <c r="D275" t="s">
@@ -28806,12 +30550,15 @@
       <c r="P275" s="24" t="s">
         <v>2812</v>
       </c>
+      <c r="Q275" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="276" ht="108" spans="2:16">
+    <row r="276" ht="108" spans="2:17">
       <c r="B276" s="1" t="s">
         <v>2813</v>
       </c>
-      <c r="C276" s="30">
+      <c r="C276" s="20">
         <v>72362</v>
       </c>
       <c r="D276" t="s">
@@ -28848,12 +30595,15 @@
       <c r="P276" s="24" t="s">
         <v>2822</v>
       </c>
+      <c r="Q276" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="277" ht="121.5" spans="2:16">
+    <row r="277" ht="121.5" spans="2:17">
       <c r="B277" s="1" t="s">
         <v>2823</v>
       </c>
-      <c r="C277" s="30">
+      <c r="C277" s="20">
         <v>72655</v>
       </c>
       <c r="D277" t="s">
@@ -28889,12 +30639,15 @@
       <c r="P277" s="24" t="s">
         <v>2833</v>
       </c>
+      <c r="Q277" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="278" ht="121.5" spans="2:16">
+    <row r="278" ht="121.5" spans="2:17">
       <c r="B278" s="1" t="s">
         <v>2834</v>
       </c>
-      <c r="C278" s="30">
+      <c r="C278" s="20">
         <v>72658</v>
       </c>
       <c r="D278" t="s">
@@ -28930,12 +30683,15 @@
       <c r="P278" s="24" t="s">
         <v>2843</v>
       </c>
+      <c r="Q278" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="279" ht="108" spans="2:16">
+    <row r="279" ht="108" spans="2:17">
       <c r="B279" s="1" t="s">
         <v>2844</v>
       </c>
-      <c r="C279" s="30">
+      <c r="C279" s="20">
         <v>72653</v>
       </c>
       <c r="D279" t="s">
@@ -28971,12 +30727,15 @@
       <c r="P279" s="24" t="s">
         <v>2853</v>
       </c>
+      <c r="Q279" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="280" ht="108" spans="2:16">
+    <row r="280" ht="108" spans="2:17">
       <c r="B280" s="1" t="s">
         <v>2854</v>
       </c>
-      <c r="C280" s="30">
+      <c r="C280" s="20">
         <v>72654</v>
       </c>
       <c r="D280" t="s">
@@ -29012,15 +30771,18 @@
       <c r="P280" s="24" t="s">
         <v>2863</v>
       </c>
+      <c r="Q280" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="281" ht="121.5" spans="2:16">
+    <row r="281" ht="121.5" spans="2:17">
       <c r="B281" s="1" t="s">
         <v>2864</v>
       </c>
-      <c r="C281" s="30">
+      <c r="C281" s="20">
         <v>72657</v>
       </c>
-      <c r="D281" s="31" t="s">
+      <c r="D281" s="27" t="s">
         <v>2865</v>
       </c>
       <c r="E281" t="s">
@@ -29053,12 +30815,15 @@
       <c r="P281" s="24" t="s">
         <v>2873</v>
       </c>
+      <c r="Q281" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="282" ht="121.5" spans="2:16">
+    <row r="282" ht="121.5" spans="2:17">
       <c r="B282" s="1" t="s">
         <v>2874</v>
       </c>
-      <c r="C282" s="30">
+      <c r="C282" s="20">
         <v>72656</v>
       </c>
       <c r="D282" t="s">
@@ -29094,6 +30859,2308 @@
       <c r="P282" s="24" t="s">
         <v>2883</v>
       </c>
+      <c r="Q282" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="283" ht="135" spans="2:17">
+      <c r="B283" s="1" t="s">
+        <v>2884</v>
+      </c>
+      <c r="C283" s="20">
+        <v>74291</v>
+      </c>
+      <c r="D283" t="s">
+        <v>2885</v>
+      </c>
+      <c r="E283" t="s">
+        <v>233</v>
+      </c>
+      <c r="F283" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I283" t="s">
+        <v>2886</v>
+      </c>
+      <c r="J283" t="s">
+        <v>2887</v>
+      </c>
+      <c r="K283" s="24" t="s">
+        <v>2888</v>
+      </c>
+      <c r="L283" s="24" t="s">
+        <v>2889</v>
+      </c>
+      <c r="M283" t="s">
+        <v>2890</v>
+      </c>
+      <c r="N283" s="24" t="s">
+        <v>2891</v>
+      </c>
+      <c r="O283" s="24" t="s">
+        <v>2892</v>
+      </c>
+      <c r="P283" s="24" t="s">
+        <v>2893</v>
+      </c>
+    </row>
+    <row r="284" ht="135" spans="2:17">
+      <c r="B284" s="1" t="s">
+        <v>2894</v>
+      </c>
+      <c r="C284" s="20">
+        <v>74293</v>
+      </c>
+      <c r="D284" t="s">
+        <v>2895</v>
+      </c>
+      <c r="E284" t="s">
+        <v>233</v>
+      </c>
+      <c r="F284" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I284" t="s">
+        <v>2896</v>
+      </c>
+      <c r="J284" t="s">
+        <v>2897</v>
+      </c>
+      <c r="K284" s="24" t="s">
+        <v>2898</v>
+      </c>
+      <c r="L284" s="24" t="s">
+        <v>2899</v>
+      </c>
+      <c r="M284" t="s">
+        <v>2900</v>
+      </c>
+      <c r="N284" s="24" t="s">
+        <v>2901</v>
+      </c>
+      <c r="O284" s="24" t="s">
+        <v>2902</v>
+      </c>
+      <c r="P284" s="24" t="s">
+        <v>2903</v>
+      </c>
+    </row>
+    <row r="285" ht="121.5" spans="2:17">
+      <c r="B285" s="1" t="s">
+        <v>2904</v>
+      </c>
+      <c r="C285" s="20">
+        <v>74295</v>
+      </c>
+      <c r="D285" t="s">
+        <v>2905</v>
+      </c>
+      <c r="E285" t="s">
+        <v>233</v>
+      </c>
+      <c r="F285" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I285" t="s">
+        <v>2906</v>
+      </c>
+      <c r="J285" t="s">
+        <v>2907</v>
+      </c>
+      <c r="K285" s="24" t="s">
+        <v>2908</v>
+      </c>
+      <c r="L285" s="24" t="s">
+        <v>2909</v>
+      </c>
+      <c r="M285" t="s">
+        <v>2910</v>
+      </c>
+      <c r="N285" s="24" t="s">
+        <v>2911</v>
+      </c>
+      <c r="O285" s="24" t="s">
+        <v>2912</v>
+      </c>
+      <c r="P285" s="24" t="s">
+        <v>2913</v>
+      </c>
+    </row>
+    <row r="286" ht="121.5" spans="2:17">
+      <c r="B286" s="1" t="s">
+        <v>2914</v>
+      </c>
+      <c r="C286" s="20">
+        <v>74292</v>
+      </c>
+      <c r="D286" t="s">
+        <v>2915</v>
+      </c>
+      <c r="E286" t="s">
+        <v>233</v>
+      </c>
+      <c r="F286" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I286" t="s">
+        <v>2916</v>
+      </c>
+      <c r="J286" t="s">
+        <v>2917</v>
+      </c>
+      <c r="K286" s="24" t="s">
+        <v>2918</v>
+      </c>
+      <c r="L286" s="24" t="s">
+        <v>2919</v>
+      </c>
+      <c r="M286" t="s">
+        <v>2920</v>
+      </c>
+      <c r="N286" s="24" t="s">
+        <v>2921</v>
+      </c>
+      <c r="O286" s="24" t="s">
+        <v>2922</v>
+      </c>
+      <c r="P286" s="24" t="s">
+        <v>2923</v>
+      </c>
+    </row>
+    <row r="287" ht="148.5" spans="2:17">
+      <c r="B287" s="1" t="s">
+        <v>2924</v>
+      </c>
+      <c r="C287" s="20">
+        <v>74290</v>
+      </c>
+      <c r="D287" t="s">
+        <v>2925</v>
+      </c>
+      <c r="E287" t="s">
+        <v>233</v>
+      </c>
+      <c r="F287" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I287" t="s">
+        <v>2926</v>
+      </c>
+      <c r="J287" t="s">
+        <v>2927</v>
+      </c>
+      <c r="K287" s="24" t="s">
+        <v>2928</v>
+      </c>
+      <c r="L287" s="24" t="s">
+        <v>2929</v>
+      </c>
+      <c r="M287" t="s">
+        <v>2930</v>
+      </c>
+      <c r="N287" s="24" t="s">
+        <v>2931</v>
+      </c>
+      <c r="O287" s="24" t="s">
+        <v>2932</v>
+      </c>
+      <c r="P287" s="24" t="s">
+        <v>2933</v>
+      </c>
+    </row>
+    <row r="288" ht="108" spans="2:17">
+      <c r="B288" s="1" t="s">
+        <v>2934</v>
+      </c>
+      <c r="C288" s="20">
+        <v>74297</v>
+      </c>
+      <c r="D288" t="s">
+        <v>2935</v>
+      </c>
+      <c r="E288" t="s">
+        <v>233</v>
+      </c>
+      <c r="F288" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I288" t="s">
+        <v>2936</v>
+      </c>
+      <c r="J288" t="s">
+        <v>2937</v>
+      </c>
+      <c r="K288" s="24" t="s">
+        <v>2938</v>
+      </c>
+      <c r="L288" s="24" t="s">
+        <v>2939</v>
+      </c>
+      <c r="M288" t="s">
+        <v>2940</v>
+      </c>
+      <c r="N288" s="24" t="s">
+        <v>2941</v>
+      </c>
+      <c r="O288" s="24" t="s">
+        <v>2942</v>
+      </c>
+      <c r="P288" s="24" t="s">
+        <v>2943</v>
+      </c>
+    </row>
+    <row r="289" ht="108" spans="2:16">
+      <c r="B289" s="1" t="s">
+        <v>2944</v>
+      </c>
+      <c r="C289" s="20">
+        <v>74296</v>
+      </c>
+      <c r="D289" t="s">
+        <v>2945</v>
+      </c>
+      <c r="E289" t="s">
+        <v>233</v>
+      </c>
+      <c r="F289" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I289" t="s">
+        <v>2946</v>
+      </c>
+      <c r="J289" t="s">
+        <v>2947</v>
+      </c>
+      <c r="K289" s="24" t="s">
+        <v>2948</v>
+      </c>
+      <c r="L289" s="24" t="s">
+        <v>2949</v>
+      </c>
+      <c r="M289" t="s">
+        <v>2950</v>
+      </c>
+      <c r="N289" s="24" t="s">
+        <v>2951</v>
+      </c>
+      <c r="O289" s="24" t="s">
+        <v>2952</v>
+      </c>
+      <c r="P289" s="24" t="s">
+        <v>2953</v>
+      </c>
+    </row>
+    <row r="290" ht="135" spans="2:16">
+      <c r="B290" s="1" t="s">
+        <v>2954</v>
+      </c>
+      <c r="C290" s="20">
+        <v>74294</v>
+      </c>
+      <c r="D290" t="s">
+        <v>2955</v>
+      </c>
+      <c r="E290" t="s">
+        <v>233</v>
+      </c>
+      <c r="F290" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I290" t="s">
+        <v>2956</v>
+      </c>
+      <c r="J290" t="s">
+        <v>2957</v>
+      </c>
+      <c r="K290" s="24" t="s">
+        <v>2958</v>
+      </c>
+      <c r="L290" s="24" t="s">
+        <v>2959</v>
+      </c>
+      <c r="M290" t="s">
+        <v>2960</v>
+      </c>
+      <c r="N290" s="24" t="s">
+        <v>2961</v>
+      </c>
+      <c r="O290" s="24" t="s">
+        <v>2962</v>
+      </c>
+      <c r="P290" s="24" t="s">
+        <v>2963</v>
+      </c>
+    </row>
+    <row r="291" ht="81" spans="2:16">
+      <c r="B291" s="1" t="s">
+        <v>2964</v>
+      </c>
+      <c r="C291" s="20">
+        <v>74298</v>
+      </c>
+      <c r="D291" t="s">
+        <v>2965</v>
+      </c>
+      <c r="E291" t="s">
+        <v>233</v>
+      </c>
+      <c r="F291" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I291" t="s">
+        <v>2966</v>
+      </c>
+      <c r="J291" t="s">
+        <v>2967</v>
+      </c>
+      <c r="K291" s="24" t="s">
+        <v>2968</v>
+      </c>
+      <c r="L291" s="24" t="s">
+        <v>2969</v>
+      </c>
+      <c r="M291" t="s">
+        <v>2970</v>
+      </c>
+      <c r="N291" s="24" t="s">
+        <v>2971</v>
+      </c>
+      <c r="O291" s="24" t="s">
+        <v>2972</v>
+      </c>
+      <c r="P291" s="24" t="s">
+        <v>2973</v>
+      </c>
+    </row>
+    <row r="292" ht="108" spans="2:16">
+      <c r="B292" s="1" t="s">
+        <v>2974</v>
+      </c>
+      <c r="C292" s="30">
+        <v>76048</v>
+      </c>
+      <c r="D292" t="s">
+        <v>2975</v>
+      </c>
+      <c r="E292" t="s">
+        <v>2976</v>
+      </c>
+      <c r="F292" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I292" t="s">
+        <v>2977</v>
+      </c>
+      <c r="J292" t="s">
+        <v>2978</v>
+      </c>
+      <c r="K292" s="24" t="s">
+        <v>2979</v>
+      </c>
+      <c r="L292" s="24" t="s">
+        <v>2980</v>
+      </c>
+      <c r="M292" t="s">
+        <v>2981</v>
+      </c>
+      <c r="N292" s="24" t="s">
+        <v>2982</v>
+      </c>
+      <c r="O292" s="24" t="s">
+        <v>2983</v>
+      </c>
+      <c r="P292" s="24" t="s">
+        <v>2984</v>
+      </c>
+    </row>
+    <row r="293" ht="135" spans="2:16">
+      <c r="B293" s="1" t="s">
+        <v>2985</v>
+      </c>
+      <c r="C293" s="30">
+        <v>76050</v>
+      </c>
+      <c r="D293" t="s">
+        <v>2986</v>
+      </c>
+      <c r="E293" t="s">
+        <v>2976</v>
+      </c>
+      <c r="F293" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I293" t="s">
+        <v>2987</v>
+      </c>
+      <c r="J293" t="s">
+        <v>2988</v>
+      </c>
+      <c r="K293" s="24" t="s">
+        <v>2989</v>
+      </c>
+      <c r="L293" s="24" t="s">
+        <v>2990</v>
+      </c>
+      <c r="M293" t="s">
+        <v>2991</v>
+      </c>
+      <c r="N293" s="24" t="s">
+        <v>2992</v>
+      </c>
+      <c r="O293" s="24" t="s">
+        <v>2993</v>
+      </c>
+      <c r="P293" s="24" t="s">
+        <v>2994</v>
+      </c>
+    </row>
+    <row r="294" ht="108" spans="2:16">
+      <c r="B294" s="1" t="s">
+        <v>2995</v>
+      </c>
+      <c r="C294" s="30">
+        <v>76056</v>
+      </c>
+      <c r="D294" t="s">
+        <v>2996</v>
+      </c>
+      <c r="E294" t="s">
+        <v>2976</v>
+      </c>
+      <c r="F294" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I294" t="s">
+        <v>2997</v>
+      </c>
+      <c r="J294" t="s">
+        <v>2998</v>
+      </c>
+      <c r="K294" s="24" t="s">
+        <v>2999</v>
+      </c>
+      <c r="L294" s="24" t="s">
+        <v>3000</v>
+      </c>
+      <c r="M294" t="s">
+        <v>3001</v>
+      </c>
+      <c r="N294" s="24" t="s">
+        <v>3002</v>
+      </c>
+      <c r="O294" s="24" t="s">
+        <v>3003</v>
+      </c>
+      <c r="P294" s="24" t="s">
+        <v>3004</v>
+      </c>
+    </row>
+    <row r="295" ht="108" spans="2:16">
+      <c r="B295" s="1" t="s">
+        <v>3005</v>
+      </c>
+      <c r="C295" s="30">
+        <v>76049</v>
+      </c>
+      <c r="D295" t="s">
+        <v>3006</v>
+      </c>
+      <c r="E295" t="s">
+        <v>2976</v>
+      </c>
+      <c r="F295" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I295" t="s">
+        <v>3007</v>
+      </c>
+      <c r="J295" t="s">
+        <v>3008</v>
+      </c>
+      <c r="K295" s="24" t="s">
+        <v>3009</v>
+      </c>
+      <c r="L295" s="24" t="s">
+        <v>3010</v>
+      </c>
+      <c r="M295" t="s">
+        <v>3011</v>
+      </c>
+      <c r="N295" s="24" t="s">
+        <v>3012</v>
+      </c>
+      <c r="O295" s="24" t="s">
+        <v>3013</v>
+      </c>
+      <c r="P295" s="24" t="s">
+        <v>3014</v>
+      </c>
+    </row>
+    <row r="296" ht="121.5" spans="2:16">
+      <c r="B296" s="1" t="s">
+        <v>3015</v>
+      </c>
+      <c r="C296" s="30">
+        <v>76051</v>
+      </c>
+      <c r="D296" t="s">
+        <v>3016</v>
+      </c>
+      <c r="E296" t="s">
+        <v>2976</v>
+      </c>
+      <c r="F296" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I296" t="s">
+        <v>3017</v>
+      </c>
+      <c r="J296" t="s">
+        <v>3018</v>
+      </c>
+      <c r="K296" s="24" t="s">
+        <v>3019</v>
+      </c>
+      <c r="L296" s="24" t="s">
+        <v>3020</v>
+      </c>
+      <c r="M296" t="s">
+        <v>3021</v>
+      </c>
+      <c r="N296" s="24" t="s">
+        <v>3022</v>
+      </c>
+      <c r="O296" s="24" t="s">
+        <v>3023</v>
+      </c>
+      <c r="P296" s="24" t="s">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="297" ht="108" spans="2:16">
+      <c r="B297" s="1" t="s">
+        <v>3025</v>
+      </c>
+      <c r="C297" s="30">
+        <v>76055</v>
+      </c>
+      <c r="D297" t="s">
+        <v>3026</v>
+      </c>
+      <c r="E297" t="s">
+        <v>2976</v>
+      </c>
+      <c r="F297" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I297" t="s">
+        <v>3027</v>
+      </c>
+      <c r="J297" t="s">
+        <v>3028</v>
+      </c>
+      <c r="K297" s="24" t="s">
+        <v>3029</v>
+      </c>
+      <c r="L297" s="24" t="s">
+        <v>3030</v>
+      </c>
+      <c r="M297" t="s">
+        <v>3031</v>
+      </c>
+      <c r="N297" s="24" t="s">
+        <v>3032</v>
+      </c>
+      <c r="O297" s="24" t="s">
+        <v>3033</v>
+      </c>
+      <c r="P297" s="24" t="s">
+        <v>3034</v>
+      </c>
+    </row>
+    <row r="298" ht="121.5" spans="2:16">
+      <c r="B298" s="1" t="s">
+        <v>3035</v>
+      </c>
+      <c r="C298" s="30">
+        <v>76053</v>
+      </c>
+      <c r="D298" t="s">
+        <v>3036</v>
+      </c>
+      <c r="E298" t="s">
+        <v>2976</v>
+      </c>
+      <c r="F298" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I298" t="s">
+        <v>3037</v>
+      </c>
+      <c r="J298" t="s">
+        <v>3038</v>
+      </c>
+      <c r="K298" s="24" t="s">
+        <v>3039</v>
+      </c>
+      <c r="L298" s="24" t="s">
+        <v>3040</v>
+      </c>
+      <c r="M298" t="s">
+        <v>3041</v>
+      </c>
+      <c r="N298" s="24" t="s">
+        <v>3042</v>
+      </c>
+      <c r="O298" s="24" t="s">
+        <v>3043</v>
+      </c>
+      <c r="P298" s="24" t="s">
+        <v>3044</v>
+      </c>
+    </row>
+    <row r="299" ht="108" spans="2:16">
+      <c r="B299" s="1" t="s">
+        <v>3045</v>
+      </c>
+      <c r="C299" s="30">
+        <v>76047</v>
+      </c>
+      <c r="D299" t="s">
+        <v>3046</v>
+      </c>
+      <c r="E299" t="s">
+        <v>2976</v>
+      </c>
+      <c r="F299" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I299" t="s">
+        <v>3047</v>
+      </c>
+      <c r="J299" t="s">
+        <v>3048</v>
+      </c>
+      <c r="K299" s="24" t="s">
+        <v>3049</v>
+      </c>
+      <c r="L299" s="24" t="s">
+        <v>3050</v>
+      </c>
+      <c r="M299" t="s">
+        <v>3051</v>
+      </c>
+      <c r="N299" s="24" t="s">
+        <v>3052</v>
+      </c>
+      <c r="O299" s="24" t="s">
+        <v>3053</v>
+      </c>
+      <c r="P299" s="24" t="s">
+        <v>3054</v>
+      </c>
+    </row>
+    <row r="300" ht="94.5" spans="2:16">
+      <c r="B300" s="1" t="s">
+        <v>3055</v>
+      </c>
+      <c r="C300" s="30">
+        <v>76052</v>
+      </c>
+      <c r="D300" t="s">
+        <v>3056</v>
+      </c>
+      <c r="E300" t="s">
+        <v>2976</v>
+      </c>
+      <c r="F300" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I300" t="s">
+        <v>3057</v>
+      </c>
+      <c r="J300" t="s">
+        <v>3058</v>
+      </c>
+      <c r="K300" s="24" t="s">
+        <v>3059</v>
+      </c>
+      <c r="L300" s="24" t="s">
+        <v>3060</v>
+      </c>
+      <c r="M300" t="s">
+        <v>3061</v>
+      </c>
+      <c r="N300" s="24" t="s">
+        <v>3062</v>
+      </c>
+      <c r="O300" s="24" t="s">
+        <v>3063</v>
+      </c>
+      <c r="P300" s="24" t="s">
+        <v>3064</v>
+      </c>
+    </row>
+    <row r="301" ht="108" spans="2:16">
+      <c r="B301" s="1" t="s">
+        <v>3065</v>
+      </c>
+      <c r="C301" s="30">
+        <v>76054</v>
+      </c>
+      <c r="D301" t="s">
+        <v>3066</v>
+      </c>
+      <c r="E301" t="s">
+        <v>2976</v>
+      </c>
+      <c r="F301" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I301" t="s">
+        <v>3067</v>
+      </c>
+      <c r="J301" t="s">
+        <v>3068</v>
+      </c>
+      <c r="K301" s="24" t="s">
+        <v>3069</v>
+      </c>
+      <c r="L301" s="24" t="s">
+        <v>3070</v>
+      </c>
+      <c r="M301" t="s">
+        <v>3071</v>
+      </c>
+      <c r="N301" s="24" t="s">
+        <v>3072</v>
+      </c>
+      <c r="O301" s="24" t="s">
+        <v>3073</v>
+      </c>
+      <c r="P301" s="24" t="s">
+        <v>3074</v>
+      </c>
+    </row>
+    <row r="302" ht="108" spans="2:16">
+      <c r="B302" s="1" t="s">
+        <v>3075</v>
+      </c>
+      <c r="C302" s="30">
+        <v>76349</v>
+      </c>
+      <c r="D302" t="s">
+        <v>3076</v>
+      </c>
+      <c r="E302" t="s">
+        <v>233</v>
+      </c>
+      <c r="F302" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I302" t="s">
+        <v>3077</v>
+      </c>
+      <c r="J302" t="s">
+        <v>3078</v>
+      </c>
+      <c r="K302" s="24" t="s">
+        <v>3079</v>
+      </c>
+      <c r="L302" s="24" t="s">
+        <v>3080</v>
+      </c>
+      <c r="M302" t="s">
+        <v>3081</v>
+      </c>
+      <c r="N302" s="24" t="s">
+        <v>3082</v>
+      </c>
+      <c r="O302" s="24" t="s">
+        <v>3083</v>
+      </c>
+      <c r="P302" s="24" t="s">
+        <v>3084</v>
+      </c>
+    </row>
+    <row r="303" ht="94.5" spans="2:16">
+      <c r="B303" s="1" t="s">
+        <v>3085</v>
+      </c>
+      <c r="C303" s="30">
+        <v>76346</v>
+      </c>
+      <c r="D303" t="s">
+        <v>3086</v>
+      </c>
+      <c r="E303" t="s">
+        <v>233</v>
+      </c>
+      <c r="F303" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I303" t="s">
+        <v>3087</v>
+      </c>
+      <c r="J303" t="s">
+        <v>3088</v>
+      </c>
+      <c r="K303" s="24" t="s">
+        <v>3089</v>
+      </c>
+      <c r="L303" s="24" t="s">
+        <v>3090</v>
+      </c>
+      <c r="M303" t="s">
+        <v>3091</v>
+      </c>
+      <c r="N303" s="24" t="s">
+        <v>3092</v>
+      </c>
+      <c r="O303" s="24" t="s">
+        <v>3093</v>
+      </c>
+      <c r="P303" s="24" t="s">
+        <v>3094</v>
+      </c>
+    </row>
+    <row r="304" ht="94.5" spans="2:16">
+      <c r="B304" s="1" t="s">
+        <v>3095</v>
+      </c>
+      <c r="C304" s="30">
+        <v>76343</v>
+      </c>
+      <c r="D304" t="s">
+        <v>3096</v>
+      </c>
+      <c r="E304" t="s">
+        <v>233</v>
+      </c>
+      <c r="F304" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I304" t="s">
+        <v>3097</v>
+      </c>
+      <c r="J304" t="s">
+        <v>3098</v>
+      </c>
+      <c r="K304" s="24" t="s">
+        <v>3099</v>
+      </c>
+      <c r="L304" s="24" t="s">
+        <v>3100</v>
+      </c>
+      <c r="M304" t="s">
+        <v>3101</v>
+      </c>
+      <c r="N304" s="24" t="s">
+        <v>3102</v>
+      </c>
+      <c r="O304" s="24" t="s">
+        <v>3103</v>
+      </c>
+      <c r="P304" s="24" t="s">
+        <v>3104</v>
+      </c>
+    </row>
+    <row r="305" ht="108" spans="2:16">
+      <c r="B305" s="1" t="s">
+        <v>3105</v>
+      </c>
+      <c r="C305" s="30">
+        <v>76342</v>
+      </c>
+      <c r="D305" t="s">
+        <v>3106</v>
+      </c>
+      <c r="E305" t="s">
+        <v>233</v>
+      </c>
+      <c r="F305" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I305" t="s">
+        <v>3107</v>
+      </c>
+      <c r="J305" t="s">
+        <v>3108</v>
+      </c>
+      <c r="K305" s="24" t="s">
+        <v>3109</v>
+      </c>
+      <c r="L305" s="24" t="s">
+        <v>3110</v>
+      </c>
+      <c r="M305" t="s">
+        <v>3111</v>
+      </c>
+      <c r="N305" s="24" t="s">
+        <v>3112</v>
+      </c>
+      <c r="O305" s="24" t="s">
+        <v>2962</v>
+      </c>
+      <c r="P305" s="24" t="s">
+        <v>3113</v>
+      </c>
+    </row>
+    <row r="306" ht="67.5" spans="2:16">
+      <c r="B306" s="1" t="s">
+        <v>3114</v>
+      </c>
+      <c r="C306" s="30">
+        <v>76340</v>
+      </c>
+      <c r="D306" t="s">
+        <v>3115</v>
+      </c>
+      <c r="E306" t="s">
+        <v>233</v>
+      </c>
+      <c r="F306" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I306" t="s">
+        <v>3116</v>
+      </c>
+      <c r="J306" t="s">
+        <v>3117</v>
+      </c>
+      <c r="K306" s="24" t="s">
+        <v>3118</v>
+      </c>
+      <c r="L306" s="24" t="s">
+        <v>3119</v>
+      </c>
+      <c r="M306" t="s">
+        <v>3120</v>
+      </c>
+      <c r="N306" s="24" t="s">
+        <v>3121</v>
+      </c>
+      <c r="O306" s="24" t="s">
+        <v>3122</v>
+      </c>
+      <c r="P306" s="24" t="s">
+        <v>3123</v>
+      </c>
+    </row>
+    <row r="307" ht="94.5" spans="2:16">
+      <c r="B307" s="1" t="s">
+        <v>3124</v>
+      </c>
+      <c r="C307" s="30">
+        <v>76344</v>
+      </c>
+      <c r="D307" t="s">
+        <v>3125</v>
+      </c>
+      <c r="E307" t="s">
+        <v>233</v>
+      </c>
+      <c r="F307" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I307" t="s">
+        <v>3126</v>
+      </c>
+      <c r="J307" t="s">
+        <v>3127</v>
+      </c>
+      <c r="K307" s="24" t="s">
+        <v>3128</v>
+      </c>
+      <c r="L307" s="24" t="s">
+        <v>3129</v>
+      </c>
+      <c r="M307" t="s">
+        <v>3130</v>
+      </c>
+      <c r="N307" s="24" t="s">
+        <v>3131</v>
+      </c>
+      <c r="O307" s="24" t="s">
+        <v>3132</v>
+      </c>
+      <c r="P307" s="24" t="s">
+        <v>3133</v>
+      </c>
+    </row>
+    <row r="308" ht="67.5" spans="2:16">
+      <c r="B308" s="1" t="s">
+        <v>3134</v>
+      </c>
+      <c r="C308" s="30">
+        <v>76348</v>
+      </c>
+      <c r="D308" t="s">
+        <v>3135</v>
+      </c>
+      <c r="E308" t="s">
+        <v>233</v>
+      </c>
+      <c r="F308" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I308" t="s">
+        <v>3136</v>
+      </c>
+      <c r="J308" t="s">
+        <v>3137</v>
+      </c>
+      <c r="K308" s="24" t="s">
+        <v>3138</v>
+      </c>
+      <c r="L308" s="24" t="s">
+        <v>3139</v>
+      </c>
+      <c r="M308" t="s">
+        <v>3140</v>
+      </c>
+      <c r="N308" s="24" t="s">
+        <v>3141</v>
+      </c>
+      <c r="O308" s="24" t="s">
+        <v>2972</v>
+      </c>
+      <c r="P308" s="24" t="s">
+        <v>3142</v>
+      </c>
+    </row>
+    <row r="309" ht="67.5" spans="2:16">
+      <c r="B309" s="1" t="s">
+        <v>3143</v>
+      </c>
+      <c r="C309" s="30">
+        <v>76345</v>
+      </c>
+      <c r="D309" t="s">
+        <v>3144</v>
+      </c>
+      <c r="E309" t="s">
+        <v>233</v>
+      </c>
+      <c r="F309" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I309" t="s">
+        <v>3145</v>
+      </c>
+      <c r="J309" t="s">
+        <v>3146</v>
+      </c>
+      <c r="K309" s="24" t="s">
+        <v>3147</v>
+      </c>
+      <c r="L309" s="24" t="s">
+        <v>3148</v>
+      </c>
+      <c r="M309" t="s">
+        <v>3149</v>
+      </c>
+      <c r="N309" s="24" t="s">
+        <v>3150</v>
+      </c>
+      <c r="O309" s="24" t="s">
+        <v>3151</v>
+      </c>
+      <c r="P309" s="24" t="s">
+        <v>3152</v>
+      </c>
+    </row>
+    <row r="310" ht="108" spans="2:16">
+      <c r="B310" s="1" t="s">
+        <v>3153</v>
+      </c>
+      <c r="C310" s="30">
+        <v>76347</v>
+      </c>
+      <c r="D310" t="s">
+        <v>3154</v>
+      </c>
+      <c r="E310" t="s">
+        <v>233</v>
+      </c>
+      <c r="F310" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I310" t="s">
+        <v>3155</v>
+      </c>
+      <c r="J310" t="s">
+        <v>3156</v>
+      </c>
+      <c r="K310" s="24" t="s">
+        <v>3157</v>
+      </c>
+      <c r="L310" s="24" t="s">
+        <v>3158</v>
+      </c>
+      <c r="M310" t="s">
+        <v>3159</v>
+      </c>
+      <c r="N310" s="24" t="s">
+        <v>3160</v>
+      </c>
+      <c r="O310" s="24" t="s">
+        <v>3161</v>
+      </c>
+      <c r="P310" s="24" t="s">
+        <v>3162</v>
+      </c>
+    </row>
+    <row r="311" ht="108" spans="2:16">
+      <c r="B311" s="1" t="s">
+        <v>3163</v>
+      </c>
+      <c r="C311" s="30">
+        <v>76341</v>
+      </c>
+      <c r="D311" t="s">
+        <v>3164</v>
+      </c>
+      <c r="E311" t="s">
+        <v>233</v>
+      </c>
+      <c r="F311" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I311" t="s">
+        <v>3165</v>
+      </c>
+      <c r="J311" t="s">
+        <v>3166</v>
+      </c>
+      <c r="K311" s="24" t="s">
+        <v>3167</v>
+      </c>
+      <c r="L311" s="24" t="s">
+        <v>3168</v>
+      </c>
+      <c r="M311" t="s">
+        <v>3169</v>
+      </c>
+      <c r="N311" s="24" t="s">
+        <v>3170</v>
+      </c>
+      <c r="O311" s="24" t="s">
+        <v>3171</v>
+      </c>
+      <c r="P311" s="24" t="s">
+        <v>3172</v>
+      </c>
+    </row>
+    <row r="312" ht="135" spans="2:16">
+      <c r="B312" s="1" t="s">
+        <v>3173</v>
+      </c>
+      <c r="C312" s="30">
+        <v>76449</v>
+      </c>
+      <c r="D312" t="s">
+        <v>3174</v>
+      </c>
+      <c r="E312" t="s">
+        <v>279</v>
+      </c>
+      <c r="F312" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I312" t="s">
+        <v>3175</v>
+      </c>
+      <c r="J312" t="s">
+        <v>3176</v>
+      </c>
+      <c r="K312" s="24" t="s">
+        <v>3177</v>
+      </c>
+      <c r="L312" s="24" t="s">
+        <v>3178</v>
+      </c>
+      <c r="M312" t="s">
+        <v>3179</v>
+      </c>
+      <c r="N312" s="24" t="s">
+        <v>3180</v>
+      </c>
+      <c r="O312" s="24" t="s">
+        <v>3181</v>
+      </c>
+      <c r="P312" s="24" t="s">
+        <v>3182</v>
+      </c>
+    </row>
+    <row r="313" ht="148.5" spans="2:16">
+      <c r="B313" s="1" t="s">
+        <v>3183</v>
+      </c>
+      <c r="C313" s="30">
+        <v>76451</v>
+      </c>
+      <c r="D313" t="s">
+        <v>3184</v>
+      </c>
+      <c r="E313" t="s">
+        <v>279</v>
+      </c>
+      <c r="F313" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I313" t="s">
+        <v>3185</v>
+      </c>
+      <c r="J313" t="s">
+        <v>3186</v>
+      </c>
+      <c r="K313" s="24" t="s">
+        <v>3187</v>
+      </c>
+      <c r="L313" s="24" t="s">
+        <v>3188</v>
+      </c>
+      <c r="M313" t="s">
+        <v>3189</v>
+      </c>
+      <c r="N313" s="24" t="s">
+        <v>3190</v>
+      </c>
+      <c r="O313" s="24" t="s">
+        <v>3191</v>
+      </c>
+      <c r="P313" s="24" t="s">
+        <v>3192</v>
+      </c>
+    </row>
+    <row r="314" ht="108" spans="2:16">
+      <c r="B314" s="1" t="s">
+        <v>3193</v>
+      </c>
+      <c r="C314" s="31">
+        <v>76452</v>
+      </c>
+      <c r="D314" t="s">
+        <v>3194</v>
+      </c>
+      <c r="E314" t="s">
+        <v>279</v>
+      </c>
+      <c r="F314" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I314" t="s">
+        <v>3195</v>
+      </c>
+      <c r="J314" t="s">
+        <v>3196</v>
+      </c>
+      <c r="K314" s="24" t="s">
+        <v>3197</v>
+      </c>
+      <c r="L314" s="24" t="s">
+        <v>3198</v>
+      </c>
+      <c r="M314" t="s">
+        <v>3199</v>
+      </c>
+      <c r="N314" s="24" t="s">
+        <v>3200</v>
+      </c>
+      <c r="O314" s="24" t="s">
+        <v>3201</v>
+      </c>
+      <c r="P314" s="24" t="s">
+        <v>3202</v>
+      </c>
+    </row>
+    <row r="315" ht="108" spans="2:16">
+      <c r="B315" s="1" t="s">
+        <v>3203</v>
+      </c>
+      <c r="C315" s="30">
+        <v>76450</v>
+      </c>
+      <c r="D315" t="s">
+        <v>3204</v>
+      </c>
+      <c r="E315" t="s">
+        <v>279</v>
+      </c>
+      <c r="F315" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I315" t="s">
+        <v>3205</v>
+      </c>
+      <c r="J315" t="s">
+        <v>3206</v>
+      </c>
+      <c r="K315" s="24" t="s">
+        <v>3207</v>
+      </c>
+      <c r="L315" s="24" t="s">
+        <v>3208</v>
+      </c>
+      <c r="M315" t="s">
+        <v>3209</v>
+      </c>
+      <c r="N315" s="24" t="s">
+        <v>3210</v>
+      </c>
+      <c r="O315" s="24" t="s">
+        <v>3211</v>
+      </c>
+      <c r="P315" s="24" t="s">
+        <v>3212</v>
+      </c>
+    </row>
+    <row r="316" ht="175.5" spans="2:16">
+      <c r="B316" s="1" t="s">
+        <v>3213</v>
+      </c>
+      <c r="C316" s="30">
+        <v>76498</v>
+      </c>
+      <c r="D316" t="s">
+        <v>3214</v>
+      </c>
+      <c r="E316" t="s">
+        <v>745</v>
+      </c>
+      <c r="F316" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I316" t="s">
+        <v>3215</v>
+      </c>
+      <c r="J316" t="s">
+        <v>3166</v>
+      </c>
+      <c r="K316" s="24" t="s">
+        <v>3216</v>
+      </c>
+      <c r="L316" s="24" t="s">
+        <v>3217</v>
+      </c>
+      <c r="M316" t="s">
+        <v>3218</v>
+      </c>
+      <c r="N316" s="24" t="s">
+        <v>3219</v>
+      </c>
+      <c r="O316" s="24" t="s">
+        <v>3220</v>
+      </c>
+      <c r="P316" s="24" t="s">
+        <v>3221</v>
+      </c>
+    </row>
+    <row r="317" ht="148.5" spans="2:16">
+      <c r="B317" s="1" t="s">
+        <v>3222</v>
+      </c>
+      <c r="C317" s="30">
+        <v>76490</v>
+      </c>
+      <c r="D317" t="s">
+        <v>3223</v>
+      </c>
+      <c r="E317" t="s">
+        <v>745</v>
+      </c>
+      <c r="F317" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I317" t="s">
+        <v>3224</v>
+      </c>
+      <c r="J317" t="s">
+        <v>3225</v>
+      </c>
+      <c r="K317" s="24" t="s">
+        <v>3226</v>
+      </c>
+      <c r="L317" s="24" t="s">
+        <v>3227</v>
+      </c>
+      <c r="M317" t="s">
+        <v>3228</v>
+      </c>
+      <c r="N317" s="24" t="s">
+        <v>3229</v>
+      </c>
+      <c r="O317" s="24" t="s">
+        <v>3230</v>
+      </c>
+      <c r="P317" s="24" t="s">
+        <v>3231</v>
+      </c>
+    </row>
+    <row r="318" ht="121.5" spans="2:16">
+      <c r="B318" s="1" t="s">
+        <v>3232</v>
+      </c>
+      <c r="C318" s="30">
+        <v>76494</v>
+      </c>
+      <c r="D318" t="s">
+        <v>3233</v>
+      </c>
+      <c r="E318" t="s">
+        <v>745</v>
+      </c>
+      <c r="F318" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I318" t="s">
+        <v>3234</v>
+      </c>
+      <c r="J318" t="s">
+        <v>3235</v>
+      </c>
+      <c r="K318" s="24" t="s">
+        <v>3236</v>
+      </c>
+      <c r="L318" s="24" t="s">
+        <v>3237</v>
+      </c>
+      <c r="M318" t="s">
+        <v>3238</v>
+      </c>
+      <c r="N318" s="24" t="s">
+        <v>3239</v>
+      </c>
+      <c r="O318" s="24" t="s">
+        <v>3240</v>
+      </c>
+      <c r="P318" s="24" t="s">
+        <v>3241</v>
+      </c>
+    </row>
+    <row r="319" ht="121.5" spans="2:16">
+      <c r="B319" s="1" t="s">
+        <v>3242</v>
+      </c>
+      <c r="C319" s="30">
+        <v>76500</v>
+      </c>
+      <c r="D319" t="s">
+        <v>3243</v>
+      </c>
+      <c r="E319" t="s">
+        <v>745</v>
+      </c>
+      <c r="F319" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I319" t="s">
+        <v>3244</v>
+      </c>
+      <c r="J319" t="s">
+        <v>3245</v>
+      </c>
+      <c r="K319" s="24" t="s">
+        <v>3246</v>
+      </c>
+      <c r="L319" s="24" t="s">
+        <v>3247</v>
+      </c>
+      <c r="M319" t="s">
+        <v>3248</v>
+      </c>
+      <c r="N319" s="24" t="s">
+        <v>3249</v>
+      </c>
+      <c r="O319" s="24" t="s">
+        <v>3250</v>
+      </c>
+      <c r="P319" s="24" t="s">
+        <v>3251</v>
+      </c>
+    </row>
+    <row r="320" ht="108" spans="2:16">
+      <c r="B320" s="1" t="s">
+        <v>3252</v>
+      </c>
+      <c r="C320" s="30">
+        <v>76491</v>
+      </c>
+      <c r="D320" t="s">
+        <v>3253</v>
+      </c>
+      <c r="E320" t="s">
+        <v>745</v>
+      </c>
+      <c r="F320" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I320" t="s">
+        <v>3254</v>
+      </c>
+      <c r="J320" t="s">
+        <v>3255</v>
+      </c>
+      <c r="K320" s="24" t="s">
+        <v>3256</v>
+      </c>
+      <c r="L320" s="24" t="s">
+        <v>3257</v>
+      </c>
+      <c r="M320" t="s">
+        <v>3258</v>
+      </c>
+      <c r="N320" s="24" t="s">
+        <v>3259</v>
+      </c>
+      <c r="O320" s="24" t="s">
+        <v>3260</v>
+      </c>
+      <c r="P320" s="24" t="s">
+        <v>3261</v>
+      </c>
+    </row>
+    <row r="321" ht="108" spans="2:16">
+      <c r="B321" s="1" t="s">
+        <v>3262</v>
+      </c>
+      <c r="C321" s="30">
+        <v>76493</v>
+      </c>
+      <c r="D321" t="s">
+        <v>3263</v>
+      </c>
+      <c r="E321" t="s">
+        <v>745</v>
+      </c>
+      <c r="F321" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I321" t="s">
+        <v>3264</v>
+      </c>
+      <c r="J321" t="s">
+        <v>3265</v>
+      </c>
+      <c r="K321" s="24" t="s">
+        <v>3266</v>
+      </c>
+      <c r="L321" s="24" t="s">
+        <v>3267</v>
+      </c>
+      <c r="M321" t="s">
+        <v>3268</v>
+      </c>
+      <c r="N321" s="24" t="s">
+        <v>3269</v>
+      </c>
+      <c r="O321" s="24" t="s">
+        <v>3270</v>
+      </c>
+      <c r="P321" s="24" t="s">
+        <v>3271</v>
+      </c>
+    </row>
+    <row r="322" ht="94.5" spans="2:16">
+      <c r="B322" s="1" t="s">
+        <v>3272</v>
+      </c>
+      <c r="C322" s="30">
+        <v>76495</v>
+      </c>
+      <c r="D322" t="s">
+        <v>3273</v>
+      </c>
+      <c r="E322" t="s">
+        <v>745</v>
+      </c>
+      <c r="F322" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I322" t="s">
+        <v>3274</v>
+      </c>
+      <c r="J322" t="s">
+        <v>3275</v>
+      </c>
+      <c r="K322" s="24" t="s">
+        <v>3276</v>
+      </c>
+      <c r="L322" s="24" t="s">
+        <v>3277</v>
+      </c>
+      <c r="M322" t="s">
+        <v>3278</v>
+      </c>
+      <c r="N322" s="24" t="s">
+        <v>3279</v>
+      </c>
+      <c r="O322" s="24" t="s">
+        <v>3280</v>
+      </c>
+      <c r="P322" s="24" t="s">
+        <v>3281</v>
+      </c>
+    </row>
+    <row r="323" ht="94.5" spans="2:16">
+      <c r="B323" s="1" t="s">
+        <v>3282</v>
+      </c>
+      <c r="C323" s="30">
+        <v>76499</v>
+      </c>
+      <c r="D323" t="s">
+        <v>3283</v>
+      </c>
+      <c r="E323" t="s">
+        <v>745</v>
+      </c>
+      <c r="F323" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I323" t="s">
+        <v>3284</v>
+      </c>
+      <c r="J323" t="s">
+        <v>3285</v>
+      </c>
+      <c r="K323" s="24" t="s">
+        <v>3286</v>
+      </c>
+      <c r="L323" s="24" t="s">
+        <v>3287</v>
+      </c>
+      <c r="M323" t="s">
+        <v>3288</v>
+      </c>
+      <c r="N323" s="24" t="s">
+        <v>3289</v>
+      </c>
+      <c r="O323" s="24" t="s">
+        <v>3290</v>
+      </c>
+      <c r="P323" s="24" t="s">
+        <v>3291</v>
+      </c>
+    </row>
+    <row r="324" ht="108" spans="2:16">
+      <c r="B324" s="1" t="s">
+        <v>3292</v>
+      </c>
+      <c r="C324" s="30">
+        <v>76496</v>
+      </c>
+      <c r="D324" t="s">
+        <v>3293</v>
+      </c>
+      <c r="E324" t="s">
+        <v>745</v>
+      </c>
+      <c r="F324" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I324" t="s">
+        <v>3294</v>
+      </c>
+      <c r="J324" t="s">
+        <v>3295</v>
+      </c>
+      <c r="K324" s="24" t="s">
+        <v>3296</v>
+      </c>
+      <c r="L324" s="24" t="s">
+        <v>3297</v>
+      </c>
+      <c r="M324" t="s">
+        <v>3298</v>
+      </c>
+      <c r="N324" s="24" t="s">
+        <v>3299</v>
+      </c>
+      <c r="O324" s="24" t="s">
+        <v>3300</v>
+      </c>
+      <c r="P324" s="24" t="s">
+        <v>3301</v>
+      </c>
+    </row>
+    <row r="325" ht="81" spans="2:16">
+      <c r="B325" s="1" t="s">
+        <v>3302</v>
+      </c>
+      <c r="C325" s="30">
+        <v>76497</v>
+      </c>
+      <c r="D325" t="s">
+        <v>3303</v>
+      </c>
+      <c r="E325" t="s">
+        <v>745</v>
+      </c>
+      <c r="F325" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I325" t="s">
+        <v>3304</v>
+      </c>
+      <c r="J325" t="s">
+        <v>3305</v>
+      </c>
+      <c r="K325" s="24" t="s">
+        <v>3306</v>
+      </c>
+      <c r="L325" s="24" t="s">
+        <v>3307</v>
+      </c>
+      <c r="M325" t="s">
+        <v>3308</v>
+      </c>
+      <c r="N325" s="24" t="s">
+        <v>3309</v>
+      </c>
+      <c r="O325" s="24" t="s">
+        <v>3310</v>
+      </c>
+      <c r="P325" s="24" t="s">
+        <v>3311</v>
+      </c>
+    </row>
+    <row r="326" ht="67.5" spans="2:16">
+      <c r="B326" s="1" t="s">
+        <v>3312</v>
+      </c>
+      <c r="C326" s="30">
+        <v>76492</v>
+      </c>
+      <c r="D326" t="s">
+        <v>3313</v>
+      </c>
+      <c r="E326" t="s">
+        <v>745</v>
+      </c>
+      <c r="F326" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I326" s="25" t="s">
+        <v>3314</v>
+      </c>
+      <c r="J326" t="s">
+        <v>3315</v>
+      </c>
+      <c r="K326" s="24" t="s">
+        <v>3316</v>
+      </c>
+      <c r="L326" s="24" t="s">
+        <v>3317</v>
+      </c>
+      <c r="M326" t="s">
+        <v>3318</v>
+      </c>
+      <c r="N326" s="24" t="s">
+        <v>3319</v>
+      </c>
+      <c r="O326" s="24" t="s">
+        <v>3320</v>
+      </c>
+      <c r="P326" s="24" t="s">
+        <v>3321</v>
+      </c>
+    </row>
+    <row r="327" ht="94.5" spans="2:16">
+      <c r="B327" s="1" t="s">
+        <v>3322</v>
+      </c>
+      <c r="C327" s="30">
+        <v>76730</v>
+      </c>
+      <c r="D327" t="s">
+        <v>3323</v>
+      </c>
+      <c r="E327" t="s">
+        <v>500</v>
+      </c>
+      <c r="F327" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I327" t="s">
+        <v>3324</v>
+      </c>
+      <c r="J327" t="s">
+        <v>3325</v>
+      </c>
+      <c r="K327" s="24" t="s">
+        <v>3326</v>
+      </c>
+      <c r="L327" s="24" t="s">
+        <v>3327</v>
+      </c>
+      <c r="M327" t="s">
+        <v>3328</v>
+      </c>
+      <c r="N327" s="24" t="s">
+        <v>3329</v>
+      </c>
+      <c r="O327" s="24" t="s">
+        <v>3330</v>
+      </c>
+      <c r="P327" s="24" t="s">
+        <v>3331</v>
+      </c>
+    </row>
+    <row r="328" ht="108" spans="2:16">
+      <c r="B328" s="1" t="s">
+        <v>3332</v>
+      </c>
+      <c r="C328" s="30">
+        <v>76735</v>
+      </c>
+      <c r="D328" t="s">
+        <v>3333</v>
+      </c>
+      <c r="E328" t="s">
+        <v>500</v>
+      </c>
+      <c r="F328" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I328" t="s">
+        <v>3334</v>
+      </c>
+      <c r="J328" t="s">
+        <v>3335</v>
+      </c>
+      <c r="K328" s="24" t="s">
+        <v>3336</v>
+      </c>
+      <c r="L328" s="24" t="s">
+        <v>3337</v>
+      </c>
+      <c r="M328" t="s">
+        <v>3338</v>
+      </c>
+      <c r="N328" s="24" t="s">
+        <v>3339</v>
+      </c>
+      <c r="O328" s="24" t="s">
+        <v>3340</v>
+      </c>
+      <c r="P328" s="24" t="s">
+        <v>3341</v>
+      </c>
+    </row>
+    <row r="329" ht="135" spans="2:16">
+      <c r="B329" s="1" t="s">
+        <v>3342</v>
+      </c>
+      <c r="C329" s="30">
+        <v>76740</v>
+      </c>
+      <c r="D329" t="s">
+        <v>3343</v>
+      </c>
+      <c r="E329" t="s">
+        <v>500</v>
+      </c>
+      <c r="F329" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I329" t="s">
+        <v>3344</v>
+      </c>
+      <c r="J329" t="s">
+        <v>3345</v>
+      </c>
+      <c r="K329" s="24" t="s">
+        <v>3346</v>
+      </c>
+      <c r="L329" s="24" t="s">
+        <v>3347</v>
+      </c>
+      <c r="M329" t="s">
+        <v>3348</v>
+      </c>
+      <c r="N329" s="24" t="s">
+        <v>3349</v>
+      </c>
+      <c r="O329" s="24" t="s">
+        <v>3350</v>
+      </c>
+      <c r="P329" s="24" t="s">
+        <v>3351</v>
+      </c>
+    </row>
+    <row r="330" ht="108" spans="2:16">
+      <c r="B330" s="1" t="s">
+        <v>3352</v>
+      </c>
+      <c r="C330" s="30">
+        <v>76731</v>
+      </c>
+      <c r="D330" t="s">
+        <v>3353</v>
+      </c>
+      <c r="E330" t="s">
+        <v>500</v>
+      </c>
+      <c r="F330" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I330" t="s">
+        <v>3354</v>
+      </c>
+      <c r="J330" t="s">
+        <v>3355</v>
+      </c>
+      <c r="K330" s="24" t="s">
+        <v>3356</v>
+      </c>
+      <c r="L330" s="24" t="s">
+        <v>3357</v>
+      </c>
+      <c r="M330" t="s">
+        <v>3358</v>
+      </c>
+      <c r="N330" s="24" t="s">
+        <v>3359</v>
+      </c>
+      <c r="O330" s="24" t="s">
+        <v>3360</v>
+      </c>
+      <c r="P330" s="24" t="s">
+        <v>3361</v>
+      </c>
+    </row>
+    <row r="331" ht="108" spans="2:16">
+      <c r="B331" s="1" t="s">
+        <v>3362</v>
+      </c>
+      <c r="C331" s="30">
+        <v>76733</v>
+      </c>
+      <c r="D331" t="s">
+        <v>3363</v>
+      </c>
+      <c r="E331" t="s">
+        <v>500</v>
+      </c>
+      <c r="F331" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I331" t="s">
+        <v>3364</v>
+      </c>
+      <c r="J331" t="s">
+        <v>3365</v>
+      </c>
+      <c r="K331" s="24" t="s">
+        <v>3366</v>
+      </c>
+      <c r="L331" s="24" t="s">
+        <v>3367</v>
+      </c>
+      <c r="M331" t="s">
+        <v>3368</v>
+      </c>
+      <c r="N331" s="24" t="s">
+        <v>3369</v>
+      </c>
+      <c r="O331" s="24" t="s">
+        <v>3370</v>
+      </c>
+      <c r="P331" s="24" t="s">
+        <v>3371</v>
+      </c>
+    </row>
+    <row r="332" ht="108" spans="2:16">
+      <c r="B332" s="1" t="s">
+        <v>3372</v>
+      </c>
+      <c r="C332" s="31">
+        <v>76739</v>
+      </c>
+      <c r="D332" t="s">
+        <v>3373</v>
+      </c>
+      <c r="E332" t="s">
+        <v>500</v>
+      </c>
+      <c r="F332" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I332" t="s">
+        <v>3374</v>
+      </c>
+      <c r="J332" t="s">
+        <v>3375</v>
+      </c>
+      <c r="K332" s="24" t="s">
+        <v>3376</v>
+      </c>
+      <c r="L332" s="24" t="s">
+        <v>3377</v>
+      </c>
+      <c r="M332" t="s">
+        <v>3378</v>
+      </c>
+      <c r="N332" s="24" t="s">
+        <v>3379</v>
+      </c>
+      <c r="O332" s="24" t="s">
+        <v>3380</v>
+      </c>
+      <c r="P332" s="24" t="s">
+        <v>3381</v>
+      </c>
+    </row>
+    <row r="333" ht="121.5" spans="2:16">
+      <c r="B333" s="1" t="s">
+        <v>3382</v>
+      </c>
+      <c r="C333" s="30">
+        <v>76732</v>
+      </c>
+      <c r="D333" t="s">
+        <v>3383</v>
+      </c>
+      <c r="E333" t="s">
+        <v>500</v>
+      </c>
+      <c r="F333" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I333" t="s">
+        <v>3384</v>
+      </c>
+      <c r="J333" t="s">
+        <v>3385</v>
+      </c>
+      <c r="K333" s="24" t="s">
+        <v>3386</v>
+      </c>
+      <c r="L333" s="24" t="s">
+        <v>3387</v>
+      </c>
+      <c r="M333" t="s">
+        <v>3388</v>
+      </c>
+      <c r="N333" s="24" t="s">
+        <v>3389</v>
+      </c>
+      <c r="O333" s="24" t="s">
+        <v>3390</v>
+      </c>
+      <c r="P333" s="24" t="s">
+        <v>3391</v>
+      </c>
+    </row>
+    <row r="334" ht="148.5" spans="2:16">
+      <c r="B334" s="1" t="s">
+        <v>3392</v>
+      </c>
+      <c r="C334" s="30">
+        <v>76729</v>
+      </c>
+      <c r="D334" t="s">
+        <v>3393</v>
+      </c>
+      <c r="E334" t="s">
+        <v>500</v>
+      </c>
+      <c r="F334" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I334" t="s">
+        <v>3394</v>
+      </c>
+      <c r="J334" t="s">
+        <v>3395</v>
+      </c>
+      <c r="K334" s="24" t="s">
+        <v>3396</v>
+      </c>
+      <c r="L334" s="24" t="s">
+        <v>3397</v>
+      </c>
+      <c r="M334" t="s">
+        <v>3398</v>
+      </c>
+      <c r="N334" s="24" t="s">
+        <v>3399</v>
+      </c>
+      <c r="O334" s="24" t="s">
+        <v>1962</v>
+      </c>
+      <c r="P334" s="24" t="s">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="335" ht="148.5" spans="2:16">
+      <c r="B335" s="1" t="s">
+        <v>3401</v>
+      </c>
+      <c r="C335" s="30">
+        <v>76736</v>
+      </c>
+      <c r="D335" t="s">
+        <v>3402</v>
+      </c>
+      <c r="E335" t="s">
+        <v>500</v>
+      </c>
+      <c r="F335" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I335" t="s">
+        <v>3403</v>
+      </c>
+      <c r="J335" t="s">
+        <v>3404</v>
+      </c>
+      <c r="K335" s="24" t="s">
+        <v>3405</v>
+      </c>
+      <c r="L335" s="24" t="s">
+        <v>3406</v>
+      </c>
+      <c r="M335" t="s">
+        <v>3407</v>
+      </c>
+      <c r="N335" s="24" t="s">
+        <v>3408</v>
+      </c>
+      <c r="O335" s="24" t="s">
+        <v>3409</v>
+      </c>
+      <c r="P335" s="24" t="s">
+        <v>3410</v>
+      </c>
+    </row>
+    <row r="336" ht="135" spans="2:16">
+      <c r="B336" s="1" t="s">
+        <v>3411</v>
+      </c>
+      <c r="C336" s="30">
+        <v>76734</v>
+      </c>
+      <c r="D336" t="s">
+        <v>3412</v>
+      </c>
+      <c r="E336" t="s">
+        <v>500</v>
+      </c>
+      <c r="F336" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I336" t="s">
+        <v>3413</v>
+      </c>
+      <c r="J336" t="s">
+        <v>3414</v>
+      </c>
+      <c r="K336" s="24" t="s">
+        <v>3415</v>
+      </c>
+      <c r="L336" s="24" t="s">
+        <v>3416</v>
+      </c>
+      <c r="M336" t="s">
+        <v>3417</v>
+      </c>
+      <c r="N336" s="24" t="s">
+        <v>3418</v>
+      </c>
+      <c r="O336" s="24" t="s">
+        <v>3419</v>
+      </c>
+      <c r="P336" s="24" t="s">
+        <v>3420</v>
+      </c>
+    </row>
+    <row r="337" ht="121.5" spans="2:16">
+      <c r="B337" s="1" t="s">
+        <v>3421</v>
+      </c>
+      <c r="C337" s="30">
+        <v>76737</v>
+      </c>
+      <c r="D337" t="s">
+        <v>3422</v>
+      </c>
+      <c r="E337" t="s">
+        <v>500</v>
+      </c>
+      <c r="F337" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I337" t="s">
+        <v>3423</v>
+      </c>
+      <c r="J337" t="s">
+        <v>3424</v>
+      </c>
+      <c r="K337" s="24" t="s">
+        <v>3425</v>
+      </c>
+      <c r="L337" s="24" t="s">
+        <v>3426</v>
+      </c>
+      <c r="M337" t="s">
+        <v>3427</v>
+      </c>
+      <c r="N337" s="24" t="s">
+        <v>3428</v>
+      </c>
+      <c r="O337" s="24" t="s">
+        <v>3429</v>
+      </c>
+      <c r="P337" s="24" t="s">
+        <v>3430</v>
+      </c>
+    </row>
+    <row r="338" ht="121.5" spans="2:16">
+      <c r="B338" s="1" t="s">
+        <v>3431</v>
+      </c>
+      <c r="C338" s="30">
+        <v>76738</v>
+      </c>
+      <c r="D338" t="s">
+        <v>3432</v>
+      </c>
+      <c r="E338" t="s">
+        <v>500</v>
+      </c>
+      <c r="F338" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I338" t="s">
+        <v>3433</v>
+      </c>
+      <c r="J338" t="s">
+        <v>3434</v>
+      </c>
+      <c r="K338" s="24" t="s">
+        <v>3435</v>
+      </c>
+      <c r="L338" s="24" t="s">
+        <v>3436</v>
+      </c>
+      <c r="M338" t="s">
+        <v>3437</v>
+      </c>
+      <c r="N338" s="24" t="s">
+        <v>3438</v>
+      </c>
+      <c r="O338" s="24" t="s">
+        <v>3439</v>
+      </c>
+      <c r="P338" s="24" t="s">
+        <v>3440</v>
+      </c>
+    </row>
+    <row r="339" ht="16.5" spans="2:16">
+      <c r="F339" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/uploads/网站信息.xlsx
+++ b/uploads/网站信息.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4627" uniqueCount="3441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4672" uniqueCount="3476">
   <si>
     <t>分类</t>
   </si>
@@ -10766,6 +10766,111 @@
   </si>
   <si>
     <t>buy ski bindings online; ski bindings for all-mountain skiing; ski bindings for beginners; lightweight ski bindings for touring; durable ski bindings for park skiing; ski binding set with brakes; ski bindings bundle with straps; ski bindings like Marker; Marker ski binding alternatives; replacement ski bindings for skiers; order ski bindings online; adjustable ski bindings for growing feet; freeride ski bindings for powder</t>
+  </si>
+  <si>
+    <t>81227,81228,81229,81230,81232,81233,81235,81237,81239,81240</t>
+  </si>
+  <si>
+    <t>2-piece Toilets - Toilet Tanks</t>
+  </si>
+  <si>
+    <t>5520 Fargo Rd, Riverside, CA 92506</t>
+  </si>
+  <si>
+    <t>toilettankhub.com</t>
+  </si>
+  <si>
+    <t>Toilet Tanks &amp; 2-Piece Toilets - Bowls, Parts &amp; Kits</t>
+  </si>
+  <si>
+    <t>Shop premium toilet tanks, 2-piece toilets, bowls, and repair kits. Find replacement parts, flush valves, and more with fast US shipping.</t>
+  </si>
+  <si>
+    <t>Toilet Tanks, Bowls &amp; Repair Parts</t>
+  </si>
+  <si>
+    <t>81194,81195,81196,81197,81198,81199,81200,81201,81202,81203</t>
+  </si>
+  <si>
+    <t>American Standard Toilet</t>
+  </si>
+  <si>
+    <t>3196 Tomahawk Cir, Riverside, CA 92503</t>
+  </si>
+  <si>
+    <t>americanstandardtoilet.com</t>
+  </si>
+  <si>
+    <t>American Standard Toilets, Seats &amp; Repair Parts</t>
+  </si>
+  <si>
+    <t>Shop American Standard toilets plus a huge selection of toilet parts, seats, fill valves, flappers, and repair kits for every model.</t>
+  </si>
+  <si>
+    <t>American Standard Toilets &amp; Repair Parts</t>
+  </si>
+  <si>
+    <t>81242,81244,81246,81247,81249,81251,81252,81255,81257,81258</t>
+  </si>
+  <si>
+    <t>Toilet Tank</t>
+  </si>
+  <si>
+    <t>3203 Cherokee St, Riverside, CA 92503</t>
+  </si>
+  <si>
+    <t>toilettankpro.com</t>
+  </si>
+  <si>
+    <t>Toilet Tanks &amp; Repair Parts for Every Bathroom</t>
+  </si>
+  <si>
+    <t>Shop 365+ toilet tanks and repair parts, plus faucets, valves, and plumbing essentials for every US bathroom. Find the right fit fast.</t>
+  </si>
+  <si>
+    <t>Toilet Tanks &amp; Repair Parts</t>
+  </si>
+  <si>
+    <t>81216,81217,81218,81219,81220,81221,81222,81223,81224,81225</t>
+  </si>
+  <si>
+    <t>Toilet Tank Lid</t>
+  </si>
+  <si>
+    <t>1102 El Camino Dr, Costa Mesa, CA 92626</t>
+  </si>
+  <si>
+    <t>tanklidhub.com</t>
+  </si>
+  <si>
+    <t>Toilet Tank Lids &amp; Levers | Tank Lid Hub</t>
+  </si>
+  <si>
+    <t>Shop 1,000+ toilet tank lids plus trip levers and repair parts for all major toilet models. Fast shipping and reliable replacements across the US.</t>
+  </si>
+  <si>
+    <t>Toilet Tank Lids &amp; Repair Parts</t>
+  </si>
+  <si>
+    <t>81205,81206,81207,81208,81209,81210,81211,81212,81213,81214</t>
+  </si>
+  <si>
+    <t>Toilet Tank Lid - Reproduction</t>
+  </si>
+  <si>
+    <t>6382 Cornell Dr, Huntington Beach, CA 92647</t>
+  </si>
+  <si>
+    <t>reprolid.com</t>
+  </si>
+  <si>
+    <t>Reproduction Toilet Tank Lids for Vintage Bathrooms</t>
+  </si>
+  <si>
+    <t>Reproduction toilet tank lids for vintage bathrooms. Plus a wide selection of replacement tanks, parts, and plumbing fixtures.</t>
+  </si>
+  <si>
+    <t>Reproduction Toilet Tank Lids &amp; Tanks</t>
   </si>
 </sst>
 </file>
@@ -11485,7 +11590,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -11573,12 +11678,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -17390,7 +17489,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q339"/>
+  <dimension ref="A1:Q343"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="50.625" customWidth="1"/>
@@ -17466,10 +17565,10 @@
       <c r="A2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="C2" s="31" t="s">
         <v>19</v>
       </c>
       <c r="D2" s="6" t="s">
@@ -17572,7 +17671,7 @@
       <c r="A4" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="30" t="s">
         <v>46</v>
       </c>
       <c r="C4" s="4">
@@ -17625,7 +17724,7 @@
       <c r="A5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="30" t="s">
         <v>58</v>
       </c>
       <c r="C5" s="4">
@@ -17678,7 +17777,7 @@
       <c r="A6" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="30" t="s">
         <v>70</v>
       </c>
       <c r="C6" s="4">
@@ -17731,7 +17830,7 @@
       <c r="A7" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="30" t="s">
         <v>82</v>
       </c>
       <c r="C7" s="8">
@@ -17784,7 +17883,7 @@
       <c r="A8" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="30" t="s">
         <v>95</v>
       </c>
       <c r="C8" s="4">
@@ -17837,7 +17936,7 @@
       <c r="A9" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="30" t="s">
         <v>107</v>
       </c>
       <c r="C9" s="4">
@@ -17890,7 +17989,7 @@
       <c r="A10" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="30" t="s">
         <v>118</v>
       </c>
       <c r="C10" s="4">
@@ -17943,7 +18042,7 @@
       <c r="A11" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B11" s="32" t="s">
+      <c r="B11" s="30" t="s">
         <v>130</v>
       </c>
       <c r="C11" s="4">
@@ -17996,7 +18095,7 @@
       <c r="A12" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="30" t="s">
         <v>141</v>
       </c>
       <c r="C12" s="4">
@@ -18208,7 +18307,7 @@
       <c r="A16" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="B16" s="32" t="s">
+      <c r="B16" s="30" t="s">
         <v>186</v>
       </c>
       <c r="C16" s="4">
@@ -19374,7 +19473,7 @@
       <c r="A38" s="4" t="s">
         <v>430</v>
       </c>
-      <c r="B38" s="34" t="s">
+      <c r="B38" s="32" t="s">
         <v>431</v>
       </c>
       <c r="C38" s="8">
@@ -19427,7 +19526,7 @@
       <c r="A39" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="B39" s="34" t="s">
+      <c r="B39" s="32" t="s">
         <v>442</v>
       </c>
       <c r="C39" s="8">
@@ -19845,7 +19944,7 @@
       <c r="A47" t="s">
         <v>531</v>
       </c>
-      <c r="B47" s="32" t="s">
+      <c r="B47" s="30" t="s">
         <v>532</v>
       </c>
       <c r="C47" s="8">
@@ -20559,7 +20658,7 @@
       <c r="A61" t="s">
         <v>687</v>
       </c>
-      <c r="B61" s="32" t="s">
+      <c r="B61" s="30" t="s">
         <v>688</v>
       </c>
       <c r="C61" s="8">
@@ -20810,7 +20909,7 @@
       <c r="A66" t="s">
         <v>742</v>
       </c>
-      <c r="B66" s="32" t="s">
+      <c r="B66" s="30" t="s">
         <v>743</v>
       </c>
       <c r="C66" s="4">
@@ -20860,7 +20959,7 @@
       <c r="A67" t="s">
         <v>753</v>
       </c>
-      <c r="B67" s="32" t="s">
+      <c r="B67" s="30" t="s">
         <v>754</v>
       </c>
       <c r="C67" s="8">
@@ -20910,7 +21009,7 @@
       <c r="A68" t="s">
         <v>763</v>
       </c>
-      <c r="B68" s="32" t="s">
+      <c r="B68" s="30" t="s">
         <v>764</v>
       </c>
       <c r="C68" s="8">
@@ -20960,7 +21059,7 @@
       <c r="A69" t="s">
         <v>773</v>
       </c>
-      <c r="B69" s="32" t="s">
+      <c r="B69" s="30" t="s">
         <v>774</v>
       </c>
       <c r="C69" s="4">
@@ -21010,7 +21109,7 @@
       <c r="A70" t="s">
         <v>783</v>
       </c>
-      <c r="B70" s="32" t="s">
+      <c r="B70" s="30" t="s">
         <v>784</v>
       </c>
       <c r="C70" s="8">
@@ -21060,7 +21159,7 @@
       <c r="A71" t="s">
         <v>793</v>
       </c>
-      <c r="B71" s="32" t="s">
+      <c r="B71" s="30" t="s">
         <v>794</v>
       </c>
       <c r="C71" s="8">
@@ -21110,7 +21209,7 @@
       <c r="A72" t="s">
         <v>803</v>
       </c>
-      <c r="B72" s="32" t="s">
+      <c r="B72" s="30" t="s">
         <v>804</v>
       </c>
       <c r="C72" s="8">
@@ -21161,7 +21260,7 @@
       <c r="A73" t="s">
         <v>813</v>
       </c>
-      <c r="B73" s="32" t="s">
+      <c r="B73" s="30" t="s">
         <v>814</v>
       </c>
       <c r="C73" s="8">
@@ -21212,7 +21311,7 @@
       <c r="A74" t="s">
         <v>823</v>
       </c>
-      <c r="B74" s="32" t="s">
+      <c r="B74" s="30" t="s">
         <v>824</v>
       </c>
       <c r="C74" s="8">
@@ -21263,7 +21362,7 @@
       <c r="A75" t="s">
         <v>834</v>
       </c>
-      <c r="B75" s="32" t="s">
+      <c r="B75" s="30" t="s">
         <v>835</v>
       </c>
       <c r="C75" s="8">
@@ -21314,7 +21413,7 @@
       <c r="A76" t="s">
         <v>844</v>
       </c>
-      <c r="B76" s="32" t="s">
+      <c r="B76" s="30" t="s">
         <v>845</v>
       </c>
       <c r="C76" s="8">
@@ -21365,7 +21464,7 @@
       <c r="A77" t="s">
         <v>854</v>
       </c>
-      <c r="B77" s="32" t="s">
+      <c r="B77" s="30" t="s">
         <v>855</v>
       </c>
       <c r="C77" s="8">
@@ -21415,7 +21514,7 @@
       <c r="A78" t="s">
         <v>865</v>
       </c>
-      <c r="B78" s="35" t="s">
+      <c r="B78" s="33" t="s">
         <v>866</v>
       </c>
       <c r="C78" s="8">
@@ -21465,7 +21564,7 @@
       <c r="A79" t="s">
         <v>877</v>
       </c>
-      <c r="B79" s="35" t="s">
+      <c r="B79" s="33" t="s">
         <v>878</v>
       </c>
       <c r="C79" s="8">
@@ -21515,7 +21614,7 @@
       <c r="A80" t="s">
         <v>888</v>
       </c>
-      <c r="B80" s="35" t="s">
+      <c r="B80" s="33" t="s">
         <v>889</v>
       </c>
       <c r="C80" s="8">
@@ -21565,7 +21664,7 @@
       <c r="A81" t="s">
         <v>899</v>
       </c>
-      <c r="B81" s="35" t="s">
+      <c r="B81" s="33" t="s">
         <v>900</v>
       </c>
       <c r="C81" s="8">
@@ -21616,7 +21715,7 @@
       <c r="A82" t="s">
         <v>910</v>
       </c>
-      <c r="B82" s="35" t="s">
+      <c r="B82" s="33" t="s">
         <v>911</v>
       </c>
       <c r="C82" s="8">
@@ -21667,7 +21766,7 @@
       <c r="A83" t="s">
         <v>921</v>
       </c>
-      <c r="B83" s="32" t="s">
+      <c r="B83" s="30" t="s">
         <v>922</v>
       </c>
       <c r="C83" s="8">
@@ -21718,7 +21817,7 @@
       <c r="A84" t="s">
         <v>932</v>
       </c>
-      <c r="B84" s="32" t="s">
+      <c r="B84" s="30" t="s">
         <v>933</v>
       </c>
       <c r="C84" s="8">
@@ -21769,7 +21868,7 @@
       <c r="A85" t="s">
         <v>943</v>
       </c>
-      <c r="B85" s="32" t="s">
+      <c r="B85" s="30" t="s">
         <v>944</v>
       </c>
       <c r="C85" s="4">
@@ -21820,7 +21919,7 @@
       <c r="A86" t="s">
         <v>953</v>
       </c>
-      <c r="B86" s="32" t="s">
+      <c r="B86" s="30" t="s">
         <v>954</v>
       </c>
       <c r="C86" s="4">
@@ -21871,7 +21970,7 @@
       <c r="A87" t="s">
         <v>963</v>
       </c>
-      <c r="B87" s="32" t="s">
+      <c r="B87" s="30" t="s">
         <v>964</v>
       </c>
       <c r="C87" s="8">
@@ -30060,7 +30159,7 @@
       </c>
     </row>
     <row r="265" ht="121.5" spans="2:17">
-      <c r="B265" s="36" t="s">
+      <c r="B265" s="34" t="s">
         <v>2703</v>
       </c>
       <c r="C265" s="20">
@@ -31236,7 +31335,7 @@
       <c r="B292" s="1" t="s">
         <v>2974</v>
       </c>
-      <c r="C292" s="30">
+      <c r="C292" s="20">
         <v>76048</v>
       </c>
       <c r="D292" t="s">
@@ -31277,7 +31376,7 @@
       <c r="B293" s="1" t="s">
         <v>2985</v>
       </c>
-      <c r="C293" s="30">
+      <c r="C293" s="20">
         <v>76050</v>
       </c>
       <c r="D293" t="s">
@@ -31318,7 +31417,7 @@
       <c r="B294" s="1" t="s">
         <v>2995</v>
       </c>
-      <c r="C294" s="30">
+      <c r="C294" s="20">
         <v>76056</v>
       </c>
       <c r="D294" t="s">
@@ -31359,7 +31458,7 @@
       <c r="B295" s="1" t="s">
         <v>3005</v>
       </c>
-      <c r="C295" s="30">
+      <c r="C295" s="20">
         <v>76049</v>
       </c>
       <c r="D295" t="s">
@@ -31400,7 +31499,7 @@
       <c r="B296" s="1" t="s">
         <v>3015</v>
       </c>
-      <c r="C296" s="30">
+      <c r="C296" s="20">
         <v>76051</v>
       </c>
       <c r="D296" t="s">
@@ -31441,7 +31540,7 @@
       <c r="B297" s="1" t="s">
         <v>3025</v>
       </c>
-      <c r="C297" s="30">
+      <c r="C297" s="20">
         <v>76055</v>
       </c>
       <c r="D297" t="s">
@@ -31482,7 +31581,7 @@
       <c r="B298" s="1" t="s">
         <v>3035</v>
       </c>
-      <c r="C298" s="30">
+      <c r="C298" s="20">
         <v>76053</v>
       </c>
       <c r="D298" t="s">
@@ -31523,7 +31622,7 @@
       <c r="B299" s="1" t="s">
         <v>3045</v>
       </c>
-      <c r="C299" s="30">
+      <c r="C299" s="20">
         <v>76047</v>
       </c>
       <c r="D299" t="s">
@@ -31564,7 +31663,7 @@
       <c r="B300" s="1" t="s">
         <v>3055</v>
       </c>
-      <c r="C300" s="30">
+      <c r="C300" s="20">
         <v>76052</v>
       </c>
       <c r="D300" t="s">
@@ -31605,7 +31704,7 @@
       <c r="B301" s="1" t="s">
         <v>3065</v>
       </c>
-      <c r="C301" s="30">
+      <c r="C301" s="20">
         <v>76054</v>
       </c>
       <c r="D301" t="s">
@@ -31646,7 +31745,7 @@
       <c r="B302" s="1" t="s">
         <v>3075</v>
       </c>
-      <c r="C302" s="30">
+      <c r="C302" s="20">
         <v>76349</v>
       </c>
       <c r="D302" t="s">
@@ -31687,7 +31786,7 @@
       <c r="B303" s="1" t="s">
         <v>3085</v>
       </c>
-      <c r="C303" s="30">
+      <c r="C303" s="20">
         <v>76346</v>
       </c>
       <c r="D303" t="s">
@@ -31728,7 +31827,7 @@
       <c r="B304" s="1" t="s">
         <v>3095</v>
       </c>
-      <c r="C304" s="30">
+      <c r="C304" s="20">
         <v>76343</v>
       </c>
       <c r="D304" t="s">
@@ -31769,7 +31868,7 @@
       <c r="B305" s="1" t="s">
         <v>3105</v>
       </c>
-      <c r="C305" s="30">
+      <c r="C305" s="20">
         <v>76342</v>
       </c>
       <c r="D305" t="s">
@@ -31810,7 +31909,7 @@
       <c r="B306" s="1" t="s">
         <v>3114</v>
       </c>
-      <c r="C306" s="30">
+      <c r="C306" s="20">
         <v>76340</v>
       </c>
       <c r="D306" t="s">
@@ -31851,7 +31950,7 @@
       <c r="B307" s="1" t="s">
         <v>3124</v>
       </c>
-      <c r="C307" s="30">
+      <c r="C307" s="20">
         <v>76344</v>
       </c>
       <c r="D307" t="s">
@@ -31892,7 +31991,7 @@
       <c r="B308" s="1" t="s">
         <v>3134</v>
       </c>
-      <c r="C308" s="30">
+      <c r="C308" s="20">
         <v>76348</v>
       </c>
       <c r="D308" t="s">
@@ -31933,7 +32032,7 @@
       <c r="B309" s="1" t="s">
         <v>3143</v>
       </c>
-      <c r="C309" s="30">
+      <c r="C309" s="20">
         <v>76345</v>
       </c>
       <c r="D309" t="s">
@@ -31974,7 +32073,7 @@
       <c r="B310" s="1" t="s">
         <v>3153</v>
       </c>
-      <c r="C310" s="30">
+      <c r="C310" s="20">
         <v>76347</v>
       </c>
       <c r="D310" t="s">
@@ -32015,7 +32114,7 @@
       <c r="B311" s="1" t="s">
         <v>3163</v>
       </c>
-      <c r="C311" s="30">
+      <c r="C311" s="20">
         <v>76341</v>
       </c>
       <c r="D311" t="s">
@@ -32056,7 +32155,7 @@
       <c r="B312" s="1" t="s">
         <v>3173</v>
       </c>
-      <c r="C312" s="30">
+      <c r="C312" s="20">
         <v>76449</v>
       </c>
       <c r="D312" t="s">
@@ -32097,7 +32196,7 @@
       <c r="B313" s="1" t="s">
         <v>3183</v>
       </c>
-      <c r="C313" s="30">
+      <c r="C313" s="20">
         <v>76451</v>
       </c>
       <c r="D313" t="s">
@@ -32138,7 +32237,7 @@
       <c r="B314" s="1" t="s">
         <v>3193</v>
       </c>
-      <c r="C314" s="31">
+      <c r="C314" s="20">
         <v>76452</v>
       </c>
       <c r="D314" t="s">
@@ -32179,7 +32278,7 @@
       <c r="B315" s="1" t="s">
         <v>3203</v>
       </c>
-      <c r="C315" s="30">
+      <c r="C315" s="20">
         <v>76450</v>
       </c>
       <c r="D315" t="s">
@@ -32220,7 +32319,7 @@
       <c r="B316" s="1" t="s">
         <v>3213</v>
       </c>
-      <c r="C316" s="30">
+      <c r="C316" s="20">
         <v>76498</v>
       </c>
       <c r="D316" t="s">
@@ -32261,7 +32360,7 @@
       <c r="B317" s="1" t="s">
         <v>3222</v>
       </c>
-      <c r="C317" s="30">
+      <c r="C317" s="20">
         <v>76490</v>
       </c>
       <c r="D317" t="s">
@@ -32302,7 +32401,7 @@
       <c r="B318" s="1" t="s">
         <v>3232</v>
       </c>
-      <c r="C318" s="30">
+      <c r="C318" s="20">
         <v>76494</v>
       </c>
       <c r="D318" t="s">
@@ -32343,7 +32442,7 @@
       <c r="B319" s="1" t="s">
         <v>3242</v>
       </c>
-      <c r="C319" s="30">
+      <c r="C319" s="20">
         <v>76500</v>
       </c>
       <c r="D319" t="s">
@@ -32384,7 +32483,7 @@
       <c r="B320" s="1" t="s">
         <v>3252</v>
       </c>
-      <c r="C320" s="30">
+      <c r="C320" s="20">
         <v>76491</v>
       </c>
       <c r="D320" t="s">
@@ -32425,7 +32524,7 @@
       <c r="B321" s="1" t="s">
         <v>3262</v>
       </c>
-      <c r="C321" s="30">
+      <c r="C321" s="20">
         <v>76493</v>
       </c>
       <c r="D321" t="s">
@@ -32466,7 +32565,7 @@
       <c r="B322" s="1" t="s">
         <v>3272</v>
       </c>
-      <c r="C322" s="30">
+      <c r="C322" s="20">
         <v>76495</v>
       </c>
       <c r="D322" t="s">
@@ -32507,7 +32606,7 @@
       <c r="B323" s="1" t="s">
         <v>3282</v>
       </c>
-      <c r="C323" s="30">
+      <c r="C323" s="20">
         <v>76499</v>
       </c>
       <c r="D323" t="s">
@@ -32548,7 +32647,7 @@
       <c r="B324" s="1" t="s">
         <v>3292</v>
       </c>
-      <c r="C324" s="30">
+      <c r="C324" s="20">
         <v>76496</v>
       </c>
       <c r="D324" t="s">
@@ -32589,7 +32688,7 @@
       <c r="B325" s="1" t="s">
         <v>3302</v>
       </c>
-      <c r="C325" s="30">
+      <c r="C325" s="20">
         <v>76497</v>
       </c>
       <c r="D325" t="s">
@@ -32630,7 +32729,7 @@
       <c r="B326" s="1" t="s">
         <v>3312</v>
       </c>
-      <c r="C326" s="30">
+      <c r="C326" s="20">
         <v>76492</v>
       </c>
       <c r="D326" t="s">
@@ -32671,7 +32770,7 @@
       <c r="B327" s="1" t="s">
         <v>3322</v>
       </c>
-      <c r="C327" s="30">
+      <c r="C327" s="20">
         <v>76730</v>
       </c>
       <c r="D327" t="s">
@@ -32712,7 +32811,7 @@
       <c r="B328" s="1" t="s">
         <v>3332</v>
       </c>
-      <c r="C328" s="30">
+      <c r="C328" s="20">
         <v>76735</v>
       </c>
       <c r="D328" t="s">
@@ -32753,7 +32852,7 @@
       <c r="B329" s="1" t="s">
         <v>3342</v>
       </c>
-      <c r="C329" s="30">
+      <c r="C329" s="20">
         <v>76740</v>
       </c>
       <c r="D329" t="s">
@@ -32794,7 +32893,7 @@
       <c r="B330" s="1" t="s">
         <v>3352</v>
       </c>
-      <c r="C330" s="30">
+      <c r="C330" s="20">
         <v>76731</v>
       </c>
       <c r="D330" t="s">
@@ -32835,7 +32934,7 @@
       <c r="B331" s="1" t="s">
         <v>3362</v>
       </c>
-      <c r="C331" s="30">
+      <c r="C331" s="20">
         <v>76733</v>
       </c>
       <c r="D331" t="s">
@@ -32876,7 +32975,7 @@
       <c r="B332" s="1" t="s">
         <v>3372</v>
       </c>
-      <c r="C332" s="31">
+      <c r="C332" s="20">
         <v>76739</v>
       </c>
       <c r="D332" t="s">
@@ -32917,7 +33016,7 @@
       <c r="B333" s="1" t="s">
         <v>3382</v>
       </c>
-      <c r="C333" s="30">
+      <c r="C333" s="20">
         <v>76732</v>
       </c>
       <c r="D333" t="s">
@@ -32958,7 +33057,7 @@
       <c r="B334" s="1" t="s">
         <v>3392</v>
       </c>
-      <c r="C334" s="30">
+      <c r="C334" s="20">
         <v>76729</v>
       </c>
       <c r="D334" t="s">
@@ -32999,7 +33098,7 @@
       <c r="B335" s="1" t="s">
         <v>3401</v>
       </c>
-      <c r="C335" s="30">
+      <c r="C335" s="20">
         <v>76736</v>
       </c>
       <c r="D335" t="s">
@@ -33040,7 +33139,7 @@
       <c r="B336" s="1" t="s">
         <v>3411</v>
       </c>
-      <c r="C336" s="30">
+      <c r="C336" s="20">
         <v>76734</v>
       </c>
       <c r="D336" t="s">
@@ -33081,7 +33180,7 @@
       <c r="B337" s="1" t="s">
         <v>3421</v>
       </c>
-      <c r="C337" s="30">
+      <c r="C337" s="20">
         <v>76737</v>
       </c>
       <c r="D337" t="s">
@@ -33122,7 +33221,7 @@
       <c r="B338" s="1" t="s">
         <v>3431</v>
       </c>
-      <c r="C338" s="30">
+      <c r="C338" s="20">
         <v>76738</v>
       </c>
       <c r="D338" t="s">
@@ -33160,7 +33259,164 @@
       </c>
     </row>
     <row r="339" ht="16.5" spans="2:16">
-      <c r="F339" s="4"/>
+      <c r="B339" s="1" t="s">
+        <v>3441</v>
+      </c>
+      <c r="C339">
+        <v>81226</v>
+      </c>
+      <c r="D339" t="s">
+        <v>3442</v>
+      </c>
+      <c r="E339" t="s">
+        <v>21</v>
+      </c>
+      <c r="F339" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I339" t="s">
+        <v>3443</v>
+      </c>
+      <c r="J339" t="s">
+        <v>3444</v>
+      </c>
+      <c r="K339" t="s">
+        <v>3445</v>
+      </c>
+      <c r="M339" t="s">
+        <v>3446</v>
+      </c>
+      <c r="O339" t="s">
+        <v>3447</v>
+      </c>
+    </row>
+    <row r="340" ht="16.5" spans="2:16">
+      <c r="B340" s="1" t="s">
+        <v>3448</v>
+      </c>
+      <c r="C340">
+        <v>81193</v>
+      </c>
+      <c r="D340" t="s">
+        <v>3449</v>
+      </c>
+      <c r="E340" t="s">
+        <v>21</v>
+      </c>
+      <c r="F340" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I340" t="s">
+        <v>3450</v>
+      </c>
+      <c r="J340" t="s">
+        <v>3451</v>
+      </c>
+      <c r="K340" t="s">
+        <v>3452</v>
+      </c>
+      <c r="M340" t="s">
+        <v>3453</v>
+      </c>
+      <c r="O340" t="s">
+        <v>3454</v>
+      </c>
+    </row>
+    <row r="341" ht="16.5" spans="2:16">
+      <c r="B341" s="1" t="s">
+        <v>3455</v>
+      </c>
+      <c r="C341">
+        <v>81241</v>
+      </c>
+      <c r="D341" t="s">
+        <v>3456</v>
+      </c>
+      <c r="E341" t="s">
+        <v>21</v>
+      </c>
+      <c r="F341" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I341" t="s">
+        <v>3457</v>
+      </c>
+      <c r="J341" t="s">
+        <v>3458</v>
+      </c>
+      <c r="K341" t="s">
+        <v>3459</v>
+      </c>
+      <c r="M341" t="s">
+        <v>3460</v>
+      </c>
+      <c r="O341" t="s">
+        <v>3461</v>
+      </c>
+    </row>
+    <row r="342" ht="16.5" spans="2:16">
+      <c r="B342" s="1" t="s">
+        <v>3462</v>
+      </c>
+      <c r="C342">
+        <v>81215</v>
+      </c>
+      <c r="D342" t="s">
+        <v>3463</v>
+      </c>
+      <c r="E342" t="s">
+        <v>21</v>
+      </c>
+      <c r="F342" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I342" t="s">
+        <v>3464</v>
+      </c>
+      <c r="J342" t="s">
+        <v>3465</v>
+      </c>
+      <c r="K342" t="s">
+        <v>3466</v>
+      </c>
+      <c r="M342" t="s">
+        <v>3467</v>
+      </c>
+      <c r="O342" t="s">
+        <v>3468</v>
+      </c>
+    </row>
+    <row r="343" ht="16.5" spans="2:16">
+      <c r="B343" s="1" t="s">
+        <v>3469</v>
+      </c>
+      <c r="C343">
+        <v>81204</v>
+      </c>
+      <c r="D343" t="s">
+        <v>3470</v>
+      </c>
+      <c r="E343" t="s">
+        <v>21</v>
+      </c>
+      <c r="F343" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I343" t="s">
+        <v>3471</v>
+      </c>
+      <c r="J343" t="s">
+        <v>3472</v>
+      </c>
+      <c r="K343" t="s">
+        <v>3473</v>
+      </c>
+      <c r="M343" t="s">
+        <v>3474</v>
+      </c>
+      <c r="O343" t="s">
+        <v>3475</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>

--- a/uploads/网站信息.xlsx
+++ b/uploads/网站信息.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11775"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4672" uniqueCount="3476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5392" uniqueCount="3982">
   <si>
     <t>分类</t>
   </si>
@@ -10831,7 +10831,10 @@
     <t>Toilet Tanks &amp; Repair Parts</t>
   </si>
   <si>
-    <t>81216,81217,81218,81219,81220,81221,81222,81223,81224,81225</t>
+    <t>,81219</t>
+  </si>
+  <si>
+    <t>81216,81217,81218,81220,81221,81222,81223,81224,81225</t>
   </si>
   <si>
     <t>Toilet Tank Lid</t>
@@ -10871,6 +10874,1521 @@
   </si>
   <si>
     <t>Reproduction Toilet Tank Lids &amp; Tanks</t>
+  </si>
+  <si>
+    <t>82686,82687,82688,82689,82690,82691,82692,82693,82694,82695</t>
+  </si>
+  <si>
+    <t>Pet Toys|||Ball &amp; Chaser</t>
+  </si>
+  <si>
+    <t>2305 Pebblebrook Ct, Grand Prairie, TX 75050</t>
+  </si>
+  <si>
+    <t>chaserforge.com</t>
+  </si>
+  <si>
+    <t>Ball and Chaser Pet Toys Built for Rough Play</t>
+  </si>
+  <si>
+    <t>A 3-inch natural rubber ball with a sealed squeaker leads our ball and chaser pet toy lineup, plus launchers and ropes.</t>
+  </si>
+  <si>
+    <t>Ball and chaser pet toys</t>
+  </si>
+  <si>
+    <t>ball and chaser pet toys, dog ball launcher toys, interactive dog chase toys, durable rubber dog balls, pet toy ball launcher, fetch and chase dog toys, squeaky dog balls for fetch, dog toy balls for aggressive chewers, replacement ball for dog launcher, outdoor dog chase ball toy, pet ball chaser toy for dogs</t>
+  </si>
+  <si>
+    <t>82740,82741,82742,82743,82744,82745,82746,82747,82748,82749</t>
+  </si>
+  <si>
+    <t>Cat Apparel|||Cat T-Shirts</t>
+  </si>
+  <si>
+    <t>1515 Commercial St SE, Salem, OR 97302</t>
+  </si>
+  <si>
+    <t>rivetcat.com</t>
+  </si>
+  <si>
+    <t>Heavyweight Cotton Cat T-Shirts for Jobsite and Couch</t>
+  </si>
+  <si>
+    <t>Your old cat tee has blown a seam? We stock heavyweight cotton cat t-shirts that hold up on job sites, in shops, and on the couch.</t>
+  </si>
+  <si>
+    <t>Cat t-shirts and cat-themed apparel</t>
+  </si>
+  <si>
+    <t>cat t-shirts, funny cat t-shirts, cat lover t-shirts, heavyweight cat t-shirts, cat graphic tees, durable cat t-shirts, cat t-shirts for work, cat t-shirts for men, cat t-shirts for women, bulk cat t-shirts, cat print t-shirts</t>
+  </si>
+  <si>
+    <t>82697,82698,82699,82700,82701,82702,82703,82704,82705,82706</t>
+  </si>
+  <si>
+    <t>Poultry Supplies|||Chicken Supplies</t>
+  </si>
+  <si>
+    <t>217 Buist Ave, Greenville, SC 29609</t>
+  </si>
+  <si>
+    <t>coopcraft.com</t>
+  </si>
+  <si>
+    <t>Handcrafted Cedar Chicken Coops &amp; Poultry Supplies</t>
+  </si>
+  <si>
+    <t>Building a backyard flock? We make small-batch cedar coops, feeders, and care tools for chicken keepers who want gear that lasts.</t>
+  </si>
+  <si>
+    <t>Chicken coop and poultry supplies</t>
+  </si>
+  <si>
+    <t>chicken supplies, poultry supplies, chicken coop supplies, backyard chicken supplies, chicken feeders, chicken waterers, chicken coops, poultry equipment, chicken nesting boxes, poultry feeders, poultry waterers, chicken health supplies, small flock supplies, chicken keeping tools</t>
+  </si>
+  <si>
+    <t>82708,82709,82710,82711,82712,82713,82714,82715,82716,82717</t>
+  </si>
+  <si>
+    <t>Pet Supplies|||Dog Travel Crates</t>
+  </si>
+  <si>
+    <t>1858 W Nob Hill St SE, Salem, OR 97302</t>
+  </si>
+  <si>
+    <t>cratewright.com</t>
+  </si>
+  <si>
+    <t>Hand-Built Dog Travel Crates for Road &amp; Cabin</t>
+  </si>
+  <si>
+    <t>Your dog outgrew the back seat, so we build rugged travel crates that fit trucks, SUVs, and cabin trips.</t>
+  </si>
+  <si>
+    <t>Dog travel crates and vehicle kennels</t>
+  </si>
+  <si>
+    <t>dog travel crates, dog crates for travel, crash tested dog crate, dog crate for suv, dog crate for truck, aluminum dog crate, collapsible dog crate, portable dog crate, dog travel kennel, suv dog kennel, truck dog kennel, airline dog crate, dog crate for car, pet travel crate, heavy duty dog crate, dog crate tie down</t>
+  </si>
+  <si>
+    <t>82730,82731,82732,82733,82734,82735,82736,82737,82738</t>
+  </si>
+  <si>
+    <t>Horse Tack|||Halters &amp; Shanks</t>
+  </si>
+  <si>
+    <t>652 N Kachina, Mesa, AZ 85203</t>
+  </si>
+  <si>
+    <t>haltora.com</t>
+  </si>
+  <si>
+    <t>Horse Tack for Calm Handling, Halters &amp; Shanks</t>
+  </si>
+  <si>
+    <t>A horse that won't stand still for haltering makes every day harder. Our family shop makes halters, shanks, and tack that fit and last.</t>
+  </si>
+  <si>
+    <t>Horse tack, halters, and shanks</t>
+  </si>
+  <si>
+    <t>horse tack, horse halters, horse shanks, horse saddles, english bits, western breast collars, western saddle pads, horse bits and chinstraps, lead shanks for horses, halter and lead sets, english saddles, western saddles, horse saddle pads, breast collars for horses, chinstraps for horse bits</t>
+  </si>
+  <si>
+    <t>82719,82720,82721,82722,82723,82724,82725,82726,82727,82728</t>
+  </si>
+  <si>
+    <t>Cat Food|||Wet Food</t>
+  </si>
+  <si>
+    <t>38 Banks St, Somerville, MA 02144</t>
+  </si>
+  <si>
+    <t>gravycrate.com</t>
+  </si>
+  <si>
+    <t>GravyCrate: Bulk Wet Cat Food Cases</t>
+  </si>
+  <si>
+    <t>Wet cat food and dog food cases, pouches, pates, and bulk variety packs. Orders ship in heavy-duty boxes with tracking and responsive support.</t>
+  </si>
+  <si>
+    <t>Bulk wet cat food and dog food cases</t>
+  </si>
+  <si>
+    <t>wet cat food, cat food, canned cat food, wet dog food, dog food, canned dog food, bulk cat food, bulk wet cat food, cat food cases, dog food cases, pate cat food, gravy cat food, wet food variety packs, bulk pet food</t>
+  </si>
+  <si>
+    <t>82773,82774,82775,82776,82777,82778,82779,82780,82781,82782</t>
+  </si>
+  <si>
+    <t>Pet Supplies|||Poop Bags</t>
+  </si>
+  <si>
+    <t>22 Jerome St, Boston, MA 02125</t>
+  </si>
+  <si>
+    <t>waxedpoopbag.com</t>
+  </si>
+  <si>
+    <t>Leak-Proof Poop Bags for Daily Walks and Cleanup</t>
+  </si>
+  <si>
+    <t>A deep stock of leak-proof, compostable, and extra-thick poop bags, sized from teacup dogs to giant breeds. Built for Anchorage pet owners who walk in cold, wet weather.</t>
+  </si>
+  <si>
+    <t>Dog poop bags and pet waste bags</t>
+  </si>
+  <si>
+    <t>poop bags, dog poop bags, leak proof poop bags, compostable dog poop bags, extra thick poop bags, biodegradable poop bags, poop bags for large dogs, poop bags for small dogs, unscented dog poop bags, poop bag refills</t>
+  </si>
+  <si>
+    <t>82762,82763,82764,82765,82766,82767,82768,82769,82770,82771</t>
+  </si>
+  <si>
+    <t>Veterinary Supplies|||Equipment</t>
+  </si>
+  <si>
+    <t>57 Woodward Ave, Quincy, MA 02169</t>
+  </si>
+  <si>
+    <t>vetforge.com</t>
+  </si>
+  <si>
+    <t>Equip Your Practice with Veterinary Supplies That Last</t>
+  </si>
+  <si>
+    <t>For mixed-animal veterinarians and clinic owners, we're a second-generation family shop offering field-ready veterinary equipment and supplies, chosen for dependable daily use.</t>
+  </si>
+  <si>
+    <t>Veterinary supplies and equipment</t>
+  </si>
+  <si>
+    <t>veterinary equipment, veterinary supplies, veterinary instruments, veterinary surgical instruments, animal clinic supplies, veterinary exam equipment, large animal veterinary supplies, veterinary clinic equipment, veterinary diagnostic equipment</t>
+  </si>
+  <si>
+    <t>82751,82752,82753,82754,82755,82756,82757,82758,82759,82760</t>
+  </si>
+  <si>
+    <t>Bird Supplies|||Wild Bird Food</t>
+  </si>
+  <si>
+    <t>149 Kent St, Hackensack, NJ 07601</t>
+  </si>
+  <si>
+    <t>seedandcedar.com</t>
+  </si>
+  <si>
+    <t>Wild bird food and feeders from our family to yours</t>
+  </si>
+  <si>
+    <t>We stock suet, seed blends, and squirrel-proof feeders for backyard birds. Our family helps you pick what works.</t>
+  </si>
+  <si>
+    <t>Wild bird food and backyard bird supplies</t>
+  </si>
+  <si>
+    <t>wild bird food, bird seed, wild bird seed, suet cakes, nyjer seed, mealworms for birds, squirrel proof bird feeders, wild bird feeders, bird seed blends</t>
+  </si>
+  <si>
+    <t>82784,82785,82786,82787,82788,82789,82790,82791,82792,82793</t>
+  </si>
+  <si>
+    <t>Animals &amp; Pet Supplies|||Zoanthids</t>
+  </si>
+  <si>
+    <t>1172 E 49th St, Los Angeles, CA 90011</t>
+  </si>
+  <si>
+    <t>zoanthidforge.com</t>
+  </si>
+  <si>
+    <t>Zoanthids - Workshop-Grown Coral Frags &amp; Colonies</t>
+  </si>
+  <si>
+    <t>Zoanthid frags, colonies, and reef-grade supplies for dedicated aquarists. Every order is hand-inspected and packed in Marietta workshop.</t>
+  </si>
+  <si>
+    <t>Zoanthid coral frags and colonies</t>
+  </si>
+  <si>
+    <t>zoanthids for sale, zoanthid frags, zoanthid colonies, live zoanthids, aquacultured zoanthids, buy zoanthid coral, rare zoanthids, zoanthid packs</t>
+  </si>
+  <si>
+    <t>82815,82816,82817,82818,82819,82820,82821,82822,82823</t>
+  </si>
+  <si>
+    <t>Art &amp; Crafting Materials|||Gouache Paint</t>
+  </si>
+  <si>
+    <t>13619 Rayen St, Arleta, CA 91331</t>
+  </si>
+  <si>
+    <t>gouachepaintco.com</t>
+  </si>
+  <si>
+    <t>Gouache Paint and Canvas for Daily Painting Practice</t>
+  </si>
+  <si>
+    <t>Our family has stocked Holbein gouache sets since 1987, plus canvas, airbrushes, and art pencils.</t>
+  </si>
+  <si>
+    <t>Gouache paint and art crafting supplies</t>
+  </si>
+  <si>
+    <t>gouache paint, gouache paint sets, art crafting materials, canvas for painting, airbrushes, art pencils, gouache tubes, artist canvas, craft supplies, painting supplies, canvas panels, airbrush accessories, colored pencils, art materials</t>
+  </si>
+  <si>
+    <t>82825,82826,82827,82828,82829,82830,82831,82832,82833</t>
+  </si>
+  <si>
+    <t>Arts &amp; Entertainment|||Oil Pastels</t>
+  </si>
+  <si>
+    <t>399 Prospect Ave, Cranford, NJ 07016</t>
+  </si>
+  <si>
+    <t>pasteliot.com</t>
+  </si>
+  <si>
+    <t>Oil Pastels for Rich, Blendable Color on Any Paper</t>
+  </si>
+  <si>
+    <t>Cheap pastels crumble and dull your drawing — we pack studio-grade oil pastels and art prints made to hold their color.</t>
+  </si>
+  <si>
+    <t>Oil pastels, art prints, and original artwork</t>
+  </si>
+  <si>
+    <t>oil pastels, buy oil pastels, oil pastel set, artist oil pastels, soft oil pastels, oil pastel artwork, original art prints, oil pastel paper</t>
+  </si>
+  <si>
+    <t>82805,82806,82807,82808,82809,82810,82811,82812,82813</t>
+  </si>
+  <si>
+    <t>Arts &amp; Entertainment|||Original Bollywood Posters</t>
+  </si>
+  <si>
+    <t>1405 Cedar St, San Carlos, CA 94070</t>
+  </si>
+  <si>
+    <t>bollyvint.com</t>
+  </si>
+  <si>
+    <t>Original Bollywood Posters for Set &amp; Wall Projects</t>
+  </si>
+  <si>
+    <t>Framing a retro cinema room or sourcing set dressing? We supply original Bollywood posters and vintage Indian film art in trade-ready condition.</t>
+  </si>
+  <si>
+    <t>Original Bollywood posters and vintage Indian film art</t>
+  </si>
+  <si>
+    <t>original bollywood posters, bollywood movie posters, vintage bollywood posters, indian film posters, bollywood wall art, retro bollywood prints, classic bollywood posters, original indian movie posters, bollywood memorabilia, vintage indian cinema posters, hand-painted bollywood posters, old bollywood film posters, bollywood poster art, indian cinema wall decor</t>
+  </si>
+  <si>
+    <t>82835,82836,82837,82838,82839,82840,82841,82842,82843</t>
+  </si>
+  <si>
+    <t>Arts &amp; Entertainment|||Pixel Art</t>
+  </si>
+  <si>
+    <t>859 E 52nd Pl, Los Angeles, CA 90011</t>
+  </si>
+  <si>
+    <t>pixelmosai.com</t>
+  </si>
+  <si>
+    <t>Pixel Art Prints &amp; Posters — Independent Curator's Picks</t>
+  </si>
+  <si>
+    <t>Pixel art prints, posters, stickers, and limited-edition digital artwork, selected with an editorial eye. Each order is packed carefully and shipped from Pennsylvania.</t>
+  </si>
+  <si>
+    <t>Pixel art prints, posters, and original digital artwork</t>
+  </si>
+  <si>
+    <t>pixel art prints, original pixel art, pixel art posters, limited edition pixel art, pixel art stickers, buy pixel art, pixel art canvas, pixel art for sale</t>
+  </si>
+  <si>
+    <t>82855,82856,82857,82858,82859,82860,82861,82862,82863</t>
+  </si>
+  <si>
+    <t>Arts &amp; Entertainment|||Soft Pastels</t>
+  </si>
+  <si>
+    <t>4422 Cahill St, Fremont, CA 94538</t>
+  </si>
+  <si>
+    <t>softpastt.com</t>
+  </si>
+  <si>
+    <t>Soft Pastels - Bulk Art Supply Packs</t>
+  </si>
+  <si>
+    <t>Artists and classrooms buy soft pastels in bulk; we pick budget-friendly sets, sticks, and paper for high-volume use.</t>
+  </si>
+  <si>
+    <t>Soft pastels and pastel art supplies</t>
+  </si>
+  <si>
+    <t>bulk soft pastels, soft pastel sets, soft pastel sticks, soft pastel paper, buy soft pastels, soft pastels for artists, wholesale soft pastels, soft pastel art supplies</t>
+  </si>
+  <si>
+    <t>82795,82796,82797,82798,82799,82800,82801,82802,82803</t>
+  </si>
+  <si>
+    <t>Arts &amp; Entertainment|||Spray Paint</t>
+  </si>
+  <si>
+    <t>4240 W 59th Pl, Los Angeles, CA 90043</t>
+  </si>
+  <si>
+    <t>aerocanva.com</t>
+  </si>
+  <si>
+    <t>Spray Paint for Canvas, Mural and Sign Work</t>
+  </si>
+  <si>
+    <t>Deep in artist-grade spray paint, caps, and surface prep for muralists, sign painters, and studio artists.</t>
+  </si>
+  <si>
+    <t>Spray paint and art materials</t>
+  </si>
+  <si>
+    <t>spray paint for artists, artist grade spray paint, mural spray paint, spray paint for canvas, low pressure spray paint, high pigment spray paint, spray paint caps and nozzles, surface prep for spray paint, sign painter spray paint, spray paint for custom work, aerosol art supplies</t>
+  </si>
+  <si>
+    <t>82845,82846,82847,82848,82849,82850,82851,82852,82853</t>
+  </si>
+  <si>
+    <t>Artwork|||Frameable Prints</t>
+  </si>
+  <si>
+    <t>457 Winchester Ave, Staten Island, NY 10312</t>
+  </si>
+  <si>
+    <t>printpulp.com</t>
+  </si>
+  <si>
+    <t>Frameable Art Prints for Gallery Walls &amp; Gifts</t>
+  </si>
+  <si>
+    <t>Decorating a rental, filling a gallery wall, or restocking your booth? We bundle frameable art prints in budget-friendly packs, so you can frame more and spend less.</t>
+  </si>
+  <si>
+    <t>Frameable art and wall prints</t>
+  </si>
+  <si>
+    <t>frameable art prints, art prints, wall art prints, architecture prints, digital prints, dictionary art prints, framed wall art prints, bulk art prints, budget art prints, print packs, gallery wall prints, unframed art prints</t>
+  </si>
+  <si>
+    <t>82865,82866,82867,82868,82869,82870,82871,82872,82873,82874</t>
+  </si>
+  <si>
+    <t>Party Supplies|||Graduation</t>
+  </si>
+  <si>
+    <t>947 Ellis St, San Francisco, CA 94109</t>
+  </si>
+  <si>
+    <t>gradfete.com</t>
+  </si>
+  <si>
+    <t>Graduation Party Supplies for Fast, Stress-Free Setups</t>
+  </si>
+  <si>
+    <t>Graduation party supplies run deep here—thousands of napkins, mylar balloons, gift bags, and bulk New Year's Eve/Mardi Gras kits for event contractors and school crews who need trade-grade reliability</t>
+  </si>
+  <si>
+    <t>Graduation party supplies and decorations</t>
+  </si>
+  <si>
+    <t>graduation party supplies, graduation decorations, party supplies, mylar balloons, graduation napkins, bulk party supplies, kids birthday party supplies, new years eve party supplies, mardi gras party supplies</t>
+  </si>
+  <si>
+    <t>82876,82877,82878,82879,82880,82881,82882,82883,82884,82885</t>
+  </si>
+  <si>
+    <t>Party Supplies|||Halloween Bulk</t>
+  </si>
+  <si>
+    <t>4653 Porter St, Fremont, CA 94538</t>
+  </si>
+  <si>
+    <t>partybulkt.com</t>
+  </si>
+  <si>
+    <t>Stock the Whole Party: Bulk Party Supplies &amp; Favors</t>
+  </si>
+  <si>
+    <t>Party hosts, teachers, and Halloween lovers: we've picked bulk party supplies, favors, tableware, and decorations for easy, budget-friendly celebrations.</t>
+  </si>
+  <si>
+    <t>Bulk party supplies and Halloween favors</t>
+  </si>
+  <si>
+    <t>bulk party supplies, halloween party favors in bulk, party favors for kids, bulk halloween decorations, party tableware sets, honeycomb party decorations, new years eve party supplies, luau party decorations bulk, photobooth props for parties, paper lanterns party pack, bulk party favors for adults</t>
+  </si>
+  <si>
+    <t>82887,82888,82889,82890,82891,82892,82893,82894,82895,82896</t>
+  </si>
+  <si>
+    <t>Party Supplies|||Kids Birthday Decorations &amp; Accessories</t>
+  </si>
+  <si>
+    <t>190 Thornycroft Ave, Staten Island, NY 10312</t>
+  </si>
+  <si>
+    <t>partypacky.com</t>
+  </si>
+  <si>
+    <t>Kids Birthday Decorations &amp; Accessories, Ready to Party</t>
+  </si>
+  <si>
+    <t>Deep in kids birthday decorations, from piñatas and banners to latex balloons, for parents and room parents who need the right pieces fast.</t>
+  </si>
+  <si>
+    <t>Kids birthday decorations and party accessories</t>
+  </si>
+  <si>
+    <t>kids birthday decorations, birthday party supplies, kids party decorations, birthday decorations for kids, kids birthday party supplies, party accessories for kids, children's birthday decorations, kids birthday party decorations, birthday party decorations</t>
+  </si>
+  <si>
+    <t>82898,82899,82900,82901,82902,82903,82904,82905,82906,82907</t>
+  </si>
+  <si>
+    <t>Trendtex</t>
+  </si>
+  <si>
+    <t>302 Alameda de las Pulgas, Belmont, CA 94002</t>
+  </si>
+  <si>
+    <t>trendtexia.com</t>
+  </si>
+  <si>
+    <t>Trendtex fabrics for sewing quilting and crafting</t>
+  </si>
+  <si>
+    <t>Trendtex fabrics, batik yardage, dress textiles, and craft supplies fill this specialist catalog. We provide careful order support and detailed fabric guidance.</t>
+  </si>
+  <si>
+    <t>Trendtex fabrics and textile supplies</t>
+  </si>
+  <si>
+    <t>trendtex fabric, trendtex textiles, trendtex sewing fabric, trendtex craft fabric, batik fabric by the yard, dress fabric for sewing, new wave textile prints, quilting cotton fabric, fabric for craft projects, dressmaking fabric supplies</t>
+  </si>
+  <si>
+    <t>82931,82932,82933,82934,82935,82936,82937,82938,82939,82940</t>
+  </si>
+  <si>
+    <t>Food, Beverages &amp; Tobacco|||Australian Gin</t>
+  </si>
+  <si>
+    <t>1346 Union St, San Francisco, CA 94109</t>
+  </si>
+  <si>
+    <t>gincask.com</t>
+  </si>
+  <si>
+    <t>Australian Gin, Wine, Whisky and Fine Spirits</t>
+  </si>
+  <si>
+    <t>Our barrel-aged Australian gin sits beside red wine, Champagne, whiskey and sake.</t>
+  </si>
+  <si>
+    <t>Australian gin, wine and spirits</t>
+  </si>
+  <si>
+    <t>australian gin, gin, wine, red wine, white wine, champagne, spirits, whiskey, whisky, sake, beer, bourbon, tequila, rum, liqueur, vodka</t>
+  </si>
+  <si>
+    <t>82942,82943,82944,82945,82946,82947,82948,82949,82950,82951</t>
+  </si>
+  <si>
+    <t>Food, Beverages &amp; Tobacco|||Beer Mak Ingredient</t>
+  </si>
+  <si>
+    <t>23 Hampton Rd, Cranford, NJ 07016</t>
+  </si>
+  <si>
+    <t>mashcratt.com</t>
+  </si>
+  <si>
+    <t>Stock Your Brew Day: Bulk Beer Making Ingredients</t>
+  </si>
+  <si>
+    <t>Planning a big brew day on a small budget? We stock bulk malt, hops, yeast, and kits so your next batch costs less per pint.</t>
+  </si>
+  <si>
+    <t>Bulk beer making ingredients and homebrew supplies</t>
+  </si>
+  <si>
+    <t>beer making ingredients, homebrew supplies, beer making kits, bulk brewing ingredients, brewing malt, brewing hops, brewer's yeast, beer recipe kits, wine making kits, wine ingredients, brewing grains, malt extract, flavor concentrate, home brewing supplies, beer ingredient kit, bulk malt extract</t>
+  </si>
+  <si>
+    <t>82920,82921,82922,82923,82924,82925,82926,82927,82928,82929</t>
+  </si>
+  <si>
+    <t>Food, Beverages &amp; Tobacco|||Canadian Whisky</t>
+  </si>
+  <si>
+    <t>1408 Overland Dr, San Mateo, CA 94403</t>
+  </si>
+  <si>
+    <t>dramstea.com</t>
+  </si>
+  <si>
+    <t>Dramstead: Canadian Whisky and Small-Batch Spirits</t>
+  </si>
+  <si>
+    <t>For American whisky drinkers: a second-generation family selects Canadian whisky, rye, bourbon, and bar staples for your shelf.</t>
+  </si>
+  <si>
+    <t>Canadian whisky and small-batch spirits</t>
+  </si>
+  <si>
+    <t>canadian whisky, canadian rye whisky, rye whisky, canadian whiskey, whisky, single malt scotch, bourbon, spirits, red wine, white wine, tequila, rum, gin, vodka, beer, snacks</t>
+  </si>
+  <si>
+    <t>82975,82976,82977,82978,82979,82980,82981,82982,82983,82984</t>
+  </si>
+  <si>
+    <t>Food, Beverages &amp; Tobacco|||Champagne &amp; Sparkl</t>
+  </si>
+  <si>
+    <t>1039 Sylvan Dr, San Carlos, CA 94070</t>
+  </si>
+  <si>
+    <t>spumorae.com</t>
+  </si>
+  <si>
+    <t>Traditional-Method Champagne &amp; Sparkling Wine for Cellars</t>
+  </si>
+  <si>
+    <t>Louis Roederer Brut Premier anchors our Champagne and sparkling wine range, from blanc de blancs to Prosecco, Cava, and rosé.</t>
+  </si>
+  <si>
+    <t>Champagne and sparkling wine</t>
+  </si>
+  <si>
+    <t>champagne, sparkling wine, buy champagne online, vintage champagne, brut champagne, blanc de blancs, prosecco, cava, sparkling rosé</t>
+  </si>
+  <si>
+    <t>82964,82965,82966,82967,82968,82969,82970,82971,82972,82973</t>
+  </si>
+  <si>
+    <t>Food, Beverages &amp; Tobacco|||Mezcal Tequila</t>
+  </si>
+  <si>
+    <t>1230 Avon St, Belmont, CA 94002</t>
+  </si>
+  <si>
+    <t>smokeagave.com</t>
+  </si>
+  <si>
+    <t>SmokeAgave: Mezcal &amp; Tequila Bottles</t>
+  </si>
+  <si>
+    <t>A smoky Espadín mezcal from Oaxaca anchors our shelves, alongside reposado tequila, bourbon, rum, and small-lot wine. We're a Tyler hobbyist outfit that tastes every bottle before listing it.</t>
+  </si>
+  <si>
+    <t>Mezcal, tequila, and agave spirits</t>
+  </si>
+  <si>
+    <t>mezcal tequila bottles, smoky espadin mezcal, reposado tequila, anejo tequila, blanco tequila, small batch agave spirits, artisanal mezcal, tequila and mezcal gift set, agave spirits, mezcal tasting notes</t>
+  </si>
+  <si>
+    <t>82953,82954,82955,82956,82957,82958,82959,82960,82961,82962</t>
+  </si>
+  <si>
+    <t>Food, Beverages &amp; Tobacco|||Sauvignon Blanc</t>
+  </si>
+  <si>
+    <t>1658 Filbert St, San Francisco, CA 94123</t>
+  </si>
+  <si>
+    <t>sauvignonsteel.com</t>
+  </si>
+  <si>
+    <t>Sauvignon Blanc for Trade Cellars and Service Pros</t>
+  </si>
+  <si>
+    <t>Marlborough Sauvignon Blanc leads our trade-grade wines, spirits, and bar supplies for pros.</t>
+  </si>
+  <si>
+    <t>Sauvignon Blanc and trade-grade beverage supply</t>
+  </si>
+  <si>
+    <t>sauvignon blanc, white wine, wine, red wine, spirits, whiskey, rye whiskey, bourbon, tequila, rum, gin, vodka, liqueur, beer, chocolate</t>
+  </si>
+  <si>
+    <t>82909,82910,82911,82912,82913,82914,82915,82916,82917,82918</t>
+  </si>
+  <si>
+    <t>Food, Beverages &amp; Tobacco|||Tequila &amp; Mezcal</t>
+  </si>
+  <si>
+    <t>324 Spruce Ave, Garwood, NJ 07027</t>
+  </si>
+  <si>
+    <t>agavecask.com</t>
+  </si>
+  <si>
+    <t>Real tequila and mezcal chosen by two hobbyists</t>
+  </si>
+  <si>
+    <t>Building a home bar or hunting a rare agave pour? We test every bottle and ship small-batch tequila, mezcal, and more to your door.</t>
+  </si>
+  <si>
+    <t>Tequila, mezcal, and agave spirits</t>
+  </si>
+  <si>
+    <t>tequila, mezcal, agave spirits, blanco tequila, reposado tequila, anejo tequila, mezcal espadin, small batch tequila, artisanal mezcal, tequila gifts, mezcal gifts, agave, red wine, whiskey, bourbon, spirits</t>
+  </si>
+  <si>
+    <t>84258,84260,84262,84264,84266,84268,84269,84271,84273,84274</t>
+  </si>
+  <si>
+    <t>Watch Accessories|||Straps</t>
+  </si>
+  <si>
+    <t>2680 Green St, San Francisco, CA 94123</t>
+  </si>
+  <si>
+    <t>strapandcrown.com</t>
+  </si>
+  <si>
+    <t>Watch Straps That Make Daily Swaps Easy</t>
+  </si>
+  <si>
+    <t>Watch folks who swap bands with the seasons will find leather, nylon, steel, and deployant straps picked by our small Fort Collins shop, plus charms and crowns for quick fixes.</t>
+  </si>
+  <si>
+    <t>watch straps, watch bands, and small watch parts</t>
+  </si>
+  <si>
+    <t>watch bands, watch straps, leather watch straps, nylon watch straps, watch band replacement, quick release watch bands, deployment straps, watch charms, watch crowns, chapter rings, metal watch bands, watch strap pins, watch band tools, watch accessories, deployant clasp, silicone watch bands</t>
+  </si>
+  <si>
+    <t>84238,84240,84242,84244,84246,84248,84249,84251,84253,84254</t>
+  </si>
+  <si>
+    <t>Watches|||Automatic Watches</t>
+  </si>
+  <si>
+    <t>7718 2nd St, Downey, CA 90241</t>
+  </si>
+  <si>
+    <t>mainspringwatcht.com</t>
+  </si>
+  <si>
+    <t>Mainspring Watch: Automatic Watches</t>
+  </si>
+  <si>
+    <t>Budget-minded collectors and small retailers: we've picked automatic watches and bands for bulk buys and daily wear.</t>
+  </si>
+  <si>
+    <t>Automatic watches</t>
+  </si>
+  <si>
+    <t>automatic watches, mechanical watches, self-winding watches, automatic wrist watches, men's automatic watches, women's automatic watches, affordable automatic watches, automatic dive watches, automatic dress watches, automatic field watches, japanese automatic watches, swiss automatic watches, automatic watch bands, replacement watch bands, watch accessories</t>
+  </si>
+  <si>
+    <t>84200,84202,84203,84205,84206,84208,84209,84211,84212,84214</t>
+  </si>
+  <si>
+    <t>Watches|||Couple Watches</t>
+  </si>
+  <si>
+    <t>4705 Olden Rd, Rockville, MD 20852</t>
+  </si>
+  <si>
+    <t>couplehorology.com</t>
+  </si>
+  <si>
+    <t>Couple Horology: The Couple Watches Edit</t>
+  </si>
+  <si>
+    <t>For couples who mark time together, a quiet edit of matched watches and his-and-hers timepieces.</t>
+  </si>
+  <si>
+    <t>Couple watches and matching timepieces for two</t>
+  </si>
+  <si>
+    <t>couple watches, matching couple watches, his and hers watches, couples watch set, matching watches for couples, his and hers watch set, pair watches, couple wrist watches, matching wrist watches, anniversary couple watches, couple watch gift, matching timepieces, his and hers timepieces, engraved couple watches, luxury couple watches, couple watch bands</t>
+  </si>
+  <si>
+    <t>84219,84221,84223,84225,84226,84228,84230,84232,84233,84235</t>
+  </si>
+  <si>
+    <t>Watches|||Swiss &amp; Japanese Made</t>
+  </si>
+  <si>
+    <t>4132 Corliss Ave N, Seattle, WA 98103</t>
+  </si>
+  <si>
+    <t>dialcrownt.com</t>
+  </si>
+  <si>
+    <t>Swiss &amp; Japanese Made Watches for Daily Wear</t>
+  </si>
+  <si>
+    <t>Watch collectors who care about movement origin get Swiss and Japanese made watches picked for daily wear, clean styling, and easy servicing.</t>
+  </si>
+  <si>
+    <t>Swiss and Japanese made watches</t>
+  </si>
+  <si>
+    <t>swiss and japanese made watches, swiss made watches, japanese made watches, swiss japanese chinese made watches, swiss movement watches, japanese movement watches, automatic watches, quartz watches, mechanical watches, chronograph watches, dive watches, wristwatches, watch bands, watch accessories, mens watches, womens watches</t>
+  </si>
+  <si>
+    <t>84387,84388,84389,84390,84391,84392,84393,84394,84395,84396</t>
+  </si>
+  <si>
+    <t>Audio|||Stereo Components</t>
+  </si>
+  <si>
+    <t>电子产品</t>
+  </si>
+  <si>
+    <t>8213 Harris Ave, Parkville, MD 21234</t>
+  </si>
+  <si>
+    <t>stereoandson.com</t>
+  </si>
+  <si>
+    <t>Stereo Components for Vinyl Nights and Movie Sound</t>
+  </si>
+  <si>
+    <t>For folks who care how records, movies, and game nights sound, we pick stereo components that earn their shelf space.</t>
+  </si>
+  <si>
+    <t>Stereo components and home audio electronics</t>
+  </si>
+  <si>
+    <t>stereo components, home stereo components, vintage stereo components, stereo receiver and amplifier, hi-fi stereo components, audio stereo components, stereo component system, stereo preamp and tuner, stereo power amplifier, home audio separates</t>
+  </si>
+  <si>
+    <t>84320,84322,84324,84325,84327,84330,84332,84335,84336,84338</t>
+  </si>
+  <si>
+    <t>Cooling Fans|||Fan Accessories</t>
+  </si>
+  <si>
+    <t>5104 Roanoke Pl, College Park, MD 20740</t>
+  </si>
+  <si>
+    <t>coolingfanaisle.com</t>
+  </si>
+  <si>
+    <t>CoolingFanAisle: Cooling Fans &amp; Accessories</t>
+  </si>
+  <si>
+    <t>For folks who need reliable airflow, we've gathered cooling fans and fan accessories with the depth of a real independent dealer.</t>
+  </si>
+  <si>
+    <t>Cooling fans and fan accessories</t>
+  </si>
+  <si>
+    <t>cooling fans, fan accessories, computer cooling fans, case fans, cpu fans, pc fans, quiet cooling fans, rgb fans, fan grills, fan filters, fan controllers, fan cables, replacement fan blades, radiator fans, usb fans</t>
+  </si>
+  <si>
+    <t>84342,84343,84344,84346,84347,84348,84349,84350,84351,84352</t>
+  </si>
+  <si>
+    <t>Electronics|||Chromebook Keyboards &amp; Palmrests</t>
+  </si>
+  <si>
+    <t>14026 Charlemagne Ave, Bellflower, CA 90706</t>
+  </si>
+  <si>
+    <t>keypalmly.com</t>
+  </si>
+  <si>
+    <t>Replace Worn Chromebook Keyboards and Palmrests Fast</t>
+  </si>
+  <si>
+    <t>Chromebook keyboards, palmrests and boards for Acer, Lenovo, HP and Dell models. Same-day shipping from Cedar Rapids.</t>
+  </si>
+  <si>
+    <t>Chromebook keyboards, palmrests and boards</t>
+  </si>
+  <si>
+    <t>chromebook keyboard, chromebook palmrest, chromebook keyboard replacement, chromebook palmrest assembly, chromebook motherboard, chromebook boards, acer chromebook keyboard, lenovo chromebook keyboard, hp chromebook keyboard, dell chromebook keyboard, chromebook touchpad, chromebook keyboard bezel, chromebook top case, chromebook replacement parts, chromebook palmrest keyboard combo, chromebook logic board</t>
+  </si>
+  <si>
+    <t>84278,84280,84282,84284,84285,84288,84290,84292,84294,84296</t>
+  </si>
+  <si>
+    <t>Electronics|||Laptop Cases</t>
+  </si>
+  <si>
+    <t>3420 Yardley Dr, Dundalk, MD 21222</t>
+  </si>
+  <si>
+    <t>casefoliot.com</t>
+  </si>
+  <si>
+    <t>Laptop cases built for bulk buyers and repair shops</t>
+  </si>
+  <si>
+    <t>Laptop cases, folio covers, LCD cables, touchpads, and motherboards for major notebook models. Bulk pricing and detailed fit notes help resellers and repair desks order accurately.</t>
+  </si>
+  <si>
+    <t>Laptop cases, folio covers, and notebook accessories</t>
+  </si>
+  <si>
+    <t>laptop cases, laptop case, folio case, laptop sleeve, notebook case, bulk laptop cases, wholesale laptop cases, laptop cases in bulk, hard shell laptop case, laptop carrying case, replacement laptop case, laptop cases for resellers, laptop case bulk lot</t>
+  </si>
+  <si>
+    <t>84354,84355,84356,84357,84358,84359,84360,84361,84362,84363</t>
+  </si>
+  <si>
+    <t>Electronics|||Loudspeakers</t>
+  </si>
+  <si>
+    <t>4809 Delaware St, College Park, MD 20740</t>
+  </si>
+  <si>
+    <t>resonarat.com</t>
+  </si>
+  <si>
+    <t>Loudspeakers for Small Rooms, Studios, and Daily Listening</t>
+  </si>
+  <si>
+    <t>Critical listeners and home DJs: a focused selection of loudspeakers, from compact monitors to floorstanding pairs.</t>
+  </si>
+  <si>
+    <t>Loudspeakers and speaker systems</t>
+  </si>
+  <si>
+    <t>loudspeakers, bookshelf loudspeakers, floorstanding loudspeakers, powered loudspeakers, passive loudspeakers, studio monitors, home audio speakers, stereo speakers, active speakers, bluetooth speakers, center channel speakers, outdoor speakers, wall mount speakers, speaker accessories, subwoofers, speaker pairs</t>
+  </si>
+  <si>
+    <t>84300,84302,84303,84305,84306,84308,84311,84313,84315,84316</t>
+  </si>
+  <si>
+    <t>Electronics|||Mobile Phone Cases</t>
+  </si>
+  <si>
+    <t>1807 Warren Ave N, Seattle, WA 98109</t>
+  </si>
+  <si>
+    <t>caseframet.com</t>
+  </si>
+  <si>
+    <t>Impact-Grade Phone Cases &amp; Replacement Shells</t>
+  </si>
+  <si>
+    <t>Phone repair techs and case fitters: molded shells, clear guards, and exact-fit replacements are picked for this trade.</t>
+  </si>
+  <si>
+    <t>Mobile phone cases and protective shells</t>
+  </si>
+  <si>
+    <t>phone cases, mobile phone cases, smartphone cases, clear phone cases, cell phone cases, protective phone cases, phone case replacement, phone shells, impact resistant phone cases, slim phone cases, mobile phone accessories, exact fit phone cases, polycarbonate phone cases, tpu phone cases</t>
+  </si>
+  <si>
+    <t>84376,84377,84378,84379,84380,84381,84382,84383,84384,84385</t>
+  </si>
+  <si>
+    <t>Electronics|||Portable Bluetooth Speakers</t>
+  </si>
+  <si>
+    <t>1516 Tunlaw Rd, Baltimore, MD 21218</t>
+  </si>
+  <si>
+    <t>sonicrigt.com</t>
+  </si>
+  <si>
+    <t>SonicRig: Portable Bluetooth Speakers</t>
+  </si>
+  <si>
+    <t>Bluetooth speaker guts, drivers, amps, and rugged portables fill our shelves; we stock repair techs, installers, and sound contractors who need parts that fit.</t>
+  </si>
+  <si>
+    <t>Portable Bluetooth speakers and speaker components</t>
+  </si>
+  <si>
+    <t>portable bluetooth speakers, bluetooth speakers, wireless portable speakers, outdoor bluetooth speakers, waterproof bluetooth speakers, speaker drivers, speaker components, replacement speaker drivers, bluetooth speaker parts, portable speaker, mini bluetooth speaker, party bluetooth speaker, speaker repair parts, audio speakers, powered speakers, speaker kits</t>
+  </si>
+  <si>
+    <t>84409,84410,84411,84412,84413,84414,84415,84416,84417,84418</t>
+  </si>
+  <si>
+    <t>Electronics|||Power Banks</t>
+  </si>
+  <si>
+    <t>6724 Bessemer Ave, Baltimore, MD 21222</t>
+  </si>
+  <si>
+    <t>wattkinl.com</t>
+  </si>
+  <si>
+    <t>Power Banks, Chargers &amp; Backup Power</t>
+  </si>
+  <si>
+    <t>Dad started us with a 20,000mAh USB-C power bank; now we also stock cords, strips, and power stations.</t>
+  </si>
+  <si>
+    <t>Power banks and portable charging gear</t>
+  </si>
+  <si>
+    <t>power bank, portable power bank, usb c power bank, 20000mah power bank, laptop power bank, power station, surge protector power strip, power supply</t>
+  </si>
+  <si>
+    <t>84398,84399,84400,84401,84402,84403,84404,84405,84406,84407</t>
+  </si>
+  <si>
+    <t>Electronics|||Pro Audio &amp; DJ Equipment</t>
+  </si>
+  <si>
+    <t>619 E Santa Ana Blvd, Santa Ana, CA 92701</t>
+  </si>
+  <si>
+    <t>tonedeckl.com</t>
+  </si>
+  <si>
+    <t>Pro Audio &amp; DJ Equipment - Second Generation</t>
+  </si>
+  <si>
+    <t>Your mixer crackles or your turntable needs a new cartridge? We carry pro audio and DJ gear to keep your rig running.</t>
+  </si>
+  <si>
+    <t>Pro audio and DJ equipment</t>
+  </si>
+  <si>
+    <t>pro audio equipment, dj equipment, pro audio, dj gear, audio equipment, dj controllers, mixers, turntables, studio monitors, microphones, dj mixer replacement parts, turntable cartridge for vinyl, pro audio cables and connectors, pa system for small venue</t>
+  </si>
+  <si>
+    <t>84365,84366,84367,84368,84369,84370,84371,84372,84373,84374</t>
+  </si>
+  <si>
+    <t>Electronics|||Wireless Microphones</t>
+  </si>
+  <si>
+    <t>11 Wendover Rd, Baltimore, MD 21218</t>
+  </si>
+  <si>
+    <t>signalmic.com</t>
+  </si>
+  <si>
+    <t>Stage-Ready Wireless Microphones for Clean Vocals</t>
+  </si>
+  <si>
+    <t>A handheld UHF wireless mic with selectable channels leads our receivers, lavalier systems, headset mics, antennas, and capsules.</t>
+  </si>
+  <si>
+    <t>Wireless microphones and headsets</t>
+  </si>
+  <si>
+    <t>wireless microphones, wireless headsets, uhf wireless microphones, handheld wireless microphones, lavalier wireless microphones, wireless headset microphones, wireless microphone systems, wireless mic receivers, wireless mic transmitters, stage wireless microphone systems, church wireless microphone systems, wireless microphone antennas, replacement wireless mic capsules</t>
+  </si>
+  <si>
+    <t>84420,84421,84422,84423,84424,84425,84426,84427,84428,84429</t>
+  </si>
+  <si>
+    <t>Electronics|||Woofers</t>
+  </si>
+  <si>
+    <t>831 Prospect Ave, Oakland, CA 94610</t>
+  </si>
+  <si>
+    <t>wooferyl.com</t>
+  </si>
+  <si>
+    <t>Woofery Sells Raw Woofers and Sub Drivers</t>
+  </si>
+  <si>
+    <t>A 12-inch dual-voice-coil subwoofer driver sits beside recone kits, spiders, tinsel leads, and raw woofers for car, home, and pro audio builds. Each order is checked by hand.</t>
+  </si>
+  <si>
+    <t>Raw woofers and subwoofer parts</t>
+  </si>
+  <si>
+    <t>woofers, subwoofers, raw woofers, replacement woofers, subwoofer parts, recone kits, voice coils, subwoofer spiders, tinsel leads, speaker gaskets, car subwoofers, home audio woofers, pro audio woofers, dual voice coil woofers, 12 inch subwoofers, 15 inch subwoofers</t>
+  </si>
+  <si>
+    <t>84497,84498,84499,84500,84501,84502,84503,84504,84505,84506</t>
+  </si>
+  <si>
+    <t>Building Materials|||Glass Clamps</t>
+  </si>
+  <si>
+    <t>7618 Baird Way, Citrus Heights, CA 95610</t>
+  </si>
+  <si>
+    <t>paneclamp.com</t>
+  </si>
+  <si>
+    <t>Glass Clamps and Building Materials for Installers</t>
+  </si>
+  <si>
+    <t>Your glass panel project needs clamps that hold true; we stock precise glass clamps and building materials.</t>
+  </si>
+  <si>
+    <t>Glass clamps and building materials</t>
+  </si>
+  <si>
+    <t>glass clamps for glass railings, stainless steel glass clamps, glass railing clamp hardware, building materials glass clamps, glass panel clamp fittings, architectural glass clamp hardware, glass balustrade clamps, commercial glass clamp installation, drywall and building materials, glass clamp mounting hardware, heavy duty glass clamps</t>
+  </si>
+  <si>
+    <t>84486,84487,84488,84489,84490,84491,84492,84493,84494,84495</t>
+  </si>
+  <si>
+    <t>Door Hardware|||Commercial Door Hardware</t>
+  </si>
+  <si>
+    <t>7104 SE 86th Ave, Portland, OR 97266</t>
+  </si>
+  <si>
+    <t>latchandknocker.com</t>
+  </si>
+  <si>
+    <t>Commercial Door Hardware: Locks, Latches, and Hinges</t>
+  </si>
+  <si>
+    <t>Espagnolette handles, fire door hinges, and commercial locks fill the shelves here — built for locksmiths, facilities crews, and contractors who fix doors daily.</t>
+  </si>
+  <si>
+    <t>Commercial door hardware, locks, and hinges</t>
+  </si>
+  <si>
+    <t>commercial door hardware, door knockers, door knobs, door handles, espagnolette handles, fire door hinges, locks and latches, commercial door locks</t>
+  </si>
+  <si>
+    <t>84475,84476,84477,84478,84479,84480,84481,84482,84483,84484</t>
+  </si>
+  <si>
+    <t>Hardware|||Abrasives</t>
+  </si>
+  <si>
+    <t>9316 52nd Ave S, Seattle, WA 98118</t>
+  </si>
+  <si>
+    <t>gritandgarnet.com</t>
+  </si>
+  <si>
+    <t>Contractor-grade abrasives for metalwork and wood finishing</t>
+  </si>
+  <si>
+    <t>Aluminum oxide flap discs and zirconia sanding belts sit beside cutoff wheels, sanding sheets, and surface-conditioning pads for metal, wood, and concrete, with abrasives for every step.</t>
+  </si>
+  <si>
+    <t>Abrasives and surface preparation supplies</t>
+  </si>
+  <si>
+    <t>abrasives, sandpaper, sanding discs, grinding wheels, cut off wheels, flap discs, sanding belts, surface conditioning discs, zirconia sanding belts, aluminum oxide sandpaper, metal grinding abrasives, wood sanding supplies, concrete surface prep abrasives, abrasive belts and rolls</t>
+  </si>
+  <si>
+    <t>84464,84465,84466,84467,84468,84469,84470,84471,84472,84473</t>
+  </si>
+  <si>
+    <t>Hardware|||Safety Gloves</t>
+  </si>
+  <si>
+    <t>7016 Hunter Ln, Hyattsville, MD 20782</t>
+  </si>
+  <si>
+    <t>glovoral.com</t>
+  </si>
+  <si>
+    <t>Safety Gloves — Picked by a Workshop Hobbyist</t>
+  </si>
+  <si>
+    <t>The shelves here run unusually deep in cut-resistant, impact, and chemical safety gloves—picked for hobbyist welders, mechanics, and weekend builders.</t>
+  </si>
+  <si>
+    <t>Safety gloves and work gloves</t>
+  </si>
+  <si>
+    <t>safety gloves, work gloves, cut resistant gloves, impact gloves, chemical resistant gloves, welding gloves, mechanics gloves, leather work gloves</t>
+  </si>
+  <si>
+    <t>84431,84432,84433,84434,84435,84436,84437,84438,84439,84440</t>
+  </si>
+  <si>
+    <t>Hardware|||Shelf Bracket</t>
+  </si>
+  <si>
+    <t>24651 Coleford St, Lake Forest, CA 92630</t>
+  </si>
+  <si>
+    <t>bracketryl.com</t>
+  </si>
+  <si>
+    <t>Heavy-Duty Shelf Brackets for Real Loads</t>
+  </si>
+  <si>
+    <t>DIYers and small-shop builders: we pick shelf brackets for real loads, odd spans, and tight installs, then stock anchors, plugs, and bits to finish the job.</t>
+  </si>
+  <si>
+    <t>Shelf brackets and support hardware</t>
+  </si>
+  <si>
+    <t>shelf brackets, heavy duty shelf brackets, floating shelf brackets, wall shelf brackets, decorative shelf brackets, industrial shelf brackets, hidden shelf brackets, wood shelf brackets, metal shelf brackets, adjustable shelf brackets, shelf support brackets, countertop brackets, mantel brackets, garage shelf brackets</t>
+  </si>
+  <si>
+    <t>84442,84443,84444,84445,84446,84447,84448,84449,84450,84451</t>
+  </si>
+  <si>
+    <t>Paint &amp; Supplies|||Paint Brush</t>
+  </si>
+  <si>
+    <t>35 N Highland St, Arlington, VA 22201</t>
+  </si>
+  <si>
+    <t>bristleandbrass.com</t>
+  </si>
+  <si>
+    <t>Bristle, Wood, and Steel: Paint Brush Craft for Real Work</t>
+  </si>
+  <si>
+    <t>Start with a 2-inch angled sash brush for trim, then stock rollers, primer, spray cans, and painter's tape for whole-room jobs. We carry 900+ brush and paint supply options.</t>
+  </si>
+  <si>
+    <t>Paint brushes and painting supplies</t>
+  </si>
+  <si>
+    <t>paint brush, paint brushes, paint supplies, paint tool, primer, spray cans, paint primer, angled paint brush, trim paint brush, paint brush set, bristle paint brush, paint tools and supplies, spray paint, wood primer, paint brush for trim, paint applicator</t>
+  </si>
+  <si>
+    <t>84508,84509,84510,84511,84512,84513,84514,84515,84516,84517</t>
+  </si>
+  <si>
+    <t>Tool Storage|||Bags &amp; Storage</t>
+  </si>
+  <si>
+    <t>13523 SW 63rd Ave, Portland, OR 97219</t>
+  </si>
+  <si>
+    <t>stowforgehu.com</t>
+  </si>
+  <si>
+    <t>Keep Every Tool in Reach with Smart Tool Storage</t>
+  </si>
+  <si>
+    <t>Tool bags, belt pouches, chests, cabinets, bins, and rack systems for shop and job site. Independent dealer with deep stock and spec help.</t>
+  </si>
+  <si>
+    <t>Tool storage bags and workshop organization</t>
+  </si>
+  <si>
+    <t>tool storage bags and organizers, heavy duty tool bags for mechanics, tool box organization systems, rolling tool chest storage, portable tool storage solutions, canvas tool bags with pockets, garage tool storage racks, jobsite tool bag storage, wall mounted tool storage, small parts organization bins, tool cabinet organizers</t>
+  </si>
+  <si>
+    <t>84453,84454,84455,84456,84457,84458,84459,84460,84461,84462</t>
+  </si>
+  <si>
+    <t>Tools|||Woodworking Tools</t>
+  </si>
+  <si>
+    <t>2373 E 21st St, Oakland, CA 94601</t>
+  </si>
+  <si>
+    <t>burlbitty.com</t>
+  </si>
+  <si>
+    <t>Burlbit: Woodworking Tools &amp; Accessories</t>
+  </si>
+  <si>
+    <t>Replacement bits, blades, and woodworking accessories run deep here for furniture makers, cabinet installers, and trim carpenters.</t>
+  </si>
+  <si>
+    <t>Woodworking tools and power tool accessories</t>
+  </si>
+  <si>
+    <t>woodworking tools, power tool accessories, woodworking accessories, router bits, drill bits, saw blades, forstner bits, dado blades, chisels, woodworking replacement parts, carbide router bits, table saw accessories, drill press accessories, sanding accessories</t>
+  </si>
+  <si>
+    <t>84563,84564,84565,84566,84567,84568,84569,84570,84571,84572</t>
+  </si>
+  <si>
+    <t>Health &amp; Beauty|||Dietary Supplements</t>
+  </si>
+  <si>
+    <t>2821 Walton Way, Sacramento, CA 95821</t>
+  </si>
+  <si>
+    <t>supploomn.com</t>
+  </si>
+  <si>
+    <t>Stock Your Shelves: Dietary Supplements in Bulk</t>
+  </si>
+  <si>
+    <t>A 500-count bottle of vitamin C tablets is just the start—we stock bulk dietary supplements, nail polish, fragrances, knee braces, and daily health staples at wallet-friendly prices.</t>
+  </si>
+  <si>
+    <t>Bulk dietary supplements and health &amp; beauty products</t>
+  </si>
+  <si>
+    <t>dietary supplements, bulk supplements, health and beauty, nutritional supplements, vitamins, nail polish, fragrances, makeup, hair care, medical supplies, body care, soap, face masks, knee braces, beauty tools, temporary tattoos</t>
+  </si>
+  <si>
+    <t>84519,84520,84521,84522,84523,84524,84525,84526,84527,84528</t>
+  </si>
+  <si>
+    <t>Health &amp; Beauty|||Hand Cream</t>
+  </si>
+  <si>
+    <t>7045 Barbara Rd, Alexandria, VA 22315</t>
+  </si>
+  <si>
+    <t>handorae.com</t>
+  </si>
+  <si>
+    <t>Bulk Hand Cream and Health &amp; Beauty Supplies</t>
+  </si>
+  <si>
+    <t>A 3-pack of shea butter hand cream kicks things off, then shampoo, nail polish, soap, and everyday personal care in bulk sizes.</t>
+  </si>
+  <si>
+    <t>Hand cream and health &amp; beauty supplies</t>
+  </si>
+  <si>
+    <t>hand cream, bulk hand cream, shea butter hand cream, health and beauty, personal care, nail polish, shampoo, fragrance, beauty tools, hair care, nail art, body care, soap, lip balm, medical supplies, hand soap</t>
+  </si>
+  <si>
+    <t>84530,84531,84532,84533,84534,84535,84536,84537,84538,84539</t>
+  </si>
+  <si>
+    <t>Health &amp; Beauty|||Mascara</t>
+  </si>
+  <si>
+    <t>25 Bloch Terrace, Lake Oswego, OR 97035</t>
+  </si>
+  <si>
+    <t>lashfoundry.com</t>
+  </si>
+  <si>
+    <t>Waterproof Mascara for Active Lifestyles</t>
+  </si>
+  <si>
+    <t>Contact lens wearers and allergy-prone eyes: we stock smudge-resistant, flake-free mascaras chosen for sensitive tear films and long, active days.</t>
+  </si>
+  <si>
+    <t>Mascara and lash cosmetics</t>
+  </si>
+  <si>
+    <t>mascara, waterproof mascara, volumizing mascara, lengthening mascara, smudge proof mascara, tubing mascara, mascara for sensitive eyes, contact lens friendly mascara, mascara for short lashes, mascara for oily eyelids, flake free mascara, hypoallergenic mascara, long wear mascara, mascara for fine lashes</t>
+  </si>
+  <si>
+    <t>84541,84542,84543,84544,84545,84546,84547,84548,84549,84550</t>
+  </si>
+  <si>
+    <t>Health &amp; Beauty|||Nail Extension</t>
+  </si>
+  <si>
+    <t>17135 NE 5th St, Bellevue, WA 98008</t>
+  </si>
+  <si>
+    <t>nailforgea.com</t>
+  </si>
+  <si>
+    <t>NailForge: Nail Extension Bulk Supplies</t>
+  </si>
+  <si>
+    <t>Acrylic nail tips and gel extension kits anchor our stock of nail care, polish, and beauty tools for bulk buyers.</t>
+  </si>
+  <si>
+    <t>Nail extension supplies and nail care essentials</t>
+  </si>
+  <si>
+    <t>nail extensions, nail extension kit, acrylic nail extensions, gel nail extensions, nail extension supplies, nail tips, nail forms, bulk nail extensions, nail extension kit bulk, acrylic nail extension kit, gel nail extension kit, nail extension tools, nail extension products, nail extension accessories</t>
+  </si>
+  <si>
+    <t>84552,84553,84554,84555,84556,84557,84558,84559,84560,84561</t>
+  </si>
+  <si>
+    <t>Health &amp; Beauty|||Sunscreen</t>
+  </si>
+  <si>
+    <t>3729 Belle Ave, Baltimore, MD 21215</t>
+  </si>
+  <si>
+    <t>sunbenchm.com</t>
+  </si>
+  <si>
+    <t>Sunbench: Mineral Sunscreen and Body Care</t>
+  </si>
+  <si>
+    <t>A zinc oxide face stick anchors the line, with mineral lotions, tinted SPF, lip balms, kids' formulas, and after-sun salves made in small batches for daily outdoor use.</t>
+  </si>
+  <si>
+    <t>mineral sunscreen and daily sun care</t>
+  </si>
+  <si>
+    <t>sunscreen, mineral sunscreen, zinc oxide sunscreen, face sunscreen, body sunscreen, kids sunscreen, sensitive skin sunscreen, reef safe sunscreen, tinted sunscreen, sunscreen stick, spray sunscreen, spf 30, spf 50, daily sunscreen, travel sunscreen, after sun care</t>
+  </si>
+  <si>
+    <t>84618,84619,84620,84621,84622,84623,84624,84625,84626,84627</t>
+  </si>
+  <si>
+    <t>Bathroom Accessories|||Toilet Paper Holders</t>
+  </si>
+  <si>
+    <t>1937 102nd Ave, Oakland, CA 94603</t>
+  </si>
+  <si>
+    <t>rollcaddly.com</t>
+  </si>
+  <si>
+    <t>Solid Brass Toilet Paper Holders &amp; Bathroom Accessories</t>
+  </si>
+  <si>
+    <t>Toilet paper holders, bath rugs, towel bars, mirror cabinets and other bathroom fittings are stocked in bulk, with simple ordering and fast U.S. shipping for contractors and households.</t>
+  </si>
+  <si>
+    <t>Bathroom accessories and toilet paper holders</t>
+  </si>
+  <si>
+    <t>toilet paper holder, bathroom accessories, wall mount toilet paper holder, freestanding toilet paper holder, toilet tissue holder, toilet paper holder bulk, bathroom accessory set, bath rug, towel holder, toilet brush holder, mirror cabinet</t>
+  </si>
+  <si>
+    <t>84607,84608,84609,84610,84611,84612,84613,84614,84615,84616</t>
+  </si>
+  <si>
+    <t>Cleaning &amp; Laundry|||Carpet Cleaning</t>
+  </si>
+  <si>
+    <t>3929 La Verne Way, Sacramento, CA 95864</t>
+  </si>
+  <si>
+    <t>naplift.com</t>
+  </si>
+  <si>
+    <t>Carpet Cleaning for Busy Homes With Pets and Kids</t>
+  </si>
+  <si>
+    <t>The pet-stain enzyme spray we keep by the door is just one favorite. We also stock carpet shampoos, spot removers, brushes, and rental-style machines for every mess.</t>
+  </si>
+  <si>
+    <t>Carpet cleaning supplies and equipment</t>
+  </si>
+  <si>
+    <t>carpet cleaning, carpet stain remover, pet stain remover for carpet, carpet shampoo, carpet cleaning machine, carpet cleaning supplies, upholstery cleaner, carpet spot cleaner, carpet deodorizer</t>
+  </si>
+  <si>
+    <t>84585,84586,84587,84588,84589,84590,84591,84592,84593,84594</t>
+  </si>
+  <si>
+    <t>Flags|||Country Flags</t>
+  </si>
+  <si>
+    <t>507 Wellesley Rd, Philadelphia, PA 19119</t>
+  </si>
+  <si>
+    <t>fllagenatio.com</t>
+  </si>
+  <si>
+    <t>Country Flags - A Curated World in Every Stitch</t>
+  </si>
+  <si>
+    <t>A single Canadian flag can warm a classroom wall, while the wider shelves cover national banners from Albania to Zimbabwe and city flags for local pride.</t>
+  </si>
+  <si>
+    <t>Country flags and national banners</t>
+  </si>
+  <si>
+    <t>country flags, national flags, world flags, flags of the world, international flags, country flag banners, outdoor country flags, indoor country flags, 3x5 country flags, country flags with grommets, small country flags, country flags for sale</t>
+  </si>
+  <si>
+    <t>84574,84575,84576,84577,84578,84579,84580,84581,84582,84583</t>
+  </si>
+  <si>
+    <t>Home &amp; Garden|||Intruder Alarms</t>
+  </si>
+  <si>
+    <t>2906 Pierpont St, Alexandria, VA 22302</t>
+  </si>
+  <si>
+    <t>brassbellalarms.com</t>
+  </si>
+  <si>
+    <t>Brass Bell Alarms Sells Intruder Alarms for Old Houses</t>
+  </si>
+  <si>
+    <t>A drafty back door and a noisy gate keep you up at night? We stock intruder alarms, sensors, and brass bells that fit old homes.</t>
+  </si>
+  <si>
+    <t>Intruder alarms and home security</t>
+  </si>
+  <si>
+    <t>intruder alarms, home intruder alarm system, wireless intruder alarm kit, diy home security alarm, door and window alarm sensors, motion sensor alarm for home, brass door alarm bell, pet friendly intruder alarm, old house security alarm, backyard gate alarm, garage intruder alarm</t>
+  </si>
+  <si>
+    <t>84629,84630,84631,84632,84633,84634,84635,84636,84637,84638</t>
+  </si>
+  <si>
+    <t>Shower Curtains</t>
+  </si>
+  <si>
+    <t>2746 NE 17th Ave, Portland, OR 97212</t>
+  </si>
+  <si>
+    <t>showerweft.com</t>
+  </si>
+  <si>
+    <t>Shower curtains and rings made for professional installations</t>
+  </si>
+  <si>
+    <t>Deep inventory of shower curtains, liners, rings and rods for contractors, property managers and repair techs who need dependable bath fittings fast.</t>
+  </si>
+  <si>
+    <t>Shower curtains and curtain rings</t>
+  </si>
+  <si>
+    <t>shower curtains, shower curtain rings, shower curtain liners, shower curtain rods, commercial shower curtains, shower curtain hooks, shower curtain sets, shower curtain hardware</t>
+  </si>
+  <si>
+    <t>84596,84597,84598,84599,84600,84601,84602,84603,84604,84605</t>
+  </si>
+  <si>
+    <t>Tableware ||| Ceramic Tableware</t>
+  </si>
+  <si>
+    <t>13050 Knaus Rd, Lake Oswego, OR 97034</t>
+  </si>
+  <si>
+    <t>kilnandtable.com</t>
+  </si>
+  <si>
+    <t>Ceramic Tableware, Dinnerware, and Stoneware Bowls</t>
+  </si>
+  <si>
+    <t>Ceramic plates, bowls, mugs, and serving pieces fired for daily use. Orders packed by hand and shipped from our Greenville, SC workshop.</t>
+  </si>
+  <si>
+    <t>Ceramic tableware and stoneware dinnerware</t>
+  </si>
+  <si>
+    <t>ceramic tableware, handmade ceramic dinnerware, stoneware plates and bowls, kiln fired ceramic mugs, artisan ceramic serving dishes, glazed stoneware tableware, ceramic dinner plates set, pottery bowls and platters, stoneware bakeware and serveware, ceramic cups and saucers</t>
+  </si>
+  <si>
+    <t>84640,84641,84642,84643,84644,84645,84646,84647,84648,84649</t>
+  </si>
+  <si>
+    <t>Toilet Parts|||Toilet Tanks</t>
+  </si>
+  <si>
+    <t>4705 SE Reedway St, Portland, OR 97206</t>
+  </si>
+  <si>
+    <t>tankwrightty.com</t>
+  </si>
+  <si>
+    <t>Tankwright: Toilet Tank Parts &amp; Repair Valves</t>
+  </si>
+  <si>
+    <t>Toilet tank internals, flush valves, and fill assemblies run deep here for repair techs and DIY fixers.</t>
+  </si>
+  <si>
+    <t>Toilet tank parts and repair components</t>
+  </si>
+  <si>
+    <t>toilet tank parts, toilet tank, toilet flush valve, toilet fill valve, toilet flapper, toilet repair kit, toilet tank lid, toilet tank bolts, toilet tank gasket, toilet tank replacement, toilet tank fittings, toilet tank lever, toilet fill valve assembly, toilet flush valve seal, toilet tank flush valve, toilet parts</t>
   </si>
 </sst>
 </file>
@@ -17489,7 +19007,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q343"/>
+  <dimension ref="A1:Q409"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="50.625" customWidth="1"/>
@@ -31002,6 +32520,9 @@
       <c r="P283" s="24" t="s">
         <v>2893</v>
       </c>
+      <c r="Q283" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="284" ht="135" spans="2:17">
       <c r="B284" s="1" t="s">
@@ -31043,6 +32564,9 @@
       <c r="P284" s="24" t="s">
         <v>2903</v>
       </c>
+      <c r="Q284" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="285" ht="121.5" spans="2:17">
       <c r="B285" s="1" t="s">
@@ -31084,6 +32608,9 @@
       <c r="P285" s="24" t="s">
         <v>2913</v>
       </c>
+      <c r="Q285" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="286" ht="121.5" spans="2:17">
       <c r="B286" s="1" t="s">
@@ -31125,6 +32652,9 @@
       <c r="P286" s="24" t="s">
         <v>2923</v>
       </c>
+      <c r="Q286" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="287" ht="148.5" spans="2:17">
       <c r="B287" s="1" t="s">
@@ -31166,6 +32696,9 @@
       <c r="P287" s="24" t="s">
         <v>2933</v>
       </c>
+      <c r="Q287" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="288" ht="108" spans="2:17">
       <c r="B288" s="1" t="s">
@@ -31207,8 +32740,11 @@
       <c r="P288" s="24" t="s">
         <v>2943</v>
       </c>
-    </row>
-    <row r="289" ht="108" spans="2:16">
+      <c r="Q288" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="289" ht="108" spans="2:17">
       <c r="B289" s="1" t="s">
         <v>2944</v>
       </c>
@@ -31248,8 +32784,11 @@
       <c r="P289" s="24" t="s">
         <v>2953</v>
       </c>
-    </row>
-    <row r="290" ht="135" spans="2:16">
+      <c r="Q289" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="290" ht="135" spans="2:17">
       <c r="B290" s="1" t="s">
         <v>2954</v>
       </c>
@@ -31289,8 +32828,11 @@
       <c r="P290" s="24" t="s">
         <v>2963</v>
       </c>
-    </row>
-    <row r="291" ht="81" spans="2:16">
+      <c r="Q290" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="291" ht="81" spans="2:17">
       <c r="B291" s="1" t="s">
         <v>2964</v>
       </c>
@@ -31330,8 +32872,11 @@
       <c r="P291" s="24" t="s">
         <v>2973</v>
       </c>
-    </row>
-    <row r="292" ht="108" spans="2:16">
+      <c r="Q291" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="292" ht="108" spans="2:17">
       <c r="B292" s="1" t="s">
         <v>2974</v>
       </c>
@@ -31371,8 +32916,11 @@
       <c r="P292" s="24" t="s">
         <v>2984</v>
       </c>
-    </row>
-    <row r="293" ht="135" spans="2:16">
+      <c r="Q292" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="293" ht="135" spans="2:17">
       <c r="B293" s="1" t="s">
         <v>2985</v>
       </c>
@@ -31412,8 +32960,11 @@
       <c r="P293" s="24" t="s">
         <v>2994</v>
       </c>
-    </row>
-    <row r="294" ht="108" spans="2:16">
+      <c r="Q293" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="294" ht="108" spans="2:17">
       <c r="B294" s="1" t="s">
         <v>2995</v>
       </c>
@@ -31453,8 +33004,11 @@
       <c r="P294" s="24" t="s">
         <v>3004</v>
       </c>
-    </row>
-    <row r="295" ht="108" spans="2:16">
+      <c r="Q294" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="295" ht="108" spans="2:17">
       <c r="B295" s="1" t="s">
         <v>3005</v>
       </c>
@@ -31494,8 +33048,11 @@
       <c r="P295" s="24" t="s">
         <v>3014</v>
       </c>
-    </row>
-    <row r="296" ht="121.5" spans="2:16">
+      <c r="Q295" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="296" ht="121.5" spans="2:17">
       <c r="B296" s="1" t="s">
         <v>3015</v>
       </c>
@@ -31535,8 +33092,11 @@
       <c r="P296" s="24" t="s">
         <v>3024</v>
       </c>
-    </row>
-    <row r="297" ht="108" spans="2:16">
+      <c r="Q296" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="297" ht="108" spans="2:17">
       <c r="B297" s="1" t="s">
         <v>3025</v>
       </c>
@@ -31576,8 +33136,11 @@
       <c r="P297" s="24" t="s">
         <v>3034</v>
       </c>
-    </row>
-    <row r="298" ht="121.5" spans="2:16">
+      <c r="Q297" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="298" ht="121.5" spans="2:17">
       <c r="B298" s="1" t="s">
         <v>3035</v>
       </c>
@@ -31617,8 +33180,11 @@
       <c r="P298" s="24" t="s">
         <v>3044</v>
       </c>
-    </row>
-    <row r="299" ht="108" spans="2:16">
+      <c r="Q298" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="299" ht="108" spans="2:17">
       <c r="B299" s="1" t="s">
         <v>3045</v>
       </c>
@@ -31658,8 +33224,11 @@
       <c r="P299" s="24" t="s">
         <v>3054</v>
       </c>
-    </row>
-    <row r="300" ht="94.5" spans="2:16">
+      <c r="Q299" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="300" ht="94.5" spans="2:17">
       <c r="B300" s="1" t="s">
         <v>3055</v>
       </c>
@@ -31699,8 +33268,11 @@
       <c r="P300" s="24" t="s">
         <v>3064</v>
       </c>
-    </row>
-    <row r="301" ht="108" spans="2:16">
+      <c r="Q300" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="301" ht="108" spans="2:17">
       <c r="B301" s="1" t="s">
         <v>3065</v>
       </c>
@@ -31740,8 +33312,11 @@
       <c r="P301" s="24" t="s">
         <v>3074</v>
       </c>
-    </row>
-    <row r="302" ht="108" spans="2:16">
+      <c r="Q301" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="302" ht="108" spans="2:17">
       <c r="B302" s="1" t="s">
         <v>3075</v>
       </c>
@@ -31781,8 +33356,11 @@
       <c r="P302" s="24" t="s">
         <v>3084</v>
       </c>
-    </row>
-    <row r="303" ht="94.5" spans="2:16">
+      <c r="Q302" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="303" ht="94.5" spans="2:17">
       <c r="B303" s="1" t="s">
         <v>3085</v>
       </c>
@@ -31822,8 +33400,11 @@
       <c r="P303" s="24" t="s">
         <v>3094</v>
       </c>
-    </row>
-    <row r="304" ht="94.5" spans="2:16">
+      <c r="Q303" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="304" ht="94.5" spans="2:17">
       <c r="B304" s="1" t="s">
         <v>3095</v>
       </c>
@@ -31863,8 +33444,11 @@
       <c r="P304" s="24" t="s">
         <v>3104</v>
       </c>
-    </row>
-    <row r="305" ht="108" spans="2:16">
+      <c r="Q304" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="305" ht="108" spans="2:17">
       <c r="B305" s="1" t="s">
         <v>3105</v>
       </c>
@@ -31904,8 +33488,11 @@
       <c r="P305" s="24" t="s">
         <v>3113</v>
       </c>
-    </row>
-    <row r="306" ht="67.5" spans="2:16">
+      <c r="Q305" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="306" ht="67.5" spans="2:17">
       <c r="B306" s="1" t="s">
         <v>3114</v>
       </c>
@@ -31945,8 +33532,11 @@
       <c r="P306" s="24" t="s">
         <v>3123</v>
       </c>
-    </row>
-    <row r="307" ht="94.5" spans="2:16">
+      <c r="Q306" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="307" ht="94.5" spans="2:17">
       <c r="B307" s="1" t="s">
         <v>3124</v>
       </c>
@@ -31986,8 +33576,11 @@
       <c r="P307" s="24" t="s">
         <v>3133</v>
       </c>
-    </row>
-    <row r="308" ht="67.5" spans="2:16">
+      <c r="Q307" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="308" ht="67.5" spans="2:17">
       <c r="B308" s="1" t="s">
         <v>3134</v>
       </c>
@@ -32027,8 +33620,11 @@
       <c r="P308" s="24" t="s">
         <v>3142</v>
       </c>
-    </row>
-    <row r="309" ht="67.5" spans="2:16">
+      <c r="Q308" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="309" ht="67.5" spans="2:17">
       <c r="B309" s="1" t="s">
         <v>3143</v>
       </c>
@@ -32068,8 +33664,11 @@
       <c r="P309" s="24" t="s">
         <v>3152</v>
       </c>
-    </row>
-    <row r="310" ht="108" spans="2:16">
+      <c r="Q309" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="310" ht="108" spans="2:17">
       <c r="B310" s="1" t="s">
         <v>3153</v>
       </c>
@@ -32109,8 +33708,11 @@
       <c r="P310" s="24" t="s">
         <v>3162</v>
       </c>
-    </row>
-    <row r="311" ht="108" spans="2:16">
+      <c r="Q310" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="311" ht="108" spans="2:17">
       <c r="B311" s="1" t="s">
         <v>3163</v>
       </c>
@@ -32150,8 +33752,11 @@
       <c r="P311" s="24" t="s">
         <v>3172</v>
       </c>
-    </row>
-    <row r="312" ht="135" spans="2:16">
+      <c r="Q311" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="312" ht="135" spans="2:17">
       <c r="B312" s="1" t="s">
         <v>3173</v>
       </c>
@@ -32191,8 +33796,11 @@
       <c r="P312" s="24" t="s">
         <v>3182</v>
       </c>
-    </row>
-    <row r="313" ht="148.5" spans="2:16">
+      <c r="Q312" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="313" ht="148.5" spans="2:17">
       <c r="B313" s="1" t="s">
         <v>3183</v>
       </c>
@@ -32232,8 +33840,11 @@
       <c r="P313" s="24" t="s">
         <v>3192</v>
       </c>
-    </row>
-    <row r="314" ht="108" spans="2:16">
+      <c r="Q313" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="314" ht="108" spans="2:17">
       <c r="B314" s="1" t="s">
         <v>3193</v>
       </c>
@@ -32273,8 +33884,11 @@
       <c r="P314" s="24" t="s">
         <v>3202</v>
       </c>
-    </row>
-    <row r="315" ht="108" spans="2:16">
+      <c r="Q314" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="315" ht="108" spans="2:17">
       <c r="B315" s="1" t="s">
         <v>3203</v>
       </c>
@@ -32314,8 +33928,11 @@
       <c r="P315" s="24" t="s">
         <v>3212</v>
       </c>
-    </row>
-    <row r="316" ht="175.5" spans="2:16">
+      <c r="Q315" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="316" ht="175.5" spans="2:17">
       <c r="B316" s="1" t="s">
         <v>3213</v>
       </c>
@@ -32355,8 +33972,11 @@
       <c r="P316" s="24" t="s">
         <v>3221</v>
       </c>
-    </row>
-    <row r="317" ht="148.5" spans="2:16">
+      <c r="Q316" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="317" ht="148.5" spans="2:17">
       <c r="B317" s="1" t="s">
         <v>3222</v>
       </c>
@@ -32396,8 +34016,11 @@
       <c r="P317" s="24" t="s">
         <v>3231</v>
       </c>
-    </row>
-    <row r="318" ht="121.5" spans="2:16">
+      <c r="Q317" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="318" ht="121.5" spans="2:17">
       <c r="B318" s="1" t="s">
         <v>3232</v>
       </c>
@@ -32437,8 +34060,11 @@
       <c r="P318" s="24" t="s">
         <v>3241</v>
       </c>
-    </row>
-    <row r="319" ht="121.5" spans="2:16">
+      <c r="Q318" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="319" ht="121.5" spans="2:17">
       <c r="B319" s="1" t="s">
         <v>3242</v>
       </c>
@@ -32478,8 +34104,11 @@
       <c r="P319" s="24" t="s">
         <v>3251</v>
       </c>
-    </row>
-    <row r="320" ht="108" spans="2:16">
+      <c r="Q319" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="320" ht="108" spans="2:17">
       <c r="B320" s="1" t="s">
         <v>3252</v>
       </c>
@@ -32519,8 +34148,11 @@
       <c r="P320" s="24" t="s">
         <v>3261</v>
       </c>
-    </row>
-    <row r="321" ht="108" spans="2:16">
+      <c r="Q320" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="321" ht="108" spans="2:17">
       <c r="B321" s="1" t="s">
         <v>3262</v>
       </c>
@@ -32560,8 +34192,11 @@
       <c r="P321" s="24" t="s">
         <v>3271</v>
       </c>
-    </row>
-    <row r="322" ht="94.5" spans="2:16">
+      <c r="Q321" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="322" ht="94.5" spans="2:17">
       <c r="B322" s="1" t="s">
         <v>3272</v>
       </c>
@@ -32601,8 +34236,11 @@
       <c r="P322" s="24" t="s">
         <v>3281</v>
       </c>
-    </row>
-    <row r="323" ht="94.5" spans="2:16">
+      <c r="Q322" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="323" ht="94.5" spans="2:17">
       <c r="B323" s="1" t="s">
         <v>3282</v>
       </c>
@@ -32642,8 +34280,11 @@
       <c r="P323" s="24" t="s">
         <v>3291</v>
       </c>
-    </row>
-    <row r="324" ht="108" spans="2:16">
+      <c r="Q323" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="324" ht="108" spans="2:17">
       <c r="B324" s="1" t="s">
         <v>3292</v>
       </c>
@@ -32683,8 +34324,11 @@
       <c r="P324" s="24" t="s">
         <v>3301</v>
       </c>
-    </row>
-    <row r="325" ht="81" spans="2:16">
+      <c r="Q324" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="325" ht="81" spans="2:17">
       <c r="B325" s="1" t="s">
         <v>3302</v>
       </c>
@@ -32724,8 +34368,11 @@
       <c r="P325" s="24" t="s">
         <v>3311</v>
       </c>
-    </row>
-    <row r="326" ht="67.5" spans="2:16">
+      <c r="Q325" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="326" ht="67.5" spans="2:17">
       <c r="B326" s="1" t="s">
         <v>3312</v>
       </c>
@@ -32765,8 +34412,11 @@
       <c r="P326" s="24" t="s">
         <v>3321</v>
       </c>
-    </row>
-    <row r="327" ht="94.5" spans="2:16">
+      <c r="Q326" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="327" ht="94.5" spans="2:17">
       <c r="B327" s="1" t="s">
         <v>3322</v>
       </c>
@@ -32806,8 +34456,11 @@
       <c r="P327" s="24" t="s">
         <v>3331</v>
       </c>
-    </row>
-    <row r="328" ht="108" spans="2:16">
+      <c r="Q327" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="328" ht="108" spans="2:17">
       <c r="B328" s="1" t="s">
         <v>3332</v>
       </c>
@@ -32847,8 +34500,11 @@
       <c r="P328" s="24" t="s">
         <v>3341</v>
       </c>
-    </row>
-    <row r="329" ht="135" spans="2:16">
+      <c r="Q328" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="329" ht="135" spans="2:17">
       <c r="B329" s="1" t="s">
         <v>3342</v>
       </c>
@@ -32888,8 +34544,11 @@
       <c r="P329" s="24" t="s">
         <v>3351</v>
       </c>
-    </row>
-    <row r="330" ht="108" spans="2:16">
+      <c r="Q329" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="330" ht="108" spans="2:17">
       <c r="B330" s="1" t="s">
         <v>3352</v>
       </c>
@@ -32929,8 +34588,11 @@
       <c r="P330" s="24" t="s">
         <v>3361</v>
       </c>
-    </row>
-    <row r="331" ht="108" spans="2:16">
+      <c r="Q330" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="331" ht="108" spans="2:17">
       <c r="B331" s="1" t="s">
         <v>3362</v>
       </c>
@@ -32970,8 +34632,11 @@
       <c r="P331" s="24" t="s">
         <v>3371</v>
       </c>
-    </row>
-    <row r="332" ht="108" spans="2:16">
+      <c r="Q331" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="332" ht="108" spans="2:17">
       <c r="B332" s="1" t="s">
         <v>3372</v>
       </c>
@@ -33011,8 +34676,11 @@
       <c r="P332" s="24" t="s">
         <v>3381</v>
       </c>
-    </row>
-    <row r="333" ht="121.5" spans="2:16">
+      <c r="Q332" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="333" ht="121.5" spans="2:17">
       <c r="B333" s="1" t="s">
         <v>3382</v>
       </c>
@@ -33052,8 +34720,11 @@
       <c r="P333" s="24" t="s">
         <v>3391</v>
       </c>
-    </row>
-    <row r="334" ht="148.5" spans="2:16">
+      <c r="Q333" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="334" ht="148.5" spans="2:17">
       <c r="B334" s="1" t="s">
         <v>3392</v>
       </c>
@@ -33093,8 +34764,11 @@
       <c r="P334" s="24" t="s">
         <v>3400</v>
       </c>
-    </row>
-    <row r="335" ht="148.5" spans="2:16">
+      <c r="Q334" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="335" ht="148.5" spans="2:17">
       <c r="B335" s="1" t="s">
         <v>3401</v>
       </c>
@@ -33134,8 +34808,11 @@
       <c r="P335" s="24" t="s">
         <v>3410</v>
       </c>
-    </row>
-    <row r="336" ht="135" spans="2:16">
+      <c r="Q335" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="336" ht="135" spans="2:17">
       <c r="B336" s="1" t="s">
         <v>3411</v>
       </c>
@@ -33175,8 +34852,11 @@
       <c r="P336" s="24" t="s">
         <v>3420</v>
       </c>
-    </row>
-    <row r="337" ht="121.5" spans="2:16">
+      <c r="Q336" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="337" ht="121.5" spans="1:17">
       <c r="B337" s="1" t="s">
         <v>3421</v>
       </c>
@@ -33216,8 +34896,11 @@
       <c r="P337" s="24" t="s">
         <v>3430</v>
       </c>
-    </row>
-    <row r="338" ht="121.5" spans="2:16">
+      <c r="Q337" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="338" ht="121.5" spans="1:17">
       <c r="B338" s="1" t="s">
         <v>3431</v>
       </c>
@@ -33257,12 +34940,15 @@
       <c r="P338" s="24" t="s">
         <v>3440</v>
       </c>
-    </row>
-    <row r="339" ht="16.5" spans="2:16">
+      <c r="Q338" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="339" ht="16.5" spans="1:17">
       <c r="B339" s="1" t="s">
         <v>3441</v>
       </c>
-      <c r="C339">
+      <c r="C339" s="1">
         <v>81226</v>
       </c>
       <c r="D339" t="s">
@@ -33289,12 +34975,15 @@
       <c r="O339" t="s">
         <v>3447</v>
       </c>
-    </row>
-    <row r="340" ht="16.5" spans="2:16">
+      <c r="Q339" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="340" ht="16.5" spans="1:17">
       <c r="B340" s="1" t="s">
         <v>3448</v>
       </c>
-      <c r="C340">
+      <c r="C340" s="1">
         <v>81193</v>
       </c>
       <c r="D340" t="s">
@@ -33321,12 +35010,15 @@
       <c r="O340" t="s">
         <v>3454</v>
       </c>
-    </row>
-    <row r="341" ht="16.5" spans="2:16">
+      <c r="Q340" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="341" ht="16.5" spans="1:17">
       <c r="B341" s="1" t="s">
         <v>3455</v>
       </c>
-      <c r="C341">
+      <c r="C341" s="1">
         <v>81241</v>
       </c>
       <c r="D341" t="s">
@@ -33353,16 +35045,22 @@
       <c r="O341" t="s">
         <v>3461</v>
       </c>
-    </row>
-    <row r="342" ht="16.5" spans="2:16">
+      <c r="Q341" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="342" ht="16.5" spans="1:17">
+      <c r="A342" t="s">
+        <v>3462</v>
+      </c>
       <c r="B342" s="1" t="s">
-        <v>3462</v>
-      </c>
-      <c r="C342">
+        <v>3463</v>
+      </c>
+      <c r="C342" s="1">
         <v>81215</v>
       </c>
       <c r="D342" t="s">
-        <v>3463</v>
+        <v>3464</v>
       </c>
       <c r="E342" t="s">
         <v>21</v>
@@ -33371,30 +35069,33 @@
         <v>72</v>
       </c>
       <c r="I342" t="s">
-        <v>3464</v>
+        <v>3465</v>
       </c>
       <c r="J342" t="s">
-        <v>3465</v>
+        <v>3466</v>
       </c>
       <c r="K342" t="s">
-        <v>3466</v>
+        <v>3467</v>
       </c>
       <c r="M342" t="s">
-        <v>3467</v>
+        <v>3468</v>
       </c>
       <c r="O342" t="s">
-        <v>3468</v>
-      </c>
-    </row>
-    <row r="343" ht="16.5" spans="2:16">
+        <v>3469</v>
+      </c>
+      <c r="Q342" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="343" ht="16.5" spans="1:17">
       <c r="B343" s="1" t="s">
-        <v>3469</v>
-      </c>
-      <c r="C343">
+        <v>3470</v>
+      </c>
+      <c r="C343" s="1">
         <v>81204</v>
       </c>
       <c r="D343" t="s">
-        <v>3470</v>
+        <v>3471</v>
       </c>
       <c r="E343" t="s">
         <v>21</v>
@@ -33403,20 +35104,2321 @@
         <v>85</v>
       </c>
       <c r="I343" t="s">
-        <v>3471</v>
+        <v>3472</v>
       </c>
       <c r="J343" t="s">
-        <v>3472</v>
+        <v>3473</v>
       </c>
       <c r="K343" t="s">
-        <v>3473</v>
+        <v>3474</v>
       </c>
       <c r="M343" t="s">
-        <v>3474</v>
+        <v>3475</v>
       </c>
       <c r="O343" t="s">
-        <v>3475</v>
-      </c>
+        <v>3476</v>
+      </c>
+      <c r="Q343" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="344" ht="16.5" spans="1:17">
+      <c r="B344" s="1" t="s">
+        <v>3477</v>
+      </c>
+      <c r="C344" s="1">
+        <v>82685</v>
+      </c>
+      <c r="D344" t="s">
+        <v>3478</v>
+      </c>
+      <c r="E344" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F344" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I344" t="s">
+        <v>3479</v>
+      </c>
+      <c r="J344" t="s">
+        <v>3480</v>
+      </c>
+      <c r="K344" t="s">
+        <v>3481</v>
+      </c>
+      <c r="M344" t="s">
+        <v>3482</v>
+      </c>
+      <c r="O344" t="s">
+        <v>3483</v>
+      </c>
+      <c r="P344" t="s">
+        <v>3484</v>
+      </c>
+      <c r="Q344" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="345" ht="16.5" spans="1:17">
+      <c r="B345" s="1" t="s">
+        <v>3485</v>
+      </c>
+      <c r="C345" s="1">
+        <v>82739</v>
+      </c>
+      <c r="D345" t="s">
+        <v>3486</v>
+      </c>
+      <c r="E345" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F345" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I345" t="s">
+        <v>3487</v>
+      </c>
+      <c r="J345" t="s">
+        <v>3488</v>
+      </c>
+      <c r="K345" t="s">
+        <v>3489</v>
+      </c>
+      <c r="M345" t="s">
+        <v>3490</v>
+      </c>
+      <c r="O345" t="s">
+        <v>3491</v>
+      </c>
+      <c r="P345" t="s">
+        <v>3492</v>
+      </c>
+      <c r="Q345" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="346" ht="16.5" spans="1:17">
+      <c r="B346" s="1" t="s">
+        <v>3493</v>
+      </c>
+      <c r="C346" s="1">
+        <v>82696</v>
+      </c>
+      <c r="D346" t="s">
+        <v>3494</v>
+      </c>
+      <c r="E346" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F346" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I346" t="s">
+        <v>3495</v>
+      </c>
+      <c r="J346" t="s">
+        <v>3496</v>
+      </c>
+      <c r="K346" t="s">
+        <v>3497</v>
+      </c>
+      <c r="M346" t="s">
+        <v>3498</v>
+      </c>
+      <c r="O346" t="s">
+        <v>3499</v>
+      </c>
+      <c r="P346" t="s">
+        <v>3500</v>
+      </c>
+      <c r="Q346" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="347" ht="16.5" spans="1:17">
+      <c r="B347" s="1" t="s">
+        <v>3501</v>
+      </c>
+      <c r="C347" s="1">
+        <v>82707</v>
+      </c>
+      <c r="D347" t="s">
+        <v>3502</v>
+      </c>
+      <c r="E347" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F347" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I347" t="s">
+        <v>3503</v>
+      </c>
+      <c r="J347" t="s">
+        <v>3504</v>
+      </c>
+      <c r="K347" t="s">
+        <v>3505</v>
+      </c>
+      <c r="M347" t="s">
+        <v>3506</v>
+      </c>
+      <c r="O347" t="s">
+        <v>3507</v>
+      </c>
+      <c r="P347" t="s">
+        <v>3508</v>
+      </c>
+      <c r="Q347" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="348" ht="16.5" spans="1:17">
+      <c r="B348" s="1" t="s">
+        <v>3509</v>
+      </c>
+      <c r="C348" s="1">
+        <v>82729</v>
+      </c>
+      <c r="D348" t="s">
+        <v>3510</v>
+      </c>
+      <c r="E348" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F348" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I348" t="s">
+        <v>3511</v>
+      </c>
+      <c r="J348" t="s">
+        <v>3512</v>
+      </c>
+      <c r="K348" t="s">
+        <v>3513</v>
+      </c>
+      <c r="M348" t="s">
+        <v>3514</v>
+      </c>
+      <c r="O348" t="s">
+        <v>3515</v>
+      </c>
+      <c r="P348" t="s">
+        <v>3516</v>
+      </c>
+      <c r="Q348" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="349" ht="16.5" spans="1:17">
+      <c r="B349" s="1" t="s">
+        <v>3517</v>
+      </c>
+      <c r="C349" s="1">
+        <v>82718</v>
+      </c>
+      <c r="D349" t="s">
+        <v>3518</v>
+      </c>
+      <c r="E349" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F349" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I349" t="s">
+        <v>3519</v>
+      </c>
+      <c r="J349" t="s">
+        <v>3520</v>
+      </c>
+      <c r="K349" t="s">
+        <v>3521</v>
+      </c>
+      <c r="M349" t="s">
+        <v>3522</v>
+      </c>
+      <c r="O349" t="s">
+        <v>3523</v>
+      </c>
+      <c r="P349" t="s">
+        <v>3524</v>
+      </c>
+      <c r="Q349" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="350" ht="16.5" spans="1:17">
+      <c r="B350" s="1" t="s">
+        <v>3525</v>
+      </c>
+      <c r="C350" s="1">
+        <v>82772</v>
+      </c>
+      <c r="D350" t="s">
+        <v>3526</v>
+      </c>
+      <c r="E350" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F350" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I350" t="s">
+        <v>3527</v>
+      </c>
+      <c r="J350" t="s">
+        <v>3528</v>
+      </c>
+      <c r="K350" t="s">
+        <v>3529</v>
+      </c>
+      <c r="M350" t="s">
+        <v>3530</v>
+      </c>
+      <c r="O350" t="s">
+        <v>3531</v>
+      </c>
+      <c r="P350" t="s">
+        <v>3532</v>
+      </c>
+      <c r="Q350" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="351" ht="16.5" spans="1:17">
+      <c r="B351" s="1" t="s">
+        <v>3533</v>
+      </c>
+      <c r="C351" s="1">
+        <v>82761</v>
+      </c>
+      <c r="D351" t="s">
+        <v>3534</v>
+      </c>
+      <c r="E351" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F351" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I351" t="s">
+        <v>3535</v>
+      </c>
+      <c r="J351" t="s">
+        <v>3536</v>
+      </c>
+      <c r="K351" t="s">
+        <v>3537</v>
+      </c>
+      <c r="M351" t="s">
+        <v>3538</v>
+      </c>
+      <c r="O351" t="s">
+        <v>3539</v>
+      </c>
+      <c r="P351" t="s">
+        <v>3540</v>
+      </c>
+      <c r="Q351" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="352" ht="16.5" spans="1:17">
+      <c r="B352" s="1" t="s">
+        <v>3541</v>
+      </c>
+      <c r="C352" s="1">
+        <v>82750</v>
+      </c>
+      <c r="D352" t="s">
+        <v>3542</v>
+      </c>
+      <c r="E352" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F352" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I352" t="s">
+        <v>3543</v>
+      </c>
+      <c r="J352" t="s">
+        <v>3544</v>
+      </c>
+      <c r="K352" t="s">
+        <v>3545</v>
+      </c>
+      <c r="M352" t="s">
+        <v>3546</v>
+      </c>
+      <c r="O352" t="s">
+        <v>3547</v>
+      </c>
+      <c r="P352" t="s">
+        <v>3548</v>
+      </c>
+      <c r="Q352" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="353" ht="16.5" spans="2:17">
+      <c r="B353" s="1" t="s">
+        <v>3549</v>
+      </c>
+      <c r="C353" s="1">
+        <v>82783</v>
+      </c>
+      <c r="D353" t="s">
+        <v>3550</v>
+      </c>
+      <c r="E353" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F353" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I353" t="s">
+        <v>3551</v>
+      </c>
+      <c r="J353" t="s">
+        <v>3552</v>
+      </c>
+      <c r="K353" t="s">
+        <v>3553</v>
+      </c>
+      <c r="M353" t="s">
+        <v>3554</v>
+      </c>
+      <c r="O353" t="s">
+        <v>3555</v>
+      </c>
+      <c r="P353" t="s">
+        <v>3556</v>
+      </c>
+      <c r="Q353" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="354" ht="16.5" spans="2:17">
+      <c r="B354" s="1" t="s">
+        <v>3557</v>
+      </c>
+      <c r="C354" s="1">
+        <v>82814</v>
+      </c>
+      <c r="D354" t="s">
+        <v>3558</v>
+      </c>
+      <c r="E354" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F354" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I354" t="s">
+        <v>3559</v>
+      </c>
+      <c r="J354" t="s">
+        <v>3560</v>
+      </c>
+      <c r="K354" t="s">
+        <v>3561</v>
+      </c>
+      <c r="M354" t="s">
+        <v>3562</v>
+      </c>
+      <c r="O354" t="s">
+        <v>3563</v>
+      </c>
+      <c r="P354" t="s">
+        <v>3564</v>
+      </c>
+      <c r="Q354" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="355" ht="16.5" spans="2:17">
+      <c r="B355" s="1" t="s">
+        <v>3565</v>
+      </c>
+      <c r="C355" s="1">
+        <v>82824</v>
+      </c>
+      <c r="D355" t="s">
+        <v>3566</v>
+      </c>
+      <c r="E355" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F355" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I355" t="s">
+        <v>3567</v>
+      </c>
+      <c r="J355" t="s">
+        <v>3568</v>
+      </c>
+      <c r="K355" t="s">
+        <v>3569</v>
+      </c>
+      <c r="M355" t="s">
+        <v>3570</v>
+      </c>
+      <c r="O355" t="s">
+        <v>3571</v>
+      </c>
+      <c r="P355" t="s">
+        <v>3572</v>
+      </c>
+      <c r="Q355" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="356" ht="16.5" spans="2:17">
+      <c r="B356" s="1" t="s">
+        <v>3573</v>
+      </c>
+      <c r="C356" s="1">
+        <v>82804</v>
+      </c>
+      <c r="D356" t="s">
+        <v>3574</v>
+      </c>
+      <c r="E356" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F356" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I356" t="s">
+        <v>3575</v>
+      </c>
+      <c r="J356" t="s">
+        <v>3576</v>
+      </c>
+      <c r="K356" t="s">
+        <v>3577</v>
+      </c>
+      <c r="M356" t="s">
+        <v>3578</v>
+      </c>
+      <c r="O356" t="s">
+        <v>3579</v>
+      </c>
+      <c r="P356" t="s">
+        <v>3580</v>
+      </c>
+      <c r="Q356" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="357" ht="16.5" spans="2:17">
+      <c r="B357" s="1" t="s">
+        <v>3581</v>
+      </c>
+      <c r="C357" s="1">
+        <v>82834</v>
+      </c>
+      <c r="D357" t="s">
+        <v>3582</v>
+      </c>
+      <c r="E357" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F357" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I357" t="s">
+        <v>3583</v>
+      </c>
+      <c r="J357" t="s">
+        <v>3584</v>
+      </c>
+      <c r="K357" t="s">
+        <v>3585</v>
+      </c>
+      <c r="M357" t="s">
+        <v>3586</v>
+      </c>
+      <c r="O357" t="s">
+        <v>3587</v>
+      </c>
+      <c r="P357" t="s">
+        <v>3588</v>
+      </c>
+      <c r="Q357" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="358" ht="16.5" spans="2:17">
+      <c r="B358" s="1" t="s">
+        <v>3589</v>
+      </c>
+      <c r="C358" s="1">
+        <v>82854</v>
+      </c>
+      <c r="D358" t="s">
+        <v>3590</v>
+      </c>
+      <c r="E358" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F358" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I358" t="s">
+        <v>3591</v>
+      </c>
+      <c r="J358" t="s">
+        <v>3592</v>
+      </c>
+      <c r="K358" t="s">
+        <v>3593</v>
+      </c>
+      <c r="M358" t="s">
+        <v>3594</v>
+      </c>
+      <c r="O358" t="s">
+        <v>3595</v>
+      </c>
+      <c r="P358" t="s">
+        <v>3596</v>
+      </c>
+      <c r="Q358" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="359" ht="16.5" spans="2:17">
+      <c r="B359" s="1" t="s">
+        <v>3597</v>
+      </c>
+      <c r="C359" s="1">
+        <v>82794</v>
+      </c>
+      <c r="D359" t="s">
+        <v>3598</v>
+      </c>
+      <c r="E359" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F359" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I359" t="s">
+        <v>3599</v>
+      </c>
+      <c r="J359" t="s">
+        <v>3600</v>
+      </c>
+      <c r="K359" t="s">
+        <v>3601</v>
+      </c>
+      <c r="M359" t="s">
+        <v>3602</v>
+      </c>
+      <c r="O359" t="s">
+        <v>3603</v>
+      </c>
+      <c r="P359" t="s">
+        <v>3604</v>
+      </c>
+      <c r="Q359" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="360" ht="16.5" spans="2:17">
+      <c r="B360" s="1" t="s">
+        <v>3605</v>
+      </c>
+      <c r="C360" s="1">
+        <v>82844</v>
+      </c>
+      <c r="D360" t="s">
+        <v>3606</v>
+      </c>
+      <c r="E360" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F360" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I360" t="s">
+        <v>3607</v>
+      </c>
+      <c r="J360" t="s">
+        <v>3608</v>
+      </c>
+      <c r="K360" t="s">
+        <v>3609</v>
+      </c>
+      <c r="M360" t="s">
+        <v>3610</v>
+      </c>
+      <c r="O360" t="s">
+        <v>3611</v>
+      </c>
+      <c r="P360" t="s">
+        <v>3612</v>
+      </c>
+      <c r="Q360" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="361" ht="16.5" spans="2:17">
+      <c r="B361" s="1" t="s">
+        <v>3613</v>
+      </c>
+      <c r="C361" s="1">
+        <v>82864</v>
+      </c>
+      <c r="D361" t="s">
+        <v>3614</v>
+      </c>
+      <c r="E361" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F361" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I361" t="s">
+        <v>3615</v>
+      </c>
+      <c r="J361" t="s">
+        <v>3616</v>
+      </c>
+      <c r="K361" t="s">
+        <v>3617</v>
+      </c>
+      <c r="M361" t="s">
+        <v>3618</v>
+      </c>
+      <c r="O361" t="s">
+        <v>3619</v>
+      </c>
+      <c r="P361" t="s">
+        <v>3620</v>
+      </c>
+      <c r="Q361" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="362" ht="16.5" spans="2:17">
+      <c r="B362" s="1" t="s">
+        <v>3621</v>
+      </c>
+      <c r="C362" s="1">
+        <v>82875</v>
+      </c>
+      <c r="D362" t="s">
+        <v>3622</v>
+      </c>
+      <c r="E362" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F362" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I362" t="s">
+        <v>3623</v>
+      </c>
+      <c r="J362" t="s">
+        <v>3624</v>
+      </c>
+      <c r="K362" t="s">
+        <v>3625</v>
+      </c>
+      <c r="M362" t="s">
+        <v>3626</v>
+      </c>
+      <c r="O362" t="s">
+        <v>3627</v>
+      </c>
+      <c r="P362" t="s">
+        <v>3628</v>
+      </c>
+      <c r="Q362" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="363" ht="16.5" spans="2:17">
+      <c r="B363" s="1" t="s">
+        <v>3629</v>
+      </c>
+      <c r="C363" s="1">
+        <v>82886</v>
+      </c>
+      <c r="D363" t="s">
+        <v>3630</v>
+      </c>
+      <c r="E363" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F363" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I363" t="s">
+        <v>3631</v>
+      </c>
+      <c r="J363" t="s">
+        <v>3632</v>
+      </c>
+      <c r="K363" t="s">
+        <v>3633</v>
+      </c>
+      <c r="M363" t="s">
+        <v>3634</v>
+      </c>
+      <c r="O363" t="s">
+        <v>3635</v>
+      </c>
+      <c r="P363" t="s">
+        <v>3636</v>
+      </c>
+      <c r="Q363" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="364" ht="16.5" spans="2:17">
+      <c r="B364" s="1" t="s">
+        <v>3637</v>
+      </c>
+      <c r="C364" s="1">
+        <v>82897</v>
+      </c>
+      <c r="D364" t="s">
+        <v>3638</v>
+      </c>
+      <c r="E364" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F364" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I364" t="s">
+        <v>3639</v>
+      </c>
+      <c r="J364" t="s">
+        <v>3640</v>
+      </c>
+      <c r="K364" t="s">
+        <v>3641</v>
+      </c>
+      <c r="M364" t="s">
+        <v>3642</v>
+      </c>
+      <c r="O364" t="s">
+        <v>3643</v>
+      </c>
+      <c r="P364" t="s">
+        <v>3644</v>
+      </c>
+      <c r="Q364" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="365" ht="16.5" spans="2:17">
+      <c r="B365" s="1" t="s">
+        <v>3645</v>
+      </c>
+      <c r="C365" s="1">
+        <v>82930</v>
+      </c>
+      <c r="D365" t="s">
+        <v>3646</v>
+      </c>
+      <c r="E365" t="s">
+        <v>2613</v>
+      </c>
+      <c r="F365" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I365" t="s">
+        <v>3647</v>
+      </c>
+      <c r="J365" t="s">
+        <v>3648</v>
+      </c>
+      <c r="K365" t="s">
+        <v>3649</v>
+      </c>
+      <c r="M365" t="s">
+        <v>3650</v>
+      </c>
+      <c r="O365" t="s">
+        <v>3651</v>
+      </c>
+      <c r="P365" t="s">
+        <v>3652</v>
+      </c>
+      <c r="Q365" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="366" ht="16.5" spans="2:17">
+      <c r="B366" s="1" t="s">
+        <v>3653</v>
+      </c>
+      <c r="C366" s="1">
+        <v>82941</v>
+      </c>
+      <c r="D366" t="s">
+        <v>3654</v>
+      </c>
+      <c r="E366" t="s">
+        <v>2613</v>
+      </c>
+      <c r="F366" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I366" t="s">
+        <v>3655</v>
+      </c>
+      <c r="J366" t="s">
+        <v>3656</v>
+      </c>
+      <c r="K366" t="s">
+        <v>3657</v>
+      </c>
+      <c r="M366" t="s">
+        <v>3658</v>
+      </c>
+      <c r="O366" t="s">
+        <v>3659</v>
+      </c>
+      <c r="P366" t="s">
+        <v>3660</v>
+      </c>
+      <c r="Q366" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="367" ht="16.5" spans="2:17">
+      <c r="B367" s="1" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C367" s="1">
+        <v>82919</v>
+      </c>
+      <c r="D367" t="s">
+        <v>3662</v>
+      </c>
+      <c r="E367" t="s">
+        <v>2613</v>
+      </c>
+      <c r="F367" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I367" t="s">
+        <v>3663</v>
+      </c>
+      <c r="J367" t="s">
+        <v>3664</v>
+      </c>
+      <c r="K367" t="s">
+        <v>3665</v>
+      </c>
+      <c r="M367" t="s">
+        <v>3666</v>
+      </c>
+      <c r="O367" t="s">
+        <v>3667</v>
+      </c>
+      <c r="P367" t="s">
+        <v>3668</v>
+      </c>
+      <c r="Q367" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="368" ht="16.5" spans="2:17">
+      <c r="B368" s="1" t="s">
+        <v>3669</v>
+      </c>
+      <c r="C368" s="1">
+        <v>82974</v>
+      </c>
+      <c r="D368" t="s">
+        <v>3670</v>
+      </c>
+      <c r="E368" t="s">
+        <v>2613</v>
+      </c>
+      <c r="F368" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I368" t="s">
+        <v>3671</v>
+      </c>
+      <c r="J368" t="s">
+        <v>3672</v>
+      </c>
+      <c r="K368" t="s">
+        <v>3673</v>
+      </c>
+      <c r="M368" t="s">
+        <v>3674</v>
+      </c>
+      <c r="O368" t="s">
+        <v>3675</v>
+      </c>
+      <c r="P368" t="s">
+        <v>3676</v>
+      </c>
+      <c r="Q368" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="369" ht="16.5" spans="2:17">
+      <c r="B369" s="1" t="s">
+        <v>3677</v>
+      </c>
+      <c r="C369" s="1">
+        <v>82963</v>
+      </c>
+      <c r="D369" t="s">
+        <v>3678</v>
+      </c>
+      <c r="E369" t="s">
+        <v>2613</v>
+      </c>
+      <c r="F369" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I369" t="s">
+        <v>3679</v>
+      </c>
+      <c r="J369" t="s">
+        <v>3680</v>
+      </c>
+      <c r="K369" t="s">
+        <v>3681</v>
+      </c>
+      <c r="M369" t="s">
+        <v>3682</v>
+      </c>
+      <c r="O369" t="s">
+        <v>3683</v>
+      </c>
+      <c r="P369" t="s">
+        <v>3684</v>
+      </c>
+      <c r="Q369" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="370" ht="16.5" spans="2:17">
+      <c r="B370" s="1" t="s">
+        <v>3685</v>
+      </c>
+      <c r="C370" s="1">
+        <v>82952</v>
+      </c>
+      <c r="D370" t="s">
+        <v>3686</v>
+      </c>
+      <c r="E370" t="s">
+        <v>2613</v>
+      </c>
+      <c r="F370" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I370" t="s">
+        <v>3687</v>
+      </c>
+      <c r="J370" t="s">
+        <v>3688</v>
+      </c>
+      <c r="K370" t="s">
+        <v>3689</v>
+      </c>
+      <c r="M370" t="s">
+        <v>3690</v>
+      </c>
+      <c r="O370" t="s">
+        <v>3691</v>
+      </c>
+      <c r="P370" t="s">
+        <v>3692</v>
+      </c>
+      <c r="Q370" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="371" ht="16.5" spans="2:17">
+      <c r="B371" s="1" t="s">
+        <v>3693</v>
+      </c>
+      <c r="C371" s="1">
+        <v>82908</v>
+      </c>
+      <c r="D371" t="s">
+        <v>3694</v>
+      </c>
+      <c r="E371" t="s">
+        <v>2613</v>
+      </c>
+      <c r="F371" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I371" t="s">
+        <v>3695</v>
+      </c>
+      <c r="J371" t="s">
+        <v>3696</v>
+      </c>
+      <c r="K371" t="s">
+        <v>3697</v>
+      </c>
+      <c r="M371" t="s">
+        <v>3698</v>
+      </c>
+      <c r="O371" t="s">
+        <v>3699</v>
+      </c>
+      <c r="P371" t="s">
+        <v>3700</v>
+      </c>
+      <c r="Q371" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="372" ht="16.5" spans="2:17">
+      <c r="B372" s="34" t="s">
+        <v>3701</v>
+      </c>
+      <c r="C372" s="1">
+        <v>84256</v>
+      </c>
+      <c r="D372" s="28" t="s">
+        <v>3702</v>
+      </c>
+      <c r="E372" t="s">
+        <v>2976</v>
+      </c>
+      <c r="F372" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I372" t="s">
+        <v>3703</v>
+      </c>
+      <c r="J372" t="s">
+        <v>3704</v>
+      </c>
+      <c r="K372" t="s">
+        <v>3705</v>
+      </c>
+      <c r="M372" t="s">
+        <v>3706</v>
+      </c>
+      <c r="O372" t="s">
+        <v>3707</v>
+      </c>
+      <c r="P372" t="s">
+        <v>3708</v>
+      </c>
+    </row>
+    <row r="373" ht="16.5" spans="2:17">
+      <c r="B373" s="34" t="s">
+        <v>3709</v>
+      </c>
+      <c r="C373" s="1">
+        <v>84237</v>
+      </c>
+      <c r="D373" s="28" t="s">
+        <v>3710</v>
+      </c>
+      <c r="E373" t="s">
+        <v>2976</v>
+      </c>
+      <c r="F373" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I373" t="s">
+        <v>3711</v>
+      </c>
+      <c r="J373" t="s">
+        <v>3712</v>
+      </c>
+      <c r="K373" t="s">
+        <v>3713</v>
+      </c>
+      <c r="M373" t="s">
+        <v>3714</v>
+      </c>
+      <c r="O373" t="s">
+        <v>3715</v>
+      </c>
+      <c r="P373" t="s">
+        <v>3716</v>
+      </c>
+    </row>
+    <row r="374" ht="16.5" spans="2:17">
+      <c r="B374" s="34" t="s">
+        <v>3717</v>
+      </c>
+      <c r="C374" s="1">
+        <v>84199</v>
+      </c>
+      <c r="D374" s="28" t="s">
+        <v>3718</v>
+      </c>
+      <c r="E374" t="s">
+        <v>2976</v>
+      </c>
+      <c r="F374" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I374" t="s">
+        <v>3719</v>
+      </c>
+      <c r="J374" t="s">
+        <v>3720</v>
+      </c>
+      <c r="K374" t="s">
+        <v>3721</v>
+      </c>
+      <c r="M374" t="s">
+        <v>3722</v>
+      </c>
+      <c r="O374" t="s">
+        <v>3723</v>
+      </c>
+      <c r="P374" t="s">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="375" ht="16.5" spans="2:17">
+      <c r="B375" s="34" t="s">
+        <v>3725</v>
+      </c>
+      <c r="C375" s="1">
+        <v>84217</v>
+      </c>
+      <c r="D375" s="28" t="s">
+        <v>3726</v>
+      </c>
+      <c r="E375" t="s">
+        <v>2976</v>
+      </c>
+      <c r="F375" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I375" t="s">
+        <v>3727</v>
+      </c>
+      <c r="J375" t="s">
+        <v>3728</v>
+      </c>
+      <c r="K375" t="s">
+        <v>3729</v>
+      </c>
+      <c r="M375" t="s">
+        <v>3730</v>
+      </c>
+      <c r="O375" t="s">
+        <v>3731</v>
+      </c>
+      <c r="P375" t="s">
+        <v>3732</v>
+      </c>
+    </row>
+    <row r="376" ht="16.5" spans="2:17">
+      <c r="B376" s="34" t="s">
+        <v>3733</v>
+      </c>
+      <c r="C376" s="1">
+        <v>84386</v>
+      </c>
+      <c r="D376" s="28" t="s">
+        <v>3734</v>
+      </c>
+      <c r="E376" t="s">
+        <v>3735</v>
+      </c>
+      <c r="F376" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I376" t="s">
+        <v>3736</v>
+      </c>
+      <c r="J376" t="s">
+        <v>3737</v>
+      </c>
+      <c r="K376" t="s">
+        <v>3738</v>
+      </c>
+      <c r="M376" t="s">
+        <v>3739</v>
+      </c>
+      <c r="O376" t="s">
+        <v>3740</v>
+      </c>
+      <c r="P376" t="s">
+        <v>3741</v>
+      </c>
+    </row>
+    <row r="377" ht="16.5" spans="2:17">
+      <c r="B377" s="34" t="s">
+        <v>3742</v>
+      </c>
+      <c r="C377" s="1">
+        <v>84319</v>
+      </c>
+      <c r="D377" s="28" t="s">
+        <v>3743</v>
+      </c>
+      <c r="E377" t="s">
+        <v>3735</v>
+      </c>
+      <c r="F377" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I377" t="s">
+        <v>3744</v>
+      </c>
+      <c r="J377" t="s">
+        <v>3745</v>
+      </c>
+      <c r="K377" t="s">
+        <v>3746</v>
+      </c>
+      <c r="M377" t="s">
+        <v>3747</v>
+      </c>
+      <c r="O377" t="s">
+        <v>3748</v>
+      </c>
+      <c r="P377" t="s">
+        <v>3749</v>
+      </c>
+    </row>
+    <row r="378" ht="16.5" spans="2:17">
+      <c r="B378" s="34" t="s">
+        <v>3750</v>
+      </c>
+      <c r="C378" s="1">
+        <v>84340</v>
+      </c>
+      <c r="D378" s="28" t="s">
+        <v>3751</v>
+      </c>
+      <c r="E378" t="s">
+        <v>3735</v>
+      </c>
+      <c r="F378" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I378" t="s">
+        <v>3752</v>
+      </c>
+      <c r="J378" t="s">
+        <v>3753</v>
+      </c>
+      <c r="K378" t="s">
+        <v>3754</v>
+      </c>
+      <c r="M378" t="s">
+        <v>3755</v>
+      </c>
+      <c r="O378" t="s">
+        <v>3756</v>
+      </c>
+      <c r="P378" t="s">
+        <v>3757</v>
+      </c>
+    </row>
+    <row r="379" ht="16.5" spans="2:17">
+      <c r="B379" s="34" t="s">
+        <v>3758</v>
+      </c>
+      <c r="C379" s="1">
+        <v>84277</v>
+      </c>
+      <c r="D379" s="28" t="s">
+        <v>3759</v>
+      </c>
+      <c r="E379" t="s">
+        <v>3735</v>
+      </c>
+      <c r="F379" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I379" t="s">
+        <v>3760</v>
+      </c>
+      <c r="J379" t="s">
+        <v>3761</v>
+      </c>
+      <c r="K379" t="s">
+        <v>3762</v>
+      </c>
+      <c r="M379" t="s">
+        <v>3763</v>
+      </c>
+      <c r="O379" t="s">
+        <v>3764</v>
+      </c>
+      <c r="P379" t="s">
+        <v>3765</v>
+      </c>
+    </row>
+    <row r="380" ht="16.5" spans="2:17">
+      <c r="B380" s="34" t="s">
+        <v>3766</v>
+      </c>
+      <c r="C380" s="1">
+        <v>84353</v>
+      </c>
+      <c r="D380" s="28" t="s">
+        <v>3767</v>
+      </c>
+      <c r="E380" t="s">
+        <v>3735</v>
+      </c>
+      <c r="F380" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I380" t="s">
+        <v>3768</v>
+      </c>
+      <c r="J380" t="s">
+        <v>3769</v>
+      </c>
+      <c r="K380" t="s">
+        <v>3770</v>
+      </c>
+      <c r="M380" t="s">
+        <v>3771</v>
+      </c>
+      <c r="O380" t="s">
+        <v>3772</v>
+      </c>
+      <c r="P380" t="s">
+        <v>3773</v>
+      </c>
+    </row>
+    <row r="381" ht="16.5" spans="2:17">
+      <c r="B381" s="34" t="s">
+        <v>3774</v>
+      </c>
+      <c r="C381" s="1">
+        <v>84298</v>
+      </c>
+      <c r="D381" s="28" t="s">
+        <v>3775</v>
+      </c>
+      <c r="E381" t="s">
+        <v>3735</v>
+      </c>
+      <c r="F381" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I381" t="s">
+        <v>3776</v>
+      </c>
+      <c r="J381" t="s">
+        <v>3777</v>
+      </c>
+      <c r="K381" t="s">
+        <v>3778</v>
+      </c>
+      <c r="M381" t="s">
+        <v>3779</v>
+      </c>
+      <c r="O381" t="s">
+        <v>3780</v>
+      </c>
+      <c r="P381" t="s">
+        <v>3781</v>
+      </c>
+    </row>
+    <row r="382" ht="16.5" spans="2:17">
+      <c r="B382" s="34" t="s">
+        <v>3782</v>
+      </c>
+      <c r="C382" s="1">
+        <v>84375</v>
+      </c>
+      <c r="D382" s="28" t="s">
+        <v>3783</v>
+      </c>
+      <c r="E382" t="s">
+        <v>3735</v>
+      </c>
+      <c r="F382" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I382" t="s">
+        <v>3784</v>
+      </c>
+      <c r="J382" t="s">
+        <v>3785</v>
+      </c>
+      <c r="K382" t="s">
+        <v>3786</v>
+      </c>
+      <c r="M382" t="s">
+        <v>3787</v>
+      </c>
+      <c r="O382" t="s">
+        <v>3788</v>
+      </c>
+      <c r="P382" t="s">
+        <v>3789</v>
+      </c>
+    </row>
+    <row r="383" ht="16.5" spans="2:17">
+      <c r="B383" s="34" t="s">
+        <v>3790</v>
+      </c>
+      <c r="C383" s="1">
+        <v>84408</v>
+      </c>
+      <c r="D383" s="28" t="s">
+        <v>3791</v>
+      </c>
+      <c r="E383" t="s">
+        <v>3735</v>
+      </c>
+      <c r="F383" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I383" t="s">
+        <v>3792</v>
+      </c>
+      <c r="J383" t="s">
+        <v>3793</v>
+      </c>
+      <c r="K383" t="s">
+        <v>3794</v>
+      </c>
+      <c r="M383" t="s">
+        <v>3795</v>
+      </c>
+      <c r="O383" t="s">
+        <v>3796</v>
+      </c>
+      <c r="P383" t="s">
+        <v>3797</v>
+      </c>
+    </row>
+    <row r="384" ht="16.5" spans="2:17">
+      <c r="B384" s="34" t="s">
+        <v>3798</v>
+      </c>
+      <c r="C384" s="1">
+        <v>84397</v>
+      </c>
+      <c r="D384" s="28" t="s">
+        <v>3799</v>
+      </c>
+      <c r="E384" t="s">
+        <v>3735</v>
+      </c>
+      <c r="F384" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I384" t="s">
+        <v>3800</v>
+      </c>
+      <c r="J384" t="s">
+        <v>3801</v>
+      </c>
+      <c r="K384" t="s">
+        <v>3802</v>
+      </c>
+      <c r="M384" t="s">
+        <v>3803</v>
+      </c>
+      <c r="O384" t="s">
+        <v>3804</v>
+      </c>
+      <c r="P384" t="s">
+        <v>3805</v>
+      </c>
+    </row>
+    <row r="385" ht="16.5" spans="2:16">
+      <c r="B385" s="34" t="s">
+        <v>3806</v>
+      </c>
+      <c r="C385" s="1">
+        <v>84364</v>
+      </c>
+      <c r="D385" s="28" t="s">
+        <v>3807</v>
+      </c>
+      <c r="E385" t="s">
+        <v>3735</v>
+      </c>
+      <c r="F385" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I385" t="s">
+        <v>3808</v>
+      </c>
+      <c r="J385" t="s">
+        <v>3809</v>
+      </c>
+      <c r="K385" t="s">
+        <v>3810</v>
+      </c>
+      <c r="M385" t="s">
+        <v>3811</v>
+      </c>
+      <c r="O385" t="s">
+        <v>3812</v>
+      </c>
+      <c r="P385" t="s">
+        <v>3813</v>
+      </c>
+    </row>
+    <row r="386" ht="16.5" spans="2:16">
+      <c r="B386" s="34" t="s">
+        <v>3814</v>
+      </c>
+      <c r="C386" s="1">
+        <v>84419</v>
+      </c>
+      <c r="D386" s="28" t="s">
+        <v>3815</v>
+      </c>
+      <c r="E386" t="s">
+        <v>3735</v>
+      </c>
+      <c r="F386" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I386" t="s">
+        <v>3816</v>
+      </c>
+      <c r="J386" t="s">
+        <v>3817</v>
+      </c>
+      <c r="K386" t="s">
+        <v>3818</v>
+      </c>
+      <c r="M386" t="s">
+        <v>3819</v>
+      </c>
+      <c r="O386" t="s">
+        <v>3820</v>
+      </c>
+      <c r="P386" t="s">
+        <v>3821</v>
+      </c>
+    </row>
+    <row r="387" ht="16.5" spans="2:16">
+      <c r="B387" s="34" t="s">
+        <v>3822</v>
+      </c>
+      <c r="C387" s="1">
+        <v>84496</v>
+      </c>
+      <c r="D387" s="28" t="s">
+        <v>3823</v>
+      </c>
+      <c r="E387" t="s">
+        <v>21</v>
+      </c>
+      <c r="F387" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I387" t="s">
+        <v>3824</v>
+      </c>
+      <c r="J387" t="s">
+        <v>3825</v>
+      </c>
+      <c r="K387" t="s">
+        <v>3826</v>
+      </c>
+      <c r="M387" t="s">
+        <v>3827</v>
+      </c>
+      <c r="O387" t="s">
+        <v>3828</v>
+      </c>
+      <c r="P387" t="s">
+        <v>3829</v>
+      </c>
+    </row>
+    <row r="388" ht="16.5" spans="2:16">
+      <c r="B388" s="34" t="s">
+        <v>3830</v>
+      </c>
+      <c r="C388" s="1">
+        <v>84485</v>
+      </c>
+      <c r="D388" s="28" t="s">
+        <v>3831</v>
+      </c>
+      <c r="E388" t="s">
+        <v>21</v>
+      </c>
+      <c r="F388" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I388" t="s">
+        <v>3832</v>
+      </c>
+      <c r="J388" t="s">
+        <v>3833</v>
+      </c>
+      <c r="K388" t="s">
+        <v>3834</v>
+      </c>
+      <c r="M388" t="s">
+        <v>3835</v>
+      </c>
+      <c r="O388" t="s">
+        <v>3836</v>
+      </c>
+      <c r="P388" t="s">
+        <v>3837</v>
+      </c>
+    </row>
+    <row r="389" ht="16.5" spans="2:16">
+      <c r="B389" s="34" t="s">
+        <v>3838</v>
+      </c>
+      <c r="C389" s="1">
+        <v>84474</v>
+      </c>
+      <c r="D389" s="28" t="s">
+        <v>3839</v>
+      </c>
+      <c r="E389" t="s">
+        <v>21</v>
+      </c>
+      <c r="F389" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I389" t="s">
+        <v>3840</v>
+      </c>
+      <c r="J389" t="s">
+        <v>3841</v>
+      </c>
+      <c r="K389" t="s">
+        <v>3842</v>
+      </c>
+      <c r="M389" t="s">
+        <v>3843</v>
+      </c>
+      <c r="O389" t="s">
+        <v>3844</v>
+      </c>
+      <c r="P389" t="s">
+        <v>3845</v>
+      </c>
+    </row>
+    <row r="390" ht="16.5" spans="2:16">
+      <c r="B390" s="34" t="s">
+        <v>3846</v>
+      </c>
+      <c r="C390" s="1">
+        <v>84463</v>
+      </c>
+      <c r="D390" s="28" t="s">
+        <v>3847</v>
+      </c>
+      <c r="E390" t="s">
+        <v>21</v>
+      </c>
+      <c r="F390" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I390" t="s">
+        <v>3848</v>
+      </c>
+      <c r="J390" t="s">
+        <v>3849</v>
+      </c>
+      <c r="K390" t="s">
+        <v>3850</v>
+      </c>
+      <c r="M390" t="s">
+        <v>3851</v>
+      </c>
+      <c r="O390" t="s">
+        <v>3852</v>
+      </c>
+      <c r="P390" t="s">
+        <v>3853</v>
+      </c>
+    </row>
+    <row r="391" ht="16.5" spans="2:16">
+      <c r="B391" s="34" t="s">
+        <v>3854</v>
+      </c>
+      <c r="C391" s="1">
+        <v>84430</v>
+      </c>
+      <c r="D391" s="28" t="s">
+        <v>3855</v>
+      </c>
+      <c r="E391" t="s">
+        <v>21</v>
+      </c>
+      <c r="F391" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I391" t="s">
+        <v>3856</v>
+      </c>
+      <c r="J391" t="s">
+        <v>3857</v>
+      </c>
+      <c r="K391" t="s">
+        <v>3858</v>
+      </c>
+      <c r="M391" t="s">
+        <v>3859</v>
+      </c>
+      <c r="O391" t="s">
+        <v>3860</v>
+      </c>
+      <c r="P391" t="s">
+        <v>3861</v>
+      </c>
+    </row>
+    <row r="392" ht="16.5" spans="2:16">
+      <c r="B392" s="34" t="s">
+        <v>3862</v>
+      </c>
+      <c r="C392" s="1">
+        <v>84441</v>
+      </c>
+      <c r="D392" s="28" t="s">
+        <v>3863</v>
+      </c>
+      <c r="E392" t="s">
+        <v>21</v>
+      </c>
+      <c r="F392" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I392" t="s">
+        <v>3864</v>
+      </c>
+      <c r="J392" t="s">
+        <v>3865</v>
+      </c>
+      <c r="K392" t="s">
+        <v>3866</v>
+      </c>
+      <c r="M392" t="s">
+        <v>3867</v>
+      </c>
+      <c r="O392" t="s">
+        <v>3868</v>
+      </c>
+      <c r="P392" t="s">
+        <v>3869</v>
+      </c>
+    </row>
+    <row r="393" ht="16.5" spans="2:16">
+      <c r="B393" s="34" t="s">
+        <v>3870</v>
+      </c>
+      <c r="C393" s="1">
+        <v>84507</v>
+      </c>
+      <c r="D393" s="28" t="s">
+        <v>3871</v>
+      </c>
+      <c r="E393" t="s">
+        <v>21</v>
+      </c>
+      <c r="F393" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I393" t="s">
+        <v>3872</v>
+      </c>
+      <c r="J393" t="s">
+        <v>3873</v>
+      </c>
+      <c r="K393" t="s">
+        <v>3874</v>
+      </c>
+      <c r="M393" t="s">
+        <v>3875</v>
+      </c>
+      <c r="O393" t="s">
+        <v>3876</v>
+      </c>
+      <c r="P393" t="s">
+        <v>3877</v>
+      </c>
+    </row>
+    <row r="394" ht="16.5" spans="2:16">
+      <c r="B394" s="34" t="s">
+        <v>3878</v>
+      </c>
+      <c r="C394" s="1">
+        <v>84452</v>
+      </c>
+      <c r="D394" s="28" t="s">
+        <v>3879</v>
+      </c>
+      <c r="E394" t="s">
+        <v>21</v>
+      </c>
+      <c r="F394" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I394" t="s">
+        <v>3880</v>
+      </c>
+      <c r="J394" t="s">
+        <v>3881</v>
+      </c>
+      <c r="K394" t="s">
+        <v>3882</v>
+      </c>
+      <c r="M394" t="s">
+        <v>3883</v>
+      </c>
+      <c r="O394" t="s">
+        <v>3884</v>
+      </c>
+      <c r="P394" t="s">
+        <v>3885</v>
+      </c>
+    </row>
+    <row r="395" ht="16.5" spans="2:16">
+      <c r="B395" s="34" t="s">
+        <v>3886</v>
+      </c>
+      <c r="C395" s="1">
+        <v>84562</v>
+      </c>
+      <c r="D395" s="28" t="s">
+        <v>3887</v>
+      </c>
+      <c r="E395" t="s">
+        <v>2674</v>
+      </c>
+      <c r="F395" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I395" t="s">
+        <v>3888</v>
+      </c>
+      <c r="J395" t="s">
+        <v>3889</v>
+      </c>
+      <c r="K395" t="s">
+        <v>3890</v>
+      </c>
+      <c r="M395" t="s">
+        <v>3891</v>
+      </c>
+      <c r="O395" t="s">
+        <v>3892</v>
+      </c>
+      <c r="P395" t="s">
+        <v>3893</v>
+      </c>
+    </row>
+    <row r="396" ht="16.5" spans="2:16">
+      <c r="B396" s="34" t="s">
+        <v>3894</v>
+      </c>
+      <c r="C396" s="1">
+        <v>84518</v>
+      </c>
+      <c r="D396" s="28" t="s">
+        <v>3895</v>
+      </c>
+      <c r="E396" t="s">
+        <v>2674</v>
+      </c>
+      <c r="F396" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I396" t="s">
+        <v>3896</v>
+      </c>
+      <c r="J396" t="s">
+        <v>3897</v>
+      </c>
+      <c r="K396" t="s">
+        <v>3898</v>
+      </c>
+      <c r="M396" t="s">
+        <v>3899</v>
+      </c>
+      <c r="O396" t="s">
+        <v>3900</v>
+      </c>
+      <c r="P396" t="s">
+        <v>3901</v>
+      </c>
+    </row>
+    <row r="397" ht="16.5" spans="2:16">
+      <c r="B397" s="34" t="s">
+        <v>3902</v>
+      </c>
+      <c r="C397" s="1">
+        <v>84529</v>
+      </c>
+      <c r="D397" s="28" t="s">
+        <v>3903</v>
+      </c>
+      <c r="E397" t="s">
+        <v>2674</v>
+      </c>
+      <c r="F397" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I397" t="s">
+        <v>3904</v>
+      </c>
+      <c r="J397" t="s">
+        <v>3905</v>
+      </c>
+      <c r="K397" t="s">
+        <v>3906</v>
+      </c>
+      <c r="M397" t="s">
+        <v>3907</v>
+      </c>
+      <c r="O397" t="s">
+        <v>3908</v>
+      </c>
+      <c r="P397" t="s">
+        <v>3909</v>
+      </c>
+    </row>
+    <row r="398" ht="16.5" spans="2:16">
+      <c r="B398" s="34" t="s">
+        <v>3910</v>
+      </c>
+      <c r="C398" s="1">
+        <v>84540</v>
+      </c>
+      <c r="D398" s="28" t="s">
+        <v>3911</v>
+      </c>
+      <c r="E398" t="s">
+        <v>2674</v>
+      </c>
+      <c r="F398" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I398" t="s">
+        <v>3912</v>
+      </c>
+      <c r="J398" t="s">
+        <v>3913</v>
+      </c>
+      <c r="K398" t="s">
+        <v>3914</v>
+      </c>
+      <c r="M398" t="s">
+        <v>3915</v>
+      </c>
+      <c r="O398" t="s">
+        <v>3916</v>
+      </c>
+      <c r="P398" t="s">
+        <v>3917</v>
+      </c>
+    </row>
+    <row r="399" ht="16.5" spans="2:16">
+      <c r="B399" s="34" t="s">
+        <v>3918</v>
+      </c>
+      <c r="C399" s="1">
+        <v>84551</v>
+      </c>
+      <c r="D399" s="28" t="s">
+        <v>3919</v>
+      </c>
+      <c r="E399" t="s">
+        <v>2674</v>
+      </c>
+      <c r="F399" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I399" t="s">
+        <v>3920</v>
+      </c>
+      <c r="J399" t="s">
+        <v>3921</v>
+      </c>
+      <c r="K399" t="s">
+        <v>3922</v>
+      </c>
+      <c r="M399" t="s">
+        <v>3923</v>
+      </c>
+      <c r="O399" t="s">
+        <v>3924</v>
+      </c>
+      <c r="P399" t="s">
+        <v>3925</v>
+      </c>
+    </row>
+    <row r="400" ht="16.5" spans="2:16">
+      <c r="B400" s="34" t="s">
+        <v>3926</v>
+      </c>
+      <c r="C400" s="1">
+        <v>84617</v>
+      </c>
+      <c r="D400" s="28" t="s">
+        <v>3927</v>
+      </c>
+      <c r="E400" t="s">
+        <v>233</v>
+      </c>
+      <c r="F400" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I400" t="s">
+        <v>3928</v>
+      </c>
+      <c r="J400" t="s">
+        <v>3929</v>
+      </c>
+      <c r="K400" t="s">
+        <v>3930</v>
+      </c>
+      <c r="M400" t="s">
+        <v>3931</v>
+      </c>
+      <c r="O400" t="s">
+        <v>3932</v>
+      </c>
+      <c r="P400" t="s">
+        <v>3933</v>
+      </c>
+    </row>
+    <row r="401" ht="16.5" spans="2:16">
+      <c r="B401" s="34" t="s">
+        <v>3934</v>
+      </c>
+      <c r="C401" s="1">
+        <v>84606</v>
+      </c>
+      <c r="D401" s="28" t="s">
+        <v>3935</v>
+      </c>
+      <c r="E401" t="s">
+        <v>233</v>
+      </c>
+      <c r="F401" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I401" t="s">
+        <v>3936</v>
+      </c>
+      <c r="J401" t="s">
+        <v>3937</v>
+      </c>
+      <c r="K401" t="s">
+        <v>3938</v>
+      </c>
+      <c r="M401" t="s">
+        <v>3939</v>
+      </c>
+      <c r="O401" t="s">
+        <v>3940</v>
+      </c>
+      <c r="P401" t="s">
+        <v>3941</v>
+      </c>
+    </row>
+    <row r="402" ht="16.5" spans="2:16">
+      <c r="B402" s="34" t="s">
+        <v>3942</v>
+      </c>
+      <c r="C402" s="1">
+        <v>84584</v>
+      </c>
+      <c r="D402" s="28" t="s">
+        <v>3943</v>
+      </c>
+      <c r="E402" t="s">
+        <v>233</v>
+      </c>
+      <c r="F402" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I402" t="s">
+        <v>3944</v>
+      </c>
+      <c r="J402" t="s">
+        <v>3945</v>
+      </c>
+      <c r="K402" t="s">
+        <v>3946</v>
+      </c>
+      <c r="M402" t="s">
+        <v>3947</v>
+      </c>
+      <c r="O402" t="s">
+        <v>3948</v>
+      </c>
+      <c r="P402" t="s">
+        <v>3949</v>
+      </c>
+    </row>
+    <row r="403" ht="16.5" spans="2:16">
+      <c r="B403" s="34" t="s">
+        <v>3950</v>
+      </c>
+      <c r="C403" s="1">
+        <v>84573</v>
+      </c>
+      <c r="D403" s="28" t="s">
+        <v>3951</v>
+      </c>
+      <c r="E403" t="s">
+        <v>233</v>
+      </c>
+      <c r="F403" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I403" t="s">
+        <v>3952</v>
+      </c>
+      <c r="J403" t="s">
+        <v>3953</v>
+      </c>
+      <c r="K403" t="s">
+        <v>3954</v>
+      </c>
+      <c r="M403" t="s">
+        <v>3955</v>
+      </c>
+      <c r="O403" t="s">
+        <v>3956</v>
+      </c>
+      <c r="P403" t="s">
+        <v>3957</v>
+      </c>
+    </row>
+    <row r="404" ht="16.5" spans="2:16">
+      <c r="B404" s="34" t="s">
+        <v>3958</v>
+      </c>
+      <c r="C404" s="1">
+        <v>84628</v>
+      </c>
+      <c r="D404" s="28" t="s">
+        <v>3959</v>
+      </c>
+      <c r="E404" t="s">
+        <v>233</v>
+      </c>
+      <c r="F404" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I404" t="s">
+        <v>3960</v>
+      </c>
+      <c r="J404" t="s">
+        <v>3961</v>
+      </c>
+      <c r="K404" t="s">
+        <v>3962</v>
+      </c>
+      <c r="M404" t="s">
+        <v>3963</v>
+      </c>
+      <c r="O404" t="s">
+        <v>3964</v>
+      </c>
+      <c r="P404" t="s">
+        <v>3965</v>
+      </c>
+    </row>
+    <row r="405" ht="16.5" spans="2:16">
+      <c r="B405" s="34" t="s">
+        <v>3966</v>
+      </c>
+      <c r="C405" s="1">
+        <v>84595</v>
+      </c>
+      <c r="D405" s="28" t="s">
+        <v>3967</v>
+      </c>
+      <c r="E405" t="s">
+        <v>233</v>
+      </c>
+      <c r="F405" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I405" t="s">
+        <v>3968</v>
+      </c>
+      <c r="J405" t="s">
+        <v>3969</v>
+      </c>
+      <c r="K405" t="s">
+        <v>3970</v>
+      </c>
+      <c r="M405" t="s">
+        <v>3971</v>
+      </c>
+      <c r="O405" t="s">
+        <v>3972</v>
+      </c>
+      <c r="P405" t="s">
+        <v>3973</v>
+      </c>
+    </row>
+    <row r="406" ht="16.5" spans="2:16">
+      <c r="B406" s="34" t="s">
+        <v>3974</v>
+      </c>
+      <c r="C406" s="1">
+        <v>84639</v>
+      </c>
+      <c r="D406" s="28" t="s">
+        <v>3975</v>
+      </c>
+      <c r="E406" t="s">
+        <v>233</v>
+      </c>
+      <c r="F406" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I406" t="s">
+        <v>3976</v>
+      </c>
+      <c r="J406" t="s">
+        <v>3977</v>
+      </c>
+      <c r="K406" t="s">
+        <v>3978</v>
+      </c>
+      <c r="M406" t="s">
+        <v>3979</v>
+      </c>
+      <c r="O406" t="s">
+        <v>3980</v>
+      </c>
+      <c r="P406" t="s">
+        <v>3981</v>
+      </c>
+    </row>
+    <row r="407" ht="16.5" spans="2:16">
+      <c r="F407" s="4"/>
+    </row>
+    <row r="408" ht="16.5" spans="2:16">
+      <c r="F408" s="4"/>
+    </row>
+    <row r="409" ht="16.5" spans="2:16">
+      <c r="F409" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/uploads/网站信息.xlsx
+++ b/uploads/网站信息.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5392" uniqueCount="3982">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6269" uniqueCount="4617">
   <si>
     <t>分类</t>
   </si>
@@ -10933,7 +10933,7 @@
     <t>217 Buist Ave, Greenville, SC 29609</t>
   </si>
   <si>
-    <t>coopcraft.com</t>
+    <t>coopcraftt.com</t>
   </si>
   <si>
     <t>Handcrafted Cedar Chicken Coops &amp; Poultry Supplies</t>
@@ -12389,6 +12389,1911 @@
   </si>
   <si>
     <t>toilet tank parts, toilet tank, toilet flush valve, toilet fill valve, toilet flapper, toilet repair kit, toilet tank lid, toilet tank bolts, toilet tank gasket, toilet tank replacement, toilet tank fittings, toilet tank lever, toilet fill valve assembly, toilet flush valve seal, toilet tank flush valve, toilet parts</t>
+  </si>
+  <si>
+    <t>87730,87731,87732,87733,87734,87735,87736</t>
+  </si>
+  <si>
+    <t>87728</t>
+  </si>
+  <si>
+    <t>Arts &amp; Entertainment|||Art &amp; Craft Kit</t>
+  </si>
+  <si>
+    <t>11664 Avenida Marcella, El Cajon, CA 92019</t>
+  </si>
+  <si>
+    <t>kitcurator.com</t>
+  </si>
+  <si>
+    <t>Kit Curator: Art &amp; Craft Kits for Makers</t>
+  </si>
+  <si>
+    <t>The selection is unusually deep in art and craft kits, from rubber stamps and shibori supplies to pottery glazes and embroidery floss. It serves makers and teachers who want precise materials.</t>
+  </si>
+  <si>
+    <t>Art and craft kits and supplies</t>
+  </si>
+  <si>
+    <t>art and craft kits, craft kits for adults, diy art and craft kits, craft supplies for makers, raw world coins, sewing and quilt patterns, rubber stamps for crafting, pottery glazes for ceramics, embroidery floss and thread, shibori craft supplies, limited edition art prints</t>
+  </si>
+  <si>
+    <t>87697,87698,87699,87700,87701,87702,87703</t>
+  </si>
+  <si>
+    <t>87696</t>
+  </si>
+  <si>
+    <t>Arts &amp; Entertainment|||Art &amp; Crafting Materials</t>
+  </si>
+  <si>
+    <t>4150 Amaretto Way, Spring Valley, CA 91977</t>
+  </si>
+  <si>
+    <t>artthreadd.com</t>
+  </si>
+  <si>
+    <t>Artthread: Arts &amp; Entertainment and Crafting Materials</t>
+  </si>
+  <si>
+    <t>For families who make things by hand, we've picked art and craft materials, fabric, paints, and tools for real projects, not trends, from our small family shop.</t>
+  </si>
+  <si>
+    <t>arts, crafts, and original artwork</t>
+  </si>
+  <si>
+    <t>arts and entertainment supplies, art and crafting materials, original artwork for sale, digital artwork downloads, craft supplies for adults, fabric by the yard, paint brushes and paints, collage sheets for journaling, sewing machines for beginners, trophy and award supplies, limited edition mixed media sculptures</t>
+  </si>
+  <si>
+    <t>87706,87708,87709,87711,87712,87713,87715</t>
+  </si>
+  <si>
+    <t>87704</t>
+  </si>
+  <si>
+    <t>Arts &amp; Entertainment|||Cardboard Cutout</t>
+  </si>
+  <si>
+    <t>4460 Altadena Ave., San Diego, CA 92115</t>
+  </si>
+  <si>
+    <t>cardboardcutoutl.com</t>
+  </si>
+  <si>
+    <t>Cardboard Cutouts for Events, Photos &amp; Displays</t>
+  </si>
+  <si>
+    <t>17,000+ cardboard cutouts in stock for teachers, event planners, and photo booths. Second-generation family shop.</t>
+  </si>
+  <si>
+    <t>Cardboard cutouts and art supplies</t>
+  </si>
+  <si>
+    <t>cardboard cutouts, life size cardboard cutouts, custom cardboard cutouts, cardboard standees, cardboard cutout props, movie cardboard cutouts, celebrity cardboard cutouts, animal cardboard cutouts, party cardboard cutouts, photo booth cardboard cutouts, cardboard cutout decorations</t>
+  </si>
+  <si>
+    <t>87718,87720,87721,87722,87724,87725,87727</t>
+  </si>
+  <si>
+    <t>87717</t>
+  </si>
+  <si>
+    <t>Arts &amp; Entertainment|||Movie Framed Art</t>
+  </si>
+  <si>
+    <t>6044 Lawson Way, Riverside, CA 92506</t>
+  </si>
+  <si>
+    <t>celluframe.com</t>
+  </si>
+  <si>
+    <t>Movie Framed Art in Archival Wood and Glass</t>
+  </si>
+  <si>
+    <t>For film lovers and collectors, we've picked framed movie art and cinema prints for bulk-minded walls.</t>
+  </si>
+  <si>
+    <t>Framed movie art and cinema wall prints</t>
+  </si>
+  <si>
+    <t>framed movie art, movie framed art, framed movie posters, cinema wall art, film framed prints, bulk framed movie art, classic film framed art, movie room wall decor, framed film posters</t>
+  </si>
+  <si>
+    <t>87738,87739,87740,87741,87742,87743,87744</t>
+  </si>
+  <si>
+    <t>87737</t>
+  </si>
+  <si>
+    <t>Arts &amp; Entertainment|||Movie Unframed Art</t>
+  </si>
+  <si>
+    <t>432 N Lamer St, Burbank, CA 91506</t>
+  </si>
+  <si>
+    <t>reelprintf.com</t>
+  </si>
+  <si>
+    <t>ReelPrint: Movie Unframed Art Bulk Packs</t>
+  </si>
+  <si>
+    <t>Restoring a theater room or filling resale bins? We stock unframed movie art in bulk lots, with clear print sizes, paper specs, and per-unit pricing.</t>
+  </si>
+  <si>
+    <t>Movie unframed art and bulk poster prints</t>
+  </si>
+  <si>
+    <t>movie unframed art, unframed movie art prints, bulk movie posters, movie art prints bulk, unframed film art, movie poster lots, cinema wall art prints, classic movie art prints, budget movie wall art, unframed movie poster set, movie artwork bulk pack</t>
+  </si>
+  <si>
+    <t>87746,87747,87748,87749,87750,87751,87752</t>
+  </si>
+  <si>
+    <t>87745</t>
+  </si>
+  <si>
+    <t>Arts &amp; Entertainment|||Needlecraft Kits</t>
+  </si>
+  <si>
+    <t>6312 Bakman Ave, North Hollywood, CA 91606</t>
+  </si>
+  <si>
+    <t>stitchkiny.com</t>
+  </si>
+  <si>
+    <t>Stitch Your Next Project: Needlecraft Kits for Every Level</t>
+  </si>
+  <si>
+    <t>The selection runs unusually deep in needlecraft kits, with embroidery, cross-stitch, felt, and beginner projects for hobbyists, gift makers, and crafters who like a challenge.</t>
+  </si>
+  <si>
+    <t>Needlecraft kits and stitching supplies</t>
+  </si>
+  <si>
+    <t>needlecraft kits, embroidery kits, cross stitch kits, needlecraft patterns, craft supplies, craft kits, art prints, paint by number kits, resin crafts, watercolor paper, fabric, zippers, autograph memorabilia, football art, music canvas art, acrylic plaques</t>
+  </si>
+  <si>
+    <t>87754,87755,87756,87757,87758,87759,87760</t>
+  </si>
+  <si>
+    <t>87753</t>
+  </si>
+  <si>
+    <t>Arts &amp; Entertainment|||Yarn</t>
+  </si>
+  <si>
+    <t>157 N 12th St, San Jose, CA 95112</t>
+  </si>
+  <si>
+    <t>yarncraftworks.com</t>
+  </si>
+  <si>
+    <t>Yarn and Craft Supplies for Trade and Repair Pros</t>
+  </si>
+  <si>
+    <t>Yarn, craft supplies, and art materials are stocked unusually deep for trade contractors and repair professionals.</t>
+  </si>
+  <si>
+    <t>Yarn, craft and art supplies</t>
+  </si>
+  <si>
+    <t>yarn, craft supplies, art supplies, greeting cards, artwork, sewing patterns, ribbons, glass precuts, gift sets, stretcher bars, kilns, pattern downloads, quote prints, glitter, half yard bundles, gouache</t>
+  </si>
+  <si>
+    <t>89715,89716,89717,89718,89719,89720,89721,89722,89723,89724</t>
+  </si>
+  <si>
+    <t>89714</t>
+  </si>
+  <si>
+    <t>Arts &amp; Crafts|||Appliques &amp; Patches</t>
+  </si>
+  <si>
+    <t>1108 W 110th St, Chicago, IL 60643</t>
+  </si>
+  <si>
+    <t>craftcutworks.com</t>
+  </si>
+  <si>
+    <t>Die-Cutting Supplies - CraftCut Works</t>
+  </si>
+  <si>
+    <t>Die-cutting tools, embossing folders, and steel-rule dies serve scrapbookers and card makers. Appliques, patches, and sewing patterns support fabric crafters. Art and crafting materials, yarn, and yardage extend the catalog. Orders ship promptly to US addresses.</t>
+  </si>
+  <si>
+    <t>Die-cutting machines, dies, appliques, patches, and art crafting materials</t>
+  </si>
+  <si>
+    <t>die cutting supplies, embossing folders, steel rule dies, appliques patches, sewing patterns, art crafting materials, scrapbooking dies</t>
+  </si>
+  <si>
+    <t>89737,89738,89739,89740,89741,89742,89743,89744,89745,89746</t>
+  </si>
+  <si>
+    <t>89736</t>
+  </si>
+  <si>
+    <t>Arts &amp; Crafts|||Craft Patterns</t>
+  </si>
+  <si>
+    <t>642 Siena Way, Los Angeles, CA 90077</t>
+  </si>
+  <si>
+    <t>stitchcraftyard.com</t>
+  </si>
+  <si>
+    <t>Craft Patterns, Bulk Supplies in Los Angeles</t>
+  </si>
+  <si>
+    <t>Doll clothes, baby knit, and women's top patterns withstand repeated use in busy studios. Woodworking plans and paper crafts cover the making side, while beads and crystals support jewelry projects. Orders ship promptly from Los Angeles.</t>
+  </si>
+  <si>
+    <t>Bulk craft patterns and art supplies for budget-minded makers</t>
+  </si>
+  <si>
+    <t>craft patterns, doll clothes patterns, baby knit patterns, women top pattern, woodworking plans, paper crafts, artwork, art and craft materials, beads, crystals, glitter, stencils, cutting dies, embroidery floss, fabric</t>
+  </si>
+  <si>
+    <t>89759,89760,89761,89762,89763,89764,89765,89766,89767,89768</t>
+  </si>
+  <si>
+    <t>89758</t>
+  </si>
+  <si>
+    <t>Arts &amp; Crafts|||Knitting &amp; Crochet</t>
+  </si>
+  <si>
+    <t>1613 Flower Garden Ln, San Jose, CA 95124</t>
+  </si>
+  <si>
+    <t>stitchloomery.com</t>
+  </si>
+  <si>
+    <t>Knitting &amp; Crochet Supplies for Practical Makers</t>
+  </si>
+  <si>
+    <t>Worsted-weight yarns and ergonomic hooks anchor the knitting and crochet line. Pattern books, fabric bolts, and paint sets extend the craft supply range. Orders ship within two days from San Jose.</t>
+  </si>
+  <si>
+    <t>Knitting and crochet supplies with artwork and craft materials</t>
+  </si>
+  <si>
+    <t>knitting supplies, crochet hooks, yarn, knitting patterns, crochet patterns, craft supplies, artwork, fabric, paint, needlecraft, knitting needles, crochet yarn, craft kits, art materials</t>
+  </si>
+  <si>
+    <t>89726,89727,89728,89729,89730,89731,89732,89733,89734,89735</t>
+  </si>
+  <si>
+    <t>89725</t>
+  </si>
+  <si>
+    <t>Arts &amp; Entertainment ||| Art Kit</t>
+  </si>
+  <si>
+    <t>5625 Arbor Dell Way, San Jose, CA 95124</t>
+  </si>
+  <si>
+    <t>stitchandspool.com</t>
+  </si>
+  <si>
+    <t>Art Kits &amp; Craft Supplies, San Jose</t>
+  </si>
+  <si>
+    <t>Cotton, linen, and rayon fabrics anchor the sewing side, with patterns, notions, and embroidery designs close behind. Paint, stamps, yarn, and bead packs cover mixed-media projects. Balloon decor and digital art files extend the range. Orders ship from San Jose within two business days.</t>
+  </si>
+  <si>
+    <t>Art kits, fabrics, yarn, and crafting supplies for hands-on makers</t>
+  </si>
+  <si>
+    <t>art kits, sewing fabrics, embroidery designs, craft paint, yarn supplies, bead packs, stamps, balloon decor</t>
+  </si>
+  <si>
+    <t>89704,89705,89706,89707,89708,89709,89710,89711,89712,89713</t>
+  </si>
+  <si>
+    <t>89703</t>
+  </si>
+  <si>
+    <t>Arts &amp; Entertainment|||Cloth</t>
+  </si>
+  <si>
+    <t>430 Malay Dr, Sacramento, CA 95841</t>
+  </si>
+  <si>
+    <t>clothcraftia.com</t>
+  </si>
+  <si>
+    <t>Quilting Fabrics &amp; Kits, Sacramento</t>
+  </si>
+  <si>
+    <t>From fat quarters to yardage, quilting cottons, flannels, and batiks in dozens of prints. Thread, notions, and patterns support every stitch. Die cuts and cardstock add a paper-craft side. Orders ship promptly from California.</t>
+  </si>
+  <si>
+    <t>Specialty fabrics, quilting kits, and craft supplies for textile artists</t>
+  </si>
+  <si>
+    <t>quilting fabric, quilting kits, fabric by the yard, fat quarters, cotton fabric, flannel fabric, batik fabric, sewing notions, quilting patterns, thread, die cuts, cardstock, craft supplies, apparel fabric, clear stamps</t>
+  </si>
+  <si>
+    <t>89748,89749,89750,89751,89752,89753,89754,89755,89756,89757</t>
+  </si>
+  <si>
+    <t>89747</t>
+  </si>
+  <si>
+    <t>Arts &amp; Entertainment|||Embroidery Add-Ons</t>
+  </si>
+  <si>
+    <t>1278, 1280 47th Ave, San Francisco, CA 94122</t>
+  </si>
+  <si>
+    <t>stitchfount.com</t>
+  </si>
+  <si>
+    <t>Embroidery Add-Ons: Threads, Patterns, and Tools</t>
+  </si>
+  <si>
+    <t>Embroidery add-ons supply threads, patterns, and stabilizers for needleworkers. Sashiko and sewing threads cover the stitch range, while cross stitch patterns guide detailed projects. Leather craft tools also serve the wider craft trade, and orders ship with precise material counts.</t>
+  </si>
+  <si>
+    <t>Embroidery supplies and add-ons for detailed needlework</t>
+  </si>
+  <si>
+    <t>embroidery threads, cross stitch patterns, sashiko thread, embroidery kits, sewing thread, embroidery stabilizers, needlework supplies, craft tools</t>
+  </si>
+  <si>
+    <t>89770,89771,89772,89773,89774,89775,89776,89777,89778,89779</t>
+  </si>
+  <si>
+    <t>89769</t>
+  </si>
+  <si>
+    <t>Arts &amp; Entertainment|||Self Strip Yarn</t>
+  </si>
+  <si>
+    <t>4940 Hamilton St, Sacramento, CA 95841</t>
+  </si>
+  <si>
+    <t>strandloom.com</t>
+  </si>
+  <si>
+    <t>Self Strip Yarn, Craft Supplies in Sacramento</t>
+  </si>
+  <si>
+    <t>Self strip yarn anchors a deep catalog spanning fabrics, quick kits, record awards, and PDF sewing patterns. Handcrafts, buttons, stencils, and gemstone beads serve detailed makers. Paint and model supplies, plus piano accessories, extend the range. Orders ship promptly from Sacramento.</t>
+  </si>
+  <si>
+    <t>Self Strip Yarn and Arts &amp; Entertainment Supplies</t>
+  </si>
+  <si>
+    <t>self strip yarn, fabrics, quick kits, record award, art craft, notions, pdf sewing patterns, paint model supplies, buttons, art prints, stencils, gemstone beads, handcrafts, christmas cards</t>
+  </si>
+  <si>
+    <t>89781,89782,89783,89784,89785,89786,89787,89788,89789,89790</t>
+  </si>
+  <si>
+    <t>89780</t>
+  </si>
+  <si>
+    <t>Home &amp; Garden|||Trinket Box</t>
+  </si>
+  <si>
+    <t>5616 Rudy Dr, San Jose, CA 95124</t>
+  </si>
+  <si>
+    <t>tinytreasureshome.com</t>
+  </si>
+  <si>
+    <t>Trinket Boxes and Keepsake Plaques: Handpicked Home Accents</t>
+  </si>
+  <si>
+    <t>Keepsake trinket boxes, decorative plaques, and hanging ornaments anchor the collection. Flatware and bakeware serve everyday tables, while vase selections brighten mantels. Orders ship promptly from San Jose with careful packing.</t>
+  </si>
+  <si>
+    <t>Plaques, flatware, hanging ornaments, trinket boxes, box signs, vases, and bakeware</t>
+  </si>
+  <si>
+    <t>trinket boxes, decorative plaques, hanging ornaments, box signs, keepsake boxes, flatware sets, bakeware, vase decor, home accents, gift trinket boxes</t>
+  </si>
+  <si>
+    <t>89935,89936,89937,89938,89939,89940,89941,89942,89943,89944</t>
+  </si>
+  <si>
+    <t>89934</t>
+  </si>
+  <si>
+    <t>Media|||Pre-Owned DVD</t>
+  </si>
+  <si>
+    <t>4261 W 76th St, Chicago, IL 60652</t>
+  </si>
+  <si>
+    <t>useddvdvault.com</t>
+  </si>
+  <si>
+    <t>Pre-Owned DVD Collection for Film Enthusiasts</t>
+  </si>
+  <si>
+    <t>Criterion editions and cult horror discs anchor a deep pre-owned DVD catalog, with box sets and rare imports spanning every genre. Music CDs and vinyl records sit alongside the film library. Orders ship from Chicago within two business days.</t>
+  </si>
+  <si>
+    <t>Pre-Owned DVDs and Related Media</t>
+  </si>
+  <si>
+    <t>pre-owned dvd, used dvd, criterion collection, cult horror dvd, dvd box set, rare dvd, import dvd, classic film dvd, tv series dvd, music cd, vinyl record, used vinyl, punk lp, music cassette, sealed cd, remastered vinyl</t>
+  </si>
+  <si>
+    <t>89858,89859,89860,89861,89862,89863,89864,89865,89866,89867</t>
+  </si>
+  <si>
+    <t>89857</t>
+  </si>
+  <si>
+    <t>Media|||Rock</t>
+  </si>
+  <si>
+    <t>4641 Norris Ave, Sacramento, CA 95841</t>
+  </si>
+  <si>
+    <t>rockpressings.com</t>
+  </si>
+  <si>
+    <t>Rock Media Pressings for Collectors and Audiophiles</t>
+  </si>
+  <si>
+    <t>A 180-gram reissue of Led Zeppelin IV anchors a rock media selection spanning vinyl LPs, picture discs, and 45s. Used pressings and import titles broaden the catalog, while Music CDs and comic books cover adjacent listening and reading habits. Every order ships from Sacramento with protective mailers.</t>
+  </si>
+  <si>
+    <t>Rock music media on vinyl, CD, and cassette</t>
+  </si>
+  <si>
+    <t>rock vinyl records, rock music cds, picture disc rock albums, used rock 45s, import rock pressings, audiophile rock lps, rock record store, collectible rock media, 180 gram rock vinyl</t>
+  </si>
+  <si>
+    <t>89902,89903,89904,89905,89906,89907,89908,89909,89910,89911</t>
+  </si>
+  <si>
+    <t>89901</t>
+  </si>
+  <si>
+    <t>Media|||Single Vinyl</t>
+  </si>
+  <si>
+    <t>2474 Twyla Ct, San Jose, CA 95008</t>
+  </si>
+  <si>
+    <t>spindleharbor.com</t>
+  </si>
+  <si>
+    <t>Single Vinyl: Rare 45s and 7-Inch Pressings</t>
+  </si>
+  <si>
+    <t>Single vinyl records endure the test of time, offering the raw sound of 45s and 7-inch pressings. The catalog covers rock, pop, reggae, and RSD releases, plus gatefold LPs and folio editions. Orders ship from San Jose within two days.</t>
+  </si>
+  <si>
+    <t>Single vinyl records and accessories for collectors</t>
+  </si>
+  <si>
+    <t>single vinyl records, 45 rpm records, 7 inch vinyl, vinyl accessories, record store day releases, gatefold vinyl records, rock pop LP, music CDs, vinyl cleaning supplies, vinyl storage sleeves</t>
+  </si>
+  <si>
+    <t>89880,89881,89882,89883,89884,89885,89886,89887,89888,89889</t>
+  </si>
+  <si>
+    <t>89879</t>
+  </si>
+  <si>
+    <t>Media|||Soundtrack LP</t>
+  </si>
+  <si>
+    <t>1792 Wynkoop St, Denver, CO 80202</t>
+  </si>
+  <si>
+    <t>soundtracklpshop.com</t>
+  </si>
+  <si>
+    <t>Soundtrack LP Records for Film and TV Fans</t>
+  </si>
+  <si>
+    <t>Film score vinyl and original cast recordings fill the shelves, from classic Hollywood scores to modern TV themes. Music cassettes and record sleeves also sit in the bins. Orders ship quickly from Denver, with careful packing for collectors.</t>
+  </si>
+  <si>
+    <t>Soundtrack LP records and soundtracks</t>
+  </si>
+  <si>
+    <t>soundtrack lp, soundtrack vinyl, film score vinyl, movie soundtrack records, tv soundtrack lp, original cast recording, vinyl soundtrack, soundtrack record, soundtrack lp for sale, classic film score lp, new soundtrack vinyl, used soundtrack lp</t>
+  </si>
+  <si>
+    <t>89924,89925,89926,89927,89928,89929,89930,89931,89932,89933</t>
+  </si>
+  <si>
+    <t>89923</t>
+  </si>
+  <si>
+    <t>Media|||Triple Vinyl</t>
+  </si>
+  <si>
+    <t>4095 Keith Dr, San Jose, CA 95008</t>
+  </si>
+  <si>
+    <t>spinwelley.com</t>
+  </si>
+  <si>
+    <t>Triple Vinyl - Spinwell</t>
+  </si>
+  <si>
+    <t>Triple vinyl box sets, rare pressings, and classic LPs fill the shelves here. The catalog spans new releases, reissues, and used records, with CDs and cassettes for those who prefer other formats. Orders ship promptly from a dedicated hobbyist-run shop.</t>
+  </si>
+  <si>
+    <t>Triple vinyl and vintage vinyl records for collectors</t>
+  </si>
+  <si>
+    <t>triple vinyl, vinyl records, LP records, used vinyl, reissue vinyl, music CDs, music cassettes, record store day 2025</t>
+  </si>
+  <si>
+    <t>89891,89892,89893,89894,89895,89896,89897,89898,89899,89900</t>
+  </si>
+  <si>
+    <t>89890</t>
+  </si>
+  <si>
+    <t>Media|||Used 45 RPM 7" Vinyl</t>
+  </si>
+  <si>
+    <t>7110 E Montview Blvd, Denver, CO 80220</t>
+  </si>
+  <si>
+    <t>spindleden.com</t>
+  </si>
+  <si>
+    <t>Used 45 RPM 7\" Vinyl: Deep Cuts &amp; Rarities</t>
+  </si>
+  <si>
+    <t>A scratched-free copy of The Beatles' \"Hey Jude\" 45 opens a trove of vintage seven-inch singles spanning pop, soul, and garage rock. Metal 45s from obscure punk labels also surface here. Pre-owned albums and 7\" picture sleeves share shelf space with music memorabilia, and orders ship from Denver.</t>
+  </si>
+  <si>
+    <t>Used 45 RPM 7-inch vinyl records and more</t>
+  </si>
+  <si>
+    <t>used 45 rpm 7 inch vinyl, vintage 45 records, rare 45 singles, pre-owned vinyl records, 7 inch picture sleeves, collectible 45 rpm, oldies 45s, garage rock 45s, soul 45 records</t>
+  </si>
+  <si>
+    <t>89825,89826,89827,89828,89829,89830,89831,89832,89833,89834</t>
+  </si>
+  <si>
+    <t>89824</t>
+  </si>
+  <si>
+    <t>Media|||Vintage Vinyl Records</t>
+  </si>
+  <si>
+    <t>1740 N Pontiac St, Denver, CO 80220</t>
+  </si>
+  <si>
+    <t>grooveweave.com</t>
+  </si>
+  <si>
+    <t>Vintage Vinyl Records - Grooveweave</t>
+  </si>
+  <si>
+    <t>Vinyl records span jazz, funk, soul, and indie pressings in sealed and used condition. Music CDs and cassettes accompany the main catalog. Orders ship from Denver with careful packing and grading notes.</t>
+  </si>
+  <si>
+    <t>Vintage vinyl records, sealed LPs, jazz pressings, and used records</t>
+  </si>
+  <si>
+    <t>vinyl records, vintage vinyl, sealed vinyl, jazz vinyl, used vinyl, records and lps, vinyl lp, music cds, music cassettes, funk and soul music, indie music, vinyl box set, pre-order vinyl, records</t>
+  </si>
+  <si>
+    <t>89946,89947,89948,89949,89950,89951,89952,89953,89954,89955</t>
+  </si>
+  <si>
+    <t>89945</t>
+  </si>
+  <si>
+    <t>Music &amp; Sound Recording|||Colored Vinyl Records</t>
+  </si>
+  <si>
+    <t>2570 N Monaco Street Pkwy, Denver, CO 80207</t>
+  </si>
+  <si>
+    <t>vinylcellarco.com</t>
+  </si>
+  <si>
+    <t>Colored Vinyl Records &amp; Sound Recordings</t>
+  </si>
+  <si>
+    <t>Heavy 180-gram colored vinyl records spin in every shade from marbled splatter to translucent sunburst. Used pressings and sealed originals share shelf space with soundtracks and metal rarities. CDs, cassettes, and SACDs sit alongside for the full listening room.</t>
+  </si>
+  <si>
+    <t>Colored vinyl records and sound recordings</t>
+  </si>
+  <si>
+    <t>colored vinyl records, vinyl records, sealed vinyl records, used vinyl records, soundtracks, metal vinyl records, 180 gram vinyl, splatter vinyl, translucent vinyl, marble vinyl, music cds, music cassettes, sacd discs, vintage vinyl records</t>
+  </si>
+  <si>
+    <t>89847,89848,89849,89850,89851,89852,89853,89854,89855,89856</t>
+  </si>
+  <si>
+    <t>89846</t>
+  </si>
+  <si>
+    <t>Music &amp; Sound Recording|||Folk &amp; Americana Music</t>
+  </si>
+  <si>
+    <t>10917 S Racine Ave, Chicago, IL 60643</t>
+  </si>
+  <si>
+    <t>hollowgroove.com</t>
+  </si>
+  <si>
+    <t>Folk &amp; Americana Records with Rare Pressings</t>
+  </si>
+  <si>
+    <t>Late-night listening sessions find folk and Americana vinyl, cassettes, and CDs spanning decades of songwriting. Sheet music and songbooks for the home player join the catalog. Orders ship within two days, packed with care for safe arrival.</t>
+  </si>
+  <si>
+    <t>Folk and Americana vinyl, cassettes, and CDs</t>
+  </si>
+  <si>
+    <t>folk vinyl records, americana cassettes, folk cds, vinyl records, cassette tapes, americana music, sheet music songbooks, rare folk pressings</t>
+  </si>
+  <si>
+    <t>89792,89793,89794,89795,89796,89797,89798,89799,89800,89801</t>
+  </si>
+  <si>
+    <t>89791</t>
+  </si>
+  <si>
+    <t>Music &amp; Sound Recording|||Jazz Music</t>
+  </si>
+  <si>
+    <t>4230 Carle Ln., Sacramento, CA 95841</t>
+  </si>
+  <si>
+    <t>groovepressings.com</t>
+  </si>
+  <si>
+    <t>Jazz Vinyl Records: Pressings for True Collectors</t>
+  </si>
+  <si>
+    <t>Pressed jazz vinyl and mint-condition CDs anchor the collection, with rare mono editions drawing serious listeners. Backing tracks and vintage pressings broaden the shelf for practicing musicians. Orders ship from Sacramento within two days.</t>
+  </si>
+  <si>
+    <t>Jazz vinyl records, CDs, and music for collectors</t>
+  </si>
+  <si>
+    <t>jazz vinyl records, rare jazz pressings, jazz CDs for collectors, mono jazz editions, vintage jazz vinyl, jazz music collection, jazz record store, used jazz LPs, jazz backing tracks</t>
+  </si>
+  <si>
+    <t>89814,89815,89816,89817,89818,89819,89820,89821,89822,89823</t>
+  </si>
+  <si>
+    <t>89813</t>
+  </si>
+  <si>
+    <t>Music &amp; Sound Recording|||K-Pop Albums</t>
+  </si>
+  <si>
+    <t>1720 Wazee St, Denver, CO 80202</t>
+  </si>
+  <si>
+    <t>groovevaultt.com</t>
+  </si>
+  <si>
+    <t>K-Pop Albums: Groove Vault for Collectors</t>
+  </si>
+  <si>
+    <t>Pressed vinyl and glossy K-pop album sleeves fill the shelves, with instrumental tracks for study sessions. CDs and pre-owned records sit nearby for budget diggers. Orders ship from Denver in sturdy mailers.</t>
+  </si>
+  <si>
+    <t>K-pop albums and vinyl records</t>
+  </si>
+  <si>
+    <t>k-pop albums, vinyl records, instrumental music, k-pop cds, lp records, used vinyl, record store day, k-pop photobooks, k-pop merch, r&amp;b vinyl, pre-owned cds, vocal guide tracks, k-pop imports, audiophile vinyl</t>
+  </si>
+  <si>
+    <t>89803,89804,89805,89806,89807,89808,89809,89810,89811,89812</t>
+  </si>
+  <si>
+    <t>89802</t>
+  </si>
+  <si>
+    <t>Music &amp; Sound Recording|||Punk &amp; Hardcore Music</t>
+  </si>
+  <si>
+    <t>1641 Orchard View Dr, San Jose, CA 95124</t>
+  </si>
+  <si>
+    <t>groovepressvinyl.com</t>
+  </si>
+  <si>
+    <t>Vinyl Records: Punk, Hardcore, and Pressing Plant Finds</t>
+  </si>
+  <si>
+    <t>Punk and hardcore vinyl pressings anchor the catalog, from 7-inch singles to full-length LPs. CDs and cassettes cover the same aggressive spectrum. Turntable accessories and second-hand records extend the listening setup. Orders ship from San Jose with protective mailers.</t>
+  </si>
+  <si>
+    <t>Punk and hardcore vinyl records, CDs, and sound recording media</t>
+  </si>
+  <si>
+    <t>punk vinyl records, hardcore vinyl, punk rock LPs, hardcore 7 inch, punk CDs, hardcore CDs, vinyl records, second hand vinyl, music cassettes, record players, turntable accessories, compilation vinyl</t>
+  </si>
+  <si>
+    <t>89836,89837,89838,89839,89840,89841,89842,89843,89844,89845</t>
+  </si>
+  <si>
+    <t>89835</t>
+  </si>
+  <si>
+    <t>Music &amp; Sound Recording|||R&amp;B Music</t>
+  </si>
+  <si>
+    <t>6700 S Keating Ave, Chicago, IL 60629</t>
+  </si>
+  <si>
+    <t>grooveyardvinyl.com</t>
+  </si>
+  <si>
+    <t>Vinyl Records, Chicago Family-Run Record Shop</t>
+  </si>
+  <si>
+    <t>Turntables spin rock, R&amp;B, and handbell music in a Chicago living room. Sealed vinyl, vocal records, and CDs fill the shelves. Paperback books and sheet music sit nearby. Orders ship from 6700 S Keating Ave.</t>
+  </si>
+  <si>
+    <t>Vinyl records and music for collectors and listeners</t>
+  </si>
+  <si>
+    <t>vinyl records, sealed vinyl records, rock music, r&amp;b music, handbell music, vocal music, lp, music cds, records and lps, sheet music, paperback books, hardcover books, music, vinyl</t>
+  </si>
+  <si>
+    <t>89869,89870,89871,89872,89873,89874,89875,89876,89877,89878</t>
+  </si>
+  <si>
+    <t>89868</t>
+  </si>
+  <si>
+    <t>Music &amp; Sound Recording|||Reggae Music</t>
+  </si>
+  <si>
+    <t>11000 Weyburn Dr, Los Angeles, CA 90024</t>
+  </si>
+  <si>
+    <t>rootsvinylsounds.com</t>
+  </si>
+  <si>
+    <t>Reggae Vinyl Records, CDs, and Cassettes</t>
+  </si>
+  <si>
+    <t>Reggae vinyl records in 7-inch, 10-inch, and 12-inch pressings anchor the catalog. Rock music CDs and used vinyl fill out the shelves. Cassettes and picture discs cover the analog side, with orders shipped in sturdy mailers.</t>
+  </si>
+  <si>
+    <t>Reggae and rock vinyl records, CDs, and music media</t>
+  </si>
+  <si>
+    <t>reggae vinyl records, reggae CDs, rock music vinyl, used vinyl records, music cassettes, picture discs, LP records, reggae music</t>
+  </si>
+  <si>
+    <t>89913,89914,89915,89916,89917,89918,89919,89920,89921,89922</t>
+  </si>
+  <si>
+    <t>89912</t>
+  </si>
+  <si>
+    <t>Rap|||Hip-Hop LP</t>
+  </si>
+  <si>
+    <t>4551 Summit Way, Sacramento, CA 95820</t>
+  </si>
+  <si>
+    <t>spinwaxworks.com</t>
+  </si>
+  <si>
+    <t>Rap Hip-Hop LP: Deep-Cut Vinyl Pressings</t>
+  </si>
+  <si>
+    <t>Rap and hip-hop LP pressings endure heavy rotation, from golden-era 12-inches to modern double-LP sets. Used and new vinyl covers breakbeats, conscious rap, and underground tapes. Music CDs and cassettes fill the archival side. Orders ship from Sacramento within two days.</t>
+  </si>
+  <si>
+    <t>Rap and hip-hop LP records</t>
+  </si>
+  <si>
+    <t>rap hip hop lp, hip hop vinyl records, rap vinyl 12 inch, underground rap lp, golden era hip hop records, used vinyl records, new lp records, double vinyl hip hop, breakbeat records, conscious rap vinyl, rap music cds, hip hop cassettes, media vinyl lp, vinyl records for dj</t>
+  </si>
+  <si>
+    <t>90133,90134,90135,90136,90137,90138,90139,90140,90141,90142</t>
+  </si>
+  <si>
+    <t>90132</t>
+  </si>
+  <si>
+    <t>Model Railroads|||HO Scale Structures</t>
+  </si>
+  <si>
+    <t>2135 Tremont Pl, Denver, CO 80205</t>
+  </si>
+  <si>
+    <t>trackshadeworks.com</t>
+  </si>
+  <si>
+    <t>HO Scale Structures, Trackwork &amp; Scenery Supplies</t>
+  </si>
+  <si>
+    <t>HO scale laser-cut wood kits, injection-molded plastic storefronts, and resin-cast details span every era from steam to modern. Diecast vehicles and slot car racing sets add motion. Orders ship within 24 hours from Denver.</t>
+  </si>
+  <si>
+    <t>HO scale model railroad structures and accessories</t>
+  </si>
+  <si>
+    <t>ho scale structures, model railroad buildings, laser cut wood kits, resin cast details, ho scale scenery, model train accessories, scale model storefronts</t>
+  </si>
+  <si>
+    <t>90144,90145,90146,90147,90148,90149,90150,90151,90152,90153</t>
+  </si>
+  <si>
+    <t>90143</t>
+  </si>
+  <si>
+    <t>Puzzles|||Twist &amp; Turn Puzzles</t>
+  </si>
+  <si>
+    <t>1270, 1272 47th Ave, San Francisco, CA 94122</t>
+  </si>
+  <si>
+    <t>twistlattice.com</t>
+  </si>
+  <si>
+    <t>Twist &amp; Turn Puzzles - Lattice</t>
+  </si>
+  <si>
+    <t>Rubik's cubes, gear balls, and skewb puzzles anchor a deep twist-and-turn collection. Speed cubes with magnetic cores serve competitive solvers, while beginner-friendly 2x2 models ease newcomers in. Puzzle keychains and mini cubes add pocket-sized fun.</t>
+  </si>
+  <si>
+    <t>Twist &amp; turn puzzles for every age and skill level</t>
+  </si>
+  <si>
+    <t>twist puzzles, speed cubes, rubik's cube, gear ball puzzle, skewb puzzle, magnetic speed cube, 2x2 cube, puzzle keychain, twist and turn brain teasers, fidget puzzles</t>
+  </si>
+  <si>
+    <t>90100,90101,90102,90103,90104,90105,90106,90107,90108,90109</t>
+  </si>
+  <si>
+    <t>90099</t>
+  </si>
+  <si>
+    <t>Puzzles|||Wooden Puzzles</t>
+  </si>
+  <si>
+    <t>14115 Kelann Ct, Dallas, TX 75253</t>
+  </si>
+  <si>
+    <t>puzzlecraftworks.com</t>
+  </si>
+  <si>
+    <t>Wooden Puzzles: Handcrafted Heirloom Jigsaws</t>
+  </si>
+  <si>
+    <t>Solid hardwood jigsaw puzzles and interlocking brain teasers define this collection. Precision-cut pieces fit snugly, while custom shapes add challenge. Plush toys and model kits accompany the puzzle range. Orders ship from Texas within two business days.</t>
+  </si>
+  <si>
+    <t>Wooden jigsaw puzzles and brain teasers</t>
+  </si>
+  <si>
+    <t>wooden puzzles, jigsaw puzzles, wooden brain teasers, custom wooden puzzles, handcrafted puzzles, interlocking puzzles, wooden jigsaw puzzles</t>
+  </si>
+  <si>
+    <t>90001,90002,90003,90004,90005,90006,90007,90008,90009,90010</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>Toys &amp; Games ||| Basketball Card</t>
+  </si>
+  <si>
+    <t>333 Copa de Oro Rd, Los Angeles, CA 90077</t>
+  </si>
+  <si>
+    <t>dunkdocket.com</t>
+  </si>
+  <si>
+    <t>Basketball Cards - Dunkdocket</t>
+  </si>
+  <si>
+    <t>Basketball cards endure rough handling and grading scrutiny, with rookie inserts, autographs, and numbered parallels covering the court. Plush toys, action figures, and dice sets fill adjacent shelves. Every order ships securely from Los Angeles within two days.</t>
+  </si>
+  <si>
+    <t>Basketball cards and collectible toys for enthusiasts</t>
+  </si>
+  <si>
+    <t>basketball cards, rookie basketball cards, autographed basketball cards, numbered parallels, trading card accessories, collectible toys, plush toys, action figures, polyhedral dice sets, sports card supplies</t>
+  </si>
+  <si>
+    <t>89957,89958,89959,89960,89961,89962,89963,89964,89965,89966</t>
+  </si>
+  <si>
+    <t>89956</t>
+  </si>
+  <si>
+    <t>Toys &amp; Games ||| Block &amp; Build Set</t>
+  </si>
+  <si>
+    <t>419 E Lawson Rd, Dallas, TX 75253</t>
+  </si>
+  <si>
+    <t>blockhaven.toys</t>
+  </si>
+  <si>
+    <t>Block &amp; Build Sets: Construction Toys for Creative Builders</t>
+  </si>
+  <si>
+    <t>Block and build sets occupy the playroom floor, with interlocking bricks, construction vehicles, and themed playsets. Plush animals and action figures fill the shelves beside them. Orders ship from Dallas within one business day.</t>
+  </si>
+  <si>
+    <t>Block and build sets with plush toys, action figures, and collectible cards</t>
+  </si>
+  <si>
+    <t>block and build sets, construction toys, interlocking blocks, building bricks, playsets, plush toys, action figures, collectible toys, puzzles, miniatures, toy vehicles, educational toys, pretend play, die-cast toys, board games</t>
+  </si>
+  <si>
+    <t>89990,89991,89992,89993,89994,89995,89996,89997,89998,89999</t>
+  </si>
+  <si>
+    <t>89989</t>
+  </si>
+  <si>
+    <t>Toys &amp; Games ||| Boat, Plane &amp; Train</t>
+  </si>
+  <si>
+    <t>3327 Chicago St, San Diego, CA 92117</t>
+  </si>
+  <si>
+    <t>chuggleworks.com</t>
+  </si>
+  <si>
+    <t>Plush Toys for Collectors and Players</t>
+  </si>
+  <si>
+    <t>Plush toys in every size and character variant anchor this catalog. Collectible figures, board games, dice sets, and model kits expand the inventory. Orders ship quickly from San Diego.</t>
+  </si>
+  <si>
+    <t>Specialty toy dealer for plush, collectible, board games, and model kits</t>
+  </si>
+  <si>
+    <t>plush toys, collectible toys, board games, dice games, model kits, stuffed animals, pretend play</t>
+  </si>
+  <si>
+    <t>90111,90112,90113,90114,90115,90116,90117,90118,90119,90120</t>
+  </si>
+  <si>
+    <t>90110</t>
+  </si>
+  <si>
+    <t>Toys &amp; Games ||| Brainteaser &amp; Logic Puzzle</t>
+  </si>
+  <si>
+    <t>620 Siena Way, Los Angeles, CA 90077</t>
+  </si>
+  <si>
+    <t>puzzleparts.com</t>
+  </si>
+  <si>
+    <t>Brainteaser and Puzzle Replacement Parts for Collectors</t>
+  </si>
+  <si>
+    <t>Brainteaser puzzles and logic games face constant handling, yet replacement pieces restore lost corners, missing tiles, and broken mechanisms. Adhesive-backed puzzle mats and storage boxes protect completed works. Plush toys and minifigures round out the catalog, with every order shipping from Los Angeles within one business day.</t>
+  </si>
+  <si>
+    <t>Replacement parts and specialty items for brainteasers, puzzles, and classic toys</t>
+  </si>
+  <si>
+    <t>brainteaser puzzle replacement parts, logic puzzle pieces, puzzle box replacement, jigsaw puzzle accessories, fidget puzzle parts, 3d puzzle model kit parts, collectible toy repair parts, puzzle storage solutions</t>
+  </si>
+  <si>
+    <t>89968,89969,89970,89971,89972,89973,89974,89975,89976,89977</t>
+  </si>
+  <si>
+    <t>89967</t>
+  </si>
+  <si>
+    <t>Toys &amp; Games ||| Build Set And Blocks-Non Lego</t>
+  </si>
+  <si>
+    <t>3 Park Ave, New York, NY 10016</t>
+  </si>
+  <si>
+    <t>blockyardco.com</t>
+  </si>
+  <si>
+    <t>Plush Toys &amp; Bulk Games: Block Yard Co.</t>
+  </si>
+  <si>
+    <t>Rainy-day play starts with plush pals like Miffy and stuffed puppies, then stretches into dice sets, Pokemon singles, and model kits. Puzzles and party supplies add family fun. Bulk orders ship fast from New York.</t>
+  </si>
+  <si>
+    <t>Bulk plush toys, dice, Pokemon singles, model kits, puzzles, and more toys &amp; games</t>
+  </si>
+  <si>
+    <t>plush toys, dice, pokemon singles, model kits, collectible toys, party supplies, puzzles, blindbox, trading cards, board games, bulk toys, wholesale plush, mtg singles, craft kits</t>
+  </si>
+  <si>
+    <t>90023,90024,90025,90026,90027,90028,90029,90030,90031,90032</t>
+  </si>
+  <si>
+    <t>90022</t>
+  </si>
+  <si>
+    <t>Toys &amp; Games|||Kites</t>
+  </si>
+  <si>
+    <t>1247 47th Ave, San Francisco, CA 94122</t>
+  </si>
+  <si>
+    <t>kiteandkeep.com</t>
+  </si>
+  <si>
+    <t>Kites: Diamond, Delta, Parafoil, and Box Kites</t>
+  </si>
+  <si>
+    <t>Kites in diamond, delta, parafoil, and box styles fill the shelves, with line, reels, and tails for every breeze. Stuffed animals and plush toys sit nearby as soft companions. Orders ship from San Francisco within two days.</t>
+  </si>
+  <si>
+    <t>kites and kite-flying gear</t>
+  </si>
+  <si>
+    <t>kites, diamond kites, delta kites, parafoil kites, box kites, kite line, kite reels, kite tails</t>
+  </si>
+  <si>
+    <t>90056,90057,90058,90059,90060,90061,90062,90063,90064,90065</t>
+  </si>
+  <si>
+    <t>90055</t>
+  </si>
+  <si>
+    <t>Toys &amp; Games|||League of Legends TCG Singles</t>
+  </si>
+  <si>
+    <t>10730 Chalon Rd, Los Angeles, CA 90077</t>
+  </si>
+  <si>
+    <t>plushcardco.com</t>
+  </si>
+  <si>
+    <t>League of Legends TCG Singles - PlushCard</t>
+  </si>
+  <si>
+    <t>Collectors of League of Legends TCG singles find rare cards, booster packs, and protective sleeves. Plush toys, action figures, and dice sets accompany the card line. Orders ship promptly from Los Angeles.</t>
+  </si>
+  <si>
+    <t>Plush toys and trading cards for collectors</t>
+  </si>
+  <si>
+    <t>league of legends tcg singles, collectible card games, plush toys, action figures, character figures, building sets, board games, puzzles, dice, card sleeves, novelty toys, educational toys, trading card accessories, collectible figures</t>
+  </si>
+  <si>
+    <t>90034,90035,90036,90037,90038,90039,90040,90041,90042,90043</t>
+  </si>
+  <si>
+    <t>90033</t>
+  </si>
+  <si>
+    <t>Toys &amp; Games|||Miniature War Games</t>
+  </si>
+  <si>
+    <t>404 S Wells St, Chicago, IL 60607</t>
+  </si>
+  <si>
+    <t>plushbattleground.com</t>
+  </si>
+  <si>
+    <t>Miniature War Games, Plush &amp; Cards in Chicago</t>
+  </si>
+  <si>
+    <t>Hand-painted resin miniatures anchor the war game line, from infantry squads to siege engines. Plush creatures and custom figures extend the battlefields, while strategy card decks and dice sets support tabletop play. Orders ship from Chicago within two days.</t>
+  </si>
+  <si>
+    <t>Miniature war games, plush toys, and collectible playing cards</t>
+  </si>
+  <si>
+    <t>miniature war games, plush toys, collectible cards, custom figures, strategy games, playing cards, action figures, statues, dice sets, tabletop gaming, pokemon singles, stuffed animals, display cases, novelty toys</t>
+  </si>
+  <si>
+    <t>89979,89980,89981,89982,89983,89984,89985,89986,89987,89988</t>
+  </si>
+  <si>
+    <t>89978</t>
+  </si>
+  <si>
+    <t>Toys &amp; Games|||Model Trains</t>
+  </si>
+  <si>
+    <t>4030 Valerie Dr, San Jose, CA 95008</t>
+  </si>
+  <si>
+    <t>chuffleton.com</t>
+  </si>
+  <si>
+    <t>Model Trains and Collectible Toys for Enthusiasts</t>
+  </si>
+  <si>
+    <t>Brass and die-cast locomotives endure heavy running schedules, while vintage plush and trading cards fill display cases. Jigsaw puzzles and board games offer quiet evenings. Orders ship within one business day from San Jose.</t>
+  </si>
+  <si>
+    <t>Model trains and vintage toy collectibles</t>
+  </si>
+  <si>
+    <t>model trains, collectible toys, trading cards, vintage toys, jigsaw puzzles, board games, brass locomotives, die-cast vehicles, plush toys, baseball cards, model train sets, toy collectibles for adults, gift for train hobbyist</t>
+  </si>
+  <si>
+    <t>90078,90079,90080,90081,90082,90083,90084,90085,90086,90087</t>
+  </si>
+  <si>
+    <t>90077</t>
+  </si>
+  <si>
+    <t>Toys &amp; Games|||Science &amp; Discovery Toys</t>
+  </si>
+  <si>
+    <t>4939 Hamilton St, Sacramento, CA 95841</t>
+  </si>
+  <si>
+    <t>plushplaydeck.com</t>
+  </si>
+  <si>
+    <t>Science Discovery Toys - PlushPlayDeck</t>
+  </si>
+  <si>
+    <t>Rainy afternoons spark curiosity with science kits, puzzles, and marble runs. Plush toys and stuffed animals offer comfort alongside educational games. Dice, trading cards, and model kits extend the fun. Orders ship promptly from Sacramento.</t>
+  </si>
+  <si>
+    <t>Science and discovery toys with plush companions and collectible games</t>
+  </si>
+  <si>
+    <t>science discovery toys, educational games, plush toys, stuffed animals, puzzles, marble runs, dice, trading cards, model kits, collectible toys, vintage toys, action figures, party supplies, novelty toys, play sets, figures</t>
+  </si>
+  <si>
+    <t>90012,90013,90014,90015,90016,90017,90018,90019,90020,90021</t>
+  </si>
+  <si>
+    <t>90011</t>
+  </si>
+  <si>
+    <t>Toys &amp; Games|||Ship Boat</t>
+  </si>
+  <si>
+    <t>620 Sutter St, San Francisco, CA 94102</t>
+  </si>
+  <si>
+    <t>harborplaythings.com</t>
+  </si>
+  <si>
+    <t>Plush Toys &amp; Collectible Wooden Building Sets</t>
+  </si>
+  <si>
+    <t>Traditional craft origins anchor the plush and wooden toy lines, from hand-stitched stuffed animals to interlocking blocks and dollhouse miniatures. Magic tricks, puzzles, and board games extend the selection, while party supplies and novelty items cover celebrations. Orders ship from San Francisco with tracking.</t>
+  </si>
+  <si>
+    <t>Specialty toy dealer with a deep catalog of plush, collectible, wooden, and building toys</t>
+  </si>
+  <si>
+    <t>plush toys, collectible toys, wooden toys, building toys, board games, puzzles, magic tricks, dollhouse accessories, party supplies, novelty toys, stuffed animals, action figures, trading cards, pretend play</t>
+  </si>
+  <si>
+    <t>90089,90090,90091,90092,90093,90094,90095,90096,90097,90098</t>
+  </si>
+  <si>
+    <t>90088</t>
+  </si>
+  <si>
+    <t>Toys &amp; Games|||Tabletop Miniatures</t>
+  </si>
+  <si>
+    <t>4050 W 115th St, Chicago, IL 60655</t>
+  </si>
+  <si>
+    <t>plushpodium.com</t>
+  </si>
+  <si>
+    <t>Plush Toys and Tabletop Miniatures for Collectors</t>
+  </si>
+  <si>
+    <t>A 14-inch plush dragon opens this dealer's catalog of stuffed animals, plastic models, and vintage train sets. Baseball cards and trading card singles sit beside dice sets for tabletop gaming. Orders ship with careful packing from Chicago.</t>
+  </si>
+  <si>
+    <t>Plush toys, baseball cards, and tabletop miniatures</t>
+  </si>
+  <si>
+    <t>plush toys, tabletop miniatures, baseball cards, plastic models, trading cards, vintage toys, dice sets, train sets</t>
+  </si>
+  <si>
+    <t>90067,90068,90069,90070,90071,90072,90073,90074,90075,90076</t>
+  </si>
+  <si>
+    <t>90066</t>
+  </si>
+  <si>
+    <t>Toys &amp; Games|||Toy Cars</t>
+  </si>
+  <si>
+    <t>3333 S Wabash Ave, Chicago, IL 60616</t>
+  </si>
+  <si>
+    <t>plushcraftsupply.com</t>
+  </si>
+  <si>
+    <t>Plush Toys for Repair and Custom Builds</t>
+  </si>
+  <si>
+    <t>Plush toys built to withstand repeated handling and display serve collectors, customizers, and repair technicians. Stuffed animals, character figures, and model accessories form the primary stock. Dice, puzzles, and sensory toys cover adjacent play and hobby needs. Bulk orders ship from Chicago with detailed packing lists.</t>
+  </si>
+  <si>
+    <t>Trade-grade plush toys, collectible figures, and model accessories</t>
+  </si>
+  <si>
+    <t>plush toys for repair, custom plush parts, collectible character figures, model accessories for dioramas, stuffed animal replacement, sensory toys for therapy, dice for tabletop games, puzzles for adults, action figure stands, bulk plush orders</t>
+  </si>
+  <si>
+    <t>90122,90123,90124,90125,90126,90127,90128,90129,90130,90131</t>
+  </si>
+  <si>
+    <t>90121</t>
+  </si>
+  <si>
+    <t>Toys &amp; Games|||Toy Cars, Trains &amp; Vehicles</t>
+  </si>
+  <si>
+    <t>5608 Rudy Dr, San Jose, CA 95124</t>
+  </si>
+  <si>
+    <t>toyboxdepot.com</t>
+  </si>
+  <si>
+    <t>Toy Cars, Trains &amp; Vehicles - Depot</t>
+  </si>
+  <si>
+    <t>Die-cast model cars, wooden train sets, and RC trucks anchor the vehicle lineup. Plush animals and interlocking blocks extend the playroom range. Orders ship within 24 hours from San Jose.</t>
+  </si>
+  <si>
+    <t>Specialty toy cars, trains, vehicles, plus plush, collectibles, and building sets</t>
+  </si>
+  <si>
+    <t>die-cast model cars, wooden train sets, rc trucks, plush animals, interlocking blocks, collectible figures, toy vehicles, construction toys, vintage toys, fidget toys</t>
+  </si>
+  <si>
+    <t>90045,90046,90047,90048,90049,90050,90051,90052,90053,90054</t>
+  </si>
+  <si>
+    <t>90044</t>
+  </si>
+  <si>
+    <t>Toys &amp; Games|||Toy Guns &amp; Blasters</t>
+  </si>
+  <si>
+    <t>11657 Chenault St, Los Angeles, CA 90049</t>
+  </si>
+  <si>
+    <t>plushbrass.com</t>
+  </si>
+  <si>
+    <t>Toy Guns &amp; Blasters Replacement Parts for Collectors</t>
+  </si>
+  <si>
+    <t>Toy guns and blasters replacement parts anchor the range, with triggers, barrels, and loading chambers for classic and modern models. Plush toys, railway sets, and action figures cover the broader collection. Orders ship from Los Angeles.</t>
+  </si>
+  <si>
+    <t>Collectible plush toys, railway models, and replacement parts for hobbyists</t>
+  </si>
+  <si>
+    <t>toy gun parts, blaster replacement parts, collectible toys, plush toys, railway toys, action figures, statues bobbleheads, trading cards, board games, stem toys, dice sets, puzzles, novelty toys, party supplies</t>
+  </si>
+  <si>
+    <t>90177,90178,90179,90180,90181,90182,90183,90184,90185,90186</t>
+  </si>
+  <si>
+    <t>90176</t>
+  </si>
+  <si>
+    <t>Racing Car Parts|||Brake Pads</t>
+  </si>
+  <si>
+    <t>4070 2nd Ave, Sacramento, CA 95817</t>
+  </si>
+  <si>
+    <t>brakebaron.com</t>
+  </si>
+  <si>
+    <t>Racing Brake Pads for Track and Street Performance</t>
+  </si>
+  <si>
+    <t>Racing brake pads grip rotors under hard laps, from carbon-metallic to ceramic compounds. Adjacent clutch kits and coilover springs sharpen the same builds. Orders leave Sacramento within one business day.</t>
+  </si>
+  <si>
+    <t>Racing brake pads and performance braking parts</t>
+  </si>
+  <si>
+    <t>racing brake pads, carbon metallic brake pads, ceramic brake pads, track day brake pads, performance brake pads, brake pad compounds, brake pad replacement</t>
+  </si>
+  <si>
+    <t>90286,90287,90288,90289,90290,90291,90292,90293,90294,90295</t>
+  </si>
+  <si>
+    <t>90285</t>
+  </si>
+  <si>
+    <t>Tonneau Covers|||Soft Fold Tonneau Covers</t>
+  </si>
+  <si>
+    <t>14107 Kelann Ct, Dallas, TX 75253</t>
+  </si>
+  <si>
+    <t>tonneaubespoke.com</t>
+  </si>
+  <si>
+    <t>Soft Fold Tonneau Covers, Dallas Truck Bed Specialists</t>
+  </si>
+  <si>
+    <t>Hand-stitched vinyl and canvas soft fold tonneau covers protect truck beds with easy roll-up access. Retractable aluminum models add rigid security. Floor mats and dash covers support cab upkeep. Fitment help and free shipping on all orders.</t>
+  </si>
+  <si>
+    <t>Soft fold and roll-up tonneau covers for pickup trucks</t>
+  </si>
+  <si>
+    <t>soft fold tonneau covers, roll up tonneau covers, truck bed covers, retractable tonneau covers, vinyl tonneau covers, canvas bed covers, pickup bed protection, tonneau cover installation, truck bed accessories, tonneau cover fitment</t>
+  </si>
+  <si>
+    <t>90166,90167,90168,90169,90170,90171,90172,90173,90174,90175</t>
+  </si>
+  <si>
+    <t>90165</t>
+  </si>
+  <si>
+    <t>Vehicle Parts &amp; Accessories|||LED Light Mount Brackets</t>
+  </si>
+  <si>
+    <t>4100 Orange Grove Ave., Sacramento, CA 95841</t>
+  </si>
+  <si>
+    <t>bracketworksauto.com</t>
+  </si>
+  <si>
+    <t>LED Light Mount Brackets, Sacramento Auto Parts</t>
+  </si>
+  <si>
+    <t>LED light mount brackets for trucks and off-road rigs sit front and center, with suspension arms, ball joints, and lowering springs filling the chassis line. Steering wheel covers and roof rails cover cabin and cargo duty. Brackets ship fast from Sacramento.</t>
+  </si>
+  <si>
+    <t>LED light mount brackets and vehicle suspension parts</t>
+  </si>
+  <si>
+    <t>led light mount brackets, suspension parts, control arms, ball joints, lowering springs, truck accessories</t>
+  </si>
+  <si>
+    <t>90265,90266,90267,90268,90269,90270,90271,90272,90273,90274</t>
+  </si>
+  <si>
+    <t>90264</t>
+  </si>
+  <si>
+    <t>Vehicle Parts &amp; Accessories|||Side Mount Boxes</t>
+  </si>
+  <si>
+    <t>680 Siena Way, Los Angeles, CA 90077</t>
+  </si>
+  <si>
+    <t>sideboxsupply.com</t>
+  </si>
+  <si>
+    <t>Side Mount Boxes - RigWorks</t>
+  </si>
+  <si>
+    <t>Welded steel side mount boxes for trucks and Jeeps hold tools, recovery gear, and camping equipment. Brake pads, seat covers, and electrical connectors fill out the inventory. Orders ship within two business days from the Los Angeles warehouse.</t>
+  </si>
+  <si>
+    <t>Truck and Jeep side mount boxes, tool storage, and vehicle accessories</t>
+  </si>
+  <si>
+    <t>side mount boxes, truck tool boxes, jeep storage boxes, vehicle parts, seat covers, brake pads, brake shoes, boat parts, motor vehicle lighting, electrical connectors, tie rod ends, tire repair supplies, bull bars, air filters, cabin air filters, cat-back exhaust systems</t>
+  </si>
+  <si>
+    <t>90276,90277,90278,90279,90280,90281,90282,90283,90284</t>
+  </si>
+  <si>
+    <t>90275</t>
+  </si>
+  <si>
+    <t>Vehicle Parts &amp; Accessories|||Side Steps</t>
+  </si>
+  <si>
+    <t>460 22nd St, Denver, CO 80205</t>
+  </si>
+  <si>
+    <t>stepsideparts.com</t>
+  </si>
+  <si>
+    <t>Side Steps: Truck Nerf Bars &amp; Running Boards</t>
+  </si>
+  <si>
+    <t>Fabrication of steel and aluminum side steps traces back to ranch trucks needing grip in mud. The catalog covers nerf bars, running boards, and rock sliders for pickups and Jeeps, plus suspension parts and lighting. Orders ship within two days.</t>
+  </si>
+  <si>
+    <t>Side steps and vehicle parts for trucks, SUVs, and off-road builds</t>
+  </si>
+  <si>
+    <t>side steps, nerf bars, running boards, truck side steps, SUV running boards, off-road rock sliders, step nerf bar kits, suspension parts, vehicle lighting, brake pads, fender flares, truck accessories</t>
+  </si>
+  <si>
+    <t>90297,90298,90299,90300,90301,90302,90303,90304,90305,90306</t>
+  </si>
+  <si>
+    <t>90296</t>
+  </si>
+  <si>
+    <t>Vehicle Parts &amp; Accessories|||Side Window Visors</t>
+  </si>
+  <si>
+    <t>visorweave.com</t>
+  </si>
+  <si>
+    <t>Side Window Visors, Los Angeles Fitment</t>
+  </si>
+  <si>
+    <t>Injection-molded acrylic side window visors shield cabins from rain and glare. Wind deflectors, vent visors and in-channel guards anchor the lineup, while brake pads and oil filters cover maintenance needs. Orders ship from the West Coast within a day.</t>
+  </si>
+  <si>
+    <t>Side window visors and vehicle parts</t>
+  </si>
+  <si>
+    <t>side window visors, wind deflectors, vent visors, in-channel visors, vehicle parts, brake pads, oil filters</t>
+  </si>
+  <si>
+    <t>90199,90200,90201,90202,90203,90204,90205,90206,90207,90208</t>
+  </si>
+  <si>
+    <t>90198</t>
+  </si>
+  <si>
+    <t>Vehicle Parts &amp; Accessories|||Steering Dampers</t>
+  </si>
+  <si>
+    <t>555 Mission Rock St, San Francisco, CA 94158</t>
+  </si>
+  <si>
+    <t>damperscout.com</t>
+  </si>
+  <si>
+    <t>Steering Dampers for Stable Off-Road Control</t>
+  </si>
+  <si>
+    <t>A Fox 2.0 steering damper tames bump steer on lifted trucks. Stabilizer kits, tie rods, and shock absorbers form the suspension core, with sway bars and strut bars adding chassis rigidity. Brake rotors and pads cover stopping power. Orders ship promptly from San Francisco.</t>
+  </si>
+  <si>
+    <t>Steering dampers and suspension components</t>
+  </si>
+  <si>
+    <t>steering damper, steering stabilizer, off-road steering, suspension parts, shock absorber, sway bar, strut bar</t>
+  </si>
+  <si>
+    <t>90155,90156,90157,90158,90159,90160,90161,90162,90163,90164</t>
+  </si>
+  <si>
+    <t>90154</t>
+  </si>
+  <si>
+    <t>Vehicle Parts &amp; Accessories|||Tire Repair Tools</t>
+  </si>
+  <si>
+    <t>1590 Little Raven St, Denver, CO 80202</t>
+  </si>
+  <si>
+    <t>boltbenchparts.com</t>
+  </si>
+  <si>
+    <t>Tire Repair Tools for Quick Fixes and Lasting Durability</t>
+  </si>
+  <si>
+    <t>Tire repair tools anchor the lineup, covering plug kits, patch applicators, and valve stem removers for roadside and garage use. Windshield assemblies, brake kits, and suspension lift kits address broader vehicle upkeep. Orders ship from Denver with technical support.</t>
+  </si>
+  <si>
+    <t>Tire repair tools and vehicle parts</t>
+  </si>
+  <si>
+    <t>tire repair tools, tire plug kits, tire patch kits, valve stem tools, windshield assemblies, brake kits, suspension lift kits, headlight assemblies, air filters, cat-back exhaust systems, camshafts, led light bars, gauges, fuel systems, brake hoses, cylinder head gaskets</t>
+  </si>
+  <si>
+    <t>90221,90222,90223,90224,90225,90226,90227,90228,90229,90230</t>
+  </si>
+  <si>
+    <t>90220</t>
+  </si>
+  <si>
+    <t>Vehicle Parts|||Gear Oils</t>
+  </si>
+  <si>
+    <t>4060 W 115th St, Chicago, IL 60655</t>
+  </si>
+  <si>
+    <t>gearoilfoundry.com</t>
+  </si>
+  <si>
+    <t>Gear Oils: Differential, Manual Transmission &amp; Axle Fluids</t>
+  </si>
+  <si>
+    <t>Truck and off-road builders find gear oils, differential covers, axle seals, and transmission fluids in a deep drivetrain catalog. Brake rotors and pads extend the coverage. Orders ship from Chicago with tracking.</t>
+  </si>
+  <si>
+    <t>Gear oils and drivetrain fluids</t>
+  </si>
+  <si>
+    <t>gear oil, differential fluid, manual transmission fluid, axle seals, differential cover, transfer case oil, synthetic gear oil</t>
+  </si>
+  <si>
+    <t>90232,90233,90234,90235,90236,90237,90238,90239,90240,90241</t>
+  </si>
+  <si>
+    <t>90231</t>
+  </si>
+  <si>
+    <t>Vehicle Parts|||Headlight Bulbs</t>
+  </si>
+  <si>
+    <t>1918 N Olive St, Dallas, TX 75201</t>
+  </si>
+  <si>
+    <t>headlightbrass.com</t>
+  </si>
+  <si>
+    <t>Headlight Bulbs - Brassworks</t>
+  </si>
+  <si>
+    <t>Repair shops and fleet mechanics source headlight bulbs, LED tail lights, and electrical connectors here. Brake kits and radiators cover the service side. Orders ship from Dallas.</t>
+  </si>
+  <si>
+    <t>Headlight bulbs and vehicle parts for repair professionals</t>
+  </si>
+  <si>
+    <t>headlight bulbs, led tail lights, electrical connectors, brake kits, radiators, vehicle parts for mechanics, repair shop supplies, fleet maintenance parts</t>
+  </si>
+  <si>
+    <t>90243,90244,90245,90246,90247,90248,90249,90250,90251,90252</t>
+  </si>
+  <si>
+    <t>90242</t>
+  </si>
+  <si>
+    <t>Vehicles &amp; Parts|||Air Cleaners</t>
+  </si>
+  <si>
+    <t>401 21st St, Denver, CO 80205</t>
+  </si>
+  <si>
+    <t>ironairparts.com</t>
+  </si>
+  <si>
+    <t>Air Cleaners: Steel and Chrome Filters for Engine Builds</t>
+  </si>
+  <si>
+    <t>Steel and chrome air cleaners, filter elements, and breather kits cover engine intake needs for trucks, muscle cars, and off-road rigs. Related suspension components and shift knobs support full drivetrain upgrades. Orders ship from Denver stock.</t>
+  </si>
+  <si>
+    <t>Air cleaners and vehicle parts for budget-minded builders</t>
+  </si>
+  <si>
+    <t>air cleaners, chrome air cleaner assemblies, steel air filter housings, engine breather kits, replacement air filter elements, muscle car intake parts, truck air cleaner upgrades, off-road air filtration, suspension components, shift knobs</t>
+  </si>
+  <si>
+    <t>90188,90189,90190,90191,90192,90193,90194,90195,90196,90197</t>
+  </si>
+  <si>
+    <t>90187</t>
+  </si>
+  <si>
+    <t>Vehicles &amp; Parts|||Cargo Racks</t>
+  </si>
+  <si>
+    <t>5414 Crenshaw Blvd, Los Angeles, CA 90043</t>
+  </si>
+  <si>
+    <t>cargorackparts.com</t>
+  </si>
+  <si>
+    <t>Cargo Racks: Roof Racks for Trucks and SUVs</t>
+  </si>
+  <si>
+    <t>Cargo racks endure heavy loads, off-road vibration, and harsh weather. The catalog covers roof baskets, crossbars, hitch-mounted carriers, and tie-downs for trucks and SUVs. Ladder racks and tarp systems extend utility for work vehicles. Orders ship promptly from Los Angeles with dedicated support.</t>
+  </si>
+  <si>
+    <t>Cargo racks, roof racks, and vehicle parts</t>
+  </si>
+  <si>
+    <t>cargo racks, roof racks, truck racks, SUV cargo carrier, crossbars, hitch cargo carrier, roof basket, ladder racks, tarp systems, tie-downs, nerf bars, grille guards, lift kits, light bars, windshields, suspension parts</t>
+  </si>
+  <si>
+    <t>90210,90211,90212,90213,90214,90215,90216,90217,90218,90219</t>
+  </si>
+  <si>
+    <t>90209</t>
+  </si>
+  <si>
+    <t>Vehicles &amp; Parts|||Exhaust Pipes &amp; Tips</t>
+  </si>
+  <si>
+    <t>exhaustpipeiron.com</t>
+  </si>
+  <si>
+    <t>Exhaust Pipes &amp; Tips: Iron-Crafted Performance Parts</t>
+  </si>
+  <si>
+    <t>Auto enthusiasts and mechanics source exhaust pipes, tips, cat-back systems, and slip-ons for precise fitment. Suspension parts and shock struts support chassis upgrades. Bulk orders ship with technical specs and fast turnaround.</t>
+  </si>
+  <si>
+    <t>Exhaust pipes, tips, cat-back systems, and related vehicle parts</t>
+  </si>
+  <si>
+    <t>exhaust pipes, exhaust tips, cat-back exhaust systems, slip-on exhaust, exhaust clamps, suspension parts, shock struts, vehicle parts</t>
+  </si>
+  <si>
+    <t>90254,90255,90256,90257,90258,90259,90260,90261,90262,90263</t>
+  </si>
+  <si>
+    <t>90253</t>
+  </si>
+  <si>
+    <t>Vehicles &amp; Parts|||Winch Compatible Truck Front Bumpers</t>
+  </si>
+  <si>
+    <t>ruggedbumperworks.com</t>
+  </si>
+  <si>
+    <t>Winch Bumpers and Truck Parts for Off-Road Builds</t>
+  </si>
+  <si>
+    <t>Steel winch bumpers with D-ring mounts and light cutouts anchor the line. Grille guards, skid plates, and rock sliders handle trail protection. Tonneau covers and bed accessories expand the hauling side. Orders ship with fitment guidance for each truck model.</t>
+  </si>
+  <si>
+    <t>Winch compatible truck front bumpers and replacement parts</t>
+  </si>
+  <si>
+    <t>winch bumpers, truck front bumpers, winch compatible bumpers, grille guards, skid plates, rock sliders, off-road bumpers, truck armor, replacement bumpers, tonneau covers, bed covers, light mounts</t>
+  </si>
+  <si>
+    <t>91336,91337,91338,91339,91340,91341,91342,91343,91344</t>
+  </si>
+  <si>
+    <t>Books|||Catholic Books</t>
+  </si>
+  <si>
+    <t>1080 Dublin Way, Birmingham, AL 35242</t>
+  </si>
+  <si>
+    <t>dublinpressbooks.com</t>
+  </si>
+  <si>
+    <t>Catholic Books in Leather and Cloth</t>
+  </si>
+  <si>
+    <t>Daily Mass, feast days, and evening prayer find their companions in missals, Bibles, and devotional classics. Rosary bracelets and framed wall art support the same rituals. Orders ship promptly from Birmingham with careful packing for every volume.</t>
+  </si>
+  <si>
+    <t>Catholic books and religious goods</t>
+  </si>
+  <si>
+    <t>catholic books, catholic missals, leather catholic bible, daily prayer books, catholic devotional classics, rosary bracelets, catholic wall art, catholic gifts, catholic reading materials</t>
+  </si>
+  <si>
+    <t>Rosaries, holy cards, and engravable rosary bracelets anchor the religious ceremonial line. Tarot cards, Bible covers, and clerical wear serve parish and personal practice. Orders ship with trade-grade packaging and bulk pricing for contractors.</t>
+  </si>
+  <si>
+    <t>Religious ceremonial goods for churches and home devotion</t>
+  </si>
+  <si>
+    <t>91326,91327,91328,91329,91330,91331,91332,91333,91334</t>
+  </si>
+  <si>
+    <t>Religious &amp; Ceremonial|||Cross &amp; Crucifix Necklaces</t>
+  </si>
+  <si>
+    <t>12 Portsmouth Place NE, Grand Rapids, MI 49503</t>
+  </si>
+  <si>
+    <t>crossveill.com</t>
+  </si>
+  <si>
+    <t>Cross and Crucifix Necklaces and Rosary Supplies</t>
+  </si>
+  <si>
+    <t>Cross and crucifix necklaces endure daily wear and frequent blessings, built for both personal devotion and congregational use. Rosary bracelets, oracle cards, and Wicca ritual items fill the core catalog, while menorahs and anointing oils extend the ceremonial range. Orders ship from Grand Rapids within two days.</t>
+  </si>
+  <si>
+    <t>Cross and crucifix necklaces, rosaries, and religious ceremonial items</t>
+  </si>
+  <si>
+    <t>cross necklace, crucifix necklace, rosary bracelet, religious jewelry, oracle cards, wicca supplies, anointing oil, menorah</t>
+  </si>
+  <si>
+    <t>Cross and crucifix necklaces in sterling silver, gold, and wood fill the devotional cases. Rosary bracelets, prayer cards, and anointing oils sit alongside the pendant lines. Orders ship from Spokane within two business days.</t>
+  </si>
+  <si>
+    <t>Cross and crucifix necklaces for daily wear and devotional practice</t>
+  </si>
+  <si>
+    <t>91376,91377,91378,91379,91380,91381,91382,91383,91384</t>
+  </si>
+  <si>
+    <t>Religious &amp; Ceremonial|||Crosses &amp; Crucifixes</t>
+  </si>
+  <si>
+    <t>1201 Heron Pointe Dr, Nashville, TN 37214</t>
+  </si>
+  <si>
+    <t>sacredobjectry.com</t>
+  </si>
+  <si>
+    <t>Crosses &amp; Crucifixes - Sacred Objectry</t>
+  </si>
+  <si>
+    <t>Quiet mornings of prayer and reflection call for crosses, crucifixes, pyxes, and anointing oils. Pocket crosses and prayer bracelets serve daily devotion, while Ketubahs and challah covers honor family traditions. Greeting cards and ornaments accompany these sacred pieces. Orders ship promptly from Nashville.</t>
+  </si>
+  <si>
+    <t>Crosses, crucifixes, and devotional religious items</t>
+  </si>
+  <si>
+    <t>crosses, crucifixes, pocket crosses, pyxes, anointing oils, prayer bracelets, rosary bracelets, ketubahs, challah covers, miraculous medals, orthodox jewelry, sacred image candles, devotional gifts</t>
+  </si>
+  <si>
+    <t>Leather-bound personalized Bibles with embossed names anchor a deep religious catalog of engravable rosary bracelets, medals, and crucifixes. Prayer beads and wall crosses sit alongside memorial keepsakes and candles. Orders ship from San Antonio within two days.</t>
+  </si>
+  <si>
+    <t>Personalized Bibles and engravable rosary bracelets</t>
+  </si>
+  <si>
+    <t>91346,91347,91348,91349,91350,91351,91352,91353,91354</t>
+  </si>
+  <si>
+    <t>Religious &amp; Ceremonial|||Kiddush Cups</t>
+  </si>
+  <si>
+    <t>1448 Village Rd, Charleston, SC 29407</t>
+  </si>
+  <si>
+    <t>kiddushcraft.com</t>
+  </si>
+  <si>
+    <t>Kiddush Cups for Sabbath and Holiday Blessings</t>
+  </si>
+  <si>
+    <t>Sabbath and holiday evenings call for sterling silver, pewter, and hand-painted Kiddush cups that honor tradition. The collection spans ornate engravings, modern minimalist designs, and heirloom-quality sets. Mezuzahs and menorahs sit alongside for complete Jewish home observance. Orders ship promptly from Charleston.</t>
+  </si>
+  <si>
+    <t>Kiddush cups and Jewish ceremonial gifts</t>
+  </si>
+  <si>
+    <t>kiddush cups, sterling silver kiddush cup, pewter kiddush cup, hand-painted kiddush cup, kiddush cup set, jewish ceremonial gifts, shabbat cup, judaica gifts, mezuzah, menorah, heirloom kiddush cup, engraved kiddush cup, sabbath blessing cup</t>
+  </si>
+  <si>
+    <t>Rosary bracelets and traditional five-decade rosaries form the foundation, with crucifixes and saint statues for altar displays. Oracle cards and prayer books serve meditation practices. Orders ship with tracking within two business days.</t>
+  </si>
+  <si>
+    <t>Catholic rosaries, crucifixes, and prayer items</t>
+  </si>
+  <si>
+    <t>91366,91367,91368,91369,91370,91371,91372,91373,91374</t>
+  </si>
+  <si>
+    <t>Religious &amp; Ceremonial|||Prayer Books</t>
+  </si>
+  <si>
+    <t>3717 Ethel St, Detroit, MI 48217</t>
+  </si>
+  <si>
+    <t>prayerbenchworks.com</t>
+  </si>
+  <si>
+    <t>Prayer Books for Daily Devotion and Ritual Practice</t>
+  </si>
+  <si>
+    <t>Prayer books anchor a catalog spanning Tehillim, Torah, and personalized Bibles, joined by Rudraksha beads, rosaries, and Ketubah texts. Mala kits and prayer ropes serve meditation routines. Orders ship promptly from Detroit.</t>
+  </si>
+  <si>
+    <t>Religious and ceremonial prayer books, beads, and devotional items</t>
+  </si>
+  <si>
+    <t>prayer books, tehillim, torah, personalized bibles, rudraksha beads, rosaries, ketubah, mala kits, prayer ropes</t>
+  </si>
+  <si>
+    <t>91406,91407,91408,91409,91410,91411,91412,91413,91414</t>
+  </si>
+  <si>
+    <t>Religious &amp; Ceremonial|||Shabbat Candles</t>
+  </si>
+  <si>
+    <t>2975 SW 36th Ct, Miami, FL 33133</t>
+  </si>
+  <si>
+    <t>wickhalo.com</t>
+  </si>
+  <si>
+    <t>Shabbat Candles and Judaica for Every Home</t>
+  </si>
+  <si>
+    <t>Shabbat candles in beeswax and olive oil anchor the line, with wicks and holders sized for every menorah. Havdalah spice boxes and kiddush cups join the ceremonial range. Orders ship promptly from Miami, Florida.</t>
+  </si>
+  <si>
+    <t>Shabbat candles and Judaica ceremonial supplies</t>
+  </si>
+  <si>
+    <t>shabbat candles, judaica, kiddush cups, havdalah supplies, menorahs, mezuzahs, tallit bags, kippahs, passover supplies, benchers, torah mantels, wash cups, candlesticks, baptism gifts, rosaries, saint medals</t>
+  </si>
+  <si>
+    <t>91396,91397,91398,91399,91400,91401,91402,91403,91404</t>
+  </si>
+  <si>
+    <t>Religious &amp; Ceremonial|||Tasbeeh Collections</t>
+  </si>
+  <si>
+    <t>2956 SW 26th St, Miami, FL 33133</t>
+  </si>
+  <si>
+    <t>tasbihly.com</t>
+  </si>
+  <si>
+    <t>Tasbeeh Collections for Daily Prayer and Reflection</t>
+  </si>
+  <si>
+    <t>Handcrafted tasbeeh beads in wood, stone, and glass carry centuries of Islamic prayer tradition. The catalog covers rosaries, medals, crosses, and devotional items for Christian, Jewish, and Hindu ceremonies. Engravable bracelet styles and kippot also serve daily practice. Orders ship from Miami with careful packaging.</t>
+  </si>
+  <si>
+    <t>Tasbeeh collections, prayer beads, and religious ceremonial items</t>
+  </si>
+  <si>
+    <t>tasbeeh, prayer beads, rosary, medals, crosses, rakhi, kippot, devotional items, holy water bottles, saint medal necklaces, shofar, kiddush cup, tefillin, amulets</t>
+  </si>
+  <si>
+    <t>91386,91387,91388,91389,91390,91391,91392,91393,91394</t>
+  </si>
+  <si>
+    <t>Religious Items|||Bibles</t>
+  </si>
+  <si>
+    <t>515A S Santa Rita Ave, Tucson, AZ 85719</t>
+  </si>
+  <si>
+    <t>sacredthreadgoods.com</t>
+  </si>
+  <si>
+    <t>Religious Items &amp; Bibles for Everyday Practice</t>
+  </si>
+  <si>
+    <t>Wooden rosaries, sterling silver crosses, and hand-painted mezuzahs anchor a deep religious goods catalog. Bible covers, prayer rugs, and communion cups extend the selection. Tarot cards and religious art appear as adjacent lines. Orders ship from Tucson within two business days.</t>
+  </si>
+  <si>
+    <t>Religious items and Bibles</t>
+  </si>
+  <si>
+    <t>religious items, bibles, rosaries, crosses, mezuzahs, prayer accessories, bible covers, communion cups</t>
+  </si>
+  <si>
+    <t>91356,91357,91358,91359,91360,91361,91362,91363,91364</t>
+  </si>
+  <si>
+    <t>Religious Items|||Vestments &amp; Robes</t>
+  </si>
+  <si>
+    <t>18 Paddlecreek Ave, Charleston, SC 29412</t>
+  </si>
+  <si>
+    <t>paddlecreekvestments.com</t>
+  </si>
+  <si>
+    <t>Vestments &amp; Robes for Clergy and Choir</t>
+  </si>
+  <si>
+    <t>Vestments and robes anchor the collection, spanning albs, chasubles, stoles, and cassocks for clergy and choir members. Menorahs, prayer supplies, and sukkah decorations extend the religious goods line. Orders ship from Charleston, South Carolina.</t>
+  </si>
+  <si>
+    <t>Religious vestments and robes for clergy and congregations</t>
+  </si>
+  <si>
+    <t>vestments, robes, clergy vestments, choir robes, albs, chasubles, stoles, cassocks, religious robes, baptism gowns, prayer shawls, menorahs, sukkah decorations</t>
   </si>
 </sst>
 </file>
@@ -12401,7 +14306,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -12476,6 +14381,13 @@
       <color rgb="FF1F1F1F"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -12978,16 +14890,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -12996,119 +14905,122 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -13197,6 +15109,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -13210,6 +15123,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -19007,7 +20923,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q409"/>
+  <dimension ref="A1:S477"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="50.625" customWidth="1"/>
@@ -19083,10 +20999,10 @@
       <c r="A2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="32" t="s">
         <v>19</v>
       </c>
       <c r="D2" s="6" t="s">
@@ -19189,7 +21105,7 @@
       <c r="A4" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="31" t="s">
         <v>46</v>
       </c>
       <c r="C4" s="4">
@@ -19242,7 +21158,7 @@
       <c r="A5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="31" t="s">
         <v>58</v>
       </c>
       <c r="C5" s="4">
@@ -19295,7 +21211,7 @@
       <c r="A6" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="31" t="s">
         <v>70</v>
       </c>
       <c r="C6" s="4">
@@ -19348,7 +21264,7 @@
       <c r="A7" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="31" t="s">
         <v>82</v>
       </c>
       <c r="C7" s="8">
@@ -19401,7 +21317,7 @@
       <c r="A8" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="31" t="s">
         <v>95</v>
       </c>
       <c r="C8" s="4">
@@ -19454,7 +21370,7 @@
       <c r="A9" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="31" t="s">
         <v>107</v>
       </c>
       <c r="C9" s="4">
@@ -19507,7 +21423,7 @@
       <c r="A10" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="31" t="s">
         <v>118</v>
       </c>
       <c r="C10" s="4">
@@ -19560,7 +21476,7 @@
       <c r="A11" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B11" s="30" t="s">
+      <c r="B11" s="31" t="s">
         <v>130</v>
       </c>
       <c r="C11" s="4">
@@ -19613,7 +21529,7 @@
       <c r="A12" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="31" t="s">
         <v>141</v>
       </c>
       <c r="C12" s="4">
@@ -19825,7 +21741,7 @@
       <c r="A16" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="31" t="s">
         <v>186</v>
       </c>
       <c r="C16" s="4">
@@ -20991,7 +22907,7 @@
       <c r="A38" s="4" t="s">
         <v>430</v>
       </c>
-      <c r="B38" s="32" t="s">
+      <c r="B38" s="33" t="s">
         <v>431</v>
       </c>
       <c r="C38" s="8">
@@ -21044,7 +22960,7 @@
       <c r="A39" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="B39" s="32" t="s">
+      <c r="B39" s="33" t="s">
         <v>442</v>
       </c>
       <c r="C39" s="8">
@@ -21462,7 +23378,7 @@
       <c r="A47" t="s">
         <v>531</v>
       </c>
-      <c r="B47" s="30" t="s">
+      <c r="B47" s="31" t="s">
         <v>532</v>
       </c>
       <c r="C47" s="8">
@@ -22176,7 +24092,7 @@
       <c r="A61" t="s">
         <v>687</v>
       </c>
-      <c r="B61" s="30" t="s">
+      <c r="B61" s="31" t="s">
         <v>688</v>
       </c>
       <c r="C61" s="8">
@@ -22427,7 +24343,7 @@
       <c r="A66" t="s">
         <v>742</v>
       </c>
-      <c r="B66" s="30" t="s">
+      <c r="B66" s="31" t="s">
         <v>743</v>
       </c>
       <c r="C66" s="4">
@@ -22477,7 +24393,7 @@
       <c r="A67" t="s">
         <v>753</v>
       </c>
-      <c r="B67" s="30" t="s">
+      <c r="B67" s="31" t="s">
         <v>754</v>
       </c>
       <c r="C67" s="8">
@@ -22527,7 +24443,7 @@
       <c r="A68" t="s">
         <v>763</v>
       </c>
-      <c r="B68" s="30" t="s">
+      <c r="B68" s="31" t="s">
         <v>764</v>
       </c>
       <c r="C68" s="8">
@@ -22577,7 +24493,7 @@
       <c r="A69" t="s">
         <v>773</v>
       </c>
-      <c r="B69" s="30" t="s">
+      <c r="B69" s="31" t="s">
         <v>774</v>
       </c>
       <c r="C69" s="4">
@@ -22627,7 +24543,7 @@
       <c r="A70" t="s">
         <v>783</v>
       </c>
-      <c r="B70" s="30" t="s">
+      <c r="B70" s="31" t="s">
         <v>784</v>
       </c>
       <c r="C70" s="8">
@@ -22677,7 +24593,7 @@
       <c r="A71" t="s">
         <v>793</v>
       </c>
-      <c r="B71" s="30" t="s">
+      <c r="B71" s="31" t="s">
         <v>794</v>
       </c>
       <c r="C71" s="8">
@@ -22727,7 +24643,7 @@
       <c r="A72" t="s">
         <v>803</v>
       </c>
-      <c r="B72" s="30" t="s">
+      <c r="B72" s="31" t="s">
         <v>804</v>
       </c>
       <c r="C72" s="8">
@@ -22778,7 +24694,7 @@
       <c r="A73" t="s">
         <v>813</v>
       </c>
-      <c r="B73" s="30" t="s">
+      <c r="B73" s="31" t="s">
         <v>814</v>
       </c>
       <c r="C73" s="8">
@@ -22829,7 +24745,7 @@
       <c r="A74" t="s">
         <v>823</v>
       </c>
-      <c r="B74" s="30" t="s">
+      <c r="B74" s="31" t="s">
         <v>824</v>
       </c>
       <c r="C74" s="8">
@@ -22880,7 +24796,7 @@
       <c r="A75" t="s">
         <v>834</v>
       </c>
-      <c r="B75" s="30" t="s">
+      <c r="B75" s="31" t="s">
         <v>835</v>
       </c>
       <c r="C75" s="8">
@@ -22931,7 +24847,7 @@
       <c r="A76" t="s">
         <v>844</v>
       </c>
-      <c r="B76" s="30" t="s">
+      <c r="B76" s="31" t="s">
         <v>845</v>
       </c>
       <c r="C76" s="8">
@@ -22982,7 +24898,7 @@
       <c r="A77" t="s">
         <v>854</v>
       </c>
-      <c r="B77" s="30" t="s">
+      <c r="B77" s="31" t="s">
         <v>855</v>
       </c>
       <c r="C77" s="8">
@@ -23032,7 +24948,7 @@
       <c r="A78" t="s">
         <v>865</v>
       </c>
-      <c r="B78" s="33" t="s">
+      <c r="B78" s="34" t="s">
         <v>866</v>
       </c>
       <c r="C78" s="8">
@@ -23082,7 +24998,7 @@
       <c r="A79" t="s">
         <v>877</v>
       </c>
-      <c r="B79" s="33" t="s">
+      <c r="B79" s="34" t="s">
         <v>878</v>
       </c>
       <c r="C79" s="8">
@@ -23132,7 +25048,7 @@
       <c r="A80" t="s">
         <v>888</v>
       </c>
-      <c r="B80" s="33" t="s">
+      <c r="B80" s="34" t="s">
         <v>889</v>
       </c>
       <c r="C80" s="8">
@@ -23182,7 +25098,7 @@
       <c r="A81" t="s">
         <v>899</v>
       </c>
-      <c r="B81" s="33" t="s">
+      <c r="B81" s="34" t="s">
         <v>900</v>
       </c>
       <c r="C81" s="8">
@@ -23233,7 +25149,7 @@
       <c r="A82" t="s">
         <v>910</v>
       </c>
-      <c r="B82" s="33" t="s">
+      <c r="B82" s="34" t="s">
         <v>911</v>
       </c>
       <c r="C82" s="8">
@@ -23284,7 +25200,7 @@
       <c r="A83" t="s">
         <v>921</v>
       </c>
-      <c r="B83" s="30" t="s">
+      <c r="B83" s="31" t="s">
         <v>922</v>
       </c>
       <c r="C83" s="8">
@@ -23335,7 +25251,7 @@
       <c r="A84" t="s">
         <v>932</v>
       </c>
-      <c r="B84" s="30" t="s">
+      <c r="B84" s="31" t="s">
         <v>933</v>
       </c>
       <c r="C84" s="8">
@@ -23386,7 +25302,7 @@
       <c r="A85" t="s">
         <v>943</v>
       </c>
-      <c r="B85" s="30" t="s">
+      <c r="B85" s="31" t="s">
         <v>944</v>
       </c>
       <c r="C85" s="4">
@@ -23437,7 +25353,7 @@
       <c r="A86" t="s">
         <v>953</v>
       </c>
-      <c r="B86" s="30" t="s">
+      <c r="B86" s="31" t="s">
         <v>954</v>
       </c>
       <c r="C86" s="4">
@@ -23488,7 +25404,7 @@
       <c r="A87" t="s">
         <v>963</v>
       </c>
-      <c r="B87" s="30" t="s">
+      <c r="B87" s="31" t="s">
         <v>964</v>
       </c>
       <c r="C87" s="8">
@@ -31677,7 +33593,7 @@
       </c>
     </row>
     <row r="265" ht="121.5" spans="2:17">
-      <c r="B265" s="34" t="s">
+      <c r="B265" s="35" t="s">
         <v>2703</v>
       </c>
       <c r="C265" s="20">
@@ -36187,7 +38103,7 @@
       </c>
     </row>
     <row r="372" ht="16.5" spans="2:17">
-      <c r="B372" s="34" t="s">
+      <c r="B372" s="35" t="s">
         <v>3701</v>
       </c>
       <c r="C372" s="1">
@@ -36220,9 +38136,12 @@
       <c r="P372" t="s">
         <v>3708</v>
       </c>
+      <c r="Q372" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="373" ht="16.5" spans="2:17">
-      <c r="B373" s="34" t="s">
+      <c r="B373" s="35" t="s">
         <v>3709</v>
       </c>
       <c r="C373" s="1">
@@ -36255,9 +38174,12 @@
       <c r="P373" t="s">
         <v>3716</v>
       </c>
+      <c r="Q373" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="374" ht="16.5" spans="2:17">
-      <c r="B374" s="34" t="s">
+      <c r="B374" s="35" t="s">
         <v>3717</v>
       </c>
       <c r="C374" s="1">
@@ -36290,9 +38212,12 @@
       <c r="P374" t="s">
         <v>3724</v>
       </c>
+      <c r="Q374" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="375" ht="16.5" spans="2:17">
-      <c r="B375" s="34" t="s">
+      <c r="B375" s="35" t="s">
         <v>3725</v>
       </c>
       <c r="C375" s="1">
@@ -36325,9 +38250,12 @@
       <c r="P375" t="s">
         <v>3732</v>
       </c>
+      <c r="Q375" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="376" ht="16.5" spans="2:17">
-      <c r="B376" s="34" t="s">
+      <c r="B376" s="35" t="s">
         <v>3733</v>
       </c>
       <c r="C376" s="1">
@@ -36360,9 +38288,12 @@
       <c r="P376" t="s">
         <v>3741</v>
       </c>
+      <c r="Q376" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="377" ht="16.5" spans="2:17">
-      <c r="B377" s="34" t="s">
+      <c r="B377" s="35" t="s">
         <v>3742</v>
       </c>
       <c r="C377" s="1">
@@ -36395,9 +38326,12 @@
       <c r="P377" t="s">
         <v>3749</v>
       </c>
+      <c r="Q377" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="378" ht="16.5" spans="2:17">
-      <c r="B378" s="34" t="s">
+      <c r="B378" s="35" t="s">
         <v>3750</v>
       </c>
       <c r="C378" s="1">
@@ -36430,9 +38364,12 @@
       <c r="P378" t="s">
         <v>3757</v>
       </c>
+      <c r="Q378" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="379" ht="16.5" spans="2:17">
-      <c r="B379" s="34" t="s">
+      <c r="B379" s="35" t="s">
         <v>3758</v>
       </c>
       <c r="C379" s="1">
@@ -36465,9 +38402,12 @@
       <c r="P379" t="s">
         <v>3765</v>
       </c>
+      <c r="Q379" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="380" ht="16.5" spans="2:17">
-      <c r="B380" s="34" t="s">
+      <c r="B380" s="35" t="s">
         <v>3766</v>
       </c>
       <c r="C380" s="1">
@@ -36500,9 +38440,12 @@
       <c r="P380" t="s">
         <v>3773</v>
       </c>
+      <c r="Q380" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="381" ht="16.5" spans="2:17">
-      <c r="B381" s="34" t="s">
+      <c r="B381" s="35" t="s">
         <v>3774</v>
       </c>
       <c r="C381" s="1">
@@ -36535,9 +38478,12 @@
       <c r="P381" t="s">
         <v>3781</v>
       </c>
+      <c r="Q381" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="382" ht="16.5" spans="2:17">
-      <c r="B382" s="34" t="s">
+      <c r="B382" s="35" t="s">
         <v>3782</v>
       </c>
       <c r="C382" s="1">
@@ -36570,9 +38516,12 @@
       <c r="P382" t="s">
         <v>3789</v>
       </c>
+      <c r="Q382" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="383" ht="16.5" spans="2:17">
-      <c r="B383" s="34" t="s">
+      <c r="B383" s="35" t="s">
         <v>3790</v>
       </c>
       <c r="C383" s="1">
@@ -36605,9 +38554,12 @@
       <c r="P383" t="s">
         <v>3797</v>
       </c>
+      <c r="Q383" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="384" ht="16.5" spans="2:17">
-      <c r="B384" s="34" t="s">
+      <c r="B384" s="35" t="s">
         <v>3798</v>
       </c>
       <c r="C384" s="1">
@@ -36640,9 +38592,12 @@
       <c r="P384" t="s">
         <v>3805</v>
       </c>
-    </row>
-    <row r="385" ht="16.5" spans="2:16">
-      <c r="B385" s="34" t="s">
+      <c r="Q384" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="385" ht="16.5" spans="2:17">
+      <c r="B385" s="35" t="s">
         <v>3806</v>
       </c>
       <c r="C385" s="1">
@@ -36675,9 +38630,12 @@
       <c r="P385" t="s">
         <v>3813</v>
       </c>
-    </row>
-    <row r="386" ht="16.5" spans="2:16">
-      <c r="B386" s="34" t="s">
+      <c r="Q385" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="386" ht="16.5" spans="2:17">
+      <c r="B386" s="35" t="s">
         <v>3814</v>
       </c>
       <c r="C386" s="1">
@@ -36710,9 +38668,12 @@
       <c r="P386" t="s">
         <v>3821</v>
       </c>
-    </row>
-    <row r="387" ht="16.5" spans="2:16">
-      <c r="B387" s="34" t="s">
+      <c r="Q386" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="387" ht="16.5" spans="2:17">
+      <c r="B387" s="35" t="s">
         <v>3822</v>
       </c>
       <c r="C387" s="1">
@@ -36745,9 +38706,12 @@
       <c r="P387" t="s">
         <v>3829</v>
       </c>
-    </row>
-    <row r="388" ht="16.5" spans="2:16">
-      <c r="B388" s="34" t="s">
+      <c r="Q387" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="388" ht="16.5" spans="2:17">
+      <c r="B388" s="35" t="s">
         <v>3830</v>
       </c>
       <c r="C388" s="1">
@@ -36780,9 +38744,12 @@
       <c r="P388" t="s">
         <v>3837</v>
       </c>
-    </row>
-    <row r="389" ht="16.5" spans="2:16">
-      <c r="B389" s="34" t="s">
+      <c r="Q388" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="389" ht="16.5" spans="2:17">
+      <c r="B389" s="35" t="s">
         <v>3838</v>
       </c>
       <c r="C389" s="1">
@@ -36815,9 +38782,12 @@
       <c r="P389" t="s">
         <v>3845</v>
       </c>
-    </row>
-    <row r="390" ht="16.5" spans="2:16">
-      <c r="B390" s="34" t="s">
+      <c r="Q389" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="390" ht="16.5" spans="2:17">
+      <c r="B390" s="35" t="s">
         <v>3846</v>
       </c>
       <c r="C390" s="1">
@@ -36850,9 +38820,12 @@
       <c r="P390" t="s">
         <v>3853</v>
       </c>
-    </row>
-    <row r="391" ht="16.5" spans="2:16">
-      <c r="B391" s="34" t="s">
+      <c r="Q390" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="391" ht="16.5" spans="2:17">
+      <c r="B391" s="35" t="s">
         <v>3854</v>
       </c>
       <c r="C391" s="1">
@@ -36885,9 +38858,12 @@
       <c r="P391" t="s">
         <v>3861</v>
       </c>
-    </row>
-    <row r="392" ht="16.5" spans="2:16">
-      <c r="B392" s="34" t="s">
+      <c r="Q391" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="392" ht="16.5" spans="2:17">
+      <c r="B392" s="35" t="s">
         <v>3862</v>
       </c>
       <c r="C392" s="1">
@@ -36920,9 +38896,12 @@
       <c r="P392" t="s">
         <v>3869</v>
       </c>
-    </row>
-    <row r="393" ht="16.5" spans="2:16">
-      <c r="B393" s="34" t="s">
+      <c r="Q392" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="393" ht="16.5" spans="2:17">
+      <c r="B393" s="35" t="s">
         <v>3870</v>
       </c>
       <c r="C393" s="1">
@@ -36955,9 +38934,12 @@
       <c r="P393" t="s">
         <v>3877</v>
       </c>
-    </row>
-    <row r="394" ht="16.5" spans="2:16">
-      <c r="B394" s="34" t="s">
+      <c r="Q393" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="394" ht="16.5" spans="2:17">
+      <c r="B394" s="35" t="s">
         <v>3878</v>
       </c>
       <c r="C394" s="1">
@@ -36990,9 +38972,12 @@
       <c r="P394" t="s">
         <v>3885</v>
       </c>
-    </row>
-    <row r="395" ht="16.5" spans="2:16">
-      <c r="B395" s="34" t="s">
+      <c r="Q394" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="395" ht="16.5" spans="2:17">
+      <c r="B395" s="35" t="s">
         <v>3886</v>
       </c>
       <c r="C395" s="1">
@@ -37025,9 +39010,12 @@
       <c r="P395" t="s">
         <v>3893</v>
       </c>
-    </row>
-    <row r="396" ht="16.5" spans="2:16">
-      <c r="B396" s="34" t="s">
+      <c r="Q395" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="396" ht="16.5" spans="2:17">
+      <c r="B396" s="35" t="s">
         <v>3894</v>
       </c>
       <c r="C396" s="1">
@@ -37060,9 +39048,12 @@
       <c r="P396" t="s">
         <v>3901</v>
       </c>
-    </row>
-    <row r="397" ht="16.5" spans="2:16">
-      <c r="B397" s="34" t="s">
+      <c r="Q396" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="397" ht="16.5" spans="2:17">
+      <c r="B397" s="35" t="s">
         <v>3902</v>
       </c>
       <c r="C397" s="1">
@@ -37095,9 +39086,12 @@
       <c r="P397" t="s">
         <v>3909</v>
       </c>
-    </row>
-    <row r="398" ht="16.5" spans="2:16">
-      <c r="B398" s="34" t="s">
+      <c r="Q397" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="398" ht="16.5" spans="2:17">
+      <c r="B398" s="35" t="s">
         <v>3910</v>
       </c>
       <c r="C398" s="1">
@@ -37130,9 +39124,12 @@
       <c r="P398" t="s">
         <v>3917</v>
       </c>
-    </row>
-    <row r="399" ht="16.5" spans="2:16">
-      <c r="B399" s="34" t="s">
+      <c r="Q398" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="399" ht="16.5" spans="2:17">
+      <c r="B399" s="35" t="s">
         <v>3918</v>
       </c>
       <c r="C399" s="1">
@@ -37165,9 +39162,12 @@
       <c r="P399" t="s">
         <v>3925</v>
       </c>
-    </row>
-    <row r="400" ht="16.5" spans="2:16">
-      <c r="B400" s="34" t="s">
+      <c r="Q399" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="400" ht="16.5" spans="2:17">
+      <c r="B400" s="35" t="s">
         <v>3926</v>
       </c>
       <c r="C400" s="1">
@@ -37200,9 +39200,12 @@
       <c r="P400" t="s">
         <v>3933</v>
       </c>
-    </row>
-    <row r="401" ht="16.5" spans="2:16">
-      <c r="B401" s="34" t="s">
+      <c r="Q400" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="401" ht="16.5" spans="2:17">
+      <c r="B401" s="35" t="s">
         <v>3934</v>
       </c>
       <c r="C401" s="1">
@@ -37235,9 +39238,12 @@
       <c r="P401" t="s">
         <v>3941</v>
       </c>
-    </row>
-    <row r="402" ht="16.5" spans="2:16">
-      <c r="B402" s="34" t="s">
+      <c r="Q401" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="402" ht="16.5" spans="2:17">
+      <c r="B402" s="35" t="s">
         <v>3942</v>
       </c>
       <c r="C402" s="1">
@@ -37270,9 +39276,12 @@
       <c r="P402" t="s">
         <v>3949</v>
       </c>
-    </row>
-    <row r="403" ht="16.5" spans="2:16">
-      <c r="B403" s="34" t="s">
+      <c r="Q402" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="403" ht="16.5" spans="2:17">
+      <c r="B403" s="35" t="s">
         <v>3950</v>
       </c>
       <c r="C403" s="1">
@@ -37305,9 +39314,12 @@
       <c r="P403" t="s">
         <v>3957</v>
       </c>
-    </row>
-    <row r="404" ht="16.5" spans="2:16">
-      <c r="B404" s="34" t="s">
+      <c r="Q403" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="404" ht="16.5" spans="2:17">
+      <c r="B404" s="35" t="s">
         <v>3958</v>
       </c>
       <c r="C404" s="1">
@@ -37340,9 +39352,12 @@
       <c r="P404" t="s">
         <v>3965</v>
       </c>
-    </row>
-    <row r="405" ht="16.5" spans="2:16">
-      <c r="B405" s="34" t="s">
+      <c r="Q404" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="405" ht="16.5" spans="2:17">
+      <c r="B405" s="35" t="s">
         <v>3966</v>
       </c>
       <c r="C405" s="1">
@@ -37375,9 +39390,12 @@
       <c r="P405" t="s">
         <v>3973</v>
       </c>
-    </row>
-    <row r="406" ht="16.5" spans="2:16">
-      <c r="B406" s="34" t="s">
+      <c r="Q405" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="406" ht="16.5" spans="2:17">
+      <c r="B406" s="35" t="s">
         <v>3974</v>
       </c>
       <c r="C406" s="1">
@@ -37410,15 +39428,2704 @@
       <c r="P406" t="s">
         <v>3981</v>
       </c>
-    </row>
-    <row r="407" ht="16.5" spans="2:16">
-      <c r="F407" s="4"/>
-    </row>
-    <row r="408" ht="16.5" spans="2:16">
-      <c r="F408" s="4"/>
-    </row>
-    <row r="409" ht="16.5" spans="2:16">
-      <c r="F409" s="4"/>
+      <c r="Q406" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="407" ht="16.5" spans="2:17">
+      <c r="B407" s="30" t="s">
+        <v>3982</v>
+      </c>
+      <c r="C407" s="30" t="s">
+        <v>3983</v>
+      </c>
+      <c r="D407" t="s">
+        <v>3984</v>
+      </c>
+      <c r="E407" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F407" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I407" t="s">
+        <v>3985</v>
+      </c>
+      <c r="J407" t="s">
+        <v>3986</v>
+      </c>
+      <c r="K407" t="s">
+        <v>3987</v>
+      </c>
+      <c r="M407" t="s">
+        <v>3988</v>
+      </c>
+      <c r="O407" t="s">
+        <v>3989</v>
+      </c>
+      <c r="P407" t="s">
+        <v>3990</v>
+      </c>
+      <c r="Q407" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="408" ht="16.5" spans="2:17">
+      <c r="B408" s="30" t="s">
+        <v>3991</v>
+      </c>
+      <c r="C408" s="30" t="s">
+        <v>3992</v>
+      </c>
+      <c r="D408" t="s">
+        <v>3993</v>
+      </c>
+      <c r="E408" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F408" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I408" t="s">
+        <v>3994</v>
+      </c>
+      <c r="J408" t="s">
+        <v>3995</v>
+      </c>
+      <c r="K408" t="s">
+        <v>3996</v>
+      </c>
+      <c r="M408" t="s">
+        <v>3997</v>
+      </c>
+      <c r="O408" t="s">
+        <v>3998</v>
+      </c>
+      <c r="P408" t="s">
+        <v>3999</v>
+      </c>
+      <c r="Q408" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="409" ht="16.5" spans="2:17">
+      <c r="B409" s="30" t="s">
+        <v>4000</v>
+      </c>
+      <c r="C409" s="30" t="s">
+        <v>4001</v>
+      </c>
+      <c r="D409" t="s">
+        <v>4002</v>
+      </c>
+      <c r="E409" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F409" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I409" t="s">
+        <v>4003</v>
+      </c>
+      <c r="J409" t="s">
+        <v>4004</v>
+      </c>
+      <c r="K409" t="s">
+        <v>4005</v>
+      </c>
+      <c r="M409" t="s">
+        <v>4006</v>
+      </c>
+      <c r="O409" t="s">
+        <v>4007</v>
+      </c>
+      <c r="P409" t="s">
+        <v>4008</v>
+      </c>
+      <c r="Q409" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="410" ht="16.5" spans="2:17">
+      <c r="B410" s="30" t="s">
+        <v>4009</v>
+      </c>
+      <c r="C410" s="30" t="s">
+        <v>4010</v>
+      </c>
+      <c r="D410" t="s">
+        <v>4011</v>
+      </c>
+      <c r="E410" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F410" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I410" t="s">
+        <v>4012</v>
+      </c>
+      <c r="J410" t="s">
+        <v>4013</v>
+      </c>
+      <c r="K410" t="s">
+        <v>4014</v>
+      </c>
+      <c r="M410" t="s">
+        <v>4015</v>
+      </c>
+      <c r="O410" t="s">
+        <v>4016</v>
+      </c>
+      <c r="P410" t="s">
+        <v>4017</v>
+      </c>
+      <c r="Q410" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="411" ht="16.5" spans="2:17">
+      <c r="B411" s="30" t="s">
+        <v>4018</v>
+      </c>
+      <c r="C411" s="30" t="s">
+        <v>4019</v>
+      </c>
+      <c r="D411" t="s">
+        <v>4020</v>
+      </c>
+      <c r="E411" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F411" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I411" t="s">
+        <v>4021</v>
+      </c>
+      <c r="J411" t="s">
+        <v>4022</v>
+      </c>
+      <c r="K411" t="s">
+        <v>4023</v>
+      </c>
+      <c r="M411" t="s">
+        <v>4024</v>
+      </c>
+      <c r="O411" t="s">
+        <v>4025</v>
+      </c>
+      <c r="P411" t="s">
+        <v>4026</v>
+      </c>
+      <c r="Q411" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="412" ht="16.5" spans="2:17">
+      <c r="B412" s="30" t="s">
+        <v>4027</v>
+      </c>
+      <c r="C412" s="30" t="s">
+        <v>4028</v>
+      </c>
+      <c r="D412" t="s">
+        <v>4029</v>
+      </c>
+      <c r="E412" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F412" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I412" t="s">
+        <v>4030</v>
+      </c>
+      <c r="J412" t="s">
+        <v>4031</v>
+      </c>
+      <c r="K412" t="s">
+        <v>4032</v>
+      </c>
+      <c r="M412" t="s">
+        <v>4033</v>
+      </c>
+      <c r="O412" t="s">
+        <v>4034</v>
+      </c>
+      <c r="P412" t="s">
+        <v>4035</v>
+      </c>
+      <c r="Q412" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="413" ht="16.5" spans="2:17">
+      <c r="B413" s="30" t="s">
+        <v>4036</v>
+      </c>
+      <c r="C413" s="30" t="s">
+        <v>4037</v>
+      </c>
+      <c r="D413" t="s">
+        <v>4038</v>
+      </c>
+      <c r="E413" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F413" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I413" t="s">
+        <v>4039</v>
+      </c>
+      <c r="J413" t="s">
+        <v>4040</v>
+      </c>
+      <c r="K413" t="s">
+        <v>4041</v>
+      </c>
+      <c r="M413" t="s">
+        <v>4042</v>
+      </c>
+      <c r="O413" t="s">
+        <v>4043</v>
+      </c>
+      <c r="P413" t="s">
+        <v>4044</v>
+      </c>
+      <c r="Q413" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="414" ht="16.5" spans="2:17">
+      <c r="B414" s="30" t="s">
+        <v>4045</v>
+      </c>
+      <c r="C414" s="30" t="s">
+        <v>4046</v>
+      </c>
+      <c r="D414" t="s">
+        <v>4047</v>
+      </c>
+      <c r="E414" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F414" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I414" t="s">
+        <v>4048</v>
+      </c>
+      <c r="J414" t="s">
+        <v>4049</v>
+      </c>
+      <c r="K414" t="s">
+        <v>4050</v>
+      </c>
+      <c r="M414" t="s">
+        <v>4051</v>
+      </c>
+      <c r="O414" t="s">
+        <v>4052</v>
+      </c>
+      <c r="P414" t="s">
+        <v>4053</v>
+      </c>
+      <c r="Q414" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="415" ht="16.5" spans="2:17">
+      <c r="B415" s="30" t="s">
+        <v>4054</v>
+      </c>
+      <c r="C415" s="30" t="s">
+        <v>4055</v>
+      </c>
+      <c r="D415" t="s">
+        <v>4056</v>
+      </c>
+      <c r="E415" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F415" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I415" t="s">
+        <v>4057</v>
+      </c>
+      <c r="J415" t="s">
+        <v>4058</v>
+      </c>
+      <c r="K415" t="s">
+        <v>4059</v>
+      </c>
+      <c r="M415" t="s">
+        <v>4060</v>
+      </c>
+      <c r="O415" t="s">
+        <v>4061</v>
+      </c>
+      <c r="P415" t="s">
+        <v>4062</v>
+      </c>
+      <c r="Q415" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="416" ht="16.5" spans="2:17">
+      <c r="B416" s="30" t="s">
+        <v>4063</v>
+      </c>
+      <c r="C416" s="30" t="s">
+        <v>4064</v>
+      </c>
+      <c r="D416" t="s">
+        <v>4065</v>
+      </c>
+      <c r="E416" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F416" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I416" t="s">
+        <v>4066</v>
+      </c>
+      <c r="J416" t="s">
+        <v>4067</v>
+      </c>
+      <c r="K416" t="s">
+        <v>4068</v>
+      </c>
+      <c r="M416" t="s">
+        <v>4069</v>
+      </c>
+      <c r="O416" t="s">
+        <v>4070</v>
+      </c>
+      <c r="P416" t="s">
+        <v>4071</v>
+      </c>
+      <c r="Q416" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="417" ht="16.5" spans="2:17">
+      <c r="B417" s="30" t="s">
+        <v>4072</v>
+      </c>
+      <c r="C417" s="30" t="s">
+        <v>4073</v>
+      </c>
+      <c r="D417" t="s">
+        <v>4074</v>
+      </c>
+      <c r="E417" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F417" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I417" t="s">
+        <v>4075</v>
+      </c>
+      <c r="J417" t="s">
+        <v>4076</v>
+      </c>
+      <c r="K417" t="s">
+        <v>4077</v>
+      </c>
+      <c r="M417" t="s">
+        <v>4078</v>
+      </c>
+      <c r="O417" t="s">
+        <v>4079</v>
+      </c>
+      <c r="P417" t="s">
+        <v>4080</v>
+      </c>
+      <c r="Q417" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="418" ht="16.5" spans="2:17">
+      <c r="B418" s="30" t="s">
+        <v>4081</v>
+      </c>
+      <c r="C418" s="30" t="s">
+        <v>4082</v>
+      </c>
+      <c r="D418" t="s">
+        <v>4083</v>
+      </c>
+      <c r="E418" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F418" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I418" t="s">
+        <v>4084</v>
+      </c>
+      <c r="J418" t="s">
+        <v>4085</v>
+      </c>
+      <c r="K418" t="s">
+        <v>4086</v>
+      </c>
+      <c r="M418" t="s">
+        <v>4087</v>
+      </c>
+      <c r="O418" t="s">
+        <v>4088</v>
+      </c>
+      <c r="P418" t="s">
+        <v>4089</v>
+      </c>
+      <c r="Q418" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="419" ht="16.5" spans="2:17">
+      <c r="B419" s="30" t="s">
+        <v>4090</v>
+      </c>
+      <c r="C419" s="30" t="s">
+        <v>4091</v>
+      </c>
+      <c r="D419" t="s">
+        <v>4092</v>
+      </c>
+      <c r="E419" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F419" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I419" t="s">
+        <v>4093</v>
+      </c>
+      <c r="J419" t="s">
+        <v>4094</v>
+      </c>
+      <c r="K419" t="s">
+        <v>4095</v>
+      </c>
+      <c r="M419" t="s">
+        <v>4096</v>
+      </c>
+      <c r="O419" t="s">
+        <v>4097</v>
+      </c>
+      <c r="P419" t="s">
+        <v>4098</v>
+      </c>
+      <c r="Q419" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="420" ht="16.5" spans="2:17">
+      <c r="B420" s="30" t="s">
+        <v>4099</v>
+      </c>
+      <c r="C420" s="30" t="s">
+        <v>4100</v>
+      </c>
+      <c r="D420" t="s">
+        <v>4101</v>
+      </c>
+      <c r="E420" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F420" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I420" t="s">
+        <v>4102</v>
+      </c>
+      <c r="J420" t="s">
+        <v>4103</v>
+      </c>
+      <c r="K420" t="s">
+        <v>4104</v>
+      </c>
+      <c r="M420" t="s">
+        <v>4105</v>
+      </c>
+      <c r="O420" t="s">
+        <v>4106</v>
+      </c>
+      <c r="P420" t="s">
+        <v>4107</v>
+      </c>
+      <c r="Q420" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="421" ht="16.5" spans="2:17">
+      <c r="B421" s="30" t="s">
+        <v>4108</v>
+      </c>
+      <c r="C421" s="30" t="s">
+        <v>4109</v>
+      </c>
+      <c r="D421" t="s">
+        <v>4110</v>
+      </c>
+      <c r="E421" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F421" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I421" t="s">
+        <v>4111</v>
+      </c>
+      <c r="J421" t="s">
+        <v>4112</v>
+      </c>
+      <c r="K421" t="s">
+        <v>4113</v>
+      </c>
+      <c r="M421" t="s">
+        <v>4114</v>
+      </c>
+      <c r="O421" t="s">
+        <v>4115</v>
+      </c>
+      <c r="P421" t="s">
+        <v>4116</v>
+      </c>
+      <c r="Q421" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="422" ht="16.5" spans="2:17">
+      <c r="B422" s="30" t="s">
+        <v>4117</v>
+      </c>
+      <c r="C422" s="30" t="s">
+        <v>4118</v>
+      </c>
+      <c r="D422" t="s">
+        <v>4119</v>
+      </c>
+      <c r="E422" t="s">
+        <v>2006</v>
+      </c>
+      <c r="F422" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I422" t="s">
+        <v>4120</v>
+      </c>
+      <c r="J422" t="s">
+        <v>4121</v>
+      </c>
+      <c r="K422" t="s">
+        <v>4122</v>
+      </c>
+      <c r="M422" t="s">
+        <v>4123</v>
+      </c>
+      <c r="O422" t="s">
+        <v>4124</v>
+      </c>
+      <c r="P422" t="s">
+        <v>4125</v>
+      </c>
+      <c r="Q422" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="423" ht="16.5" spans="2:17">
+      <c r="B423" s="30" t="s">
+        <v>4126</v>
+      </c>
+      <c r="C423" s="30" t="s">
+        <v>4127</v>
+      </c>
+      <c r="D423" t="s">
+        <v>4128</v>
+      </c>
+      <c r="E423" t="s">
+        <v>2006</v>
+      </c>
+      <c r="F423" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I423" t="s">
+        <v>4129</v>
+      </c>
+      <c r="J423" t="s">
+        <v>4130</v>
+      </c>
+      <c r="K423" t="s">
+        <v>4131</v>
+      </c>
+      <c r="M423" t="s">
+        <v>4132</v>
+      </c>
+      <c r="O423" t="s">
+        <v>4133</v>
+      </c>
+      <c r="P423" t="s">
+        <v>4134</v>
+      </c>
+      <c r="Q423" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="424" ht="16.5" spans="2:17">
+      <c r="B424" s="30" t="s">
+        <v>4135</v>
+      </c>
+      <c r="C424" s="30" t="s">
+        <v>4136</v>
+      </c>
+      <c r="D424" t="s">
+        <v>4137</v>
+      </c>
+      <c r="E424" t="s">
+        <v>2006</v>
+      </c>
+      <c r="F424" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I424" t="s">
+        <v>4138</v>
+      </c>
+      <c r="J424" t="s">
+        <v>4139</v>
+      </c>
+      <c r="K424" t="s">
+        <v>4140</v>
+      </c>
+      <c r="M424" t="s">
+        <v>4141</v>
+      </c>
+      <c r="O424" t="s">
+        <v>4142</v>
+      </c>
+      <c r="P424" t="s">
+        <v>4143</v>
+      </c>
+      <c r="Q424" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="425" ht="16.5" spans="2:17">
+      <c r="B425" s="30" t="s">
+        <v>4144</v>
+      </c>
+      <c r="C425" s="30" t="s">
+        <v>4145</v>
+      </c>
+      <c r="D425" t="s">
+        <v>4146</v>
+      </c>
+      <c r="E425" t="s">
+        <v>2006</v>
+      </c>
+      <c r="F425" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I425" t="s">
+        <v>4147</v>
+      </c>
+      <c r="J425" t="s">
+        <v>4148</v>
+      </c>
+      <c r="K425" t="s">
+        <v>4149</v>
+      </c>
+      <c r="M425" t="s">
+        <v>4150</v>
+      </c>
+      <c r="O425" t="s">
+        <v>4151</v>
+      </c>
+      <c r="P425" t="s">
+        <v>4152</v>
+      </c>
+      <c r="Q425" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="426" ht="16.5" spans="2:17">
+      <c r="B426" s="30" t="s">
+        <v>4153</v>
+      </c>
+      <c r="C426" s="30" t="s">
+        <v>4154</v>
+      </c>
+      <c r="D426" t="s">
+        <v>4155</v>
+      </c>
+      <c r="E426" t="s">
+        <v>2006</v>
+      </c>
+      <c r="F426" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I426" t="s">
+        <v>4156</v>
+      </c>
+      <c r="J426" t="s">
+        <v>4157</v>
+      </c>
+      <c r="K426" t="s">
+        <v>4158</v>
+      </c>
+      <c r="M426" t="s">
+        <v>4159</v>
+      </c>
+      <c r="O426" t="s">
+        <v>4160</v>
+      </c>
+      <c r="P426" t="s">
+        <v>4161</v>
+      </c>
+      <c r="Q426" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="427" ht="16.5" spans="2:17">
+      <c r="B427" s="30" t="s">
+        <v>4162</v>
+      </c>
+      <c r="C427" s="30" t="s">
+        <v>4163</v>
+      </c>
+      <c r="D427" t="s">
+        <v>4164</v>
+      </c>
+      <c r="E427" t="s">
+        <v>2006</v>
+      </c>
+      <c r="F427" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I427" t="s">
+        <v>4165</v>
+      </c>
+      <c r="J427" t="s">
+        <v>4166</v>
+      </c>
+      <c r="K427" t="s">
+        <v>4167</v>
+      </c>
+      <c r="M427" t="s">
+        <v>4168</v>
+      </c>
+      <c r="O427" t="s">
+        <v>4169</v>
+      </c>
+      <c r="P427" t="s">
+        <v>4170</v>
+      </c>
+      <c r="Q427" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="428" ht="16.5" spans="2:17">
+      <c r="B428" s="30" t="s">
+        <v>4171</v>
+      </c>
+      <c r="C428" s="30" t="s">
+        <v>4172</v>
+      </c>
+      <c r="D428" t="s">
+        <v>4173</v>
+      </c>
+      <c r="E428" t="s">
+        <v>2006</v>
+      </c>
+      <c r="F428" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I428" t="s">
+        <v>4174</v>
+      </c>
+      <c r="J428" t="s">
+        <v>4175</v>
+      </c>
+      <c r="K428" t="s">
+        <v>4176</v>
+      </c>
+      <c r="M428" t="s">
+        <v>4177</v>
+      </c>
+      <c r="O428" t="s">
+        <v>4178</v>
+      </c>
+      <c r="P428" t="s">
+        <v>4179</v>
+      </c>
+      <c r="Q428" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="429" ht="16.5" spans="2:17">
+      <c r="B429" s="30" t="s">
+        <v>4180</v>
+      </c>
+      <c r="C429" s="30" t="s">
+        <v>4181</v>
+      </c>
+      <c r="D429" t="s">
+        <v>4182</v>
+      </c>
+      <c r="E429" t="s">
+        <v>2006</v>
+      </c>
+      <c r="F429" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I429" t="s">
+        <v>4183</v>
+      </c>
+      <c r="J429" t="s">
+        <v>4184</v>
+      </c>
+      <c r="K429" t="s">
+        <v>4185</v>
+      </c>
+      <c r="M429" t="s">
+        <v>4186</v>
+      </c>
+      <c r="O429" t="s">
+        <v>4187</v>
+      </c>
+      <c r="P429" t="s">
+        <v>4188</v>
+      </c>
+      <c r="Q429" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="430" ht="16.5" spans="2:17">
+      <c r="B430" s="30" t="s">
+        <v>4189</v>
+      </c>
+      <c r="C430" s="30" t="s">
+        <v>4190</v>
+      </c>
+      <c r="D430" t="s">
+        <v>4191</v>
+      </c>
+      <c r="E430" t="s">
+        <v>2006</v>
+      </c>
+      <c r="F430" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I430" t="s">
+        <v>4192</v>
+      </c>
+      <c r="J430" t="s">
+        <v>4193</v>
+      </c>
+      <c r="K430" t="s">
+        <v>4194</v>
+      </c>
+      <c r="M430" t="s">
+        <v>4195</v>
+      </c>
+      <c r="O430" t="s">
+        <v>4196</v>
+      </c>
+      <c r="P430" t="s">
+        <v>4197</v>
+      </c>
+      <c r="Q430" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="431" ht="16.5" spans="2:17">
+      <c r="B431" s="30" t="s">
+        <v>4198</v>
+      </c>
+      <c r="C431" s="30" t="s">
+        <v>4199</v>
+      </c>
+      <c r="D431" t="s">
+        <v>4200</v>
+      </c>
+      <c r="E431" t="s">
+        <v>2006</v>
+      </c>
+      <c r="F431" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I431" t="s">
+        <v>4201</v>
+      </c>
+      <c r="J431" t="s">
+        <v>4202</v>
+      </c>
+      <c r="K431" t="s">
+        <v>4203</v>
+      </c>
+      <c r="M431" t="s">
+        <v>4204</v>
+      </c>
+      <c r="O431" t="s">
+        <v>4205</v>
+      </c>
+      <c r="P431" t="s">
+        <v>4206</v>
+      </c>
+      <c r="Q431" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="432" ht="16.5" spans="2:17">
+      <c r="B432" s="30" t="s">
+        <v>4207</v>
+      </c>
+      <c r="C432" s="30" t="s">
+        <v>4208</v>
+      </c>
+      <c r="D432" t="s">
+        <v>4209</v>
+      </c>
+      <c r="E432" t="s">
+        <v>2006</v>
+      </c>
+      <c r="F432" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I432" t="s">
+        <v>4210</v>
+      </c>
+      <c r="J432" t="s">
+        <v>4211</v>
+      </c>
+      <c r="K432" t="s">
+        <v>4212</v>
+      </c>
+      <c r="M432" t="s">
+        <v>4213</v>
+      </c>
+      <c r="O432" t="s">
+        <v>4214</v>
+      </c>
+      <c r="P432" t="s">
+        <v>4215</v>
+      </c>
+      <c r="Q432" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="433" ht="16.5" spans="2:17">
+      <c r="B433" s="30" t="s">
+        <v>4216</v>
+      </c>
+      <c r="C433" s="30" t="s">
+        <v>4217</v>
+      </c>
+      <c r="D433" t="s">
+        <v>4218</v>
+      </c>
+      <c r="E433" t="s">
+        <v>2006</v>
+      </c>
+      <c r="F433" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I433" t="s">
+        <v>4219</v>
+      </c>
+      <c r="J433" t="s">
+        <v>4220</v>
+      </c>
+      <c r="K433" t="s">
+        <v>4221</v>
+      </c>
+      <c r="M433" t="s">
+        <v>4222</v>
+      </c>
+      <c r="O433" t="s">
+        <v>4223</v>
+      </c>
+      <c r="P433" t="s">
+        <v>4224</v>
+      </c>
+      <c r="Q433" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="434" ht="16.5" spans="2:17">
+      <c r="B434" s="30" t="s">
+        <v>4225</v>
+      </c>
+      <c r="C434" s="30" t="s">
+        <v>4226</v>
+      </c>
+      <c r="D434" t="s">
+        <v>4227</v>
+      </c>
+      <c r="E434" t="s">
+        <v>2006</v>
+      </c>
+      <c r="F434" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I434" t="s">
+        <v>4228</v>
+      </c>
+      <c r="J434" t="s">
+        <v>4229</v>
+      </c>
+      <c r="K434" t="s">
+        <v>4230</v>
+      </c>
+      <c r="M434" t="s">
+        <v>4231</v>
+      </c>
+      <c r="O434" t="s">
+        <v>4232</v>
+      </c>
+      <c r="P434" t="s">
+        <v>4233</v>
+      </c>
+      <c r="Q434" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="435" ht="16.5" spans="2:17">
+      <c r="B435" s="30" t="s">
+        <v>4234</v>
+      </c>
+      <c r="C435" s="30" t="s">
+        <v>4235</v>
+      </c>
+      <c r="D435" t="s">
+        <v>4236</v>
+      </c>
+      <c r="E435" t="s">
+        <v>2006</v>
+      </c>
+      <c r="F435" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I435" t="s">
+        <v>4237</v>
+      </c>
+      <c r="J435" t="s">
+        <v>4238</v>
+      </c>
+      <c r="K435" t="s">
+        <v>4239</v>
+      </c>
+      <c r="M435" t="s">
+        <v>4240</v>
+      </c>
+      <c r="O435" t="s">
+        <v>4241</v>
+      </c>
+      <c r="P435" t="s">
+        <v>4242</v>
+      </c>
+      <c r="Q435" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="436" ht="16.5" spans="2:17">
+      <c r="B436" s="30" t="s">
+        <v>4243</v>
+      </c>
+      <c r="C436" s="30" t="s">
+        <v>4244</v>
+      </c>
+      <c r="D436" t="s">
+        <v>4245</v>
+      </c>
+      <c r="E436" t="s">
+        <v>2006</v>
+      </c>
+      <c r="F436" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I436" t="s">
+        <v>4246</v>
+      </c>
+      <c r="J436" t="s">
+        <v>4247</v>
+      </c>
+      <c r="K436" t="s">
+        <v>4248</v>
+      </c>
+      <c r="M436" t="s">
+        <v>4249</v>
+      </c>
+      <c r="O436" t="s">
+        <v>4250</v>
+      </c>
+      <c r="P436" t="s">
+        <v>4251</v>
+      </c>
+      <c r="Q436" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="437" ht="16.5" spans="2:17">
+      <c r="B437" s="30" t="s">
+        <v>4252</v>
+      </c>
+      <c r="C437" s="30" t="s">
+        <v>4253</v>
+      </c>
+      <c r="D437" t="s">
+        <v>4254</v>
+      </c>
+      <c r="E437" t="s">
+        <v>745</v>
+      </c>
+      <c r="F437" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I437" t="s">
+        <v>4255</v>
+      </c>
+      <c r="J437" t="s">
+        <v>4256</v>
+      </c>
+      <c r="K437" t="s">
+        <v>4257</v>
+      </c>
+      <c r="M437" t="s">
+        <v>4258</v>
+      </c>
+      <c r="O437" t="s">
+        <v>4259</v>
+      </c>
+      <c r="P437" t="s">
+        <v>4260</v>
+      </c>
+      <c r="Q437" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="438" ht="16.5" spans="2:17">
+      <c r="B438" s="30" t="s">
+        <v>4261</v>
+      </c>
+      <c r="C438" s="30" t="s">
+        <v>4262</v>
+      </c>
+      <c r="D438" t="s">
+        <v>4263</v>
+      </c>
+      <c r="E438" t="s">
+        <v>745</v>
+      </c>
+      <c r="F438" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I438" t="s">
+        <v>4264</v>
+      </c>
+      <c r="J438" t="s">
+        <v>4265</v>
+      </c>
+      <c r="K438" t="s">
+        <v>4266</v>
+      </c>
+      <c r="M438" t="s">
+        <v>4267</v>
+      </c>
+      <c r="O438" t="s">
+        <v>4268</v>
+      </c>
+      <c r="P438" t="s">
+        <v>4269</v>
+      </c>
+      <c r="Q438" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="439" ht="16.5" spans="2:17">
+      <c r="B439" s="30" t="s">
+        <v>4270</v>
+      </c>
+      <c r="C439" s="30" t="s">
+        <v>4271</v>
+      </c>
+      <c r="D439" t="s">
+        <v>4272</v>
+      </c>
+      <c r="E439" t="s">
+        <v>745</v>
+      </c>
+      <c r="F439" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I439" t="s">
+        <v>4273</v>
+      </c>
+      <c r="J439" t="s">
+        <v>4274</v>
+      </c>
+      <c r="K439" t="s">
+        <v>4275</v>
+      </c>
+      <c r="M439" t="s">
+        <v>4276</v>
+      </c>
+      <c r="O439" t="s">
+        <v>4277</v>
+      </c>
+      <c r="P439" t="s">
+        <v>4278</v>
+      </c>
+      <c r="Q439" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="440" ht="16.5" spans="2:17">
+      <c r="B440" s="30" t="s">
+        <v>4279</v>
+      </c>
+      <c r="C440" s="30" t="s">
+        <v>4280</v>
+      </c>
+      <c r="D440" t="s">
+        <v>4281</v>
+      </c>
+      <c r="E440" t="s">
+        <v>745</v>
+      </c>
+      <c r="F440" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I440" t="s">
+        <v>4282</v>
+      </c>
+      <c r="J440" t="s">
+        <v>4283</v>
+      </c>
+      <c r="K440" t="s">
+        <v>4284</v>
+      </c>
+      <c r="M440" t="s">
+        <v>4285</v>
+      </c>
+      <c r="O440" t="s">
+        <v>4286</v>
+      </c>
+      <c r="P440" t="s">
+        <v>4287</v>
+      </c>
+      <c r="Q440" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="441" ht="16.5" spans="2:17">
+      <c r="B441" s="30" t="s">
+        <v>4288</v>
+      </c>
+      <c r="C441" s="30" t="s">
+        <v>4289</v>
+      </c>
+      <c r="D441" t="s">
+        <v>4290</v>
+      </c>
+      <c r="E441" t="s">
+        <v>745</v>
+      </c>
+      <c r="F441" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I441" t="s">
+        <v>4291</v>
+      </c>
+      <c r="J441" t="s">
+        <v>4292</v>
+      </c>
+      <c r="K441" t="s">
+        <v>4293</v>
+      </c>
+      <c r="M441" t="s">
+        <v>4294</v>
+      </c>
+      <c r="O441" t="s">
+        <v>4295</v>
+      </c>
+      <c r="P441" t="s">
+        <v>4296</v>
+      </c>
+      <c r="Q441" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="442" ht="16.5" spans="2:17">
+      <c r="B442" s="30" t="s">
+        <v>4297</v>
+      </c>
+      <c r="C442" s="30" t="s">
+        <v>4298</v>
+      </c>
+      <c r="D442" t="s">
+        <v>4299</v>
+      </c>
+      <c r="E442" t="s">
+        <v>745</v>
+      </c>
+      <c r="F442" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I442" t="s">
+        <v>4300</v>
+      </c>
+      <c r="J442" t="s">
+        <v>4301</v>
+      </c>
+      <c r="K442" t="s">
+        <v>4302</v>
+      </c>
+      <c r="M442" t="s">
+        <v>4303</v>
+      </c>
+      <c r="O442" t="s">
+        <v>4304</v>
+      </c>
+      <c r="P442" t="s">
+        <v>4305</v>
+      </c>
+      <c r="Q442" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="443" ht="16.5" spans="2:17">
+      <c r="B443" s="30" t="s">
+        <v>4306</v>
+      </c>
+      <c r="C443" s="30" t="s">
+        <v>4307</v>
+      </c>
+      <c r="D443" t="s">
+        <v>4308</v>
+      </c>
+      <c r="E443" t="s">
+        <v>745</v>
+      </c>
+      <c r="F443" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I443" t="s">
+        <v>4309</v>
+      </c>
+      <c r="J443" t="s">
+        <v>4310</v>
+      </c>
+      <c r="K443" t="s">
+        <v>4311</v>
+      </c>
+      <c r="M443" t="s">
+        <v>4312</v>
+      </c>
+      <c r="O443" t="s">
+        <v>4313</v>
+      </c>
+      <c r="P443" t="s">
+        <v>4314</v>
+      </c>
+      <c r="Q443" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="444" ht="16.5" spans="2:17">
+      <c r="B444" s="30" t="s">
+        <v>4315</v>
+      </c>
+      <c r="C444" s="30" t="s">
+        <v>4316</v>
+      </c>
+      <c r="D444" t="s">
+        <v>4317</v>
+      </c>
+      <c r="E444" t="s">
+        <v>745</v>
+      </c>
+      <c r="F444" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I444" t="s">
+        <v>4318</v>
+      </c>
+      <c r="J444" t="s">
+        <v>4319</v>
+      </c>
+      <c r="K444" t="s">
+        <v>4320</v>
+      </c>
+      <c r="M444" t="s">
+        <v>4321</v>
+      </c>
+      <c r="O444" t="s">
+        <v>4322</v>
+      </c>
+      <c r="P444" t="s">
+        <v>4323</v>
+      </c>
+      <c r="Q444" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="445" ht="16.5" spans="2:17">
+      <c r="B445" s="30" t="s">
+        <v>4324</v>
+      </c>
+      <c r="C445" s="30" t="s">
+        <v>4325</v>
+      </c>
+      <c r="D445" t="s">
+        <v>4326</v>
+      </c>
+      <c r="E445" t="s">
+        <v>745</v>
+      </c>
+      <c r="F445" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I445" t="s">
+        <v>4327</v>
+      </c>
+      <c r="J445" t="s">
+        <v>4328</v>
+      </c>
+      <c r="K445" t="s">
+        <v>4329</v>
+      </c>
+      <c r="M445" t="s">
+        <v>4330</v>
+      </c>
+      <c r="O445" t="s">
+        <v>4331</v>
+      </c>
+      <c r="P445" t="s">
+        <v>4332</v>
+      </c>
+      <c r="Q445" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="446" ht="16.5" spans="2:17">
+      <c r="B446" s="30" t="s">
+        <v>4333</v>
+      </c>
+      <c r="C446" s="30" t="s">
+        <v>4334</v>
+      </c>
+      <c r="D446" t="s">
+        <v>4335</v>
+      </c>
+      <c r="E446" t="s">
+        <v>745</v>
+      </c>
+      <c r="F446" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I446" t="s">
+        <v>4336</v>
+      </c>
+      <c r="J446" t="s">
+        <v>4337</v>
+      </c>
+      <c r="K446" t="s">
+        <v>4338</v>
+      </c>
+      <c r="M446" t="s">
+        <v>4339</v>
+      </c>
+      <c r="O446" t="s">
+        <v>4340</v>
+      </c>
+      <c r="P446" t="s">
+        <v>4341</v>
+      </c>
+      <c r="Q446" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="447" ht="16.5" spans="2:17">
+      <c r="B447" s="30" t="s">
+        <v>4342</v>
+      </c>
+      <c r="C447" s="30" t="s">
+        <v>4343</v>
+      </c>
+      <c r="D447" t="s">
+        <v>4344</v>
+      </c>
+      <c r="E447" t="s">
+        <v>745</v>
+      </c>
+      <c r="F447" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I447" t="s">
+        <v>4345</v>
+      </c>
+      <c r="J447" t="s">
+        <v>4346</v>
+      </c>
+      <c r="K447" t="s">
+        <v>4347</v>
+      </c>
+      <c r="M447" t="s">
+        <v>4348</v>
+      </c>
+      <c r="O447" t="s">
+        <v>4349</v>
+      </c>
+      <c r="P447" t="s">
+        <v>4350</v>
+      </c>
+      <c r="Q447" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="448" ht="16.5" spans="2:17">
+      <c r="B448" s="30" t="s">
+        <v>4351</v>
+      </c>
+      <c r="C448" s="30" t="s">
+        <v>4352</v>
+      </c>
+      <c r="D448" t="s">
+        <v>4353</v>
+      </c>
+      <c r="E448" t="s">
+        <v>745</v>
+      </c>
+      <c r="F448" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I448" t="s">
+        <v>4354</v>
+      </c>
+      <c r="J448" t="s">
+        <v>4355</v>
+      </c>
+      <c r="K448" t="s">
+        <v>4356</v>
+      </c>
+      <c r="M448" t="s">
+        <v>4357</v>
+      </c>
+      <c r="O448" t="s">
+        <v>4358</v>
+      </c>
+      <c r="P448" t="s">
+        <v>4359</v>
+      </c>
+      <c r="Q448" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="449" ht="16.5" spans="2:17">
+      <c r="B449" s="30" t="s">
+        <v>4360</v>
+      </c>
+      <c r="C449" s="30" t="s">
+        <v>4361</v>
+      </c>
+      <c r="D449" t="s">
+        <v>4362</v>
+      </c>
+      <c r="E449" t="s">
+        <v>745</v>
+      </c>
+      <c r="F449" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I449" t="s">
+        <v>4363</v>
+      </c>
+      <c r="J449" t="s">
+        <v>4364</v>
+      </c>
+      <c r="K449" t="s">
+        <v>4365</v>
+      </c>
+      <c r="M449" t="s">
+        <v>4366</v>
+      </c>
+      <c r="O449" t="s">
+        <v>4367</v>
+      </c>
+      <c r="P449" t="s">
+        <v>4368</v>
+      </c>
+      <c r="Q449" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="450" ht="16.5" spans="2:17">
+      <c r="B450" s="30" t="s">
+        <v>4369</v>
+      </c>
+      <c r="C450" s="30" t="s">
+        <v>4370</v>
+      </c>
+      <c r="D450" t="s">
+        <v>4371</v>
+      </c>
+      <c r="E450" t="s">
+        <v>745</v>
+      </c>
+      <c r="F450" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I450" t="s">
+        <v>4372</v>
+      </c>
+      <c r="J450" t="s">
+        <v>4373</v>
+      </c>
+      <c r="K450" t="s">
+        <v>4374</v>
+      </c>
+      <c r="M450" t="s">
+        <v>4375</v>
+      </c>
+      <c r="O450" t="s">
+        <v>4376</v>
+      </c>
+      <c r="P450" t="s">
+        <v>4377</v>
+      </c>
+      <c r="Q450" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="451" ht="16.5" spans="2:17">
+      <c r="B451" s="30" t="s">
+        <v>4378</v>
+      </c>
+      <c r="C451" s="30" t="s">
+        <v>4379</v>
+      </c>
+      <c r="D451" t="s">
+        <v>4380</v>
+      </c>
+      <c r="E451" t="s">
+        <v>745</v>
+      </c>
+      <c r="F451" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I451" t="s">
+        <v>4381</v>
+      </c>
+      <c r="J451" t="s">
+        <v>4382</v>
+      </c>
+      <c r="K451" t="s">
+        <v>4383</v>
+      </c>
+      <c r="M451" t="s">
+        <v>4384</v>
+      </c>
+      <c r="O451" t="s">
+        <v>4385</v>
+      </c>
+      <c r="P451" t="s">
+        <v>4386</v>
+      </c>
+      <c r="Q451" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="452" ht="16.5" spans="2:17">
+      <c r="B452" s="30" t="s">
+        <v>4387</v>
+      </c>
+      <c r="C452" s="30" t="s">
+        <v>4388</v>
+      </c>
+      <c r="D452" t="s">
+        <v>4389</v>
+      </c>
+      <c r="E452" t="s">
+        <v>745</v>
+      </c>
+      <c r="F452" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I452" t="s">
+        <v>4390</v>
+      </c>
+      <c r="J452" t="s">
+        <v>4391</v>
+      </c>
+      <c r="K452" t="s">
+        <v>4392</v>
+      </c>
+      <c r="M452" t="s">
+        <v>4393</v>
+      </c>
+      <c r="O452" t="s">
+        <v>4394</v>
+      </c>
+      <c r="P452" t="s">
+        <v>4395</v>
+      </c>
+      <c r="Q452" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="453" ht="16.5" spans="2:17">
+      <c r="B453" s="30" t="s">
+        <v>4396</v>
+      </c>
+      <c r="C453" s="30" t="s">
+        <v>4397</v>
+      </c>
+      <c r="D453" t="s">
+        <v>4398</v>
+      </c>
+      <c r="E453" t="s">
+        <v>745</v>
+      </c>
+      <c r="F453" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I453" t="s">
+        <v>4399</v>
+      </c>
+      <c r="J453" t="s">
+        <v>4400</v>
+      </c>
+      <c r="K453" t="s">
+        <v>4401</v>
+      </c>
+      <c r="M453" t="s">
+        <v>4402</v>
+      </c>
+      <c r="O453" t="s">
+        <v>4403</v>
+      </c>
+      <c r="P453" t="s">
+        <v>4404</v>
+      </c>
+      <c r="Q453" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="454" ht="16.5" spans="2:17">
+      <c r="B454" s="30" t="s">
+        <v>4405</v>
+      </c>
+      <c r="C454" s="30" t="s">
+        <v>4406</v>
+      </c>
+      <c r="D454" t="s">
+        <v>4407</v>
+      </c>
+      <c r="E454" t="s">
+        <v>745</v>
+      </c>
+      <c r="F454" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I454" t="s">
+        <v>4408</v>
+      </c>
+      <c r="J454" t="s">
+        <v>4409</v>
+      </c>
+      <c r="K454" t="s">
+        <v>4410</v>
+      </c>
+      <c r="M454" t="s">
+        <v>4411</v>
+      </c>
+      <c r="O454" t="s">
+        <v>4412</v>
+      </c>
+      <c r="P454" t="s">
+        <v>4413</v>
+      </c>
+      <c r="Q454" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="455" ht="16.5" spans="2:17">
+      <c r="B455" s="30" t="s">
+        <v>4414</v>
+      </c>
+      <c r="C455" s="30" t="s">
+        <v>4415</v>
+      </c>
+      <c r="D455" t="s">
+        <v>4416</v>
+      </c>
+      <c r="E455" t="s">
+        <v>1369</v>
+      </c>
+      <c r="F455" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I455" t="s">
+        <v>4417</v>
+      </c>
+      <c r="J455" t="s">
+        <v>4418</v>
+      </c>
+      <c r="K455" t="s">
+        <v>4419</v>
+      </c>
+      <c r="M455" t="s">
+        <v>4420</v>
+      </c>
+      <c r="O455" t="s">
+        <v>4421</v>
+      </c>
+      <c r="P455" t="s">
+        <v>4422</v>
+      </c>
+      <c r="Q455" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="456" ht="16.5" spans="2:17">
+      <c r="B456" s="30" t="s">
+        <v>4423</v>
+      </c>
+      <c r="C456" s="30" t="s">
+        <v>4424</v>
+      </c>
+      <c r="D456" t="s">
+        <v>4425</v>
+      </c>
+      <c r="E456" t="s">
+        <v>1369</v>
+      </c>
+      <c r="F456" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I456" t="s">
+        <v>4426</v>
+      </c>
+      <c r="J456" t="s">
+        <v>4427</v>
+      </c>
+      <c r="K456" t="s">
+        <v>4428</v>
+      </c>
+      <c r="M456" t="s">
+        <v>4429</v>
+      </c>
+      <c r="O456" t="s">
+        <v>4430</v>
+      </c>
+      <c r="P456" t="s">
+        <v>4431</v>
+      </c>
+      <c r="Q456" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="457" ht="16.5" spans="2:17">
+      <c r="B457" s="30" t="s">
+        <v>4432</v>
+      </c>
+      <c r="C457" s="30" t="s">
+        <v>4433</v>
+      </c>
+      <c r="D457" t="s">
+        <v>4434</v>
+      </c>
+      <c r="E457" t="s">
+        <v>1369</v>
+      </c>
+      <c r="F457" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I457" t="s">
+        <v>4435</v>
+      </c>
+      <c r="J457" t="s">
+        <v>4436</v>
+      </c>
+      <c r="K457" t="s">
+        <v>4437</v>
+      </c>
+      <c r="M457" t="s">
+        <v>4438</v>
+      </c>
+      <c r="O457" t="s">
+        <v>4439</v>
+      </c>
+      <c r="P457" t="s">
+        <v>4440</v>
+      </c>
+      <c r="Q457" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="458" ht="16.5" spans="2:17">
+      <c r="B458" s="30" t="s">
+        <v>4441</v>
+      </c>
+      <c r="C458" s="30" t="s">
+        <v>4442</v>
+      </c>
+      <c r="D458" t="s">
+        <v>4443</v>
+      </c>
+      <c r="E458" t="s">
+        <v>1369</v>
+      </c>
+      <c r="F458" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I458" t="s">
+        <v>4444</v>
+      </c>
+      <c r="J458" t="s">
+        <v>4445</v>
+      </c>
+      <c r="K458" t="s">
+        <v>4446</v>
+      </c>
+      <c r="M458" t="s">
+        <v>4447</v>
+      </c>
+      <c r="O458" t="s">
+        <v>4448</v>
+      </c>
+      <c r="P458" t="s">
+        <v>4449</v>
+      </c>
+      <c r="Q458" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="459" ht="16.5" spans="2:17">
+      <c r="B459" s="30" t="s">
+        <v>4450</v>
+      </c>
+      <c r="C459" s="30" t="s">
+        <v>4451</v>
+      </c>
+      <c r="D459" t="s">
+        <v>4452</v>
+      </c>
+      <c r="E459" t="s">
+        <v>1369</v>
+      </c>
+      <c r="F459" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I459" t="s">
+        <v>4453</v>
+      </c>
+      <c r="J459" t="s">
+        <v>4454</v>
+      </c>
+      <c r="K459" t="s">
+        <v>4455</v>
+      </c>
+      <c r="M459" t="s">
+        <v>4456</v>
+      </c>
+      <c r="O459" t="s">
+        <v>4457</v>
+      </c>
+      <c r="P459" t="s">
+        <v>4458</v>
+      </c>
+      <c r="Q459" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="460" ht="16.5" spans="2:17">
+      <c r="B460" s="30" t="s">
+        <v>4459</v>
+      </c>
+      <c r="C460" s="30" t="s">
+        <v>4460</v>
+      </c>
+      <c r="D460" t="s">
+        <v>4461</v>
+      </c>
+      <c r="E460" t="s">
+        <v>1369</v>
+      </c>
+      <c r="F460" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I460" t="s">
+        <v>4336</v>
+      </c>
+      <c r="J460" t="s">
+        <v>4462</v>
+      </c>
+      <c r="K460" t="s">
+        <v>4463</v>
+      </c>
+      <c r="M460" t="s">
+        <v>4464</v>
+      </c>
+      <c r="O460" t="s">
+        <v>4465</v>
+      </c>
+      <c r="P460" t="s">
+        <v>4466</v>
+      </c>
+      <c r="Q460" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="461" ht="16.5" spans="2:17">
+      <c r="B461" s="30" t="s">
+        <v>4467</v>
+      </c>
+      <c r="C461" s="30" t="s">
+        <v>4468</v>
+      </c>
+      <c r="D461" t="s">
+        <v>4469</v>
+      </c>
+      <c r="E461" t="s">
+        <v>1369</v>
+      </c>
+      <c r="F461" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I461" t="s">
+        <v>4470</v>
+      </c>
+      <c r="J461" t="s">
+        <v>4471</v>
+      </c>
+      <c r="K461" t="s">
+        <v>4472</v>
+      </c>
+      <c r="M461" t="s">
+        <v>4473</v>
+      </c>
+      <c r="O461" t="s">
+        <v>4474</v>
+      </c>
+      <c r="P461" t="s">
+        <v>4475</v>
+      </c>
+      <c r="Q461" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="462" ht="16.5" spans="2:17">
+      <c r="B462" s="30" t="s">
+        <v>4476</v>
+      </c>
+      <c r="C462" s="30" t="s">
+        <v>4477</v>
+      </c>
+      <c r="D462" t="s">
+        <v>4478</v>
+      </c>
+      <c r="E462" t="s">
+        <v>1369</v>
+      </c>
+      <c r="F462" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I462" t="s">
+        <v>4479</v>
+      </c>
+      <c r="J462" t="s">
+        <v>4480</v>
+      </c>
+      <c r="K462" t="s">
+        <v>4481</v>
+      </c>
+      <c r="M462" t="s">
+        <v>4482</v>
+      </c>
+      <c r="O462" t="s">
+        <v>4483</v>
+      </c>
+      <c r="P462" t="s">
+        <v>4484</v>
+      </c>
+      <c r="Q462" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="463" ht="16.5" spans="2:17">
+      <c r="B463" s="30" t="s">
+        <v>4485</v>
+      </c>
+      <c r="C463" s="30" t="s">
+        <v>4486</v>
+      </c>
+      <c r="D463" t="s">
+        <v>4487</v>
+      </c>
+      <c r="E463" t="s">
+        <v>1369</v>
+      </c>
+      <c r="F463" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I463" t="s">
+        <v>4488</v>
+      </c>
+      <c r="J463" t="s">
+        <v>4489</v>
+      </c>
+      <c r="K463" t="s">
+        <v>4490</v>
+      </c>
+      <c r="M463" t="s">
+        <v>4491</v>
+      </c>
+      <c r="O463" t="s">
+        <v>4492</v>
+      </c>
+      <c r="P463" t="s">
+        <v>4493</v>
+      </c>
+      <c r="Q463" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="464" ht="16.5" spans="2:17">
+      <c r="B464" s="30" t="s">
+        <v>4494</v>
+      </c>
+      <c r="C464" s="30" t="s">
+        <v>4495</v>
+      </c>
+      <c r="D464" t="s">
+        <v>4496</v>
+      </c>
+      <c r="E464" t="s">
+        <v>1369</v>
+      </c>
+      <c r="F464" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I464" t="s">
+        <v>4497</v>
+      </c>
+      <c r="J464" t="s">
+        <v>4498</v>
+      </c>
+      <c r="K464" t="s">
+        <v>4499</v>
+      </c>
+      <c r="M464" t="s">
+        <v>4500</v>
+      </c>
+      <c r="O464" t="s">
+        <v>4501</v>
+      </c>
+      <c r="P464" t="s">
+        <v>4502</v>
+      </c>
+      <c r="Q464" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="465" ht="16.5" spans="2:19">
+      <c r="B465" s="30" t="s">
+        <v>4503</v>
+      </c>
+      <c r="C465" s="30" t="s">
+        <v>4504</v>
+      </c>
+      <c r="D465" t="s">
+        <v>4505</v>
+      </c>
+      <c r="E465" t="s">
+        <v>1369</v>
+      </c>
+      <c r="F465" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I465" t="s">
+        <v>4506</v>
+      </c>
+      <c r="J465" t="s">
+        <v>4507</v>
+      </c>
+      <c r="K465" t="s">
+        <v>4508</v>
+      </c>
+      <c r="M465" t="s">
+        <v>4509</v>
+      </c>
+      <c r="O465" t="s">
+        <v>4510</v>
+      </c>
+      <c r="P465" t="s">
+        <v>4511</v>
+      </c>
+      <c r="Q465" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="466" ht="16.5" spans="2:19">
+      <c r="B466" s="30" t="s">
+        <v>4512</v>
+      </c>
+      <c r="C466" s="30" t="s">
+        <v>4513</v>
+      </c>
+      <c r="D466" t="s">
+        <v>4514</v>
+      </c>
+      <c r="E466" t="s">
+        <v>1369</v>
+      </c>
+      <c r="F466" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I466" t="s">
+        <v>4515</v>
+      </c>
+      <c r="J466" t="s">
+        <v>4516</v>
+      </c>
+      <c r="K466" t="s">
+        <v>4517</v>
+      </c>
+      <c r="M466" t="s">
+        <v>4518</v>
+      </c>
+      <c r="O466" t="s">
+        <v>4519</v>
+      </c>
+      <c r="P466" t="s">
+        <v>4520</v>
+      </c>
+      <c r="Q466" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="467" ht="16.5" spans="2:19">
+      <c r="B467" s="30" t="s">
+        <v>4521</v>
+      </c>
+      <c r="C467" s="30" t="s">
+        <v>4522</v>
+      </c>
+      <c r="D467" t="s">
+        <v>4523</v>
+      </c>
+      <c r="E467" t="s">
+        <v>1369</v>
+      </c>
+      <c r="F467" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I467" t="s">
+        <v>4210</v>
+      </c>
+      <c r="J467" t="s">
+        <v>4524</v>
+      </c>
+      <c r="K467" t="s">
+        <v>4525</v>
+      </c>
+      <c r="M467" t="s">
+        <v>4526</v>
+      </c>
+      <c r="O467" t="s">
+        <v>4527</v>
+      </c>
+      <c r="P467" t="s">
+        <v>4528</v>
+      </c>
+      <c r="Q467" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="468" ht="16.5" spans="2:19">
+      <c r="B468" s="30" t="s">
+        <v>4529</v>
+      </c>
+      <c r="C468" s="30" t="s">
+        <v>4530</v>
+      </c>
+      <c r="D468" t="s">
+        <v>4531</v>
+      </c>
+      <c r="E468" t="s">
+        <v>1369</v>
+      </c>
+      <c r="F468" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I468" t="s">
+        <v>4237</v>
+      </c>
+      <c r="J468" t="s">
+        <v>4532</v>
+      </c>
+      <c r="K468" t="s">
+        <v>4533</v>
+      </c>
+      <c r="M468" t="s">
+        <v>4534</v>
+      </c>
+      <c r="O468" t="s">
+        <v>4535</v>
+      </c>
+      <c r="P468" t="s">
+        <v>4536</v>
+      </c>
+      <c r="Q468" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="469" ht="16.5" spans="2:19">
+      <c r="B469" s="36" t="s">
+        <v>4537</v>
+      </c>
+      <c r="C469">
+        <v>91335</v>
+      </c>
+      <c r="D469" t="s">
+        <v>4538</v>
+      </c>
+      <c r="E469" t="s">
+        <v>143</v>
+      </c>
+      <c r="F469" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I469" t="s">
+        <v>4539</v>
+      </c>
+      <c r="J469" t="s">
+        <v>4540</v>
+      </c>
+      <c r="K469" t="s">
+        <v>4541</v>
+      </c>
+      <c r="M469" t="s">
+        <v>4542</v>
+      </c>
+      <c r="O469" t="s">
+        <v>4543</v>
+      </c>
+      <c r="P469" t="s">
+        <v>4544</v>
+      </c>
+      <c r="Q469" t="s">
+        <v>4545</v>
+      </c>
+      <c r="S469" t="s">
+        <v>4546</v>
+      </c>
+    </row>
+    <row r="470" ht="16.5" spans="2:19">
+      <c r="B470" s="36" t="s">
+        <v>4547</v>
+      </c>
+      <c r="C470">
+        <v>91325</v>
+      </c>
+      <c r="D470" t="s">
+        <v>4548</v>
+      </c>
+      <c r="E470" t="s">
+        <v>143</v>
+      </c>
+      <c r="F470" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I470" t="s">
+        <v>4549</v>
+      </c>
+      <c r="J470" t="s">
+        <v>4550</v>
+      </c>
+      <c r="K470" t="s">
+        <v>4551</v>
+      </c>
+      <c r="M470" t="s">
+        <v>4552</v>
+      </c>
+      <c r="O470" t="s">
+        <v>4553</v>
+      </c>
+      <c r="P470" t="s">
+        <v>4554</v>
+      </c>
+      <c r="Q470" t="s">
+        <v>4555</v>
+      </c>
+      <c r="S470" t="s">
+        <v>4556</v>
+      </c>
+    </row>
+    <row r="471" ht="16.5" spans="2:19">
+      <c r="B471" s="36" t="s">
+        <v>4557</v>
+      </c>
+      <c r="C471">
+        <v>91375</v>
+      </c>
+      <c r="D471" t="s">
+        <v>4558</v>
+      </c>
+      <c r="E471" t="s">
+        <v>143</v>
+      </c>
+      <c r="F471" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I471" t="s">
+        <v>4559</v>
+      </c>
+      <c r="J471" t="s">
+        <v>4560</v>
+      </c>
+      <c r="K471" t="s">
+        <v>4561</v>
+      </c>
+      <c r="M471" t="s">
+        <v>4562</v>
+      </c>
+      <c r="O471" t="s">
+        <v>4563</v>
+      </c>
+      <c r="P471" t="s">
+        <v>4564</v>
+      </c>
+      <c r="Q471" t="s">
+        <v>4565</v>
+      </c>
+      <c r="S471" t="s">
+        <v>4566</v>
+      </c>
+    </row>
+    <row r="472" ht="16.5" spans="2:19">
+      <c r="B472" s="36" t="s">
+        <v>4567</v>
+      </c>
+      <c r="C472">
+        <v>91345</v>
+      </c>
+      <c r="D472" t="s">
+        <v>4568</v>
+      </c>
+      <c r="E472" t="s">
+        <v>143</v>
+      </c>
+      <c r="F472" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I472" t="s">
+        <v>4569</v>
+      </c>
+      <c r="J472" t="s">
+        <v>4570</v>
+      </c>
+      <c r="K472" t="s">
+        <v>4571</v>
+      </c>
+      <c r="M472" t="s">
+        <v>4572</v>
+      </c>
+      <c r="O472" t="s">
+        <v>4573</v>
+      </c>
+      <c r="P472" t="s">
+        <v>4574</v>
+      </c>
+      <c r="Q472" t="s">
+        <v>4575</v>
+      </c>
+      <c r="S472" t="s">
+        <v>4576</v>
+      </c>
+    </row>
+    <row r="473" ht="16.5" spans="2:19">
+      <c r="B473" s="36" t="s">
+        <v>4577</v>
+      </c>
+      <c r="C473">
+        <v>91365</v>
+      </c>
+      <c r="D473" t="s">
+        <v>4578</v>
+      </c>
+      <c r="E473" t="s">
+        <v>143</v>
+      </c>
+      <c r="F473" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I473" t="s">
+        <v>4579</v>
+      </c>
+      <c r="J473" t="s">
+        <v>4580</v>
+      </c>
+      <c r="K473" t="s">
+        <v>4581</v>
+      </c>
+      <c r="M473" t="s">
+        <v>4582</v>
+      </c>
+      <c r="O473" t="s">
+        <v>4583</v>
+      </c>
+      <c r="P473" t="s">
+        <v>4584</v>
+      </c>
+    </row>
+    <row r="474" ht="16.5" spans="2:19">
+      <c r="B474" s="36" t="s">
+        <v>4585</v>
+      </c>
+      <c r="C474">
+        <v>91405</v>
+      </c>
+      <c r="D474" t="s">
+        <v>4586</v>
+      </c>
+      <c r="E474" t="s">
+        <v>143</v>
+      </c>
+      <c r="F474" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I474" t="s">
+        <v>4587</v>
+      </c>
+      <c r="J474" t="s">
+        <v>4588</v>
+      </c>
+      <c r="K474" t="s">
+        <v>4589</v>
+      </c>
+      <c r="M474" t="s">
+        <v>4590</v>
+      </c>
+      <c r="O474" t="s">
+        <v>4591</v>
+      </c>
+      <c r="P474" t="s">
+        <v>4592</v>
+      </c>
+    </row>
+    <row r="475" ht="16.5" spans="2:19">
+      <c r="B475" s="36" t="s">
+        <v>4593</v>
+      </c>
+      <c r="C475">
+        <v>91395</v>
+      </c>
+      <c r="D475" t="s">
+        <v>4594</v>
+      </c>
+      <c r="E475" t="s">
+        <v>143</v>
+      </c>
+      <c r="F475" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I475" t="s">
+        <v>4595</v>
+      </c>
+      <c r="J475" t="s">
+        <v>4596</v>
+      </c>
+      <c r="K475" t="s">
+        <v>4597</v>
+      </c>
+      <c r="M475" t="s">
+        <v>4598</v>
+      </c>
+      <c r="O475" t="s">
+        <v>4599</v>
+      </c>
+      <c r="P475" t="s">
+        <v>4600</v>
+      </c>
+    </row>
+    <row r="476" ht="16.5" spans="2:19">
+      <c r="B476" s="36" t="s">
+        <v>4601</v>
+      </c>
+      <c r="C476">
+        <v>91385</v>
+      </c>
+      <c r="D476" t="s">
+        <v>4602</v>
+      </c>
+      <c r="E476" t="s">
+        <v>143</v>
+      </c>
+      <c r="F476" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I476" t="s">
+        <v>4603</v>
+      </c>
+      <c r="J476" t="s">
+        <v>4604</v>
+      </c>
+      <c r="K476" t="s">
+        <v>4605</v>
+      </c>
+      <c r="M476" t="s">
+        <v>4606</v>
+      </c>
+      <c r="O476" t="s">
+        <v>4607</v>
+      </c>
+      <c r="P476" t="s">
+        <v>4608</v>
+      </c>
+    </row>
+    <row r="477" ht="16.5" spans="2:19">
+      <c r="B477" s="36" t="s">
+        <v>4609</v>
+      </c>
+      <c r="C477">
+        <v>91355</v>
+      </c>
+      <c r="D477" t="s">
+        <v>4610</v>
+      </c>
+      <c r="E477" t="s">
+        <v>143</v>
+      </c>
+      <c r="F477" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I477" t="s">
+        <v>4611</v>
+      </c>
+      <c r="J477" t="s">
+        <v>4612</v>
+      </c>
+      <c r="K477" t="s">
+        <v>4613</v>
+      </c>
+      <c r="M477" t="s">
+        <v>4614</v>
+      </c>
+      <c r="O477" t="s">
+        <v>4615</v>
+      </c>
+      <c r="P477" t="s">
+        <v>4616</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
